--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -50,22 +50,22 @@
     <t xml:space="preserve">5.09169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564228057861</t>
+    <t xml:space="preserve">5.14564275741577</t>
   </si>
   <si>
     <t xml:space="preserve">5.1871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659479141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958925247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523639678955</t>
+    <t xml:space="preserve">5.1165943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523544311523</t>
   </si>
   <si>
     <t xml:space="preserve">5.30333137512207</t>
@@ -77,55 +77,55 @@
     <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3448281288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3489785194397</t>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632535934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897899627686</t>
   </si>
   <si>
     <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972665786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122484207153</t>
+    <t xml:space="preserve">5.36972713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122436523438</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067964553833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462471008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761964797974</t>
+    <t xml:space="preserve">5.39462518692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47762012481689</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176956176758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93408727645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89259052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939264297485</t>
+    <t xml:space="preserve">5.71000385284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9340877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89259099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71415376663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939311981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728610992432</t>
+    <t xml:space="preserve">5.96728563308716</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">5.95068693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653701782227</t>
+    <t xml:space="preserve">5.94653654098511</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8676929473877</t>
+    <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
     <t xml:space="preserve">6.05442953109741</t>
@@ -155,22 +155,22 @@
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05028009414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327407836914</t>
+    <t xml:space="preserve">6.05027961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36150789260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239486694336</t>
+    <t xml:space="preserve">6.47355031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239534378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
@@ -179,70 +179,70 @@
     <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43205308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994560241699</t>
+    <t xml:space="preserve">6.432053565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994512557983</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559274673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464071273804</t>
+    <t xml:space="preserve">6.58559226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804105758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8055272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321630477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301336288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05450963973999</t>
+    <t xml:space="preserve">6.80552768707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">7.12920475006104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30349254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948051452637</t>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948146820068</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67289638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281675338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648653030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798519134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573791503906</t>
+    <t xml:space="preserve">8.67289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281818389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648557662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798328399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573839187622</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240310668945</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">7.20788431167603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89468193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961521148682</t>
+    <t xml:space="preserve">6.89468240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
     <t xml:space="preserve">6.80156707763672</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">6.77617263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97933053970337</t>
+    <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
     <t xml:space="preserve">6.99202871322632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49145984649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37295007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29253339767456</t>
+    <t xml:space="preserve">7.49145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37294960021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253244400024</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676580429077</t>
@@ -302,34 +302,34 @@
     <t xml:space="preserve">7.26290559768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30523109436035</t>
+    <t xml:space="preserve">7.30523014068604</t>
   </si>
   <si>
     <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1994194984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830003738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23751068115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821298599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351942062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729066848755</t>
+    <t xml:space="preserve">7.19941902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830099105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2375111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132688522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821250915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351846694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
     <t xml:space="preserve">6.45027303695679</t>
@@ -347,28 +347,28 @@
     <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96663331985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538375854492</t>
+    <t xml:space="preserve">6.96663284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99626111984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84812450408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1867208480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053657531738</t>
+    <t xml:space="preserve">6.84812498092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.05128240585327</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360694885254</t>
+    <t xml:space="preserve">7.10630464553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
@@ -389,82 +389,82 @@
     <t xml:space="preserve">7.05974769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0470495223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858470916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0555157661438</t>
+    <t xml:space="preserve">7.04705047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398010253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05551528930664</t>
   </si>
   <si>
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0004940032959</t>
+    <t xml:space="preserve">7.00049352645874</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11900186538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00895833969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476945877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327875137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402505874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597644805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43220472335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992418289185</t>
+    <t xml:space="preserve">7.11900234222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.008957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476898193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2036509513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597597122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.432204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373943328857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38141489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490194320679</t>
+    <t xml:space="preserve">7.38141536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490146636963</t>
   </si>
   <si>
     <t xml:space="preserve">7.39834499359131</t>
@@ -473,70 +473,70 @@
     <t xml:space="preserve">7.47452926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64382743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652513504028</t>
+    <t xml:space="preserve">7.64382648468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652561187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.78349828720093</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843156814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229177474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69884967803955</t>
+    <t xml:space="preserve">7.58457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843395233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884920120239</t>
   </si>
   <si>
     <t xml:space="preserve">7.74540519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86814832687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582330703735</t>
+    <t xml:space="preserve">7.86814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9316349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317056655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8258228302002</t>
   </si>
   <si>
     <t xml:space="preserve">7.88930988311768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9147047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856405258179</t>
+    <t xml:space="preserve">7.91470432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856452941895</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308208465576</t>
+    <t xml:space="preserve">7.70308256149292</t>
   </si>
   <si>
     <t xml:space="preserve">7.61420011520386</t>
@@ -545,61 +545,61 @@
     <t xml:space="preserve">7.42797136306763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34332275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020885467529</t>
+    <t xml:space="preserve">7.34332323074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
     <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63536310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30946254730225</t>
+    <t xml:space="preserve">7.63536214828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694181442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3094630241394</t>
   </si>
   <si>
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95703029632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01205253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474880218506</t>
+    <t xml:space="preserve">7.34755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01205158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474975585938</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707382202148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21097660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023220062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40990352630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.21097755432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40990447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32525253295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027572631836</t>
+    <t xml:space="preserve">8.32525444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027477264404</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
@@ -641,25 +641,25 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290828704834</t>
+    <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
     <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5653657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541826248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773338317871</t>
+    <t xml:space="preserve">9.29448795318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56536483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
@@ -674,25 +674,25 @@
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451494216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620790481567</t>
+    <t xml:space="preserve">10.9451484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620771408081</t>
   </si>
   <si>
     <t xml:space="preserve">11.0551919937134</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884828567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.76624584198</t>
+    <t xml:space="preserve">11.4191846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884819030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239217758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7662448883057</t>
   </si>
   <si>
     <t xml:space="preserve">11.9355449676514</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491878509521</t>
+    <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
     <t xml:space="preserve">14.2633991241455</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0517768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.511157989502</t>
+    <t xml:space="preserve">14.051775932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111598968506</t>
   </si>
   <si>
     <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443204879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0940990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009880065918</t>
+    <t xml:space="preserve">14.6443195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0941009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761610031128</t>
+    <t xml:space="preserve">13.4761619567871</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
@@ -767,46 +767,46 @@
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094509124756</t>
+    <t xml:space="preserve">14.0094499588013</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480501174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.601996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596714019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004177093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073038101196</t>
+    <t xml:space="preserve">14.3480491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512056350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004167556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.407301902771</t>
   </si>
   <si>
     <t xml:space="preserve">14.4157686233521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618194580078</t>
+    <t xml:space="preserve">14.3311176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618204116821</t>
   </si>
   <si>
     <t xml:space="preserve">13.8655471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7978267669678</t>
+    <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
     <t xml:space="preserve">13.9840574264526</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5269508361816</t>
+    <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
     <t xml:space="preserve">13.5523452758789</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.543098449707</t>
+    <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.03480052948</t>
+    <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
     <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9400339126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397172927856</t>
+    <t xml:space="preserve">12.940034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3018732070923</t>
+    <t xml:space="preserve">13.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.301872253418</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812601089478</t>
+    <t xml:space="preserve">13.1812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
@@ -893,52 +893,52 @@
     <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557331085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123380661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277187347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276026725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2501821517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0606479644775</t>
+    <t xml:space="preserve">12.6557321548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277196884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2760276794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2501811981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
     <t xml:space="preserve">12.9314203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8194217681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4834289550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2335872650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3369703292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0354385375977</t>
+    <t xml:space="preserve">12.8194227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4834280014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.233588218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3369693756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.035439491272</t>
   </si>
   <si>
     <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474370956421</t>
+    <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2594337463379</t>
+    <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.837287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7855978012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7166767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114433288574</t>
+    <t xml:space="preserve">11.8372888565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7855968475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7166757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286733627319</t>
@@ -971,31 +971,31 @@
     <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8200578689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7769823074341</t>
+    <t xml:space="preserve">11.8200588226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7769813537598</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511377334595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339057922363</t>
+    <t xml:space="preserve">11.7339067459106</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305227279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182075500488</t>
+    <t xml:space="preserve">11.6305236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182085037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785140991211</t>
+    <t xml:space="preserve">12.0785150527954</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157211303711</t>
+    <t xml:space="preserve">12.0871286392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157220840454</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988096237183</t>
+    <t xml:space="preserve">12.6988077163696</t>
   </si>
   <si>
     <t xml:space="preserve">12.5006589889526</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591161727905</t>
+    <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8366508483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883438110352</t>
+    <t xml:space="preserve">12.8366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883428573608</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538837432861</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7504997253418</t>
+    <t xml:space="preserve">12.6643476486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
@@ -1082,22 +1082,22 @@
     <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7246551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935771942139</t>
+    <t xml:space="preserve">12.7246561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935752868652</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418842315674</t>
+    <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917268753052</t>
+    <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089569091797</t>
@@ -1106,19 +1106,19 @@
     <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520315170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0778779983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0951080322266</t>
+    <t xml:space="preserve">13.0520324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0778770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0951070785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984910964966</t>
+    <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757091522217</t>
+    <t xml:space="preserve">13.7757081985474</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843246459961</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289319992065</t>
+    <t xml:space="preserve">14.1289329528809</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907712936401</t>
@@ -1148,43 +1148,43 @@
     <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8618621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240180969238</t>
+    <t xml:space="preserve">13.8618612289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240190505981</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547784805298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3443117141724</t>
+    <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9393978118896</t>
+    <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
     <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1117010116577</t>
+    <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929401397705</t>
+    <t xml:space="preserve">13.7929391860962</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206359863281</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637115478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8187856674194</t>
+    <t xml:space="preserve">13.6637105941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8187866210938</t>
   </si>
   <si>
     <t xml:space="preserve">13.8877077102661</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8360147476196</t>
+    <t xml:space="preserve">13.8360157012939</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7326335906982</t>
+    <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
     <t xml:space="preserve">13.7154035568237</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">13.3535642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.405255317688</t>
+    <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1238,16 +1238,16 @@
     <t xml:space="preserve">13.3880252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7670946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6292514801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3707942962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2846431732178</t>
+    <t xml:space="preserve">13.7670936584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6292495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.370795249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603294372559</t>
@@ -1256,31 +1256,31 @@
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775604248047</t>
+    <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5086374282837</t>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.951714515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693756103516</t>
+    <t xml:space="preserve">13.8634119033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9517154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693746566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1106586456299</t>
+    <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
     <t xml:space="preserve">13.9340543746948</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4219026565552</t>
+    <t xml:space="preserve">13.5278644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4219017028809</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686941146851</t>
+    <t xml:space="preserve">13.0686950683594</t>
   </si>
   <si>
     <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872619628906</t>
+    <t xml:space="preserve">14.2872629165649</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.004695892334</t>
+    <t xml:space="preserve">14.0046949386597</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753374099731</t>
+    <t xml:space="preserve">14.0753364562988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.9870347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8457517623901</t>
+    <t xml:space="preserve">13.8457527160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338272094727</t>
+    <t xml:space="preserve">13.6338262557983</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102043151855</t>
+    <t xml:space="preserve">13.5102052688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">13.1746578216553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629585266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.980393409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6095237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5035610198975</t>
+    <t xml:space="preserve">13.2629594802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9803924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6095247268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
     <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3159408569336</t>
+    <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
     <t xml:space="preserve">12.9980535507202</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569957733154</t>
+    <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
     <t xml:space="preserve">13.2099781036377</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.2673349380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790313720703</t>
+    <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.037748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0024271011353</t>
+    <t xml:space="preserve">11.0377492904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0024280548096</t>
   </si>
   <si>
     <t xml:space="preserve">11.2143526077271</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
+    <t xml:space="preserve">10.9317874908447</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792585372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441654205322</t>
+    <t xml:space="preserve">11.2849950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441644668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">11.7618246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7265033721924</t>
+    <t xml:space="preserve">11.7265043258667</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439373016357</t>
+    <t xml:space="preserve">11.4439382553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494466781616</t>
+    <t xml:space="preserve">10.9494476318359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
@@ -1577,28 +1577,28 @@
     <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41299247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831371307373</t>
+    <t xml:space="preserve">9.41299152374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831275939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
+    <t xml:space="preserve">9.53661441802979</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198619842529</t>
+    <t xml:space="preserve">10.7198629379272</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551822662354</t>
+    <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1610,25 +1610,25 @@
     <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079364776611</t>
+    <t xml:space="preserve">10.4902772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079374313354</t>
   </si>
   <si>
     <t xml:space="preserve">10.5785789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6845407485962</t>
+    <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
     <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8258237838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.613899230957</t>
+    <t xml:space="preserve">10.8258247375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
     <t xml:space="preserve">10.5609188079834</t>
@@ -1646,16 +1646,16 @@
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019746780396</t>
+    <t xml:space="preserve">10.4019756317139</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8434839248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8964653015137</t>
+    <t xml:space="preserve">10.84348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.896466255188</t>
   </si>
   <si>
     <t xml:space="preserve">10.9141263961792</t>
@@ -67706,7 +67706,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6494328704</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>40106</v>
@@ -67727,6 +67727,32 @@
         <v>897</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6495486111</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>6449</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>8.96000003814697</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>9.03999996185303</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>897</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1539421081543</t>
+    <t xml:space="preserve">5.15394163131714</t>
   </si>
   <si>
     <t xml:space="preserve">5.09169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564275741577</t>
+    <t xml:space="preserve">5.14564228057861</t>
   </si>
   <si>
     <t xml:space="preserve">5.1871395111084</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31163120269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3157811164856</t>
+    <t xml:space="preserve">5.31163167953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31578159332275</t>
   </si>
   <si>
     <t xml:space="preserve">5.34482908248901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38632535934448</t>
+    <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
     <t xml:space="preserve">5.34897899627686</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">5.39462518692017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47762012481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48176956176758</t>
+    <t xml:space="preserve">5.47761964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000385284424</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86769247055054</t>
+    <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
     <t xml:space="preserve">6.05442953109741</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">6.04198026657104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05857944488525</t>
+    <t xml:space="preserve">6.0585789680481</t>
   </si>
   <si>
     <t xml:space="preserve">6.05027961730957</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55239534378052</t>
+    <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56069469451904</t>
+    <t xml:space="preserve">6.56069421768188</t>
   </si>
   <si>
     <t xml:space="preserve">6.432053565979</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">6.58559226989746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59804105758667</t>
+    <t xml:space="preserve">6.59804153442383</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464023590088</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80552768707275</t>
+    <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321678161621</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12920475006104</t>
+    <t xml:space="preserve">7.12920522689819</t>
   </si>
   <si>
     <t xml:space="preserve">7.3034930229187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46948146820068</t>
+    <t xml:space="preserve">7.46948099136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">7.67281818389893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38648557662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798328399658</t>
+    <t xml:space="preserve">7.3864860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
     <t xml:space="preserve">7.36573839187622</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">7.16240310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21634864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643665313721</t>
+    <t xml:space="preserve">7.21634817123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
     <t xml:space="preserve">7.2205810546875</t>
@@ -263,28 +263,28 @@
     <t xml:space="preserve">6.89468240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72961568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356342315674</t>
+    <t xml:space="preserve">6.72961521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356294631958</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123888015747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617263793945</t>
+    <t xml:space="preserve">6.77617311477661</t>
   </si>
   <si>
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49145936965942</t>
+    <t xml:space="preserve">6.99202823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49145984649658</t>
   </si>
   <si>
     <t xml:space="preserve">7.37294960021973</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">7.27983665466309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29253244400024</t>
+    <t xml:space="preserve">7.2925329208374</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676580429077</t>
@@ -326,25 +326,25 @@
     <t xml:space="preserve">7.02588796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87351846694946</t>
+    <t xml:space="preserve">6.87351894378662</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036104202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56031703948975</t>
+    <t xml:space="preserve">6.45027256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036151885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5603175163269</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08514213562012</t>
+    <t xml:space="preserve">7.08514165878296</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">6.84812498092651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672132492065</t>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672180175781</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128240585327</t>
+    <t xml:space="preserve">7.05128288269043</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974769592285</t>
+    <t xml:space="preserve">7.05974817276001</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086572647095</t>
+    <t xml:space="preserve">6.97086524963379</t>
   </si>
   <si>
     <t xml:space="preserve">7.03858518600464</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00049352645874</t>
+    <t xml:space="preserve">7.0004940032959</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">7.11900234222412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.008957862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476898193359</t>
+    <t xml:space="preserve">7.00895833969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
     <t xml:space="preserve">7.10207271575928</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">7.2036509513855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23327922821045</t>
+    <t xml:space="preserve">7.23327875137329</t>
   </si>
   <si>
     <t xml:space="preserve">7.17402458190918</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">7.24597597122192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40680932998657</t>
+    <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
     <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49992322921753</t>
+    <t xml:space="preserve">7.49992370605469</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373943328857</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452926635742</t>
+    <t xml:space="preserve">7.47452878952026</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382648468018</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">7.44913387298584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53378248214722</t>
+    <t xml:space="preserve">7.53378295898438</t>
   </si>
   <si>
     <t xml:space="preserve">7.61843395233154</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">7.58880519866943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69884920120239</t>
+    <t xml:space="preserve">7.6522912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
   </si>
   <si>
     <t xml:space="preserve">7.74540519714355</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">7.9316349029541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92317056655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
+    <t xml:space="preserve">7.92316961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582330703735</t>
   </si>
   <si>
     <t xml:space="preserve">7.88930988311768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91470432281494</t>
+    <t xml:space="preserve">7.91470527648926</t>
   </si>
   <si>
     <t xml:space="preserve">7.95279788970947</t>
@@ -536,34 +536,34 @@
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
+    <t xml:space="preserve">7.70308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6141996383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.34332323074341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25020837783813</t>
+    <t xml:space="preserve">7.25020885467529</t>
   </si>
   <si>
     <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63536214828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694181442261</t>
+    <t xml:space="preserve">7.63536167144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694133758545</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3094630241394</t>
+    <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
     <t xml:space="preserve">7.40257692337036</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474975585938</t>
+    <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707382202148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21097755432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023124694824</t>
+    <t xml:space="preserve">8.21097660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023220062256</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990447998047</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32525444030762</t>
+    <t xml:space="preserve">8.3252534866333</t>
   </si>
   <si>
     <t xml:space="preserve">8.38027477264404</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290924072266</t>
+    <t xml:space="preserve">9.19290828704834</t>
   </si>
   <si>
     <t xml:space="preserve">9.1759786605835</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56536483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861217498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773433685303</t>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541826248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396213531494</t>
+    <t xml:space="preserve">9.90396118164062</t>
   </si>
   <si>
     <t xml:space="preserve">10.4965076446533</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">11.0551919937134</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191846847534</t>
+    <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7239217758179</t>
+    <t xml:space="preserve">11.7239208221436</t>
   </si>
   <si>
     <t xml:space="preserve">11.7662448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355449676514</t>
+    <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741422653198</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491868972778</t>
+    <t xml:space="preserve">13.3491878509521</t>
   </si>
   <si>
     <t xml:space="preserve">14.2633991241455</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">12.5111598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460285186768</t>
+    <t xml:space="preserve">13.1460275650024</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443195343018</t>
@@ -731,19 +731,19 @@
     <t xml:space="preserve">14.0941009521484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009870529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206340789795</t>
+    <t xml:space="preserve">14.5173463821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206350326538</t>
   </si>
   <si>
     <t xml:space="preserve">12.8243618011475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169073104858</t>
+    <t xml:space="preserve">13.4169063568115</t>
   </si>
   <si>
     <t xml:space="preserve">13.4761619567871</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184850692749</t>
+    <t xml:space="preserve">13.5184860229492</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930906295776</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">14.3480491638184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6019954681396</t>
+    <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
     <t xml:space="preserve">14.5512056350708</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">14.5088806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5004167556763</t>
+    <t xml:space="preserve">14.5004177093506</t>
   </si>
   <si>
     <t xml:space="preserve">14.407301902771</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">14.4157686233521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3311176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618204116821</t>
+    <t xml:space="preserve">14.3311185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
     <t xml:space="preserve">13.8655471801758</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9840574264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994083404541</t>
+    <t xml:space="preserve">13.9840564727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031341552734</t>
+    <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523452758789</t>
+    <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175714492798</t>
+    <t xml:space="preserve">13.0175704956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.301872253418</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557321548462</t>
+    <t xml:space="preserve">12.6557312011719</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123390197754</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501811981201</t>
+    <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314203262329</t>
+    <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834280014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.233588218689</t>
+    <t xml:space="preserve">12.4834289550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2335872650146</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369693756104</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474361419678</t>
+    <t xml:space="preserve">12.1474351882935</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597513198853</t>
+    <t xml:space="preserve">11.7597522735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769813537598</t>
+    <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511377334595</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182085037231</t>
+    <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785150527954</t>
+    <t xml:space="preserve">12.0785160064697</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157220840454</t>
+    <t xml:space="preserve">12.0871295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">12.6988077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591152191162</t>
+    <t xml:space="preserve">12.7591161727905</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231233596802</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">12.4661979675293</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628168106079</t>
+    <t xml:space="preserve">12.3628158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265054702759</t>
+    <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141893386841</t>
+    <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
     <t xml:space="preserve">12.8366527557373</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">12.8883428573608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8538837432861</t>
+    <t xml:space="preserve">12.8538827896118</t>
   </si>
   <si>
     <t xml:space="preserve">12.6471176147461</t>
@@ -1073,19 +1073,19 @@
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868110656738</t>
+    <t xml:space="preserve">12.5868120193481</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
+    <t xml:space="preserve">12.6126565933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8711128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917249679565</t>
+    <t xml:space="preserve">12.871111869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917259216309</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089569091797</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0778770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0951070785522</t>
+    <t xml:space="preserve">13.0778779983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0951080322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2674112319946</t>
+    <t xml:space="preserve">13.2674121856689</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550970077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7757081985474</t>
+    <t xml:space="preserve">13.6550960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7757091522217</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843246459961</t>
@@ -1148,19 +1148,19 @@
     <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8618612289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240190505981</t>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8618621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240180969238</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547784805298</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.844630241394</t>
+    <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.111701965332</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929391860962</t>
+    <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206359863281</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292495727539</t>
+    <t xml:space="preserve">13.6292505264282</t>
   </si>
   <si>
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846422195435</t>
+    <t xml:space="preserve">13.2846431732178</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603294372559</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775594711304</t>
+    <t xml:space="preserve">13.5775604248047</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5086393356323</t>
+    <t xml:space="preserve">13.508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693746566772</t>
+    <t xml:space="preserve">13.9693737030029</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4219017028809</t>
+    <t xml:space="preserve">13.5278635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4219026565552</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402433395386</t>
+    <t xml:space="preserve">13.0686960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402423858643</t>
   </si>
   <si>
     <t xml:space="preserve">14.2872629165649</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985059738159</t>
+    <t xml:space="preserve">13.5985069274902</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452983856201</t>
+    <t xml:space="preserve">13.3512601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452993392944</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1746578216553</t>
+    <t xml:space="preserve">13.2276382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157136917114</t>
+    <t xml:space="preserve">13.0157127380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980535507202</t>
+    <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391103744507</t>
+    <t xml:space="preserve">12.8391094207764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099781036377</t>
+    <t xml:space="preserve">13.2099771499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2386560440063</t>
+    <t xml:space="preserve">12.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379764556885</t>
+    <t xml:space="preserve">11.267333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379755020142</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4262771606445</t>
+    <t xml:space="preserve">11.4262762069702</t>
   </si>
   <si>
     <t xml:space="preserve">11.0377492904663</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317874908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0730695724487</t>
+    <t xml:space="preserve">10.9317865371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0730686187744</t>
   </si>
   <si>
     <t xml:space="preserve">11.2849950790405</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728433609009</t>
+    <t xml:space="preserve">11.2496728897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549560546875</t>
+    <t xml:space="preserve">10.4549551010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
+    <t xml:space="preserve">10.1547298431396</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299152374268</t>
@@ -1586,19 +1586,19 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53661441802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7198629379272</t>
+    <t xml:space="preserve">9.5366153717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1370687484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551832199097</t>
+    <t xml:space="preserve">10.7551822662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2430305480957</t>
+    <t xml:space="preserve">10.24303150177</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902772903442</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.5079374313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5785789489746</t>
+    <t xml:space="preserve">10.5785779953003</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375221252441</t>
+    <t xml:space="preserve">10.7375211715698</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258247375488</t>
@@ -1631,22 +1631,22 @@
     <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606906890869</t>
+    <t xml:space="preserve">10.5609178543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019756317139</t>
+    <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">10.84348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.896466255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554103851318</t>
+    <t xml:space="preserve">10.8964653015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -67732,7 +67732,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6495486111</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>6449</v>
@@ -67753,6 +67753,32 @@
         <v>897</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6495486111</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>26250</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>8.9399995803833</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>9.03999996185303</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394163131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169673919678</t>
+    <t xml:space="preserve">5.15394258499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24523544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31163167953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31578159332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482908248901</t>
+    <t xml:space="preserve">5.24523591995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31163120269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3157811164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
     <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34897899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
+    <t xml:space="preserve">5.3489785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067964553833</t>
+    <t xml:space="preserve">5.41122388839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067869186401</t>
   </si>
   <si>
     <t xml:space="preserve">5.39462518692017</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71415376663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939311981201</t>
+    <t xml:space="preserve">5.89259052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939359664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95068693161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599182128906</t>
+    <t xml:space="preserve">5.95068645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653749465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599229812622</t>
   </si>
   <si>
     <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442953109741</t>
+    <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">6.04198026657104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0585789680481</t>
+    <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
     <t xml:space="preserve">6.05027961730957</t>
@@ -161,28 +161,28 @@
     <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19137001037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47355031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239486694336</t>
+    <t xml:space="preserve">6.19137048721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47355079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36150789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239534378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56069421768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.432053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994512557983</t>
+    <t xml:space="preserve">6.56069469451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43205308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">6.58559226989746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464023590088</t>
+    <t xml:space="preserve">6.59804201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464071273804</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953876495361</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96321678161621</t>
+    <t xml:space="preserve">6.96321582794189</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301288604736</t>
@@ -215,31 +215,31 @@
     <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12920522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034930229187</t>
+    <t xml:space="preserve">7.12920427322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349349975586</t>
   </si>
   <si>
     <t xml:space="preserve">7.46948099136353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99234580993652</t>
+    <t xml:space="preserve">7.99234485626221</t>
   </si>
   <si>
     <t xml:space="preserve">8.67289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281818389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3864860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798376083374</t>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648653030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798471450806</t>
   </si>
   <si>
     <t xml:space="preserve">7.36573839187622</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">7.16240310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21634817123413</t>
+    <t xml:space="preserve">7.21634912490845</t>
   </si>
   <si>
     <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2205810546875</t>
+    <t xml:space="preserve">7.22058057785034</t>
   </si>
   <si>
     <t xml:space="preserve">7.20788431167603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89468240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961521148682</t>
+    <t xml:space="preserve">6.89468145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
     <t xml:space="preserve">6.80156755447388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98356294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123888015747</t>
+    <t xml:space="preserve">6.98356342315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
     <t xml:space="preserve">6.77617311477661</t>
@@ -284,34 +284,34 @@
     <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49145984649658</t>
+    <t xml:space="preserve">7.49145889282227</t>
   </si>
   <si>
     <t xml:space="preserve">7.37294960021973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27983665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925329208374</t>
+    <t xml:space="preserve">7.27983570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253244400024</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523014068604</t>
+    <t xml:space="preserve">7.26290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523061752319</t>
   </si>
   <si>
     <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830099105835</t>
+    <t xml:space="preserve">7.1994194984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
     <t xml:space="preserve">7.2375111579895</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588796615601</t>
+    <t xml:space="preserve">7.06821298599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588844299316</t>
   </si>
   <si>
     <t xml:space="preserve">6.87351894378662</t>
@@ -332,25 +332,25 @@
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027256011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036151885986</t>
+    <t xml:space="preserve">6.45027303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
     <t xml:space="preserve">6.5603175163269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514165878296</t>
+    <t xml:space="preserve">7.15286207199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626111984253</t>
+    <t xml:space="preserve">6.99626064300537</t>
   </si>
   <si>
     <t xml:space="preserve">6.72538328170776</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">6.84812498092651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672180175781</t>
+    <t xml:space="preserve">6.88621759414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672132492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128288269043</t>
+    <t xml:space="preserve">7.05128192901611</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0936074256897</t>
+    <t xml:space="preserve">7.10630559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360647201538</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
@@ -389,22 +389,22 @@
     <t xml:space="preserve">7.05974817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04705047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858518600464</t>
+    <t xml:space="preserve">7.04704999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06398010253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05551528930664</t>
+    <t xml:space="preserve">7.06398057937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0555157661438</t>
   </si>
   <si>
     <t xml:space="preserve">7.09783983230591</t>
@@ -413,37 +413,37 @@
     <t xml:space="preserve">7.0004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03435325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900234222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00895833969116</t>
+    <t xml:space="preserve">7.03435277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11900186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00895738601685</t>
   </si>
   <si>
     <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2036509513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327875137329</t>
+    <t xml:space="preserve">7.10207223892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987874984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327827453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.17402458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21211624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
+    <t xml:space="preserve">7.21211719512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597644805908</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680980682373</t>
@@ -458,79 +458,79 @@
     <t xml:space="preserve">7.42373943328857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38141536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406715393066</t>
+    <t xml:space="preserve">7.38141489028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406763076782</t>
   </si>
   <si>
     <t xml:space="preserve">7.44490146636963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39834499359131</t>
+    <t xml:space="preserve">7.39834451675415</t>
   </si>
   <si>
     <t xml:space="preserve">7.47452878952026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64382648468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652561187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349828720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457326889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843395233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6522912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540519714355</t>
+    <t xml:space="preserve">7.64382743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652418136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349733352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457279205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.449134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880567550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540662765503</t>
   </si>
   <si>
     <t xml:space="preserve">7.86814880371094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9316349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582330703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88930988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470527648926</t>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8258228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
     <t xml:space="preserve">7.95279788970947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94856452941895</t>
+    <t xml:space="preserve">7.9485650062561</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
@@ -539,25 +539,25 @@
     <t xml:space="preserve">7.70308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6141996383667</t>
+    <t xml:space="preserve">7.61419916152954</t>
   </si>
   <si>
     <t xml:space="preserve">7.42797183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34332323074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45759963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536167144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694133758545</t>
+    <t xml:space="preserve">7.34332227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45760011672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694229125977</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685380935669</t>
@@ -572,10 +572,10 @@
     <t xml:space="preserve">7.34755516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27137136459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838947296143</t>
+    <t xml:space="preserve">7.27137041091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838899612427</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702934265137</t>
@@ -584,28 +584,28 @@
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474880218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097660064697</t>
+    <t xml:space="preserve">8.02474784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707286834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097850799561</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40990447998047</t>
+    <t xml:space="preserve">8.40990257263184</t>
   </si>
   <si>
     <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40567111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26599979400635</t>
+    <t xml:space="preserve">8.40567016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26599884033203</t>
   </si>
   <si>
     <t xml:space="preserve">8.23213958740234</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">8.3252534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027477264404</t>
+    <t xml:space="preserve">8.38027667999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">9.01514434814453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.998215675354</t>
+    <t xml:space="preserve">8.99821662902832</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
@@ -641,61 +641,61 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290828704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1759786605835</t>
+    <t xml:space="preserve">9.19290924072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5653657913208</t>
+    <t xml:space="preserve">9.56536674499512</t>
   </si>
   <si>
     <t xml:space="preserve">9.98861122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4541826248169</t>
+    <t xml:space="preserve">10.4541845321655</t>
   </si>
   <si>
     <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1325159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90396118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4965076446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7927799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9451484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620771408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0551919937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884819030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7662448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355440139771</t>
+    <t xml:space="preserve">10.1325168609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90396308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.496506690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7927808761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9451475143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620780944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884828567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239217758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.76624584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355459213257</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741422653198</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491878509521</t>
+    <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
     <t xml:space="preserve">14.2633991241455</t>
@@ -716,22 +716,22 @@
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.051775932312</t>
+    <t xml:space="preserve">14.0517768859863</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173463821411</t>
+    <t xml:space="preserve">13.1460285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443185806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0940999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173473358154</t>
   </si>
   <si>
     <t xml:space="preserve">14.0009880065918</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">13.1206350326538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243618011475</t>
+    <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169063568115</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">13.4761619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338369369507</t>
+    <t xml:space="preserve">13.433837890625</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">14.0094499588013</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3057231903076</t>
+    <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
     <t xml:space="preserve">14.3480491638184</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512056350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004177093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.407301902771</t>
+    <t xml:space="preserve">14.5512065887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073028564453</t>
   </si>
   <si>
     <t xml:space="preserve">14.4157686233521</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">14.3311185836792</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1618194580078</t>
+    <t xml:space="preserve">14.1618185043335</t>
   </si>
   <si>
     <t xml:space="preserve">13.8655471801758</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">12.7820377349854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397136688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0275201797485</t>
+    <t xml:space="preserve">12.7397117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0275192260742</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348024368286</t>
+    <t xml:space="preserve">13.0348014831543</t>
   </si>
   <si>
     <t xml:space="preserve">13.043417930603</t>
@@ -857,52 +857,52 @@
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397163391113</t>
+    <t xml:space="preserve">13.4397172927856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.301872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1295680999756</t>
+    <t xml:space="preserve">13.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3018732070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1640291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1295690536499</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6901931762695</t>
+    <t xml:space="preserve">12.6901922225952</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812610626221</t>
+    <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228038787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557312011719</t>
+    <t xml:space="preserve">12.9228048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2760276794434</t>
+    <t xml:space="preserve">13.3277187347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
@@ -911,28 +911,28 @@
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8194227218628</t>
+    <t xml:space="preserve">12.9314203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2335872650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3369693756104</t>
+    <t xml:space="preserve">12.233588218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3369703292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.035439491272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8975944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474351882935</t>
+    <t xml:space="preserve">11.8975954055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474370956421</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302051544189</t>
+    <t xml:space="preserve">12.1302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8372888565063</t>
+    <t xml:space="preserve">11.837287902832</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8286733627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7597522735596</t>
+    <t xml:space="preserve">11.7166757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114423751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8286724090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
     <t xml:space="preserve">11.8200588226318</t>
@@ -980,28 +980,28 @@
     <t xml:space="preserve">11.7511377334595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339067459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6046781539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182075500488</t>
+    <t xml:space="preserve">11.7339057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.604679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6305246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182085037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440530776978</t>
+    <t xml:space="preserve">12.0785140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388216018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440540313721</t>
   </si>
   <si>
     <t xml:space="preserve">12.0871295928955</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">12.6988077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500659942627</t>
+    <t xml:space="preserve">12.5006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231224060059</t>
+    <t xml:space="preserve">12.4231233596802</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661979675293</t>
+    <t xml:space="preserve">12.4661998748779</t>
   </si>
   <si>
     <t xml:space="preserve">12.3628158569336</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.535120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265045166016</t>
+    <t xml:space="preserve">12.5351209640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265054702759</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8366527557373</t>
+    <t xml:space="preserve">12.9141893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.836651802063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883428573608</t>
@@ -1067,31 +1067,31 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643476486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7505006790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868120193481</t>
+    <t xml:space="preserve">12.6643486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7504997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126565933228</t>
+    <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7935762405396</t>
+    <t xml:space="preserve">12.7935752868652</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418851852417</t>
+    <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
     <t xml:space="preserve">12.871111869812</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">13.0089569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572649002075</t>
+    <t xml:space="preserve">12.9572658538818</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2674121856689</t>
+    <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914073944092</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">13.6550960540771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757091522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7498636245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1289329528809</t>
+    <t xml:space="preserve">13.7757081985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843236923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7498626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907712936401</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963203430176</t>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963222503662</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618621826172</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">14.1547784805298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3443126678467</t>
+    <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206359863281</t>
+    <t xml:space="preserve">13.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206369400024</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
+    <t xml:space="preserve">13.6637115478516</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704767227173</t>
+    <t xml:space="preserve">13.8704776763916</t>
   </si>
   <si>
     <t xml:space="preserve">13.8360157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8015556335449</t>
+    <t xml:space="preserve">13.8015546798706</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.405255317688</t>
+    <t xml:space="preserve">13.3535642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1247,19 +1247,19 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846431732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603294372559</t>
+    <t xml:space="preserve">13.2846422195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603284835815</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258684158325</t>
+    <t xml:space="preserve">13.5775594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258693695068</t>
   </si>
   <si>
     <t xml:space="preserve">13.508638381958</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693737030029</t>
+    <t xml:space="preserve">13.8634128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693756103516</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1106576919556</t>
+    <t xml:space="preserve">14.1106586456299</t>
   </si>
   <si>
     <t xml:space="preserve">13.9340543746948</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278635025024</t>
+    <t xml:space="preserve">13.5278654098511</t>
   </si>
   <si>
     <t xml:space="preserve">13.4219026565552</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">13.0686941146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0046949386597</t>
+    <t xml:space="preserve">14.004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.9870347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8457527160645</t>
+    <t xml:space="preserve">13.8457517623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985069274902</t>
+    <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338262557983</t>
+    <t xml:space="preserve">13.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1385,64 +1385,64 @@
     <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452993392944</t>
+    <t xml:space="preserve">13.351261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452983856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.174656867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629594802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9803924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6095247268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5035619735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0157127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159399032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980525970459</t>
+    <t xml:space="preserve">13.2276372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1746578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.980393409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6095237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5035610198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0157136917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159408569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980535507202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391094207764</t>
+    <t xml:space="preserve">12.8391103744507</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569967269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099771499634</t>
+    <t xml:space="preserve">13.1569957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790323257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4262762069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0377492904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0024280548096</t>
+    <t xml:space="preserve">11.1790313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4262771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.037748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0024271011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.2143526077271</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0730686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">11.0730695724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">11.7618246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7265043258667</t>
+    <t xml:space="preserve">11.7265033721924</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496728897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728424072266</t>
+    <t xml:space="preserve">11.2496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494476318359</t>
+    <t xml:space="preserve">10.9494466781616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547298431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831275939941</t>
+    <t xml:space="preserve">10.1547288894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831371307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1370687484741</t>
+    <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
     <t xml:space="preserve">10.7198619842529</t>
@@ -1607,40 +1607,40 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785779953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6845417022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7375211715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258247375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6139001846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5609178543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606916427612</t>
+    <t xml:space="preserve">10.2430305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785789489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6845407485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7375221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258237838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.613899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5609188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432567596436</t>
+    <t xml:space="preserve">10.5432577133179</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.84348487854</t>
+    <t xml:space="preserve">10.8434839248657</t>
   </si>
   <si>
     <t xml:space="preserve">10.8964653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554094314575</t>
+    <t xml:space="preserve">10.9141263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554103851318</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -67758,7 +67758,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6495486111</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>26250</v>
@@ -67779,6 +67779,32 @@
         <v>888</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6493865741</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>4008</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>893</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -50,19 +50,19 @@
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1165943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958877563477</t>
+    <t xml:space="preserve">5.14564180374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18713998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958925247192</t>
   </si>
   <si>
     <t xml:space="preserve">5.24523591995239</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3157811164856</t>
+    <t xml:space="preserve">5.31578063964844</t>
   </si>
   <si>
     <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38632583618164</t>
+    <t xml:space="preserve">5.38632535934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.3489785194397</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972713470459</t>
+    <t xml:space="preserve">5.36972665786743</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122388839722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34067869186401</t>
+    <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
     <t xml:space="preserve">5.39462518692017</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71000385284424</t>
+    <t xml:space="preserve">5.48176956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71000337600708</t>
   </si>
   <si>
     <t xml:space="preserve">5.9340877532959</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939359664917</t>
+    <t xml:space="preserve">5.85939311981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728563308716</t>
+    <t xml:space="preserve">5.96728610992432</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95068645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653749465942</t>
+    <t xml:space="preserve">5.95068693161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653654098511</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599229812622</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8676929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05443000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198026657104</t>
+    <t xml:space="preserve">5.86769247055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05442953109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04198122024536</t>
   </si>
   <si>
     <t xml:space="preserve">6.05857944488525</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327360153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137048721313</t>
+    <t xml:space="preserve">6.13327407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
     <t xml:space="preserve">6.47355079650879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36150789260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239534378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57314348220825</t>
+    <t xml:space="preserve">6.3615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239486694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57314395904541</t>
   </si>
   <si>
     <t xml:space="preserve">6.56069469451904</t>
@@ -182,52 +182,52 @@
     <t xml:space="preserve">6.43205308914185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53994607925415</t>
+    <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559226989746</t>
+    <t xml:space="preserve">6.58559274673462</t>
   </si>
   <si>
     <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61464071273804</t>
+    <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8055272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321582794189</t>
+    <t xml:space="preserve">6.80552625656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321725845337</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301288604736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02961206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920427322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289733886719</t>
+    <t xml:space="preserve">7.02961158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05450963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920475006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349206924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6728982925415</t>
   </si>
   <si>
     <t xml:space="preserve">8.12928485870361</t>
@@ -236,28 +236,28 @@
     <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38648653030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573839187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634912490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22058057785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788431167603</t>
+    <t xml:space="preserve">7.3864860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788335800171</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468145370483</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94123840332031</t>
+    <t xml:space="preserve">6.94123792648315</t>
   </si>
   <si>
     <t xml:space="preserve">6.77617311477661</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37294960021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676580429077</t>
+    <t xml:space="preserve">6.99202919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37295007705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676628112793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290607452393</t>
@@ -314,37 +314,37 @@
     <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2375111579895</t>
+    <t xml:space="preserve">7.23751163482666</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821298599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351894378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45027303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036104202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5603175163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15286207199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514261245728</t>
+    <t xml:space="preserve">7.06821346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729066848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45027256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56031703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15286159515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
@@ -353,37 +353,37 @@
     <t xml:space="preserve">6.99626064300537</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538328170776</t>
+    <t xml:space="preserve">6.72538280487061</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84812498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621759414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672132492065</t>
+    <t xml:space="preserve">6.84812450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672227859497</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128192901611</t>
+    <t xml:space="preserve">7.05128240585327</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360647201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937501907349</t>
+    <t xml:space="preserve">7.10630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0936074256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937549591064</t>
   </si>
   <si>
     <t xml:space="preserve">7.05974817276001</t>
@@ -392,70 +392,70 @@
     <t xml:space="preserve">7.04704999923706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086572647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858470916748</t>
+    <t xml:space="preserve">6.97086524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858423233032</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06398057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0555157661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09783983230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435277938843</t>
+    <t xml:space="preserve">7.0639796257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05551528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00049304962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435325622559</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00895738601685</t>
+    <t xml:space="preserve">7.008957862854</t>
   </si>
   <si>
     <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10207223892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365142822266</t>
+    <t xml:space="preserve">7.10207319259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987970352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365238189697</t>
   </si>
   <si>
     <t xml:space="preserve">7.23327827453613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17402458190918</t>
+    <t xml:space="preserve">7.17402410507202</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211719512939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597644805908</t>
+    <t xml:space="preserve">7.24597597122192</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.432204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373943328857</t>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373991012573</t>
   </si>
   <si>
     <t xml:space="preserve">7.38141489028931</t>
@@ -464,34 +464,34 @@
     <t xml:space="preserve">7.28406763076782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44490146636963</t>
+    <t xml:space="preserve">7.44490194320679</t>
   </si>
   <si>
     <t xml:space="preserve">7.39834451675415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382743835449</t>
+    <t xml:space="preserve">7.47452831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382696151733</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65652418136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378343582153</t>
+    <t xml:space="preserve">7.65652513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457231521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378248214722</t>
   </si>
   <si>
     <t xml:space="preserve">7.61843204498291</t>
@@ -503,22 +503,22 @@
     <t xml:space="preserve">7.65229225158691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69884967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540662765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316913604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
+    <t xml:space="preserve">7.69885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814737319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582378387451</t>
   </si>
   <si>
     <t xml:space="preserve">7.88931035995483</t>
@@ -527,31 +527,31 @@
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9485650062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553863525391</t>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553768157959</t>
   </si>
   <si>
     <t xml:space="preserve">7.70308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61419916152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797183990479</t>
+    <t xml:space="preserve">7.61420059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797136306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.34332227706909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25020790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45760011672974</t>
+    <t xml:space="preserve">7.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759916305542</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">7.73694229125977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51685380935669</t>
+    <t xml:space="preserve">7.51685428619385</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946350097656</t>
@@ -569,58 +569,58 @@
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755516052246</t>
+    <t xml:space="preserve">7.34755563735962</t>
   </si>
   <si>
     <t xml:space="preserve">7.27137041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50838899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702934265137</t>
+    <t xml:space="preserve">7.50838851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702981948853</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097850799561</t>
+    <t xml:space="preserve">8.02474880218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40990257263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45222759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40567016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26599884033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23213958740234</t>
+    <t xml:space="preserve">8.40990352630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45222854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26600074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3252534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027667999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040821075439</t>
+    <t xml:space="preserve">8.32525444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027572631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040916442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.87970638275146</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514434814453</t>
+    <t xml:space="preserve">9.01514625549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.99821662902832</t>
@@ -641,40 +641,40 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290924072266</t>
+    <t xml:space="preserve">9.19290828704834</t>
   </si>
   <si>
     <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56536674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1325168609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90396308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496506690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7927808761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9451475143433</t>
+    <t xml:space="preserve">9.29448699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773433685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1325149536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90396213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965057373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7927799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9451494216919</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191846847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884828567505</t>
+    <t xml:space="preserve">11.4191837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
@@ -695,61 +695,61 @@
     <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973876953125</t>
+    <t xml:space="preserve">11.9355440139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741413116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973886489868</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633991241455</t>
+    <t xml:space="preserve">13.3491878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633981704712</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0517768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443185806274</t>
+    <t xml:space="preserve">14.0517749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460294723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443204879761</t>
   </si>
   <si>
     <t xml:space="preserve">14.0940999984741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206350326538</t>
+    <t xml:space="preserve">14.5173463821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009860992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
     <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.433837890625</t>
+    <t xml:space="preserve">13.4169073104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338369369507</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184860229492</t>
+    <t xml:space="preserve">13.5184869766235</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930906295776</t>
@@ -767,70 +767,70 @@
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094499588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057241439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.601996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512065887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596714019775</t>
+    <t xml:space="preserve">14.0094509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057231903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.348048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512075424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596733093262</t>
   </si>
   <si>
     <t xml:space="preserve">14.5088815689087</t>
   </si>
   <si>
-    <t xml:space="preserve">14.500415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311185836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655471801758</t>
+    <t xml:space="preserve">14.5004167556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157667160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618194580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655462265015</t>
   </si>
   <si>
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9840564727783</t>
+    <t xml:space="preserve">13.984058380127</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385730743408</t>
+    <t xml:space="preserve">13.7385721206665</t>
   </si>
   <si>
     <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820377349854</t>
+    <t xml:space="preserve">13.1290998458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
     <t xml:space="preserve">12.7397117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0275192260742</t>
+    <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423007965088</t>
+    <t xml:space="preserve">13.4423017501831</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
@@ -848,37 +848,37 @@
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.043417930603</t>
+    <t xml:space="preserve">13.0348024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0434169769287</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397172927856</t>
+    <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175714492798</t>
+    <t xml:space="preserve">13.0175704956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.3018732070923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1640291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.1640300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6901922225952</t>
+    <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243366241455</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557331085205</t>
+    <t xml:space="preserve">12.6557321548462</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277187347412</t>
+    <t xml:space="preserve">13.3277196884155</t>
   </si>
   <si>
     <t xml:space="preserve">13.276026725769</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314203262329</t>
+    <t xml:space="preserve">12.9314184188843</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.233588218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3369703292847</t>
+    <t xml:space="preserve">12.2335872650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.035439491272</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">11.8975954055786</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3542003631592</t>
+    <t xml:space="preserve">12.1474351882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3542013168335</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594327926636</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -953,55 +953,55 @@
     <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.837287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7855968475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
+    <t xml:space="preserve">11.8372888565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7855978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286724090576</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597513198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8200588226318</t>
+    <t xml:space="preserve">11.7597522735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8200597763062</t>
   </si>
   <si>
     <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.604679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6305246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182085037231</t>
+    <t xml:space="preserve">11.7511367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339067459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6305236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388216018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440540313721</t>
+    <t xml:space="preserve">12.0785160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
     <t xml:space="preserve">12.0871295928955</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">12.6988086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
@@ -1028,37 +1028,37 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231233596802</t>
+    <t xml:space="preserve">12.4231214523315</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.4661989212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3628149032593</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5351209640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265054702759</t>
+    <t xml:space="preserve">12.535120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.836651802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883428573608</t>
+    <t xml:space="preserve">12.9141883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883438110352</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7504997253418</t>
+    <t xml:space="preserve">12.6643476486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126575469971</t>
+    <t xml:space="preserve">12.6126565933228</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7935752868652</t>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">12.9917259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0089569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572658538818</t>
+    <t xml:space="preserve">13.0089559555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572639465332</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0778779983521</t>
+    <t xml:space="preserve">13.0778789520264</t>
   </si>
   <si>
     <t xml:space="preserve">13.0951080322266</t>
@@ -1121,40 +1121,40 @@
     <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2674112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4914073944092</t>
+    <t xml:space="preserve">13.2674121856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4914064407349</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550960540771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757081985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7498626708984</t>
+    <t xml:space="preserve">13.7757091522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907712936401</t>
+    <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
     <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963222503662</t>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963203430176</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618621826172</t>
@@ -1163,37 +1163,37 @@
     <t xml:space="preserve">13.7240180969238</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1547784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443117141724</t>
+    <t xml:space="preserve">14.1547775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">13.939398765564</t>
+    <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
     <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
-    <t xml:space="preserve">14.111701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9221677780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">14.1117010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9221668243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637115478516</t>
+    <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1202,40 +1202,40 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704776763916</t>
+    <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
     <t xml:space="preserve">13.8360157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8015546798706</t>
+    <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154035568237</t>
+    <t xml:space="preserve">13.7154026031494</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569463729858</t>
+    <t xml:space="preserve">13.4569473266602</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3191032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3880252838135</t>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3191041946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3880243301392</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846422195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603284835815</t>
+    <t xml:space="preserve">13.2846431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5258693695068</t>
+    <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
     <t xml:space="preserve">13.508638381958</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.951714515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693756103516</t>
+    <t xml:space="preserve">13.8634119033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9517154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693737030029</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1106586456299</t>
+    <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
     <t xml:space="preserve">13.9340543746948</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278654098511</t>
+    <t xml:space="preserve">13.5278635025024</t>
   </si>
   <si>
     <t xml:space="preserve">13.4219026565552</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686941146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402433395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872619628906</t>
+    <t xml:space="preserve">13.0686960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872629165649</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.004695892334</t>
+    <t xml:space="preserve">14.0046949386597</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753374099731</t>
+    <t xml:space="preserve">14.0753364562988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.9870347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8457517623901</t>
+    <t xml:space="preserve">13.8457527160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985059738159</t>
+    <t xml:space="preserve">13.5985069274902</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338272094727</t>
+    <t xml:space="preserve">13.6338262557983</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1385,64 +1385,64 @@
     <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102043151855</t>
+    <t xml:space="preserve">13.5102052688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452983856201</t>
+    <t xml:space="preserve">13.3512601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452993392944</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1746578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629585266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.980393409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6095237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5035610198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0157136917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159408569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980535507202</t>
+    <t xml:space="preserve">13.2276382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.174656867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629594802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9803924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6095247268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5035619735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0157127380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159399032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391103744507</t>
+    <t xml:space="preserve">12.8391094207764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099781036377</t>
+    <t xml:space="preserve">13.1569967269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099771499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2386560440063</t>
+    <t xml:space="preserve">12.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4262771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.037748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0024271011353</t>
+    <t xml:space="preserve">11.1790323257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4262762069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0377492904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0024280548096</t>
   </si>
   <si>
     <t xml:space="preserve">11.2143526077271</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0730695724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792585372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441654205322</t>
+    <t xml:space="preserve">11.0730686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2849950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441644668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">11.7618246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7265033721924</t>
+    <t xml:space="preserve">11.7265043258667</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728433609009</t>
+    <t xml:space="preserve">11.2496728897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439373016357</t>
+    <t xml:space="preserve">11.4439382553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494466781616</t>
+    <t xml:space="preserve">10.9494476318359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831371307373</t>
+    <t xml:space="preserve">10.1547298431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299152374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831275939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1370677947998</t>
+    <t xml:space="preserve">10.1370687484741</t>
   </si>
   <si>
     <t xml:space="preserve">10.7198619842529</t>
@@ -1607,40 +1607,40 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2430305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785789489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6845407485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7375221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258237838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.613899230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606906890869</t>
+    <t xml:space="preserve">10.24303150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079374313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785779953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6845417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7375211715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258247375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6139001846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5609178543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8434839248657</t>
+    <t xml:space="preserve">10.84348487854</t>
   </si>
   <si>
     <t xml:space="preserve">10.8964653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9141263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554103851318</t>
+    <t xml:space="preserve">10.9141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -67784,7 +67784,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6493865741</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>4008</v>
@@ -67805,6 +67805,32 @@
         <v>893</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6493865741</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>10890</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>8.96000003814697</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>893</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414552688599</t>
+    <t xml:space="preserve">5.10414600372314</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394258499146</t>
+    <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564180374146</t>
+    <t xml:space="preserve">5.14564228057861</t>
   </si>
   <si>
     <t xml:space="preserve">5.18713998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659479141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958925247192</t>
+    <t xml:space="preserve">5.1165943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
     <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31163120269775</t>
+    <t xml:space="preserve">5.30333137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31163167953491</t>
   </si>
   <si>
     <t xml:space="preserve">5.31578063964844</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">5.36972665786743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122388839722</t>
+    <t xml:space="preserve">5.41122436523438</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462518692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48176956176758</t>
+    <t xml:space="preserve">5.39462566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000337600708</t>
@@ -125,52 +125,52 @@
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728610992432</t>
+    <t xml:space="preserve">5.96728563308716</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313571929932</t>
+    <t xml:space="preserve">5.96313619613647</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653654098511</t>
+    <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599229812622</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86769247055054</t>
+    <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
     <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04198122024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05857944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05027961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327407836914</t>
+    <t xml:space="preserve">6.0419807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0585789680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05027914047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239486694336</t>
+    <t xml:space="preserve">6.47355031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36150789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5523943901062</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314395904541</t>
@@ -179,13 +179,13 @@
     <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43205308914185</t>
+    <t xml:space="preserve">6.432053565979</t>
   </si>
   <si>
     <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59389209747314</t>
+    <t xml:space="preserve">6.5938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">6.58559274673462</t>
@@ -194,16 +194,16 @@
     <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61464023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80552625656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321725845337</t>
+    <t xml:space="preserve">6.61463975906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80552673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301288604736</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">7.02961158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05450963973999</t>
+    <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">7.12920475006104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30349206924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948051452637</t>
+    <t xml:space="preserve">7.30349349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948194503784</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3864860534668</t>
+    <t xml:space="preserve">7.38648653030396</t>
   </si>
   <si>
     <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36573886871338</t>
+    <t xml:space="preserve">7.36573839187622</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240262985229</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643665313721</t>
+    <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
     <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788335800171</t>
+    <t xml:space="preserve">7.20788383483887</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468145370483</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94123792648315</t>
+    <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
     <t xml:space="preserve">6.77617311477661</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202919006348</t>
+    <t xml:space="preserve">6.99202871322632</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37295007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983665466309</t>
+    <t xml:space="preserve">7.37294960021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983570098877</t>
   </si>
   <si>
     <t xml:space="preserve">7.2925329208374</t>
@@ -299,40 +299,40 @@
     <t xml:space="preserve">7.29676628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290607452393</t>
+    <t xml:space="preserve">7.26290559768677</t>
   </si>
   <si>
     <t xml:space="preserve">7.30523061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3644847869873</t>
+    <t xml:space="preserve">7.36448431015015</t>
   </si>
   <si>
     <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28830051422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23751163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132688522339</t>
+    <t xml:space="preserve">7.28830003738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2375111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132593154907</t>
   </si>
   <si>
     <t xml:space="preserve">7.06821346282959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351989746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729066848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45027256011963</t>
+    <t xml:space="preserve">7.02588796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351894378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729114532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.67036056518555</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514213562012</t>
+    <t xml:space="preserve">7.15286207199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538280487061</t>
+    <t xml:space="preserve">6.99626111984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
@@ -362,19 +362,19 @@
     <t xml:space="preserve">6.84812450408936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672227859497</t>
+    <t xml:space="preserve">6.88621711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672180175781</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016485214233</t>
+    <t xml:space="preserve">7.05128192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016532897949</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">7.05974817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04704999923706</t>
+    <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858423233032</t>
+    <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012084960938</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">7.05551528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09783935546875</t>
+    <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
     <t xml:space="preserve">7.00049304962158</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.008957862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476945877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207319259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365238189697</t>
+    <t xml:space="preserve">7.00895833969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365142822266</t>
   </si>
   <si>
     <t xml:space="preserve">7.23327827453613</t>
@@ -440,37 +440,37 @@
     <t xml:space="preserve">7.17402410507202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21211719512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
+    <t xml:space="preserve">7.21211671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597644805908</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43220376968384</t>
+    <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
     <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42373991012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406763076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490194320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452831268311</t>
+    <t xml:space="preserve">7.42374038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452926635742</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382696151733</t>
@@ -482,19 +482,19 @@
     <t xml:space="preserve">7.65652513504028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78349781036377</t>
+    <t xml:space="preserve">7.78349733352661</t>
   </si>
   <si>
     <t xml:space="preserve">7.58457231521606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913387298584</t>
+    <t xml:space="preserve">7.44913482666016</t>
   </si>
   <si>
     <t xml:space="preserve">7.53378248214722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61843204498291</t>
+    <t xml:space="preserve">7.61843299865723</t>
   </si>
   <si>
     <t xml:space="preserve">7.58880567550659</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">7.65229225158691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814737319946</t>
+    <t xml:space="preserve">7.69885110855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540567398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
   </si>
   <si>
     <t xml:space="preserve">7.93163537979126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92317008972168</t>
+    <t xml:space="preserve">7.92316913604736</t>
   </si>
   <si>
     <t xml:space="preserve">7.82582378387451</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">7.88931035995483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91470575332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856548309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553768157959</t>
+    <t xml:space="preserve">7.9147047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
     <t xml:space="preserve">7.70308208465576</t>
@@ -551,16 +551,16 @@
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45759916305542</t>
+    <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73694229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685428619385</t>
+    <t xml:space="preserve">7.73694276809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685476303101</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946350097656</t>
@@ -572,25 +572,25 @@
     <t xml:space="preserve">7.34755563735962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27137041091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702981948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01205158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474880218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097755432129</t>
+    <t xml:space="preserve">7.27137088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838804244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01205253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707286834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097850799561</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
@@ -599,16 +599,16 @@
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222854614258</t>
+    <t xml:space="preserve">8.45222663879395</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26600074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23214054107666</t>
+    <t xml:space="preserve">8.26599979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23213958740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.30832386016846</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027572631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.38027477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040821075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">9.01514625549316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99821662902832</t>
+    <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
@@ -641,43 +641,43 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290828704834</t>
+    <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
     <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5653657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861217498779</t>
+    <t xml:space="preserve">9.29448795318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56536483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861122131348</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541835784912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773433685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1325149536133</t>
+    <t xml:space="preserve">9.71773338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4965057373047</t>
+    <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451494216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620780944824</t>
+    <t xml:space="preserve">10.9451484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620771408081</t>
   </si>
   <si>
     <t xml:space="preserve">11.0551929473877</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2741413116455</t>
+    <t xml:space="preserve">12.2741422653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.6973886489868</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">13.3491878509521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2633981704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0517749786377</t>
+    <t xml:space="preserve">14.2633991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111589431763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460294723511</t>
+    <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443204879761</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0940999984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173463821411</t>
+    <t xml:space="preserve">14.0941009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173454284668</t>
   </si>
   <si>
     <t xml:space="preserve">14.0009860992432</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761600494385</t>
+    <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184869766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930906295776</t>
+    <t xml:space="preserve">13.5184860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
     <t xml:space="preserve">13.7639684677124</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">14.0094509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3057231903076</t>
+    <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
     <t xml:space="preserve">14.348048210144</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">14.5512075424194</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5596733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088815689087</t>
+    <t xml:space="preserve">14.5596714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088806152344</t>
   </si>
   <si>
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4073047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157667160034</t>
+    <t xml:space="preserve">14.4073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157676696777</t>
   </si>
   <si>
     <t xml:space="preserve">14.3311195373535</t>
@@ -809,25 +809,25 @@
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994073867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385721206665</t>
+    <t xml:space="preserve">13.9840574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994064331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
     <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290998458862</t>
+    <t xml:space="preserve">13.1290979385376</t>
   </si>
   <si>
     <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397117614746</t>
+    <t xml:space="preserve">12.7397127151489</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423017501831</t>
+    <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175704956055</t>
+    <t xml:space="preserve">13.0175714492798</t>
   </si>
   <si>
     <t xml:space="preserve">13.3018732070923</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295680999756</t>
+    <t xml:space="preserve">13.1295690536499</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123390197754</t>
+    <t xml:space="preserve">12.6557331085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123399734497</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277196884155</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501821517944</t>
+    <t xml:space="preserve">13.2501811981201</t>
   </si>
   <si>
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314184188843</t>
+    <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834289550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2335872650146</t>
+    <t xml:space="preserve">12.4834280014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369693756104</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">11.8975954055786</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474351882935</t>
+    <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542013168335</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302051544189</t>
+    <t xml:space="preserve">12.1302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114433288574</t>
+    <t xml:space="preserve">11.7166757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286724090576</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8200597763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7769823074341</t>
+    <t xml:space="preserve">11.7597513198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8200588226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7769813537598</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182075500488</t>
+    <t xml:space="preserve">12.0182085037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785160064697</t>
+    <t xml:space="preserve">12.0785150527954</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157211303711</t>
+    <t xml:space="preserve">12.0871286392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157220840454</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">12.6988086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500659942627</t>
+    <t xml:space="preserve">12.5006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591161727905</t>
+    <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231214523315</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628149032593</t>
+    <t xml:space="preserve">12.3628158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
+    <t xml:space="preserve">12.5265054702759</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141883850098</t>
+    <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
     <t xml:space="preserve">12.8366527557373</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868110656738</t>
+    <t xml:space="preserve">12.5868101119995</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126565933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935762405396</t>
+    <t xml:space="preserve">12.6126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935752868652</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917259216309</t>
+    <t xml:space="preserve">12.7418851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8711128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089559555054</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0778789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0951080322266</t>
+    <t xml:space="preserve">13.0778779983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0951070785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2674121856689</t>
+    <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914064407349</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550960540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7757091522217</t>
+    <t xml:space="preserve">13.6550970077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7757081985474</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843246459961</t>
@@ -1142,25 +1142,25 @@
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907703399658</t>
+    <t xml:space="preserve">14.4907712936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8618621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240180969238</t>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963212966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8618612289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240190505981</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547775268555</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8446311950684</t>
+    <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
     <t xml:space="preserve">14.1117010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9221668243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206359863281</t>
+    <t xml:space="preserve">13.9221677780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206369400024</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.405255317688</t>
+    <t xml:space="preserve">13.3535642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191041946411</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846431732178</t>
+    <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603294372559</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693737030029</t>
+    <t xml:space="preserve">13.9693746566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278635025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4219026565552</t>
+    <t xml:space="preserve">13.5278644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4219017028809</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
+    <t xml:space="preserve">13.0686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
     <t xml:space="preserve">14.2872629165649</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985069274902</t>
+    <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452993392944</t>
+    <t xml:space="preserve">13.351261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452983856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.174656867981</t>
+    <t xml:space="preserve">13.2276372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1746578216553</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157127380371</t>
+    <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980525970459</t>
+    <t xml:space="preserve">12.9980535507202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391094207764</t>
+    <t xml:space="preserve">12.8391103744507</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099771499634</t>
+    <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.2673349380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4262762069702</t>
+    <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
     <t xml:space="preserve">11.0377492904663</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0730686187744</t>
+    <t xml:space="preserve">10.9317874908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
     <t xml:space="preserve">11.2849950790405</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496728897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728424072266</t>
+    <t xml:space="preserve">11.2496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547298431396</t>
+    <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299152374268</t>
@@ -1586,19 +1586,19 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1370687484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7198619842529</t>
+    <t xml:space="preserve">9.53661441802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1370677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7198629379272</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551822662354</t>
+    <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
+    <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902772903442</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">10.5079374313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5785779953003</t>
+    <t xml:space="preserve">10.5785789489746</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375211715698</t>
+    <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258247375488</t>
@@ -1631,22 +1631,22 @@
     <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609178543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606916427612</t>
+    <t xml:space="preserve">10.5609188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432567596436</t>
+    <t xml:space="preserve">10.5432577133179</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019746780396</t>
+    <t xml:space="preserve">10.4019756317139</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">10.84348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8964653015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554094314575</t>
+    <t xml:space="preserve">10.896466255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554103851318</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -67810,7 +67810,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6493865741</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>10890</v>
@@ -67831,6 +67831,32 @@
         <v>893</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6495023148</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>6399</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>9.03999996185303</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>897</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -53,43 +53,43 @@
     <t xml:space="preserve">5.14564228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18713998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1165943145752</t>
+    <t xml:space="preserve">5.1871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523591995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31163167953491</t>
+    <t xml:space="preserve">5.19958925247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
     <t xml:space="preserve">5.31578063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632535934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3489785194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972665786743</t>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312795639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122436523438</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761917114258</t>
+    <t xml:space="preserve">5.39462518692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176908493042</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259052276611</t>
+    <t xml:space="preserve">5.89259099960327</t>
   </si>
   <si>
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939311981201</t>
+    <t xml:space="preserve">5.85939264297485</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
@@ -131,121 +131,121 @@
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068693161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599229812622</t>
+    <t xml:space="preserve">5.96313667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653654098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
     <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442953109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0419807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0585789680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05027914047241</t>
+    <t xml:space="preserve">6.05443000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04198026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05857944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
     <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19137001037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47355031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36150789260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5523943901062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57314395904541</t>
+    <t xml:space="preserve">6.19137048721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47355079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239534378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57314300537109</t>
   </si>
   <si>
     <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.432053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5938925743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58559274673462</t>
+    <t xml:space="preserve">6.43205308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994607925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59389209747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58559226989746</t>
   </si>
   <si>
     <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61463975906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953924179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80552673339844</t>
+    <t xml:space="preserve">6.61464071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920475006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234580993652</t>
+    <t xml:space="preserve">7.01301336288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05450916290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920522689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234485626221</t>
   </si>
   <si>
     <t xml:space="preserve">8.6728982925415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12928485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648653030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798376083374</t>
+    <t xml:space="preserve">8.12928581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281770706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798471450806</t>
   </si>
   <si>
     <t xml:space="preserve">7.36573839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16240262985229</t>
+    <t xml:space="preserve">7.16240310668945</t>
   </si>
   <si>
     <t xml:space="preserve">7.21634864807129</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468145370483</t>
+    <t xml:space="preserve">7.20788478851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468193054199</t>
   </si>
   <si>
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156755447388</t>
+    <t xml:space="preserve">6.80156707763672</t>
   </si>
   <si>
     <t xml:space="preserve">6.98356342315674</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617311477661</t>
+    <t xml:space="preserve">6.77617216110229</t>
   </si>
   <si>
     <t xml:space="preserve">6.97933101654053</t>
@@ -284,31 +284,31 @@
     <t xml:space="preserve">6.99202871322632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49145936965942</t>
+    <t xml:space="preserve">7.49145889282227</t>
   </si>
   <si>
     <t xml:space="preserve">7.37294960021973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27983570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523061752319</t>
+    <t xml:space="preserve">7.27983522415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523109436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.36448431015015</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1994194984436</t>
+    <t xml:space="preserve">7.19941902160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830003738403</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">7.2375111579895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16132593154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821346282959</t>
+    <t xml:space="preserve">7.16132688522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821298599243</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588796615601</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036056518555</t>
+    <t xml:space="preserve">6.45027256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036151885986</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.15286207199097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08514261245728</t>
+    <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
@@ -362,55 +362,55 @@
     <t xml:space="preserve">6.84812450408936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0936074256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937549591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086524963379</t>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016437530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04704999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086572647095</t>
   </si>
   <si>
     <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0639796257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05551528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09783983230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00049304962158</t>
+    <t xml:space="preserve">7.03012037277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398105621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0555157661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00049352645874</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
@@ -419,118 +419,118 @@
     <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00895833969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402410507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597644805908</t>
+    <t xml:space="preserve">7.008957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207223892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987970352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402505874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597692489624</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.432204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42374038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490146636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382696151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005571365356</t>
+    <t xml:space="preserve">7.43220520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373943328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141489028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406763076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490242004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834547042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452783584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382648468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005619049072</t>
   </si>
   <si>
     <t xml:space="preserve">7.65652513504028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457231521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913482666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
+    <t xml:space="preserve">7.78349781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457374572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.449134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843204498291</t>
   </si>
   <si>
     <t xml:space="preserve">7.58880567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885110855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540567398071</t>
+    <t xml:space="preserve">7.65229177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540615081787</t>
   </si>
   <si>
     <t xml:space="preserve">7.86814785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93163537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316913604736</t>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.82582378387451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88931035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9147047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856595993042</t>
+    <t xml:space="preserve">7.88930988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470670700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856452941895</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
@@ -539,28 +539,28 @@
     <t xml:space="preserve">7.70308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61420059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332227706909</t>
+    <t xml:space="preserve">7.61419916152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332323074341</t>
   </si>
   <si>
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45759963989258</t>
+    <t xml:space="preserve">7.45759916305542</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73694276809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685476303101</t>
+    <t xml:space="preserve">7.73694181442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946350097656</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755563735962</t>
+    <t xml:space="preserve">7.34755516052246</t>
   </si>
   <si>
     <t xml:space="preserve">7.27137088775635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50838804244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01205253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097850799561</t>
+    <t xml:space="preserve">7.50838851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702886581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01205158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474880218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097660064697</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599979400635</t>
+    <t xml:space="preserve">8.26599884033203</t>
   </si>
   <si>
     <t xml:space="preserve">8.23213958740234</t>
@@ -614,22 +614,22 @@
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32525444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027477264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87970542907715</t>
+    <t xml:space="preserve">8.3252534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027572631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040916442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514625549316</t>
+    <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
     <t xml:space="preserve">8.998215675354</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02361011505127</t>
+    <t xml:space="preserve">9.02360916137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56536483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861122131348</t>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861312866211</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541835784912</t>
@@ -671,22 +671,22 @@
     <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927799224854</t>
+    <t xml:space="preserve">10.7927808761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620771408081</t>
+    <t xml:space="preserve">10.9620780944824</t>
   </si>
   <si>
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884819030762</t>
+    <t xml:space="preserve">11.4191846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884828567505</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2741422653198</t>
+    <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.6973886489868</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">14.2633991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0156364440918</t>
+    <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
     <t xml:space="preserve">14.051775932312</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">12.5111589431763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443204879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009860992432</t>
+    <t xml:space="preserve">13.1460294723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443185806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0940999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173473358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
@@ -743,58 +743,58 @@
     <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169073104858</t>
+    <t xml:space="preserve">13.4169063568115</t>
   </si>
   <si>
     <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338369369507</t>
+    <t xml:space="preserve">13.4338359832764</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5100202560425</t>
+    <t xml:space="preserve">13.5100212097168</t>
   </si>
   <si>
     <t xml:space="preserve">13.5184860229492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4930896759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7639684677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0094509124756</t>
+    <t xml:space="preserve">13.4930906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7639694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0094518661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348048210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019954681396</t>
+    <t xml:space="preserve">14.3480501174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
     <t xml:space="preserve">14.5512075424194</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5596714019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088806152344</t>
+    <t xml:space="preserve">14.5596704483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088815689087</t>
   </si>
   <si>
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157676696777</t>
+    <t xml:space="preserve">14.4073038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157695770264</t>
   </si>
   <si>
     <t xml:space="preserve">14.3311195373535</t>
@@ -806,37 +806,37 @@
     <t xml:space="preserve">13.8655462265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7978277206421</t>
+    <t xml:space="preserve">13.7978267669678</t>
   </si>
   <si>
     <t xml:space="preserve">13.9840574264526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8994064331055</t>
+    <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031351089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.782036781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397127151489</t>
+    <t xml:space="preserve">13.6031341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397117614746</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5269498825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5523462295532</t>
+    <t xml:space="preserve">13.5269508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5523443222046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0348024368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0434169769287</t>
+    <t xml:space="preserve">13.2071046829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.03480052948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1726446151733</t>
+    <t xml:space="preserve">13.1726455688477</t>
   </si>
   <si>
     <t xml:space="preserve">13.0175714492798</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">13.3018732070923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.1640291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123399734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276026725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2501811981201</t>
+    <t xml:space="preserve">13.1123380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277187347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2760276794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
     <t xml:space="preserve">13.0606470108032</t>
@@ -917,28 +917,28 @@
     <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834280014038</t>
+    <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.035439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474361419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3542013168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2594327926636</t>
+    <t xml:space="preserve">12.3369703292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0354385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975963592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3542003631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2594337463379</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8372888565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7855978012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
+    <t xml:space="preserve">11.9837465286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.837287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7855968475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286724090576</t>
@@ -974,28 +974,28 @@
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769813537598</t>
+    <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339067459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6046781539917</t>
+    <t xml:space="preserve">11.7339057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.604679107666</t>
   </si>
   <si>
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182085037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0785150527954</t>
+    <t xml:space="preserve">12.0182075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0785140991211</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157220840454</t>
+    <t xml:space="preserve">12.0871295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988086700439</t>
+    <t xml:space="preserve">12.6988077163696</t>
   </si>
   <si>
     <t xml:space="preserve">12.5006589889526</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591152191162</t>
+    <t xml:space="preserve">12.7591161727905</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
@@ -1037,28 +1037,28 @@
     <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.535120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265054702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7849607467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9141893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8366527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883438110352</t>
+    <t xml:space="preserve">12.5351209640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9141883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.836651802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883428573608</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1067,43 +1067,43 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643476486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7505006790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868101119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7074241638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
+    <t xml:space="preserve">12.6643486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7504997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868110656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7074251174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126585006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418851852417</t>
+    <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
     <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917249679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089559555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572639465332</t>
+    <t xml:space="preserve">12.9917259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
@@ -1112,37 +1112,37 @@
     <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0951070785522</t>
+    <t xml:space="preserve">13.0951080322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984901428223</t>
+    <t xml:space="preserve">13.1984910964966</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914064407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6550970077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7757081985474</t>
+    <t xml:space="preserve">13.4914073944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6550960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7757091522217</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498636245728</t>
+    <t xml:space="preserve">13.7498626708984</t>
   </si>
   <si>
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907712936401</t>
+    <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
     <t xml:space="preserve">14.5166168212891</t>
@@ -1157,43 +1157,43 @@
     <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8618612289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1547775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0255508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9393978118896</t>
+    <t xml:space="preserve">13.8618621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240180969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1547784805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443117141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0255498886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
     <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1117010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9221677780151</t>
+    <t xml:space="preserve">14.111701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9221668243408</t>
   </si>
   <si>
     <t xml:space="preserve">13.7929391860962</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
+    <t xml:space="preserve">13.6637125015259</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1208,34 +1208,34 @@
     <t xml:space="preserve">13.8360157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8015556335449</t>
+    <t xml:space="preserve">13.8015546798706</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154026031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6809415817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4569473266602</t>
+    <t xml:space="preserve">13.7154035568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6809425354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3191041946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3880243301392</t>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3191032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3880252838135</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603294372559</t>
+    <t xml:space="preserve">13.5603284835815</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5258684158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5086393356323</t>
+    <t xml:space="preserve">13.5258693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693746566772</t>
+    <t xml:space="preserve">13.8634128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693756103516</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340543746948</t>
+    <t xml:space="preserve">13.9340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
@@ -1295,31 +1295,31 @@
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219017028809</t>
+    <t xml:space="preserve">13.4219026565552</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982797622681</t>
+    <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686950683594</t>
+    <t xml:space="preserve">13.0686941146851</t>
   </si>
   <si>
     <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0046949386597</t>
+    <t xml:space="preserve">14.004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870347976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8457527160645</t>
+    <t xml:space="preserve">13.9870357513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8457517623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8104314804077</t>
+    <t xml:space="preserve">13.810432434082</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338262557983</t>
+    <t xml:space="preserve">13.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.6691484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
+    <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
+    <t xml:space="preserve">13.2276382446289</t>
   </si>
   <si>
     <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1746578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629594802856</t>
+    <t xml:space="preserve">13.174656867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629585266113</t>
   </si>
   <si>
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095247268677</t>
+    <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
     <t xml:space="preserve">12.5035619735718</t>
@@ -1424,22 +1424,22 @@
     <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3159399032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9097509384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0333738327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1569967269897</t>
+    <t xml:space="preserve">13.3159408569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9097499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1569957733154</t>
   </si>
   <si>
     <t xml:space="preserve">13.2099781036377</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.121675491333</t>
+    <t xml:space="preserve">13.1216764450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037891387939</t>
+    <t xml:space="preserve">12.8567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037881851196</t>
   </si>
   <si>
     <t xml:space="preserve">12.2386560440063</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379764556885</t>
+    <t xml:space="preserve">11.267333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379755020142</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790323257446</t>
+    <t xml:space="preserve">11.1790313720703</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
@@ -1493,34 +1493,34 @@
     <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0024280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143526077271</t>
+    <t xml:space="preserve">11.0024271011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143535614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317874908447</t>
+    <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494476318359</t>
+    <t xml:space="preserve">10.9494466781616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299152374268</t>
+    <t xml:space="preserve">10.154727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
     <t xml:space="preserve">9.44831275939941</t>
@@ -1586,37 +1586,37 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53661441802979</t>
+    <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198629379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966924667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551832199097</t>
+    <t xml:space="preserve">10.7198619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551822662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2783517837524</t>
+    <t xml:space="preserve">10.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785789489746</t>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785779953003</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8258247375488</t>
+    <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3313331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.3313322067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019756317139</t>
+    <t xml:space="preserve">10.4019737243652</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.84348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.896466255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141263961792</t>
+    <t xml:space="preserve">10.8434839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8964653015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141254425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.0554103851318</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069110870361</t>
+    <t xml:space="preserve">10.7069101333618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027923583984</t>
+    <t xml:space="preserve">9.84669780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846300125122</t>
+    <t xml:space="preserve">10.0663261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846290588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578388214111</t>
+    <t xml:space="preserve">10.139536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578397750854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055847167969</t>
+    <t xml:space="preserve">10.5055837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5238876342773</t>
+    <t xml:space="preserve">10.523886680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5604915618896</t>
+    <t xml:space="preserve">10.560492515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716335296631</t>
+    <t xml:space="preserve">10.8716325759888</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899354934692</t>
+    <t xml:space="preserve">10.6703062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899345397949</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193794250488</t>
+    <t xml:space="preserve">11.2193784713745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533306121826</t>
+    <t xml:space="preserve">11.1644716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252140045166</t>
+    <t xml:space="preserve">10.7252130508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944842338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461687088013</t>
+    <t xml:space="preserve">10.9448432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608589172363</t>
+    <t xml:space="preserve">8.23608493804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550094604492</t>
+    <t xml:space="preserve">8.17202663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550142288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234292984009</t>
+    <t xml:space="preserve">6.01234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00982332229614</t>
+    <t xml:space="preserve">7.0098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558013916016</t>
+    <t xml:space="preserve">7.055579662323</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531558990479</t>
+    <t xml:space="preserve">7.41247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531511306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568677902222</t>
+    <t xml:space="preserve">7.48568725585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038034439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303308486938</t>
+    <t xml:space="preserve">6.68038082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229118347168</t>
+    <t xml:space="preserve">7.52229166030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364643096924</t>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364547729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818161010742</t>
+    <t xml:space="preserve">8.96818256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62043571472168</t>
+    <t xml:space="preserve">8.620436668396</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003803253174</t>
+    <t xml:space="preserve">7.7968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003755569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6321063041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361755371094</t>
+    <t xml:space="preserve">7.77852535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63210582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236180305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642868041992</t>
+    <t xml:space="preserve">7.04642820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340475082397</t>
+    <t xml:space="preserve">6.86340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3509373664856</t>
+    <t xml:space="preserve">6.46075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35093688964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130807876587</t>
+    <t xml:space="preserve">6.02149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242116928101</t>
+    <t xml:space="preserve">5.47242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279235839844</t>
+    <t xml:space="preserve">5.25279188156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626070022583</t>
+    <t xml:space="preserve">5.36260652542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884069442749</t>
+    <t xml:space="preserve">5.61884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44908237457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324684143066</t>
+    <t xml:space="preserve">7.4490818977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324731826782</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55889654159546</t>
+    <t xml:space="preserve">7.5588960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062202453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452194213867</t>
+    <t xml:space="preserve">8.51062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452289581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025035858154</t>
+    <t xml:space="preserve">8.73025131225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176208496094</t>
+    <t xml:space="preserve">8.82176303863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308940887451</t>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179000854492</t>
+    <t xml:space="preserve">9.79179096221924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866195678711</t>
+    <t xml:space="preserve">10.3866186141968</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998676300049</t>
+    <t xml:space="preserve">9.37998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8949728012085</t>
+    <t xml:space="preserve">8.89497184753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833999633789</t>
+    <t xml:space="preserve">7.88833904266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4740161895752</t>
+    <t xml:space="preserve">8.47401714324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9249439239502</t>
+    <t xml:space="preserve">7.92494487762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735593795776</t>
+    <t xml:space="preserve">6.57056617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735641479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.53396081924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661451339722</t>
+    <t xml:space="preserve">6.93661403656006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -67836,7 +67836,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495023148</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>6399</v>
@@ -67857,6 +67857,32 @@
         <v>897</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493402778</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>18718</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>8.97999954223633</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>887</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169626235962</t>
+    <t xml:space="preserve">5.09169721603394</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
@@ -56,31 +56,31 @@
     <t xml:space="preserve">5.1871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659479141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958925247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333185195923</t>
+    <t xml:space="preserve">5.1165943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523591995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482908248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632583618164</t>
+    <t xml:space="preserve">5.3157811164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482860565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632535934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.34897899627686</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972713470459</t>
+    <t xml:space="preserve">5.36972665786743</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122436523438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34067916870117</t>
+    <t xml:space="preserve">5.34067964553833</t>
   </si>
   <si>
     <t xml:space="preserve">5.39462518692017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47761964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48176908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71000337600708</t>
+    <t xml:space="preserve">5.47762012481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48176956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
     <t xml:space="preserve">5.9340877532959</t>
@@ -122,16 +122,16 @@
     <t xml:space="preserve">5.85939264297485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97558498382568</t>
+    <t xml:space="preserve">5.97558450698853</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728563308716</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9008903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96313667297363</t>
+    <t xml:space="preserve">5.90088987350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068645477295</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8676929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05443000793457</t>
+    <t xml:space="preserve">5.86769247055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
     <t xml:space="preserve">6.04198026657104</t>
@@ -158,40 +158,40 @@
     <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327360153198</t>
+    <t xml:space="preserve">6.13327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137048721313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239534378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57314300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994607925415</t>
+    <t xml:space="preserve">6.47355031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36150789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239486694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57314348220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5606951713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.432053565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804201126099</t>
+    <t xml:space="preserve">6.58559322357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804153442383</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464071273804</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8055272102356</t>
+    <t xml:space="preserve">6.80552768707275</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321630477905</t>
@@ -209,40 +209,40 @@
     <t xml:space="preserve">7.01301336288452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02961206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05450916290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034930229187</t>
+    <t xml:space="preserve">7.02961158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920475006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349349975586</t>
   </si>
   <si>
     <t xml:space="preserve">7.46948051452637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99234485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6728982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281770706177</t>
+    <t xml:space="preserve">7.99234580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67289638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928676605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
     <t xml:space="preserve">7.38648700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42798471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573839187622</t>
+    <t xml:space="preserve">7.4279842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573791503906</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240310668945</t>
@@ -254,10 +254,10 @@
     <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788478851318</t>
+    <t xml:space="preserve">7.22058057785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788431167603</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156707763672</t>
+    <t xml:space="preserve">6.80156755447388</t>
   </si>
   <si>
     <t xml:space="preserve">6.98356342315674</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617216110229</t>
+    <t xml:space="preserve">6.77617263793945</t>
   </si>
   <si>
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202871322632</t>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145889282227</t>
@@ -290,28 +290,28 @@
     <t xml:space="preserve">7.37294960021973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27983522415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29253339767456</t>
+    <t xml:space="preserve">7.27983617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2925329208374</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448431015015</t>
+    <t xml:space="preserve">7.26290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36448526382446</t>
   </si>
   <si>
     <t xml:space="preserve">7.19941902160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28830003738403</t>
+    <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
     <t xml:space="preserve">7.2375111579895</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027256011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036151885986</t>
+    <t xml:space="preserve">6.45027303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
@@ -350,34 +350,34 @@
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626111984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77194023132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84812450408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621664047241</t>
+    <t xml:space="preserve">6.99626016616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77193975448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84812498092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
     <t xml:space="preserve">7.18672132492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11053657531738</t>
+    <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.05128240585327</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14016437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630559921265</t>
+    <t xml:space="preserve">7.14016485214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
     <t xml:space="preserve">7.09360694885254</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974769592285</t>
+    <t xml:space="preserve">7.05974817276001</t>
   </si>
   <si>
     <t xml:space="preserve">7.04704999923706</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">6.97086572647095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858470916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398105621338</t>
+    <t xml:space="preserve">7.03858518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398057937622</t>
   </si>
   <si>
     <t xml:space="preserve">7.0555157661438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09783935546875</t>
+    <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
     <t xml:space="preserve">7.00049352645874</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">7.03435325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11900186538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.008957862854</t>
+    <t xml:space="preserve">7.11900234222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00895738601685</t>
   </si>
   <si>
     <t xml:space="preserve">7.11476945877075</t>
@@ -428,28 +428,28 @@
     <t xml:space="preserve">7.10207223892212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327875137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402505874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43220520019531</t>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597597122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43220472335815</t>
   </si>
   <si>
     <t xml:space="preserve">7.49992370605469</t>
@@ -464,70 +464,70 @@
     <t xml:space="preserve">7.28406763076782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44490242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834547042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452783584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382648468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652513504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457374572754</t>
+    <t xml:space="preserve">7.44490146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349828720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457279205322</t>
   </si>
   <si>
     <t xml:space="preserve">7.449134349823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53378343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843204498291</t>
+    <t xml:space="preserve">7.53378391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
   </si>
   <si>
     <t xml:space="preserve">7.58880567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229177474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69884967803955</t>
+    <t xml:space="preserve">7.65229272842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
   </si>
   <si>
     <t xml:space="preserve">7.74540615081787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86814785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582378387451</t>
+    <t xml:space="preserve">7.86814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9316349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8258228302002</t>
   </si>
   <si>
     <t xml:space="preserve">7.88930988311768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91470670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279741287231</t>
+    <t xml:space="preserve">7.91470527648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279788970947</t>
   </si>
   <si>
     <t xml:space="preserve">7.94856452941895</t>
@@ -536,22 +536,22 @@
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61419916152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332323074341</t>
+    <t xml:space="preserve">7.70308256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332275390625</t>
   </si>
   <si>
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45759916305542</t>
+    <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">7.73694181442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51685380935669</t>
+    <t xml:space="preserve">7.51685333251953</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946350097656</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755516052246</t>
+    <t xml:space="preserve">7.34755563735962</t>
   </si>
   <si>
     <t xml:space="preserve">7.27137088775635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50838851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702886581421</t>
+    <t xml:space="preserve">7.50838947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">8.06707382202148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21097660064697</t>
+    <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
@@ -599,22 +599,22 @@
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599884033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23213958740234</t>
+    <t xml:space="preserve">8.26599979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3252534866333</t>
+    <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
     <t xml:space="preserve">8.38027572631836</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">8.71040916442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.87970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.998215675354</t>
+    <t xml:space="preserve">8.99821662902832</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02360916137695</t>
+    <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17597961425781</t>
+    <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">9.98861312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4541835784912</t>
+    <t xml:space="preserve">10.4541845321655</t>
   </si>
   <si>
     <t xml:space="preserve">9.71773338317871</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927808761597</t>
+    <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">11.4191846847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884828567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239217758179</t>
+    <t xml:space="preserve">11.5884819030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239208221436</t>
   </si>
   <si>
     <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355440139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741413116455</t>
+    <t xml:space="preserve">11.9355459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741422653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.6973886489868</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491878509521</t>
+    <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
     <t xml:space="preserve">14.2633991241455</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111589431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460294723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443185806274</t>
+    <t xml:space="preserve">12.5111598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443195343018</t>
   </si>
   <si>
     <t xml:space="preserve">14.0940999984741</t>
@@ -740,25 +740,25 @@
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243608474731</t>
+    <t xml:space="preserve">12.8243618011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5100212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184860229492</t>
+    <t xml:space="preserve">13.4761619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438795089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5100193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184850692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930906295776</t>
@@ -767,22 +767,22 @@
     <t xml:space="preserve">13.7639694213867</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094518661499</t>
+    <t xml:space="preserve">14.0094499588013</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480501174927</t>
+    <t xml:space="preserve">14.3480491638184</t>
   </si>
   <si>
     <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596704483032</t>
+    <t xml:space="preserve">14.5512065887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
     <t xml:space="preserve">14.5088815689087</t>
@@ -791,25 +791,25 @@
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4073038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157695770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311195373535</t>
+    <t xml:space="preserve">14.4073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157686233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311176300049</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8655462265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978267669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840574264526</t>
+    <t xml:space="preserve">13.8655471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978277206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031341552734</t>
+    <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">12.7820377349854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0275201797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5269508361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5523443222046</t>
+    <t xml:space="preserve">12.7397127151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0275192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5269498825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5523452758789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071046829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.03480052948</t>
+    <t xml:space="preserve">13.2071056365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0348014831543</t>
   </si>
   <si>
     <t xml:space="preserve">13.043417930603</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1726455688477</t>
+    <t xml:space="preserve">13.4397172927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
     <t xml:space="preserve">13.0175714492798</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">13.1640291213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295680999756</t>
+    <t xml:space="preserve">13.1295690536499</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6901931762695</t>
+    <t xml:space="preserve">12.6901922225952</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243366241455</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123380661011</t>
+    <t xml:space="preserve">13.1123390197754</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277187347412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2760276794434</t>
+    <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314193725586</t>
+    <t xml:space="preserve">12.9314203262329</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">12.3369703292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0354385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975963592529</t>
+    <t xml:space="preserve">12.035439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975954055786</t>
   </si>
   <si>
     <t xml:space="preserve">12.1474370956421</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">12.3542003631592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2594337463379</t>
+    <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837465286255</t>
+    <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
     <t xml:space="preserve">11.837287902832</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114433288574</t>
+    <t xml:space="preserve">11.7166757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286724090576</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511367797852</t>
+    <t xml:space="preserve">11.7511377334595</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339057922363</t>
@@ -986,22 +986,22 @@
     <t xml:space="preserve">11.604679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612831115723</t>
+    <t xml:space="preserve">11.6305246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182085037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0785140991211</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1388206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440530776978</t>
+    <t xml:space="preserve">12.1388216018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440540313721</t>
   </si>
   <si>
     <t xml:space="preserve">12.0871295928955</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231224060059</t>
+    <t xml:space="preserve">12.4231233596802</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661989212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3628168106079</t>
+    <t xml:space="preserve">12.4661998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3628158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">12.5351209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7849617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9141883850098</t>
+    <t xml:space="preserve">12.5265054702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7849607467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
     <t xml:space="preserve">12.836651802063</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7074251174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126585006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246541976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935762405396</t>
+    <t xml:space="preserve">12.7074241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935752868652</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8711128234863</t>
+    <t xml:space="preserve">12.871111869812</t>
   </si>
   <si>
     <t xml:space="preserve">12.9917259216309</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">13.0089569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572649002075</t>
+    <t xml:space="preserve">12.9572658538818</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984910964966</t>
+    <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">13.6550960540771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757091522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843246459961</t>
+    <t xml:space="preserve">13.7757081985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843236923218</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498626708984</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907703399658</t>
+    <t xml:space="preserve">14.4907712936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.5166168212891</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8963212966919</t>
+    <t xml:space="preserve">13.8963222503662</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618621826172</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255498886108</t>
+    <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
     <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.844630241394</t>
+    <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9221668243408</t>
+    <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
     <t xml:space="preserve">13.7929391860962</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6206359863281</t>
+    <t xml:space="preserve">13.6206369400024</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637125015259</t>
+    <t xml:space="preserve">13.6637115478516</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704767227173</t>
+    <t xml:space="preserve">13.8704776763916</t>
   </si>
   <si>
     <t xml:space="preserve">13.8360157012939</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6809425354004</t>
+    <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
     <t xml:space="preserve">13.4569463729858</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.405255317688</t>
+    <t xml:space="preserve">13.3535642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1106576919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9340534210205</t>
+    <t xml:space="preserve">14.1106586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9340543746948</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278644561768</t>
+    <t xml:space="preserve">13.5278654098511</t>
   </si>
   <si>
     <t xml:space="preserve">13.4219026565552</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982807159424</t>
+    <t xml:space="preserve">13.2982797622681</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870357513428</t>
+    <t xml:space="preserve">13.9870347976685</t>
   </si>
   <si>
     <t xml:space="preserve">13.8457517623901</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.810432434082</t>
+    <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691484451294</t>
+    <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102043151855</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
+    <t xml:space="preserve">13.351261138916</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1400,25 +1400,25 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
+    <t xml:space="preserve">13.2276372909546</t>
   </si>
   <si>
     <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.174656867981</t>
+    <t xml:space="preserve">13.1746578216553</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629585266113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9803924560547</t>
+    <t xml:space="preserve">12.980393409729</t>
   </si>
   <si>
     <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5035619735718</t>
+    <t xml:space="preserve">12.5035610198975</t>
   </si>
   <si>
     <t xml:space="preserve">13.0157136917114</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">13.3159408569336</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980525970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9097499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.033374786377</t>
+    <t xml:space="preserve">12.9980535507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9097509384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
     <t xml:space="preserve">13.1569957733154</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1216764450073</t>
+    <t xml:space="preserve">13.121675491333</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037881851196</t>
+    <t xml:space="preserve">12.8567695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
     <t xml:space="preserve">12.2386560440063</t>
@@ -1490,19 +1490,19 @@
     <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0377492904663</t>
+    <t xml:space="preserve">11.037748336792</t>
   </si>
   <si>
     <t xml:space="preserve">11.0024271011353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2143535614014</t>
+    <t xml:space="preserve">11.2143526077271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">11.7618246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7265043258667</t>
+    <t xml:space="preserve">11.7265033721924</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549560546875</t>
+    <t xml:space="preserve">10.4549551010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.154727935791</t>
+    <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44831275939941</t>
+    <t xml:space="preserve">9.44831371307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1966915130615</t>
+    <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551822662354</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2783527374268</t>
+    <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430305480957</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">10.5079364776611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5785779953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6845417022705</t>
+    <t xml:space="preserve">10.5785789489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6845407485962</t>
   </si>
   <si>
     <t xml:space="preserve">10.7375221252441</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6139001846313</t>
+    <t xml:space="preserve">10.613899230957</t>
   </si>
   <si>
     <t xml:space="preserve">10.5609188079834</t>
@@ -1637,16 +1637,16 @@
     <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3313322067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432567596436</t>
+    <t xml:space="preserve">10.3313331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432577133179</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019737243652</t>
+    <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">10.8964653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9141254425049</t>
+    <t xml:space="preserve">10.9141263961792</t>
   </si>
   <si>
     <t xml:space="preserve">11.0554103851318</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069101333618</t>
+    <t xml:space="preserve">10.7069110870361</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027828216553</t>
+    <t xml:space="preserve">9.84669876098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027923583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846290588379</t>
+    <t xml:space="preserve">10.0663270950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846300125122</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.139536857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578397750854</t>
+    <t xml:space="preserve">10.1395359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578388214111</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055837631226</t>
+    <t xml:space="preserve">10.5055847167969</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.523886680603</t>
+    <t xml:space="preserve">10.5238876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.560492515564</t>
+    <t xml:space="preserve">10.5604915618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716325759888</t>
+    <t xml:space="preserve">10.8716335296631</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703062057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899345397949</t>
+    <t xml:space="preserve">10.6703052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984228134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899354934692</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193784713745</t>
+    <t xml:space="preserve">11.2193794250488</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644716262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533296585083</t>
+    <t xml:space="preserve">11.1644706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533306121826</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252130508423</t>
+    <t xml:space="preserve">10.7252140045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9448432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461696624756</t>
+    <t xml:space="preserve">10.944842338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109564781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461687088013</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608493804932</t>
+    <t xml:space="preserve">8.23608589172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550142288208</t>
+    <t xml:space="preserve">8.17202758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550094604492</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234245300293</t>
+    <t xml:space="preserve">6.01234292984009</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0098237991333</t>
+    <t xml:space="preserve">7.00982332229614</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.055579662323</t>
+    <t xml:space="preserve">7.05558013916016</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247749328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531511306763</t>
+    <t xml:space="preserve">7.41247701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531558990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568725585938</t>
+    <t xml:space="preserve">7.48568677902222</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303356170654</t>
+    <t xml:space="preserve">6.68038034439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303308486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229166030884</t>
+    <t xml:space="preserve">7.52229118347168</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364547729492</t>
+    <t xml:space="preserve">8.14457225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364643096924</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818256378174</t>
+    <t xml:space="preserve">8.96818161010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.620436668396</t>
+    <t xml:space="preserve">8.62043571472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7968282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003755569458</t>
+    <t xml:space="preserve">7.79682779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003803253174</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63210582733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7236180305481</t>
+    <t xml:space="preserve">7.77852582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6321063041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361755371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642820358276</t>
+    <t xml:space="preserve">7.04642868041992</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340427398682</t>
+    <t xml:space="preserve">6.86340475082397</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46075105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35093688964844</t>
+    <t xml:space="preserve">6.4607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3509373664856</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130760192871</t>
+    <t xml:space="preserve">6.02149391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130807876587</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242164611816</t>
+    <t xml:space="preserve">5.47242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279188156128</t>
+    <t xml:space="preserve">5.25279235839844</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36260652542114</t>
+    <t xml:space="preserve">5.3626070022583</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884021759033</t>
+    <t xml:space="preserve">5.61884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4490818977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324731826782</t>
+    <t xml:space="preserve">7.44908237457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324684143066</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5588960647583</t>
+    <t xml:space="preserve">7.55889654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452289581299</t>
+    <t xml:space="preserve">8.51062202453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847312927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452194213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025131225586</t>
+    <t xml:space="preserve">8.73025035858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176303863525</t>
+    <t xml:space="preserve">8.82176208496094</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0230884552002</t>
+    <t xml:space="preserve">9.13290309906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02308940887451</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179096221924</t>
+    <t xml:space="preserve">9.79179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866186141968</t>
+    <t xml:space="preserve">10.3866195678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998580932617</t>
+    <t xml:space="preserve">9.37998676300049</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89497184753418</t>
+    <t xml:space="preserve">8.8949728012085</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833904266357</t>
+    <t xml:space="preserve">7.88833999633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47401714324951</t>
+    <t xml:space="preserve">8.4740161895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92494487762451</t>
+    <t xml:space="preserve">7.9249439239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735641479492</t>
+    <t xml:space="preserve">6.57056570053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735593795776</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396081924438</t>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661403656006</t>
+    <t xml:space="preserve">6.93661451339722</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -67862,7 +67862,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6493402778</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>18718</v>
@@ -67883,6 +67883,32 @@
         <v>887</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6495023148</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>7890</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>8.9399995803833</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>893</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169721603394</t>
+    <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1871395111084</t>
+    <t xml:space="preserve">5.18713998794556</t>
   </si>
   <si>
     <t xml:space="preserve">5.1165943145752</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958877563477</t>
+    <t xml:space="preserve">5.19958925247192</t>
   </si>
   <si>
     <t xml:space="preserve">5.24523591995239</t>
@@ -74,16 +74,16 @@
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3157811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632535934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34897899627686</t>
+    <t xml:space="preserve">5.31578063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897804260254</t>
   </si>
   <si>
     <t xml:space="preserve">5.35312795639038</t>
@@ -92,43 +92,43 @@
     <t xml:space="preserve">5.36972665786743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067964553833</t>
+    <t xml:space="preserve">5.41122388839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
     <t xml:space="preserve">5.39462518692017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47762012481689</t>
+    <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176956176758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000385284424</t>
+    <t xml:space="preserve">5.71000337600708</t>
   </si>
   <si>
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259099960327</t>
+    <t xml:space="preserve">5.89259052276611</t>
   </si>
   <si>
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558450698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96728563308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90088987350464</t>
+    <t xml:space="preserve">5.85939311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558546066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96728610992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
     <t xml:space="preserve">5.96313571929932</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">5.95068645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599182128906</t>
+    <t xml:space="preserve">5.94653701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599229812622</t>
   </si>
   <si>
     <t xml:space="preserve">5.86769247055054</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04198026657104</t>
+    <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
     <t xml:space="preserve">6.05857944488525</t>
@@ -161,37 +161,37 @@
     <t xml:space="preserve">6.13327407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19137048721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47355031967163</t>
+    <t xml:space="preserve">6.19137001037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">6.36150789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55239486694336</t>
+    <t xml:space="preserve">6.55239534378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5606951713562</t>
+    <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
     <t xml:space="preserve">6.432053565979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53994560241699</t>
+    <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559322357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464071273804</t>
@@ -200,49 +200,49 @@
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80552768707275</t>
+    <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301336288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920475006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234580993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928676605225</t>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451059341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920570373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349254608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234485626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
   </si>
   <si>
     <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38648700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4279842376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573791503906</t>
+    <t xml:space="preserve">7.38648748397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798328399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573886871338</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240310668945</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643712997437</t>
+    <t xml:space="preserve">7.43643665313721</t>
   </si>
   <si>
     <t xml:space="preserve">7.22058057785034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788431167603</t>
+    <t xml:space="preserve">7.20788478851318</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156755447388</t>
+    <t xml:space="preserve">6.80156707763672</t>
   </si>
   <si>
     <t xml:space="preserve">6.98356342315674</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49145889282227</t>
+    <t xml:space="preserve">6.99202871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
     <t xml:space="preserve">7.37294960021973</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676532745361</t>
+    <t xml:space="preserve">7.29253244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676485061646</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290607452393</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">7.30523061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36448526382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941902160645</t>
+    <t xml:space="preserve">7.3644847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830051422119</t>
@@ -317,22 +317,22 @@
     <t xml:space="preserve">7.2375111579895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16132688522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821298599243</t>
+    <t xml:space="preserve">7.16132736206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821346282959</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87351894378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45027303695679</t>
+    <t xml:space="preserve">6.87351942062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729066848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45027256011963</t>
   </si>
   <si>
     <t xml:space="preserve">6.67036104202271</t>
@@ -341,22 +341,22 @@
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286207199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514213562012</t>
+    <t xml:space="preserve">7.15286159515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626016616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538280487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77193975448608</t>
+    <t xml:space="preserve">6.99626111984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538328170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84812498092651</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">7.18672132492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11053705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016485214233</t>
+    <t xml:space="preserve">7.11053657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016437530518</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09360694885254</t>
+    <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974817276001</t>
+    <t xml:space="preserve">7.05974769592285</t>
   </si>
   <si>
     <t xml:space="preserve">7.04704999923706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086572647095</t>
+    <t xml:space="preserve">6.97086620330811</t>
   </si>
   <si>
     <t xml:space="preserve">7.03858518600464</t>
@@ -401,166 +401,166 @@
     <t xml:space="preserve">7.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06398057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0555157661438</t>
+    <t xml:space="preserve">7.0639796257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05551528930664</t>
   </si>
   <si>
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00049352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900234222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00895738601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476945877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207223892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987922668457</t>
+    <t xml:space="preserve">7.00049304962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11900186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.008957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987874984741</t>
   </si>
   <si>
     <t xml:space="preserve">7.20365142822266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402410507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211719512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597644805908</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680932998657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43220472335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992370605469</t>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373943328857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38141489028931</t>
+    <t xml:space="preserve">7.38141536712646</t>
   </si>
   <si>
     <t xml:space="preserve">7.28406763076782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44490146636963</t>
+    <t xml:space="preserve">7.44490194320679</t>
   </si>
   <si>
     <t xml:space="preserve">7.39834451675415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382743835449</t>
+    <t xml:space="preserve">7.47452926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382791519165</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65652465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349828720093</t>
+    <t xml:space="preserve">7.65652513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349876403809</t>
   </si>
   <si>
     <t xml:space="preserve">7.58457279205322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229272842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9316349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88930988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470527648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856452941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
+    <t xml:space="preserve">7.44913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843252182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9147047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553958892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.34332275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25020837783813</t>
+    <t xml:space="preserve">7.25020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63536310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694181442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685333251953</t>
+    <t xml:space="preserve">7.63536262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946350097656</t>
@@ -569,22 +569,22 @@
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838947296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702934265137</t>
+    <t xml:space="preserve">7.34755611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838804244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95703077316284</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474880218506</t>
+    <t xml:space="preserve">8.02474784851074</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707382202148</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599979400635</t>
+    <t xml:space="preserve">8.26600074768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30832386016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32525444030762</t>
+    <t xml:space="preserve">8.30832481384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32525539398193</t>
   </si>
   <si>
     <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71040916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87970542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11672496795654</t>
+    <t xml:space="preserve">8.71040725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87970638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11672592163086</t>
   </si>
   <si>
     <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99821662902832</t>
+    <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
@@ -647,43 +647,43 @@
     <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5653657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541845321655</t>
+    <t xml:space="preserve">9.29448699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56536674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541835784912</t>
   </si>
   <si>
     <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1325159072876</t>
+    <t xml:space="preserve">10.1325149536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.496506690979</t>
+    <t xml:space="preserve">10.4965076446533</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620780944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191846847534</t>
+    <t xml:space="preserve">10.9451494216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620790481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.055193901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
@@ -695,16 +695,16 @@
     <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629590988159</t>
+    <t xml:space="preserve">11.9355430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741413116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629581451416</t>
   </si>
   <si>
     <t xml:space="preserve">13.3491868972778</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">14.2633991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0156383514404</t>
+    <t xml:space="preserve">16.0156364440918</t>
   </si>
   <si>
     <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111598968506</t>
+    <t xml:space="preserve">12.511157989502</t>
   </si>
   <si>
     <t xml:space="preserve">13.1460285186768</t>
@@ -731,73 +731,73 @@
     <t xml:space="preserve">14.0940999984741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009870529175</t>
+    <t xml:space="preserve">14.5173463821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009860992432</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243618011475</t>
+    <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438795089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5100193023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184850692749</t>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184860229492</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930906295776</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7639694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0094499588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057241439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.601996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512065887451</t>
+    <t xml:space="preserve">13.7639684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0094509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057231903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.348048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512056350708</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004167556763</t>
+    <t xml:space="preserve">14.508882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500415802002</t>
   </si>
   <si>
     <t xml:space="preserve">14.4073028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4157686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311176300049</t>
+    <t xml:space="preserve">14.4157695770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311185836792</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
@@ -806,22 +806,22 @@
     <t xml:space="preserve">13.8655471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7978277206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840564727783</t>
+    <t xml:space="preserve">13.7978267669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840574264526</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031351089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290988922119</t>
+    <t xml:space="preserve">13.7385740280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290979385376</t>
   </si>
   <si>
     <t xml:space="preserve">12.7820377349854</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">12.7397127151489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0275192260742</t>
+    <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">13.5523452758789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423007965088</t>
+    <t xml:space="preserve">13.4423017501831</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.043417930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.940034866333</t>
+    <t xml:space="preserve">13.0348033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0434169769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9400358200073</t>
   </si>
   <si>
     <t xml:space="preserve">13.4397172927856</t>
@@ -863,34 +863,34 @@
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175714492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3018732070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1640291213989</t>
+    <t xml:space="preserve">13.0175704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.301872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
     <t xml:space="preserve">13.1295690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8797273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901922225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2243366241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812601089478</t>
+    <t xml:space="preserve">12.8797283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901941299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2243375778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
+    <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557331085205</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">13.3277187347412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.276026725769</t>
+    <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314203262329</t>
+    <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
@@ -923,52 +923,52 @@
     <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369703292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.035439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3542003631592</t>
+    <t xml:space="preserve">12.3369693756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0354385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474361419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3542013168335</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3197402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.3197393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.837287902832</t>
+    <t xml:space="preserve">11.9837465286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8286724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7597513198853</t>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8286733627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7597522735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.8200588226318</t>
@@ -977,46 +977,46 @@
     <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.604679107666</t>
+    <t xml:space="preserve">11.7511367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339067459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
     <t xml:space="preserve">11.6305246353149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182085037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0785140991211</t>
+    <t xml:space="preserve">12.0182075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0785150527954</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388216018677</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0440540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0871295928955</t>
+    <t xml:space="preserve">12.0440530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0871286392212</t>
   </si>
   <si>
     <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.103723526001</t>
+    <t xml:space="preserve">13.1037225723267</t>
   </si>
   <si>
     <t xml:space="preserve">12.6988077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231233596802</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661998748779</t>
+    <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
     <t xml:space="preserve">12.3628158569336</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5351209640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265054702759</t>
+    <t xml:space="preserve">12.535120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141893386841</t>
+    <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
     <t xml:space="preserve">12.836651802063</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7504997253418</t>
+    <t xml:space="preserve">12.6643476486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7505016326904</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
@@ -1082,28 +1082,28 @@
     <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7246551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280372619629</t>
+    <t xml:space="preserve">12.7246541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280363082886</t>
   </si>
   <si>
     <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572658538818</t>
+    <t xml:space="preserve">12.8711128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917268753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089559555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984901428223</t>
+    <t xml:space="preserve">13.1984910964966</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
@@ -1127,25 +1127,25 @@
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550960540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7757081985474</t>
+    <t xml:space="preserve">13.6550970077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7757091522217</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843236923218</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498626708984</t>
+    <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907712936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5166168212891</t>
+    <t xml:space="preserve">14.4907703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5166177749634</t>
   </si>
   <si>
     <t xml:space="preserve">14.2150850296021</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8963222503662</t>
+    <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618621826172</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255508422852</t>
+    <t xml:space="preserve">14.0255498886108</t>
   </si>
   <si>
     <t xml:space="preserve">13.939398765564</t>
@@ -1178,40 +1178,40 @@
     <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
-    <t xml:space="preserve">14.111701965332</t>
+    <t xml:space="preserve">14.1117010116577</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">13.7929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637115478516</t>
+    <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8877077102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8704776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8015546798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7326326370239</t>
+    <t xml:space="preserve">13.8877086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.870475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360147476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8015556335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">13.7154035568237</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3191032409668</t>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
     <t xml:space="preserve">13.3880252838135</t>
@@ -1250,16 +1250,16 @@
     <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603284835815</t>
+    <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258693695068</t>
+    <t xml:space="preserve">13.5775604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
     <t xml:space="preserve">13.508638381958</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">13.8634128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.951714515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693756103516</t>
+    <t xml:space="preserve">13.9517154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693737030029</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1106586456299</t>
+    <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
     <t xml:space="preserve">13.9340543746948</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5278654098511</t>
+    <t xml:space="preserve">13.6161661148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
     <t xml:space="preserve">13.4219026565552</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982797622681</t>
+    <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686941146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402433395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872619628906</t>
+    <t xml:space="preserve">13.0686960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872629165649</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.004695892334</t>
+    <t xml:space="preserve">14.0046949386597</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.9870347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8457517623901</t>
+    <t xml:space="preserve">13.8457527160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
@@ -1352,28 +1352,28 @@
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865823745728</t>
+    <t xml:space="preserve">13.3865814208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7221298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514873504639</t>
+    <t xml:space="preserve">13.722128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514883041382</t>
   </si>
   <si>
     <t xml:space="preserve">13.4748840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6868085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.580846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6338272094727</t>
+    <t xml:space="preserve">13.6868095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5808458328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6338262557983</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102043151855</t>
+    <t xml:space="preserve">13.6691484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102052688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
+    <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1403,52 +1403,52 @@
     <t xml:space="preserve">13.2276372909546</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3689222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1746578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629585266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.980393409729</t>
+    <t xml:space="preserve">13.3689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.174656867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629594802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5035610198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0157136917114</t>
+    <t xml:space="preserve">12.5035619735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0157127380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159408569336</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980535507202</t>
+    <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391103744507</t>
+    <t xml:space="preserve">12.8391084671021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099781036377</t>
+    <t xml:space="preserve">13.1569967269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099771499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8920907974243</t>
+    <t xml:space="preserve">12.8920917510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2386560440063</t>
+    <t xml:space="preserve">12.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1481,19 +1481,19 @@
     <t xml:space="preserve">11.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615983963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1790313720703</t>
+    <t xml:space="preserve">11.461597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.037748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0024271011353</t>
+    <t xml:space="preserve">11.0377492904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0024280548096</t>
   </si>
   <si>
     <t xml:space="preserve">11.2143526077271</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">11.7618246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7265033721924</t>
+    <t xml:space="preserve">11.7265043258667</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496738433838</t>
+    <t xml:space="preserve">11.1260509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496728897095</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439373016357</t>
+    <t xml:space="preserve">11.4439382553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494466781616</t>
+    <t xml:space="preserve">10.9494476318359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198619842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966924667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551822662354</t>
+    <t xml:space="preserve">10.7198610305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966934204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2430305480957</t>
+    <t xml:space="preserve">10.24303150177</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902763366699</t>
@@ -1616,40 +1616,40 @@
     <t xml:space="preserve">10.5079364776611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5785789489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6845407485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7375221252441</t>
+    <t xml:space="preserve">10.5785779953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6845417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7375211715698</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.613899230957</t>
+    <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606906890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3313331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432577133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4196348190308</t>
+    <t xml:space="preserve">10.2606916427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3313322067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432567596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4196357727051</t>
   </si>
   <si>
     <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.437294960022</t>
+    <t xml:space="preserve">10.4372959136963</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434839248657</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">10.8964653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9141263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554103851318</t>
+    <t xml:space="preserve">10.9141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069110870361</t>
+    <t xml:space="preserve">10.7069101333618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027923583984</t>
+    <t xml:space="preserve">9.84669780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846300125122</t>
+    <t xml:space="preserve">10.0663261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846290588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578388214111</t>
+    <t xml:space="preserve">10.139536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578397750854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055847167969</t>
+    <t xml:space="preserve">10.5055837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5238876342773</t>
+    <t xml:space="preserve">10.523886680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5604915618896</t>
+    <t xml:space="preserve">10.560492515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716335296631</t>
+    <t xml:space="preserve">10.8716325759888</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899354934692</t>
+    <t xml:space="preserve">10.6703062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899345397949</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193794250488</t>
+    <t xml:space="preserve">11.2193784713745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533306121826</t>
+    <t xml:space="preserve">11.1644716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252140045166</t>
+    <t xml:space="preserve">10.7252130508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944842338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461687088013</t>
+    <t xml:space="preserve">10.9448432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608589172363</t>
+    <t xml:space="preserve">8.23608493804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550094604492</t>
+    <t xml:space="preserve">8.17202663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550142288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234292984009</t>
+    <t xml:space="preserve">6.01234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00982332229614</t>
+    <t xml:space="preserve">7.0098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558013916016</t>
+    <t xml:space="preserve">7.055579662323</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531558990479</t>
+    <t xml:space="preserve">7.41247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531511306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568677902222</t>
+    <t xml:space="preserve">7.48568725585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038034439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303308486938</t>
+    <t xml:space="preserve">6.68038082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229118347168</t>
+    <t xml:space="preserve">7.52229166030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364643096924</t>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364547729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818161010742</t>
+    <t xml:space="preserve">8.96818256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62043571472168</t>
+    <t xml:space="preserve">8.620436668396</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003803253174</t>
+    <t xml:space="preserve">7.7968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003755569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6321063041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361755371094</t>
+    <t xml:space="preserve">7.77852535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63210582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236180305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642868041992</t>
+    <t xml:space="preserve">7.04642820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340475082397</t>
+    <t xml:space="preserve">6.86340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3509373664856</t>
+    <t xml:space="preserve">6.46075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35093688964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130807876587</t>
+    <t xml:space="preserve">6.02149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242116928101</t>
+    <t xml:space="preserve">5.47242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279235839844</t>
+    <t xml:space="preserve">5.25279188156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626070022583</t>
+    <t xml:space="preserve">5.36260652542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884069442749</t>
+    <t xml:space="preserve">5.61884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44908237457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324684143066</t>
+    <t xml:space="preserve">7.4490818977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324731826782</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55889654159546</t>
+    <t xml:space="preserve">7.5588960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062202453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452194213867</t>
+    <t xml:space="preserve">8.51062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452289581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025035858154</t>
+    <t xml:space="preserve">8.73025131225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176208496094</t>
+    <t xml:space="preserve">8.82176303863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308940887451</t>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179000854492</t>
+    <t xml:space="preserve">9.79179096221924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866195678711</t>
+    <t xml:space="preserve">10.3866186141968</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998676300049</t>
+    <t xml:space="preserve">9.37998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8949728012085</t>
+    <t xml:space="preserve">8.89497184753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833999633789</t>
+    <t xml:space="preserve">7.88833904266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4740161895752</t>
+    <t xml:space="preserve">8.47401714324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9249439239502</t>
+    <t xml:space="preserve">7.92494487762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735593795776</t>
+    <t xml:space="preserve">6.57056617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735641479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.53396081924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661451339722</t>
+    <t xml:space="preserve">6.93661403656006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -67888,7 +67888,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6495023148</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>7890</v>
@@ -67909,6 +67909,32 @@
         <v>893</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.649375</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>8941</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414600372314</t>
+    <t xml:space="preserve">5.10414552688599</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564228057861</t>
+    <t xml:space="preserve">5.14564275741577</t>
   </si>
   <si>
     <t xml:space="preserve">5.18713998794556</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958925247192</t>
+    <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
     <t xml:space="preserve">5.24523591995239</t>
@@ -74,37 +74,37 @@
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31578063964844</t>
+    <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
     <t xml:space="preserve">5.34482908248901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38632583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34897804260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
+    <t xml:space="preserve">5.38632535934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972665786743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122388839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462518692017</t>
+    <t xml:space="preserve">5.41122436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462471008301</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176956176758</t>
+    <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000337600708</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259052276611</t>
+    <t xml:space="preserve">5.89259099960327</t>
   </si>
   <si>
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558546066284</t>
+    <t xml:space="preserve">5.85939264297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728610992432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9008903503418</t>
+    <t xml:space="preserve">5.90089082717896</t>
   </si>
   <si>
     <t xml:space="preserve">5.96313571929932</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">5.95068645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653701782227</t>
+    <t xml:space="preserve">5.94653654098511</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599229812622</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442953109741</t>
+    <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05857944488525</t>
+    <t xml:space="preserve">6.0585789680481</t>
   </si>
   <si>
     <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327407836914</t>
+    <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355079650879</t>
+    <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
     <t xml:space="preserve">6.36150789260864</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61464071273804</t>
+    <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8055272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321630477905</t>
+    <t xml:space="preserve">6.80552673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321678161621</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301288604736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02961206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451059341431</t>
+    <t xml:space="preserve">7.02961158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">7.12920570373535</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">7.30349254608154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46948146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289733886719</t>
+    <t xml:space="preserve">7.46948099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6728982925415</t>
   </si>
   <si>
     <t xml:space="preserve">8.12928485870361</t>
@@ -236,28 +236,28 @@
     <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38648748397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798328399658</t>
+    <t xml:space="preserve">7.38648700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
     <t xml:space="preserve">7.36573886871338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16240310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634864807129</t>
+    <t xml:space="preserve">7.16240262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634817123413</t>
   </si>
   <si>
     <t xml:space="preserve">7.43643665313721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22058057785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788478851318</t>
+    <t xml:space="preserve">7.2205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788431167603</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">6.77617263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97933101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202871322632</t>
+    <t xml:space="preserve">6.97933053970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29253244400024</t>
+    <t xml:space="preserve">7.2925329208374</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676485061646</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1994194984436</t>
+    <t xml:space="preserve">7.19941854476929</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2375111579895</t>
+    <t xml:space="preserve">7.23751163482666</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132736206055</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">7.02588796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87351942062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729066848755</t>
+    <t xml:space="preserve">6.87351894378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
     <t xml:space="preserve">6.45027256011963</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56031703948975</t>
+    <t xml:space="preserve">6.5603175163269</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286159515381</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538328170776</t>
+    <t xml:space="preserve">6.72538280487061</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">6.84812498092651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621711730957</t>
+    <t xml:space="preserve">6.88621759414673</t>
   </si>
   <si>
     <t xml:space="preserve">7.18672132492065</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937501907349</t>
+    <t xml:space="preserve">7.08937454223633</t>
   </si>
   <si>
     <t xml:space="preserve">7.05974769592285</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">7.04704999923706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086620330811</t>
+    <t xml:space="preserve">6.97086572647095</t>
   </si>
   <si>
     <t xml:space="preserve">7.03858518600464</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">7.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0639796257019</t>
+    <t xml:space="preserve">7.06398010253906</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.008957862854</t>
+    <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
     <t xml:space="preserve">7.11476993560791</t>
@@ -434,40 +434,40 @@
     <t xml:space="preserve">7.20365142822266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23327875137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402410507202</t>
+    <t xml:space="preserve">7.23327827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402458190918</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211719512939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597644805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680932998657</t>
+    <t xml:space="preserve">7.24597597122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
     <t xml:space="preserve">7.43220376968384</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49992322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373943328857</t>
+    <t xml:space="preserve">7.49992370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373991012573</t>
   </si>
   <si>
     <t xml:space="preserve">7.38141536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28406763076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490194320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834451675415</t>
+    <t xml:space="preserve">7.28406810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
     <t xml:space="preserve">7.47452926635742</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65652513504028</t>
+    <t xml:space="preserve">7.6565260887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.78349876403809</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">7.58457279205322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913482666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378248214722</t>
+    <t xml:space="preserve">7.449134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378343582153</t>
   </si>
   <si>
     <t xml:space="preserve">7.61843252182007</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">7.58880519866943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229225158691</t>
+    <t xml:space="preserve">7.6522912979126</t>
   </si>
   <si>
     <t xml:space="preserve">7.69884967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74540710449219</t>
+    <t xml:space="preserve">7.74540615081787</t>
   </si>
   <si>
     <t xml:space="preserve">7.86814832687378</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">7.95279741287231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94856548309326</t>
+    <t xml:space="preserve">7.94856452941895</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553958892822</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">7.61420059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45759963989258</t>
+    <t xml:space="preserve">7.42797136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759916305542</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536262512207</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40257692337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755611419678</t>
+    <t xml:space="preserve">7.4025764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755563735962</t>
   </si>
   <si>
     <t xml:space="preserve">7.27137136459351</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50838804244995</t>
+    <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
     <t xml:space="preserve">7.95703077316284</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474784851074</t>
+    <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707382202148</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40567111968994</t>
+    <t xml:space="preserve">8.40567016601562</t>
   </si>
   <si>
     <t xml:space="preserve">8.26600074768066</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30832481384277</t>
+    <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
     <t xml:space="preserve">8.32525539398193</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71040725708008</t>
+    <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
     <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11672592163086</t>
+    <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
     <t xml:space="preserve">9.01514530181885</t>
@@ -635,34 +635,34 @@
     <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04054069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02361011505127</t>
+    <t xml:space="preserve">9.04054164886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02361106872559</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1759786605835</t>
+    <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448699951172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56536674499512</t>
+    <t xml:space="preserve">9.5653657913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.98861217498779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4541835784912</t>
+    <t xml:space="preserve">10.4541826248169</t>
   </si>
   <si>
     <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1325149536133</t>
+    <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">10.4965076446533</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9451494216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620790481567</t>
+    <t xml:space="preserve">10.7927808761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9451484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620780944824</t>
   </si>
   <si>
     <t xml:space="preserve">11.055193901062</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7239208221436</t>
+    <t xml:space="preserve">11.7239217758179</t>
   </si>
   <si>
     <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355430603027</t>
+    <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741413116455</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2633991241455</t>
+    <t xml:space="preserve">14.2634000778198</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156364440918</t>
@@ -737,25 +737,25 @@
     <t xml:space="preserve">14.0009860992432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1206340789795</t>
+    <t xml:space="preserve">13.1206350326538</t>
   </si>
   <si>
     <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169063568115</t>
+    <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
     <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338359832764</t>
+    <t xml:space="preserve">13.4338369369507</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5100212097168</t>
+    <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
     <t xml:space="preserve">13.5184860229492</t>
@@ -764,37 +764,37 @@
     <t xml:space="preserve">13.4930906295776</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7639684677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0094509124756</t>
+    <t xml:space="preserve">13.7639675140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0094518661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348048210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512056350708</t>
+    <t xml:space="preserve">14.3480491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.601996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.508882522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.500415802002</t>
+    <t xml:space="preserve">14.5088815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
     <t xml:space="preserve">14.4073028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4157695770264</t>
+    <t xml:space="preserve">14.4157686233521</t>
   </si>
   <si>
     <t xml:space="preserve">14.3311185836792</t>
@@ -803,31 +803,31 @@
     <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8655471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978267669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840574264526</t>
+    <t xml:space="preserve">13.8655462265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978277206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385740280151</t>
+    <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
     <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397127151489</t>
+    <t xml:space="preserve">13.1290988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.782036781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397117614746</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
@@ -67914,7 +67914,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.649375</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>8941</v>
@@ -67935,6 +67935,32 @@
         <v>888</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6494328704</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>6890</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>892</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414552688599</t>
+    <t xml:space="preserve">5.10414505004883</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169626235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14564275741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18713998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1165943145752</t>
+    <t xml:space="preserve">5.15394163131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14564228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224145889282</t>
@@ -68,43 +68,43 @@
     <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31163120269775</t>
+    <t xml:space="preserve">5.30333089828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3116307258606</t>
   </si>
   <si>
     <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482908248901</t>
+    <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
     <t xml:space="preserve">5.38632535934448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34897899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972665786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067869186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462471008301</t>
+    <t xml:space="preserve">5.3489785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312795639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122388839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067916870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462566375732</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176908493042</t>
+    <t xml:space="preserve">5.48176956176758</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000337600708</t>
@@ -119,70 +119,70 @@
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939264297485</t>
+    <t xml:space="preserve">5.85939311981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728610992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90089082717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96313571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599229812622</t>
+    <t xml:space="preserve">5.96728563308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9008903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96313619613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068693161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05443000793457</t>
+    <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0585789680481</t>
+    <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
     <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327360153198</t>
+    <t xml:space="preserve">6.13327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355031967163</t>
+    <t xml:space="preserve">6.47354984283447</t>
   </si>
   <si>
     <t xml:space="preserve">6.36150789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55239534378052</t>
+    <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.432053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994607925415</t>
+    <t xml:space="preserve">6.5606951713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43205308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">6.58559274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59804201126099</t>
+    <t xml:space="preserve">6.59804105758667</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464023590088</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80552673339844</t>
+    <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301288604736</t>
+    <t xml:space="preserve">7.01301336288452</t>
   </si>
   <si>
     <t xml:space="preserve">7.02961158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920570373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948099136353</t>
+    <t xml:space="preserve">7.05450963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920475006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948146820068</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
@@ -230,13 +230,13 @@
     <t xml:space="preserve">8.6728982925415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12928485870361</t>
+    <t xml:space="preserve">8.12928581237793</t>
   </si>
   <si>
     <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38648700714111</t>
+    <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
     <t xml:space="preserve">7.42798376083374</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">7.16240262985229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21634817123413</t>
+    <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
     <t xml:space="preserve">7.43643665313721</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788431167603</t>
+    <t xml:space="preserve">7.20788383483887</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">6.77617263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97933053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202823638916</t>
+    <t xml:space="preserve">6.97933149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202919006348</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676485061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290607452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523061752319</t>
+    <t xml:space="preserve">7.29253244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676580429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290559768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523014068604</t>
   </si>
   <si>
     <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941854476929</t>
+    <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830051422119</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">7.23751163482666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16132736206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588796615601</t>
+    <t xml:space="preserve">7.16132640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821298599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588748931885</t>
   </si>
   <si>
     <t xml:space="preserve">6.87351894378662</t>
@@ -332,25 +332,25 @@
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027256011963</t>
+    <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5603175163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15286159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514261245728</t>
+    <t xml:space="preserve">6.56031703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15286207199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626111984253</t>
+    <t xml:space="preserve">6.99626064300537</t>
   </si>
   <si>
     <t xml:space="preserve">6.72538280487061</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84812498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621759414673</t>
+    <t xml:space="preserve">6.84812450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
     <t xml:space="preserve">7.18672132492065</t>
@@ -371,37 +371,37 @@
     <t xml:space="preserve">7.11053657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016437530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630512237549</t>
+    <t xml:space="preserve">7.05128192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016532897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630464553833</t>
   </si>
   <si>
     <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937454223633</t>
+    <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
     <t xml:space="preserve">7.05974769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04704999923706</t>
+    <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086572647095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398010253906</t>
+    <t xml:space="preserve">7.03858470916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012132644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0639796257019</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
@@ -413,52 +413,52 @@
     <t xml:space="preserve">7.00049304962158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03435277938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900186538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00895833969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476993560791</t>
+    <t xml:space="preserve">7.03435325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11900234222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.008957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
     <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38987874984741</t>
+    <t xml:space="preserve">7.38987922668457</t>
   </si>
   <si>
     <t xml:space="preserve">7.20365142822266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211719512939</t>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402410507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
     <t xml:space="preserve">7.24597597122192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40680980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43220376968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373991012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141536712646</t>
+    <t xml:space="preserve">7.40680932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.432204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42374038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141441345215</t>
   </si>
   <si>
     <t xml:space="preserve">7.28406810760498</t>
@@ -473,73 +473,73 @@
     <t xml:space="preserve">7.47452926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64382791519165</t>
+    <t xml:space="preserve">7.64382648468018</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6565260887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349876403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843252182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6522912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69884967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814832687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88931035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9147047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856452941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420059204102</t>
+    <t xml:space="preserve">7.65652465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349733352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457231521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229272842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9316349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317056655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8258228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88930988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420106887817</t>
   </si>
   <si>
     <t xml:space="preserve">7.42797136306763</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45759916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694229125977</t>
+    <t xml:space="preserve">7.45759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694181442261</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685380935669</t>
@@ -566,25 +566,25 @@
     <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4025764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137136459351</t>
+    <t xml:space="preserve">7.40257692337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137088775635</t>
   </si>
   <si>
     <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95703077316284</t>
+    <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474880218506</t>
+    <t xml:space="preserve">8.02474975585938</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707382202148</t>
@@ -593,37 +593,37 @@
     <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27023220062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40990352630615</t>
+    <t xml:space="preserve">8.27023124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40990447998047</t>
   </si>
   <si>
     <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40567016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26600074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23214054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30832386016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32525539398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027572631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.40567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26599979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23213958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30832481384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32525444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040916442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04054164886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02361106872559</t>
+    <t xml:space="preserve">9.04054069519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17597961425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29448699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5653657913208</t>
+    <t xml:space="preserve">9.1759786605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29448795318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56536483764648</t>
   </si>
   <si>
     <t xml:space="preserve">9.98861217498779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4541826248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773338317871</t>
+    <t xml:space="preserve">10.4541845321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4965076446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7927808761597</t>
+    <t xml:space="preserve">10.496506690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620780944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.055193901062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191837310791</t>
+    <t xml:space="preserve">10.9620771408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191846847534</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
@@ -692,55 +692,55 @@
     <t xml:space="preserve">11.7239217758179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.76624584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355440139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741413116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629581451416</t>
+    <t xml:space="preserve">11.7662448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355449676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973886489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
     <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156364440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.051775932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.511157989502</t>
+    <t xml:space="preserve">14.2633991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156383514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0517749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111598968506</t>
   </si>
   <si>
     <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0940999984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173463821411</t>
+    <t xml:space="preserve">14.6443214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0941009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173454284668</t>
   </si>
   <si>
     <t xml:space="preserve">14.0009860992432</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1206350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8243608474731</t>
+    <t xml:space="preserve">13.1206340789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8243618011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169073104858</t>
@@ -758,25 +758,25 @@
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184860229492</t>
+    <t xml:space="preserve">13.5184850692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930906295776</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7639675140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0094518661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057231903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.601996421814</t>
+    <t xml:space="preserve">13.7639684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0094509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.348048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019954681396</t>
   </si>
   <si>
     <t xml:space="preserve">14.5512065887451</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088815689087</t>
+    <t xml:space="preserve">14.5088806152344</t>
   </si>
   <si>
     <t xml:space="preserve">14.5004167556763</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">14.4073028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4157686233521</t>
+    <t xml:space="preserve">14.4157676696777</t>
   </si>
   <si>
     <t xml:space="preserve">14.3311185836792</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1618194580078</t>
+    <t xml:space="preserve">14.1618204116821</t>
   </si>
   <si>
     <t xml:space="preserve">13.8655462265015</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9840564727783</t>
+    <t xml:space="preserve">13.984058380127</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397117614746</t>
+    <t xml:space="preserve">12.7397127151489</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">13.5523452758789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423017501831</t>
+    <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
@@ -848,25 +848,25 @@
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348033905029</t>
+    <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
     <t xml:space="preserve">13.0434169769287</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9400358200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397172927856</t>
+    <t xml:space="preserve">12.940034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.301872253418</t>
+    <t xml:space="preserve">13.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3018732070923</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
@@ -875,37 +875,37 @@
     <t xml:space="preserve">13.1295690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8797283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901941299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2243375778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812610626221</t>
+    <t xml:space="preserve">12.8797273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2243366241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228038787842</t>
+    <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123390197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277187347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2760276794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2501821517944</t>
+    <t xml:space="preserve">13.1123399734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277196884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276026725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2501811981201</t>
   </si>
   <si>
     <t xml:space="preserve">13.0606470108032</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834289550781</t>
+    <t xml:space="preserve">12.4834280014038</t>
   </si>
   <si>
     <t xml:space="preserve">12.233588218689</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0354385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975944519043</t>
+    <t xml:space="preserve">12.035439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975954055786</t>
   </si>
   <si>
     <t xml:space="preserve">12.1474361419678</t>
@@ -941,40 +941,40 @@
     <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3197393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1302051544189</t>
+    <t xml:space="preserve">12.3197402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837465286255</t>
+    <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
     <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7855968475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7166767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8286733627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7597522735596</t>
+    <t xml:space="preserve">11.7855978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7166757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114423751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8286724090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769823074341</t>
+    <t xml:space="preserve">11.7769813537598</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612831115723</t>
+    <t xml:space="preserve">11.6305236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182085037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0785150527954</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1388216018677</t>
+    <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">12.0871286392212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2157211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6988077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.500659942627</t>
+    <t xml:space="preserve">13.2157220840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.103723526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6988086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591161727905</t>
+    <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
+    <t xml:space="preserve">12.5265054702759</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.836651802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883428573608</t>
+    <t xml:space="preserve">12.9141893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883438110352</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7505016326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868110656738</t>
+    <t xml:space="preserve">12.7505006790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868101119995</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
@@ -1082,28 +1082,28 @@
     <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7246541976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935762405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280363082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7418842315674</t>
+    <t xml:space="preserve">12.7246561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280372619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917268753052</t>
+    <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089559555054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572649002075</t>
+    <t xml:space="preserve">12.9572639465332</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
@@ -1112,28 +1112,28 @@
     <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0951080322266</t>
+    <t xml:space="preserve">13.0951070785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984910964966</t>
+    <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914073944092</t>
+    <t xml:space="preserve">13.4914064407349</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757091522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843236923218</t>
+    <t xml:space="preserve">13.7757081985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5166177749634</t>
+    <t xml:space="preserve">14.4907712936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
     <t xml:space="preserve">14.2150850296021</t>
@@ -1157,25 +1157,25 @@
     <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8618621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1547784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443117141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0255498886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.939398765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8446311950684</t>
+    <t xml:space="preserve">13.8618612289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1547775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443126678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0255508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9393978118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
     <t xml:space="preserve">14.1117010116577</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206359863281</t>
+    <t xml:space="preserve">13.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206369400024</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
@@ -1199,43 +1199,43 @@
     <t xml:space="preserve">13.8187866210938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8877086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.870475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360147476196</t>
+    <t xml:space="preserve">13.8877077102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8704767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360157012939</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7326335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154035568237</t>
+    <t xml:space="preserve">13.7326326370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154026031494</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569463729858</t>
+    <t xml:space="preserve">13.4569473266602</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.405255317688</t>
+    <t xml:space="preserve">13.3535642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880252838135</t>
+    <t xml:space="preserve">13.3880243301392</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
@@ -1256,25 +1256,25 @@
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775604248047</t>
+    <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634128570557</t>
+    <t xml:space="preserve">13.8634119033813</t>
   </si>
   <si>
     <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693737030029</t>
+    <t xml:space="preserve">13.9693746566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1289,28 +1289,28 @@
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161661148071</t>
+    <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219026565552</t>
+    <t xml:space="preserve">13.4219017028809</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982807159424</t>
+    <t xml:space="preserve">13.2982797622681</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
+    <t xml:space="preserve">13.0686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
     <t xml:space="preserve">14.2872629165649</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753374099731</t>
+    <t xml:space="preserve">14.0753364562988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1352,25 +1352,25 @@
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865814208984</t>
+    <t xml:space="preserve">13.3865823745728</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.722128868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514883041382</t>
+    <t xml:space="preserve">13.7221298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514873504639</t>
   </si>
   <si>
     <t xml:space="preserve">13.4748840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6868095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5808458328247</t>
+    <t xml:space="preserve">13.6868085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
     <t xml:space="preserve">13.6338262557983</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691484451294</t>
+    <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102052688599</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
+    <t xml:space="preserve">13.351261138916</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">13.2276372909546</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.174656867981</t>
+    <t xml:space="preserve">13.3689222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1746578216553</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095237731934</t>
+    <t xml:space="preserve">12.6095247268677</t>
   </si>
   <si>
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159408569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980525970459</t>
+    <t xml:space="preserve">13.0157136917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159399032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980535507202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391084671021</t>
+    <t xml:space="preserve">12.8391103744507</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099771499634</t>
+    <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8920917510986</t>
+    <t xml:space="preserve">12.8920907974243</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
@@ -1466,22 +1466,22 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.2673349380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.461597442627</t>
+    <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
     <t xml:space="preserve">11.1790323257446</t>
@@ -1502,25 +1502,25 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
+    <t xml:space="preserve">10.9317874908447</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792585372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441654205322</t>
+    <t xml:space="preserve">11.2849950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441644668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1260509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496728897095</t>
+    <t xml:space="preserve">11.126051902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496738433838</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1577,25 +1577,25 @@
     <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41299247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831371307373</t>
+    <t xml:space="preserve">9.41299152374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831275939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
+    <t xml:space="preserve">9.53661441802979</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198610305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966934204102</t>
+    <t xml:space="preserve">10.7198629379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551832199097</t>
@@ -1607,25 +1607,25 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785779953003</t>
+    <t xml:space="preserve">10.2430305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079374313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785789489746</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375211715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258237838745</t>
+    <t xml:space="preserve">10.7375221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258247375488</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
@@ -1634,34 +1634,34 @@
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606916427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3313322067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432567596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4196357727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4019746780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4372959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8434839248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8964653015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554094314575</t>
+    <t xml:space="preserve">10.2606906890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3313331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4196348190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4019756317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.437294960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.84348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.896466255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554103851318</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069101333618</t>
+    <t xml:space="preserve">10.7069110870361</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027828216553</t>
+    <t xml:space="preserve">9.84669876098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027923583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846290588379</t>
+    <t xml:space="preserve">10.0663270950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846300125122</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.139536857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578397750854</t>
+    <t xml:space="preserve">10.1395359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578388214111</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055837631226</t>
+    <t xml:space="preserve">10.5055847167969</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.523886680603</t>
+    <t xml:space="preserve">10.5238876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.560492515564</t>
+    <t xml:space="preserve">10.5604915618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716325759888</t>
+    <t xml:space="preserve">10.8716335296631</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703062057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899345397949</t>
+    <t xml:space="preserve">10.6703052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984228134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899354934692</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193784713745</t>
+    <t xml:space="preserve">11.2193794250488</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644716262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533296585083</t>
+    <t xml:space="preserve">11.1644706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533306121826</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252130508423</t>
+    <t xml:space="preserve">10.7252140045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9448432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461696624756</t>
+    <t xml:space="preserve">10.944842338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109564781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461687088013</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608493804932</t>
+    <t xml:space="preserve">8.23608589172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550142288208</t>
+    <t xml:space="preserve">8.17202758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550094604492</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234245300293</t>
+    <t xml:space="preserve">6.01234292984009</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0098237991333</t>
+    <t xml:space="preserve">7.00982332229614</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.055579662323</t>
+    <t xml:space="preserve">7.05558013916016</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247749328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531511306763</t>
+    <t xml:space="preserve">7.41247701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531558990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568725585938</t>
+    <t xml:space="preserve">7.48568677902222</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303356170654</t>
+    <t xml:space="preserve">6.68038034439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303308486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229166030884</t>
+    <t xml:space="preserve">7.52229118347168</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364547729492</t>
+    <t xml:space="preserve">8.14457225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364643096924</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818256378174</t>
+    <t xml:space="preserve">8.96818161010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.620436668396</t>
+    <t xml:space="preserve">8.62043571472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7968282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003755569458</t>
+    <t xml:space="preserve">7.79682779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003803253174</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63210582733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7236180305481</t>
+    <t xml:space="preserve">7.77852582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6321063041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361755371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642820358276</t>
+    <t xml:space="preserve">7.04642868041992</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340427398682</t>
+    <t xml:space="preserve">6.86340475082397</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46075105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35093688964844</t>
+    <t xml:space="preserve">6.4607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3509373664856</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130760192871</t>
+    <t xml:space="preserve">6.02149391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130807876587</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242164611816</t>
+    <t xml:space="preserve">5.47242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279188156128</t>
+    <t xml:space="preserve">5.25279235839844</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36260652542114</t>
+    <t xml:space="preserve">5.3626070022583</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884021759033</t>
+    <t xml:space="preserve">5.61884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4490818977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324731826782</t>
+    <t xml:space="preserve">7.44908237457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324684143066</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5588960647583</t>
+    <t xml:space="preserve">7.55889654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452289581299</t>
+    <t xml:space="preserve">8.51062202453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847312927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452194213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025131225586</t>
+    <t xml:space="preserve">8.73025035858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176303863525</t>
+    <t xml:space="preserve">8.82176208496094</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0230884552002</t>
+    <t xml:space="preserve">9.13290309906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02308940887451</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179096221924</t>
+    <t xml:space="preserve">9.79179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866186141968</t>
+    <t xml:space="preserve">10.3866195678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998580932617</t>
+    <t xml:space="preserve">9.37998676300049</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89497184753418</t>
+    <t xml:space="preserve">8.8949728012085</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833904266357</t>
+    <t xml:space="preserve">7.88833999633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47401714324951</t>
+    <t xml:space="preserve">8.4740161895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92494487762451</t>
+    <t xml:space="preserve">7.9249439239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735641479492</t>
+    <t xml:space="preserve">6.57056570053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735593795776</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396081924438</t>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661403656006</t>
+    <t xml:space="preserve">6.93661451339722</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -67940,7 +67940,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6494328704</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>6890</v>
@@ -67961,6 +67961,32 @@
         <v>892</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6781828704</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>35384</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>894</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,91 +38,91 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414505004883</t>
+    <t xml:space="preserve">5.10414600372314</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394163131714</t>
+    <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">5.09169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564228057861</t>
+    <t xml:space="preserve">5.14564275741577</t>
   </si>
   <si>
     <t xml:space="preserve">5.1871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659479141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958877563477</t>
+    <t xml:space="preserve">5.11659383773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958925247192</t>
   </si>
   <si>
     <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3116307258606</t>
+    <t xml:space="preserve">5.30333137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31163167953491</t>
   </si>
   <si>
     <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632535934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3489785194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122388839722</t>
+    <t xml:space="preserve">5.41122436523438</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462566375732</t>
+    <t xml:space="preserve">5.39462518692017</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71000337600708</t>
+    <t xml:space="preserve">5.48176908493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558498382568</t>
+    <t xml:space="preserve">5.89259052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71415376663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558546066284</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728563308716</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313619613647</t>
+    <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653701782227</t>
+    <t xml:space="preserve">5.94653654098511</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599182128906</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0419807434082</t>
+    <t xml:space="preserve">6.04198026657104</t>
   </si>
   <si>
     <t xml:space="preserve">6.05857944488525</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327407836914</t>
+    <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47354984283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36150789260864</t>
+    <t xml:space="preserve">6.47355031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
     <t xml:space="preserve">6.55239486694336</t>
@@ -176,88 +176,88 @@
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5606951713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59389209747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58559274673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804105758667</t>
+    <t xml:space="preserve">6.56069421768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43205404281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994607925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5938925743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58559226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804153442383</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63953876495361</t>
+    <t xml:space="preserve">6.63953924179077</t>
   </si>
   <si>
     <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96321678161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301336288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05450963973999</t>
+    <t xml:space="preserve">6.96321630477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">7.12920475006104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30349349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948146820068</t>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948099136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6728982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
+    <t xml:space="preserve">8.67289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1292839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281818389893</t>
   </si>
   <si>
     <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42798376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573886871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240262985229</t>
+    <t xml:space="preserve">7.42798328399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240310668945</t>
   </si>
   <si>
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643665313721</t>
+    <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
     <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788383483887</t>
+    <t xml:space="preserve">7.20788431167603</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156707763672</t>
+    <t xml:space="preserve">6.80156755447388</t>
   </si>
   <si>
     <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94123840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202919006348</t>
+    <t xml:space="preserve">6.94123888015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617311477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933053970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -293,28 +293,28 @@
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676580429077</t>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676628112793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290559768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30523014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3644847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994194984436</t>
+    <t xml:space="preserve">7.30523061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36448431015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941902160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23751163482666</t>
+    <t xml:space="preserve">7.23751068115234</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132640838623</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">7.06821298599243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351894378662</t>
+    <t xml:space="preserve">7.02588844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351846694946</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
@@ -341,67 +341,67 @@
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286207199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514213562012</t>
+    <t xml:space="preserve">7.15286159515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538280487061</t>
+    <t xml:space="preserve">6.99626159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84812450408936</t>
+    <t xml:space="preserve">6.84812498092651</t>
   </si>
   <si>
     <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18672132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053657531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630464553833</t>
+    <t xml:space="preserve">7.18672180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053705215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016485214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
     <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937501907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974769592285</t>
+    <t xml:space="preserve">7.08937549591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974817276001</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086572647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858470916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012132644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0639796257019</t>
+    <t xml:space="preserve">6.97086524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012037277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398010253906</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00049304962158</t>
+    <t xml:space="preserve">7.00049352645874</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">7.11900234222412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.008957862854</t>
+    <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
     <t xml:space="preserve">7.11476945877075</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">7.38987922668457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20365142822266</t>
+    <t xml:space="preserve">7.2036509513855</t>
   </si>
   <si>
     <t xml:space="preserve">7.23327875137329</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">7.17402410507202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21211671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680932998657</t>
+    <t xml:space="preserve">7.21211624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
     <t xml:space="preserve">7.432204246521</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42374038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406810760498</t>
+    <t xml:space="preserve">7.42373943328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406715393066</t>
   </si>
   <si>
     <t xml:space="preserve">7.44490146636963</t>
@@ -473,133 +473,133 @@
     <t xml:space="preserve">7.47452926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64382648468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457231521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913482666016</t>
+    <t xml:space="preserve">7.64382696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6565260887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349828720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913387298584</t>
   </si>
   <si>
     <t xml:space="preserve">7.53378248214722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229272842407</t>
+    <t xml:space="preserve">7.61843395233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880567550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6522912979126</t>
   </si>
   <si>
     <t xml:space="preserve">7.69885015487671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74540519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9316349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317056655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88930988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470432281494</t>
+    <t xml:space="preserve">7.74540567398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9147047996521</t>
   </si>
   <si>
     <t xml:space="preserve">7.95279788970947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94856548309326</t>
+    <t xml:space="preserve">7.9485650062561</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420106887817</t>
+    <t xml:space="preserve">7.70308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6141996383667</t>
   </si>
   <si>
     <t xml:space="preserve">7.42797136306763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34332227706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020837783813</t>
+    <t xml:space="preserve">7.34332275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020885467529</t>
   </si>
   <si>
     <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63536310195923</t>
+    <t xml:space="preserve">7.63536262512207</t>
   </si>
   <si>
     <t xml:space="preserve">7.73694181442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51685380935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30946350097656</t>
+    <t xml:space="preserve">7.51685476303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3094630241394</t>
   </si>
   <si>
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838851928711</t>
+    <t xml:space="preserve">7.34755563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838899612427</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01205158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707382202148</t>
+    <t xml:space="preserve">8.01205253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707286834717</t>
   </si>
   <si>
     <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27023124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40990447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45222759246826</t>
+    <t xml:space="preserve">8.27023220062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40990352630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45222663879395</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">8.23213958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30832481384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32525444030762</t>
+    <t xml:space="preserve">8.30832290649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3252534866333</t>
   </si>
   <si>
     <t xml:space="preserve">8.38027477264404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71040916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87970542907715</t>
+    <t xml:space="preserve">8.71040821075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1759786605835</t>
+    <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">9.56536483764648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98861217498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773433685303</t>
+    <t xml:space="preserve">9.98861122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.496506690979</t>
+    <t xml:space="preserve">10.4965076446533</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
@@ -680,52 +680,52 @@
     <t xml:space="preserve">10.9620771408081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191846847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884819030762</t>
+    <t xml:space="preserve">11.0551919937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884809494019</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7662448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355449676514</t>
+    <t xml:space="preserve">11.76624584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741422653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973886489868</t>
+    <t xml:space="preserve">12.6973876953125</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491868972778</t>
+    <t xml:space="preserve">13.3491878509521</t>
   </si>
   <si>
     <t xml:space="preserve">14.2633991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0156383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0517749786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111598968506</t>
+    <t xml:space="preserve">16.0156364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0517768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111589431763</t>
   </si>
   <si>
     <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443214416504</t>
+    <t xml:space="preserve">14.6443185806274</t>
   </si>
   <si>
     <t xml:space="preserve">14.0941009521484</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">14.5173454284668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009860992432</t>
+    <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243618011475</t>
+    <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761610031128</t>
+    <t xml:space="preserve">13.4761619567871</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930906295776</t>
+    <t xml:space="preserve">13.5184860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094509124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057241439819</t>
+    <t xml:space="preserve">14.0094499588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
     <t xml:space="preserve">14.348048210144</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">14.5088806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5004167556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311185836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655462265015</t>
+    <t xml:space="preserve">14.5004177093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.407301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157686233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618194580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655471801758</t>
   </si>
   <si>
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984058380127</t>
+    <t xml:space="preserve">13.9840564727783</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031341552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.782036781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397127151489</t>
+    <t xml:space="preserve">13.6031351089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397136688232</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523452758789</t>
+    <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0434169769287</t>
+    <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">13.0175714492798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3018732070923</t>
+    <t xml:space="preserve">13.301872253418</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
@@ -884,25 +884,25 @@
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812601089478</t>
+    <t xml:space="preserve">13.1812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557331085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123399734497</t>
+    <t xml:space="preserve">12.9228038787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557321548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123390197754</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277196884155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.276026725769</t>
+    <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501811981201</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8194217681885</t>
+    <t xml:space="preserve">12.9314203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8194227218628</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834280014038</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">12.035439491272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8975954055786</t>
+    <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
     <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3542013168335</t>
+    <t xml:space="preserve">12.3542003631592</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594327926636</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7855978012085</t>
+    <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166757583618</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286724090576</t>
+    <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597513198853</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">11.7769813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511367797852</t>
+    <t xml:space="preserve">11.7511377334595</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339067459106</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988086700439</t>
+    <t xml:space="preserve">12.6988077163696</t>
   </si>
   <si>
     <t xml:space="preserve">12.5006589889526</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231224060059</t>
+    <t xml:space="preserve">12.4231233596802</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661989212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.4661979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">12.8366527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8883438110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8538827896118</t>
+    <t xml:space="preserve">12.8883428573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8538837432861</t>
   </si>
   <si>
     <t xml:space="preserve">12.6471176147461</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868101119995</t>
+    <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0089559555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572639465332</t>
+    <t xml:space="preserve">13.0089569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0778779983521</t>
+    <t xml:space="preserve">13.0778770446777</t>
   </si>
   <si>
     <t xml:space="preserve">13.0951070785522</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914064407349</t>
+    <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550970077515</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289319992065</t>
+    <t xml:space="preserve">14.1289329528809</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907712936401</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">13.7240190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1547775268555</t>
+    <t xml:space="preserve">14.1547784805298</t>
   </si>
   <si>
     <t xml:space="preserve">14.3443126678467</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9393978118896</t>
+    <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
     <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1117010116577</t>
+    <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">13.7929391860962</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154026031494</t>
+    <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569473266602</t>
+    <t xml:space="preserve">13.4569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3191041946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3880243301392</t>
+    <t xml:space="preserve">13.3191032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3880252838135</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292505264282</t>
+    <t xml:space="preserve">13.6292495727539</t>
   </si>
   <si>
     <t xml:space="preserve">13.370795249939</t>
@@ -67966,7 +67966,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6781828704</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>35384</v>
@@ -67987,6 +67987,32 @@
         <v>894</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6874421296</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>5072</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="899">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414600372314</t>
+    <t xml:space="preserve">5.10414552688599</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169673919678</t>
+    <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564275741577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11659383773804</t>
+    <t xml:space="preserve">5.18713998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958925247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523591995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31163167953491</t>
+    <t xml:space="preserve">5.19958877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
     <t xml:space="preserve">5.3157811164856</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">5.34897899627686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35312843322754</t>
+    <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972713470459</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">5.41122436523438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34067916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462518692017</t>
+    <t xml:space="preserve">5.34067964553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462566375732</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259052276611</t>
+    <t xml:space="preserve">5.89259099960327</t>
   </si>
   <si>
     <t xml:space="preserve">5.71415376663208</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">5.85939359664917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97558546066284</t>
+    <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728563308716</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">5.95068693161011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653654098511</t>
+    <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599182128906</t>
@@ -146,31 +146,31 @@
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442953109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05857944488525</t>
+    <t xml:space="preserve">6.05443000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0419807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05857992172241</t>
   </si>
   <si>
     <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327360153198</t>
+    <t xml:space="preserve">6.13327312469482</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355031967163</t>
+    <t xml:space="preserve">6.47355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55239486694336</t>
+    <t xml:space="preserve">6.55239534378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">6.56069421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43205404281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994607925415</t>
+    <t xml:space="preserve">6.43205308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.5938925743103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464023590088</t>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61463975906372</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953924179077</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96321630477905</t>
+    <t xml:space="preserve">6.96321725845337</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301288604736</t>
@@ -218,25 +218,25 @@
     <t xml:space="preserve">7.12920475006104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3034930229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948099136353</t>
+    <t xml:space="preserve">7.30349349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948051452637</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67289733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1292839050293</t>
+    <t xml:space="preserve">8.6728982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
   </si>
   <si>
     <t xml:space="preserve">7.67281818389893</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3864860534668</t>
+    <t xml:space="preserve">7.38648700714111</t>
   </si>
   <si>
     <t xml:space="preserve">7.42798328399658</t>
@@ -254,34 +254,34 @@
     <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788431167603</t>
+    <t xml:space="preserve">7.22058057785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788383483887</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72961568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156755447388</t>
+    <t xml:space="preserve">6.72961521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156707763672</t>
   </si>
   <si>
     <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94123888015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617311477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202823638916</t>
+    <t xml:space="preserve">6.94123840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202919006348</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2925329208374</t>
+    <t xml:space="preserve">7.29253244400024</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676628112793</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">7.36448431015015</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941902160645</t>
+    <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23751068115234</t>
+    <t xml:space="preserve">7.23751163482666</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132640838623</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">7.06821298599243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351846694946</t>
+    <t xml:space="preserve">7.02588748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351894378662</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286159515381</t>
+    <t xml:space="preserve">7.15286207199097</t>
   </si>
   <si>
     <t xml:space="preserve">7.08514261245728</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626159667969</t>
+    <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
     <t xml:space="preserve">6.72538328170776</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84812498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621711730957</t>
+    <t xml:space="preserve">6.84812450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621759414673</t>
   </si>
   <si>
     <t xml:space="preserve">7.18672180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11053705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016485214233</t>
+    <t xml:space="preserve">7.11053657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016532897949</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937549591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974817276001</t>
+    <t xml:space="preserve">7.08937501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974769592285</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705047607422</t>
@@ -395,31 +395,31 @@
     <t xml:space="preserve">6.97086524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398010253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05551528930664</t>
+    <t xml:space="preserve">7.03858470916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012132644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0639796257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0555157661438</t>
   </si>
   <si>
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00049352645874</t>
+    <t xml:space="preserve">7.00049304962158</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11900234222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00895833969116</t>
+    <t xml:space="preserve">7.11900186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.008957862854</t>
   </si>
   <si>
     <t xml:space="preserve">7.11476945877075</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">7.38987922668457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2036509513855</t>
+    <t xml:space="preserve">7.20365142822266</t>
   </si>
   <si>
     <t xml:space="preserve">7.23327875137329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17402410507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211624145508</t>
+    <t xml:space="preserve">7.17402362823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
     <t xml:space="preserve">7.24597644805908</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42373943328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406715393066</t>
+    <t xml:space="preserve">7.42374038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406810760498</t>
   </si>
   <si>
     <t xml:space="preserve">7.44490146636963</t>
@@ -473,34 +473,34 @@
     <t xml:space="preserve">7.47452926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64382696151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6565260887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349828720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457326889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913387298584</t>
+    <t xml:space="preserve">7.64382648468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349733352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457231521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913482666016</t>
   </si>
   <si>
     <t xml:space="preserve">7.53378248214722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61843395233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6522912979126</t>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229272842407</t>
   </si>
   <si>
     <t xml:space="preserve">7.69885015487671</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">7.74540567398071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316913604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582378387451</t>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8258228302002</t>
   </si>
   <si>
     <t xml:space="preserve">7.88931035995483</t>
@@ -536,70 +536,70 @@
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6141996383667</t>
+    <t xml:space="preserve">7.70308256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420059204102</t>
   </si>
   <si>
     <t xml:space="preserve">7.42797136306763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34332275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020885467529</t>
+    <t xml:space="preserve">7.34332227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
     <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63536262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694181442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685476303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3094630241394</t>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137136459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838899612427</t>
+    <t xml:space="preserve">7.34755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137041091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838804244995</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01205253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474784851074</t>
+    <t xml:space="preserve">8.01205158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707286834717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21097755432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023220062256</t>
+    <t xml:space="preserve">8.21097850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023124694824</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">8.23213958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30832290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3252534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027477264404</t>
+    <t xml:space="preserve">8.30832481384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32525444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56536483764648</t>
+    <t xml:space="preserve">9.5653657913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.98861122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4541835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773338317871</t>
+    <t xml:space="preserve">10.4541845321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4965076446533</t>
+    <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
@@ -680,52 +680,52 @@
     <t xml:space="preserve">10.9620771408081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0551919937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884809494019</t>
+    <t xml:space="preserve">11.0551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.76624584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355440139771</t>
+    <t xml:space="preserve">11.7662448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355449676514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741422653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973876953125</t>
+    <t xml:space="preserve">12.6973886489868</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491878509521</t>
+    <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
     <t xml:space="preserve">14.2633991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0156364440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0517768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111589431763</t>
+    <t xml:space="preserve">16.0156383514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0517749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111598968506</t>
   </si>
   <si>
     <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443185806274</t>
+    <t xml:space="preserve">14.6443214416504</t>
   </si>
   <si>
     <t xml:space="preserve">14.0941009521484</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">14.5173454284668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009870529175</t>
+    <t xml:space="preserve">14.0009860992432</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243608474731</t>
+    <t xml:space="preserve">12.8243618011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761619567871</t>
+    <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
@@ -758,28 +758,28 @@
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930896759033</t>
+    <t xml:space="preserve">13.5184850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930906295776</t>
   </si>
   <si>
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094499588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057231903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.348048210144</t>
+    <t xml:space="preserve">14.0094509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3480472564697</t>
   </si>
   <si>
     <t xml:space="preserve">14.6019954681396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512065887451</t>
+    <t xml:space="preserve">14.5512075424194</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">14.5088806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5004177093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.407301902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157686233521</t>
+    <t xml:space="preserve">14.5004167556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157676696777</t>
   </si>
   <si>
     <t xml:space="preserve">14.3311195373535</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1618194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655471801758</t>
+    <t xml:space="preserve">14.1618204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655462265015</t>
   </si>
   <si>
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9840564727783</t>
+    <t xml:space="preserve">13.984058380127</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031351089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397136688232</t>
+    <t xml:space="preserve">13.6031341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.782036781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397127151489</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523462295532</t>
+    <t xml:space="preserve">13.5523452758789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.043417930603</t>
+    <t xml:space="preserve">13.0434169769287</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">13.0175714492798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.301872253418</t>
+    <t xml:space="preserve">13.3018732070923</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
@@ -884,25 +884,25 @@
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812610626221</t>
+    <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228038787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123390197754</t>
+    <t xml:space="preserve">12.9228048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557331085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123399734497</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277196884155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2760276794434</t>
+    <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501811981201</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8194227218628</t>
+    <t xml:space="preserve">12.9314193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834280014038</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">12.035439491272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8975944519043</t>
+    <t xml:space="preserve">11.8975954055786</t>
   </si>
   <si>
     <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3542003631592</t>
+    <t xml:space="preserve">12.3542013168335</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594327926636</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7855968475342</t>
+    <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166757583618</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286733627319</t>
+    <t xml:space="preserve">11.8286724090576</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597513198853</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">11.7769813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511377334595</t>
+    <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339067459106</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988077163696</t>
+    <t xml:space="preserve">12.6988086700439</t>
   </si>
   <si>
     <t xml:space="preserve">12.5006589889526</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231233596802</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3628168106079</t>
+    <t xml:space="preserve">12.4661989212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3628158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">12.8366527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8883428573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8538837432861</t>
+    <t xml:space="preserve">12.8883438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8538827896118</t>
   </si>
   <si>
     <t xml:space="preserve">12.6471176147461</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868110656738</t>
+    <t xml:space="preserve">12.5868101119995</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0089569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572649002075</t>
+    <t xml:space="preserve">13.0089559555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572639465332</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0778770446777</t>
+    <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
     <t xml:space="preserve">13.0951070785522</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914073944092</t>
+    <t xml:space="preserve">13.4914064407349</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550970077515</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289329528809</t>
+    <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907712936401</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">13.7240190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1547784805298</t>
+    <t xml:space="preserve">14.1547775268555</t>
   </si>
   <si>
     <t xml:space="preserve">14.3443126678467</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">13.939398765564</t>
+    <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
     <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.111701965332</t>
+    <t xml:space="preserve">14.1117010116577</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">13.7929391860962</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6206359863281</t>
+    <t xml:space="preserve">13.6206369400024</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154035568237</t>
+    <t xml:space="preserve">13.7154026031494</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569463729858</t>
+    <t xml:space="preserve">13.4569473266602</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3191032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3880252838135</t>
+    <t xml:space="preserve">13.3191041946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3880243301392</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292495727539</t>
+    <t xml:space="preserve">13.6292505264282</t>
   </si>
   <si>
     <t xml:space="preserve">13.370795249939</t>
@@ -2706,6 +2706,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.03999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10000038146973</t>
   </si>
 </sst>
 </file>
@@ -67992,7 +67995,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6874421296</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>5072</v>
@@ -68013,6 +68016,32 @@
         <v>888</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6911805556</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>52799</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>9.03999996185303</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>898</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="901">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414600372314</t>
+    <t xml:space="preserve">5.10414505004883</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14564275741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1165943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958925247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523639678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333232879639</t>
+    <t xml:space="preserve">5.09169626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14564228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18713998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3157811164856</t>
+    <t xml:space="preserve">5.31578063964844</t>
   </si>
   <si>
     <t xml:space="preserve">5.34482860565186</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972665786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122436523438</t>
+    <t xml:space="preserve">5.36972618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122388839722</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9340877532959</t>
+    <t xml:space="preserve">5.71000385284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93408823013306</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259052276611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71415376663208</t>
+    <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939311981201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97558498382568</t>
+    <t xml:space="preserve">5.97558450698853</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728563308716</t>
@@ -134,34 +134,34 @@
     <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95068693161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653749465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599229812622</t>
+    <t xml:space="preserve">5.95068645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442953109741</t>
+    <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0585789680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05027914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327360153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137001037598</t>
+    <t xml:space="preserve">6.05857944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05027961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19137048721313</t>
   </si>
   <si>
     <t xml:space="preserve">6.47355031967163</t>
@@ -173,115 +173,115 @@
     <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57314348220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994560241699</t>
+    <t xml:space="preserve">6.57314300537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56069421768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.432053565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804201126099</t>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804153442383</t>
   </si>
   <si>
     <t xml:space="preserve">6.61463975906372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8055272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321630477905</t>
+    <t xml:space="preserve">6.63953924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80552768707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321725845337</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301288604736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02961206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451107025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034930229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289733886719</t>
+    <t xml:space="preserve">7.02961158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451059341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920570373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349254608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67289638519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.12928581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67281675338745</t>
+    <t xml:space="preserve">7.67281770706177</t>
   </si>
   <si>
     <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4279842376709</t>
+    <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
     <t xml:space="preserve">7.36573839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16240215301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643617630005</t>
+    <t xml:space="preserve">7.16240310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634912490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
     <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788478851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356342315674</t>
+    <t xml:space="preserve">7.20788431167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356294631958</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123888015747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202871322632</t>
+    <t xml:space="preserve">6.77617311477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.992027759552</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -299,31 +299,31 @@
     <t xml:space="preserve">7.29676580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448526382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830051422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2375111579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132688522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588796615601</t>
+    <t xml:space="preserve">7.26290512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36448431015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941854476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830003738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23751068115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821298599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588891983032</t>
   </si>
   <si>
     <t xml:space="preserve">6.87351894378662</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56031656265259</t>
+    <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286159515381</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96663284301758</t>
+    <t xml:space="preserve">6.96663331985474</t>
   </si>
   <si>
     <t xml:space="preserve">6.99626111984253</t>
@@ -365,25 +365,25 @@
     <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18672132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053657531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016485214233</t>
+    <t xml:space="preserve">7.18672180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053705215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016532897949</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0936074256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937454223633</t>
+    <t xml:space="preserve">7.09360790252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
     <t xml:space="preserve">7.05974769592285</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">6.97086572647095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858518600464</t>
+    <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012037277222</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">7.06398057937622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05551528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09784030914307</t>
+    <t xml:space="preserve">7.0555157661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
     <t xml:space="preserve">7.0004940032959</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">7.11900234222412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00895833969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207223892212</t>
+    <t xml:space="preserve">7.008957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476898193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207319259644</t>
   </si>
   <si>
     <t xml:space="preserve">7.38987970352173</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">7.20365142822266</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23327875137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40681076049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43220376968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992370605469</t>
+    <t xml:space="preserve">7.23327922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402410507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.432204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373991012573</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">7.38141536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28406810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490146636963</t>
+    <t xml:space="preserve">7.28406763076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490194320679</t>
   </si>
   <si>
     <t xml:space="preserve">7.39834499359131</t>
@@ -473,73 +473,73 @@
     <t xml:space="preserve">7.47452926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64382696151733</t>
+    <t xml:space="preserve">7.64382791519165</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6565260887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7834997177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378295898438</t>
+    <t xml:space="preserve">7.65652513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378248214722</t>
   </si>
   <si>
     <t xml:space="preserve">7.61843299865723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58880519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6522912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69884967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814832687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163537979126</t>
+    <t xml:space="preserve">7.58880567550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540662765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163442611694</t>
   </si>
   <si>
     <t xml:space="preserve">7.92317008972168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82582330703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88931083679199</t>
+    <t xml:space="preserve">7.82582378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931035995483</t>
   </si>
   <si>
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9485650062561</t>
+    <t xml:space="preserve">7.95279788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856595993042</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420011520386</t>
+    <t xml:space="preserve">7.70308113098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6141996383667</t>
   </si>
   <si>
     <t xml:space="preserve">7.42797136306763</t>
@@ -548,31 +548,31 @@
     <t xml:space="preserve">7.34332227706909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25020885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45759963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536214828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3094630241394</t>
+    <t xml:space="preserve">7.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45760011672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694276809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30946254730225</t>
   </si>
   <si>
     <t xml:space="preserve">7.4025764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137136459351</t>
+    <t xml:space="preserve">7.34755563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137184143066</t>
   </si>
   <si>
     <t xml:space="preserve">7.21634864807129</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01205158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474975585938</t>
+    <t xml:space="preserve">8.01205253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707286834717</t>
@@ -596,31 +596,31 @@
     <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27023124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40990447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45222759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40567016601562</t>
+    <t xml:space="preserve">8.27023315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40990352630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45222663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
     <t xml:space="preserve">8.26599979400635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23213958740234</t>
+    <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3252534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027572631836</t>
+    <t xml:space="preserve">8.32525444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027667999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11672401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01514434814453</t>
+    <t xml:space="preserve">9.11672496795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01514625549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.998215675354</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56536483764648</t>
+    <t xml:space="preserve">9.29448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5653657913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.98861122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4541826248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773338317871</t>
+    <t xml:space="preserve">10.4541835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4965076446533</t>
+    <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451484680176</t>
+    <t xml:space="preserve">10.9451475143433</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884819030762</t>
+    <t xml:space="preserve">11.5884809494019</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7662467956543</t>
+    <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
     <t xml:space="preserve">11.9355440139771</t>
@@ -704,43 +704,43 @@
     <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3491888046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.051775932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111589431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460294723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443185806274</t>
+    <t xml:space="preserve">12.6973876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629590988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3491878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0517778396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443204879761</t>
   </si>
   <si>
     <t xml:space="preserve">14.0941009521484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173454284668</t>
+    <t xml:space="preserve">14.5173463821411</t>
   </si>
   <si>
     <t xml:space="preserve">14.0009880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1206331253052</t>
+    <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
     <t xml:space="preserve">12.8243608474731</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">13.4761619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338359832764</t>
+    <t xml:space="preserve">13.4338369369507</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184850692749</t>
+    <t xml:space="preserve">13.5184869766235</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7639694213867</t>
+    <t xml:space="preserve">13.7639675140381</t>
   </si>
   <si>
     <t xml:space="preserve">14.0094509124756</t>
@@ -776,58 +776,58 @@
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.601996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512075424194</t>
+    <t xml:space="preserve">14.348048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004177093506</t>
+    <t xml:space="preserve">14.5088806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
     <t xml:space="preserve">14.4073028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4157695770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311185836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655462265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840574264526</t>
+    <t xml:space="preserve">14.4157686233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978267669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.984055519104</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385721206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031341552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290998458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.782036781311</t>
+    <t xml:space="preserve">13.7385730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031351089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820377349854</t>
   </si>
   <si>
     <t xml:space="preserve">12.7397127151489</t>
@@ -839,34 +839,34 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523452758789</t>
+    <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423017501831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.543098449707</t>
+    <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0434169769287</t>
+    <t xml:space="preserve">13.0348024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397172927856</t>
+    <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175704956055</t>
+    <t xml:space="preserve">13.0175714492798</t>
   </si>
   <si>
     <t xml:space="preserve">13.301872253418</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2243375778198</t>
+    <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812610626221</t>
@@ -893,49 +893,49 @@
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
+    <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557321548462</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123380661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277177810669</t>
+    <t xml:space="preserve">13.1123390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277196884155</t>
   </si>
   <si>
     <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501821517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0606479644775</t>
+    <t xml:space="preserve">13.2501811981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
     <t xml:space="preserve">12.9314203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8194217681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4834289550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2335872650146</t>
+    <t xml:space="preserve">12.8194227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4834280014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0354375839233</t>
+    <t xml:space="preserve">12.035439491272</t>
   </si>
   <si>
     <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474370956421</t>
+    <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114433288574</t>
+    <t xml:space="preserve">11.7166757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286733627319</t>
@@ -974,31 +974,31 @@
     <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8200578689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7769823074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7511367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6046772003174</t>
+    <t xml:space="preserve">11.8200588226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7769813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7511377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339067459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182075500488</t>
+    <t xml:space="preserve">12.0182085037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785140991211</t>
+    <t xml:space="preserve">12.0785150527954</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157211303711</t>
+    <t xml:space="preserve">12.0871286392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157220840454</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.500659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815776824951</t>
+    <t xml:space="preserve">12.6988077163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5006589889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
     <t xml:space="preserve">12.7591152191162</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231224060059</t>
+    <t xml:space="preserve">12.4231233596802</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
+    <t xml:space="preserve">12.5265054702759</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.836651802063</t>
+    <t xml:space="preserve">12.8366527557373</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883428573608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8538827896118</t>
+    <t xml:space="preserve">12.8538837432861</t>
   </si>
   <si>
     <t xml:space="preserve">12.6471176147461</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7505016326904</t>
+    <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7246541976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935771942139</t>
+    <t xml:space="preserve">12.7246561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935752868652</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917259216309</t>
+    <t xml:space="preserve">12.8711128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089569091797</t>
@@ -1109,22 +1109,22 @@
     <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520315170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0778779983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0951080322266</t>
+    <t xml:space="preserve">13.0520324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0778770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0951070785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984891891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2674121856689</t>
+    <t xml:space="preserve">13.1984901428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914073944092</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757091522217</t>
+    <t xml:space="preserve">13.7757081985474</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843246459961</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289319992065</t>
+    <t xml:space="preserve">14.1289329528809</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907712936401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166177749634</t>
+    <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
     <t xml:space="preserve">14.2150850296021</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255517959595</t>
+    <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
     <t xml:space="preserve">13.939398765564</t>
@@ -1181,37 +1181,37 @@
     <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1117010116577</t>
+    <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5517139434814</t>
+    <t xml:space="preserve">13.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206359863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
     <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8187856674194</t>
+    <t xml:space="preserve">13.8187866210938</t>
   </si>
   <si>
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360147476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8015546798706</t>
+    <t xml:space="preserve">13.8704767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360157012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">13.4569463729858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.612021446228</t>
+    <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
     <t xml:space="preserve">13.3535642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.405255317688</t>
+    <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">13.6292495727539</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3707942962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2846431732178</t>
+    <t xml:space="preserve">13.370795249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603294372559</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5775594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258684158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693737030029</t>
+    <t xml:space="preserve">13.9693746566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278635025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4219026565552</t>
+    <t xml:space="preserve">13.5278644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4219017028809</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
+    <t xml:space="preserve">13.0686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
     <t xml:space="preserve">14.2872629165649</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985069274902</t>
+    <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1394,22 +1394,22 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452993392944</t>
+    <t xml:space="preserve">13.351261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452983856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.174656867981</t>
+    <t xml:space="preserve">13.2276372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1746578216553</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157127380371</t>
+    <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980525970459</t>
+    <t xml:space="preserve">12.9980535507202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391094207764</t>
+    <t xml:space="preserve">12.8391103744507</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099771499634</t>
+    <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.2673349380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4262762069702</t>
+    <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
     <t xml:space="preserve">11.0377492904663</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0730686187744</t>
+    <t xml:space="preserve">10.9317874908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
     <t xml:space="preserve">11.2849950790405</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496728897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728424072266</t>
+    <t xml:space="preserve">11.2496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547298431396</t>
+    <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299152374268</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1370687484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7198619842529</t>
+    <t xml:space="preserve">9.53661441802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1370677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7198629379272</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551822662354</t>
+    <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
+    <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902772903442</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.5079374313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5785779953003</t>
+    <t xml:space="preserve">10.5785789489746</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375211715698</t>
+    <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258247375488</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609178543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606916427612</t>
+    <t xml:space="preserve">10.5609188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432567596436</t>
+    <t xml:space="preserve">10.5432577133179</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019746780396</t>
+    <t xml:space="preserve">10.4019756317139</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">10.84348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8964653015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554094314575</t>
+    <t xml:space="preserve">10.896466255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554103851318</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -2712,6 +2712,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.10000038146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14000034332275</t>
   </si>
 </sst>
 </file>
@@ -68050,7 +68053,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6912384259</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>6780</v>
@@ -68071,6 +68074,32 @@
         <v>895</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911921296</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>8529</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>900</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -56,16 +56,16 @@
     <t xml:space="preserve">5.18713998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659479141235</t>
+    <t xml:space="preserve">5.1165943145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523544311523</t>
+    <t xml:space="preserve">5.19958925247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
     <t xml:space="preserve">5.30333137512207</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122388839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48176908493042</t>
+    <t xml:space="preserve">5.36972665786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462518692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48176956176758</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93408823013306</t>
+    <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259052276611</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">5.85939311981201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97558450698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96728563308716</t>
+    <t xml:space="preserve">5.97558498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96728610992432</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">5.95068645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599182128906</t>
+    <t xml:space="preserve">5.94653654098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599229812622</t>
   </si>
   <si>
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05443000793457</t>
+    <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">6.13327407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19137048721313</t>
+    <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
     <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239486694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57314300537109</t>
+    <t xml:space="preserve">6.36150789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239534378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
     <t xml:space="preserve">6.56069421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.432053565979</t>
+    <t xml:space="preserve">6.43205308914185</t>
   </si>
   <si>
     <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59389209747314</t>
+    <t xml:space="preserve">6.5938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">6.58559274673462</t>
@@ -197,19 +197,19 @@
     <t xml:space="preserve">6.61463975906372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63953924179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80552768707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321725845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961158752441</t>
+    <t xml:space="preserve">6.63953876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8055272102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301336288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
   </si>
   <si>
     <t xml:space="preserve">7.05451059341431</t>
@@ -218,22 +218,22 @@
     <t xml:space="preserve">7.12920570373535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30349254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948146820068</t>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948194503784</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67289638519287</t>
+    <t xml:space="preserve">8.67289733886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.12928581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67281770706177</t>
+    <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
     <t xml:space="preserve">7.3864860534668</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36573839187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634912490845</t>
+    <t xml:space="preserve">7.36573886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240215301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634960174561</t>
   </si>
   <si>
     <t xml:space="preserve">7.43643712997437</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">7.20788431167603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89468145370483</t>
+    <t xml:space="preserve">6.89468193054199</t>
   </si>
   <si>
     <t xml:space="preserve">6.72961521148682</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.992027759552</t>
+    <t xml:space="preserve">6.99202871322632</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">7.37295007705688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27983617782593</t>
+    <t xml:space="preserve">7.27983665466309</t>
   </si>
   <si>
     <t xml:space="preserve">7.2925329208374</t>
@@ -299,40 +299,40 @@
     <t xml:space="preserve">7.29676580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448431015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941854476929</t>
+    <t xml:space="preserve">7.26290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523014068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3644847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941902160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830003738403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23751068115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132640838623</t>
+    <t xml:space="preserve">7.23751163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
     <t xml:space="preserve">7.06821298599243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588891983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351894378662</t>
+    <t xml:space="preserve">7.02588796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351942062378</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027303695679</t>
+    <t xml:space="preserve">6.45027256011963</t>
   </si>
   <si>
     <t xml:space="preserve">6.67036104202271</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286159515381</t>
+    <t xml:space="preserve">7.15286207199097</t>
   </si>
   <si>
     <t xml:space="preserve">7.08514213562012</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">6.96663331985474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626111984253</t>
+    <t xml:space="preserve">6.99626064300537</t>
   </si>
   <si>
     <t xml:space="preserve">6.72538328170776</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016532897949</t>
+    <t xml:space="preserve">7.05128288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">7.09360790252686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937501907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086572647095</t>
+    <t xml:space="preserve">7.08937454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04704999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086524963379</t>
   </si>
   <si>
     <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03012037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398010253906</t>
   </si>
   <si>
     <t xml:space="preserve">7.0555157661438</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435277938843</t>
+    <t xml:space="preserve">7.00049352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435325622559</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900234222412</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">7.008957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207319259644</t>
+    <t xml:space="preserve">7.11476945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
     <t xml:space="preserve">7.38987970352173</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">7.24597644805908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40680932998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.432204246521</t>
+    <t xml:space="preserve">7.40680980682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43220376968384</t>
   </si>
   <si>
     <t xml:space="preserve">7.49992322921753</t>
@@ -470,49 +470,49 @@
     <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382791519165</t>
+    <t xml:space="preserve">7.47452831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382696151733</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65652513504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349924087524</t>
+    <t xml:space="preserve">7.6565260887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349876403809</t>
   </si>
   <si>
     <t xml:space="preserve">7.58457326889038</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913387298584</t>
+    <t xml:space="preserve">7.44913482666016</t>
   </si>
   <si>
     <t xml:space="preserve">7.53378248214722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229225158691</t>
+    <t xml:space="preserve">7.61843395233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880472183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6522912979126</t>
   </si>
   <si>
     <t xml:space="preserve">7.69885015487671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74540662765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
+    <t xml:space="preserve">7.74540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163537979126</t>
   </si>
   <si>
     <t xml:space="preserve">7.92317008972168</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856595993042</t>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856548309326</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308113098145</t>
+    <t xml:space="preserve">7.70308208465576</t>
   </si>
   <si>
     <t xml:space="preserve">7.6141996383667</t>
@@ -545,25 +545,25 @@
     <t xml:space="preserve">7.42797136306763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34332227706909</t>
+    <t xml:space="preserve">7.34332370758057</t>
   </si>
   <si>
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45760011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694276809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685380935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30946254730225</t>
+    <t xml:space="preserve">7.45759868621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536214828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
     <t xml:space="preserve">7.4025764465332</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">7.34755563735962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27137184143066</t>
+    <t xml:space="preserve">7.27137136459351</t>
   </si>
   <si>
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50838899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702934265137</t>
+    <t xml:space="preserve">7.50838851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702981948853</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205253601074</t>
@@ -590,49 +590,49 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097755432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023315429688</t>
+    <t xml:space="preserve">8.06707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023220062256</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599979400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23214054107666</t>
+    <t xml:space="preserve">8.26600074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23213958740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32525444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027667999268</t>
+    <t xml:space="preserve">8.3252534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.87970733642578</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514625549316</t>
+    <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
     <t xml:space="preserve">8.998215675354</t>
@@ -641,22 +641,22 @@
     <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02361011505127</t>
+    <t xml:space="preserve">9.02360916137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17597961425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29448890686035</t>
+    <t xml:space="preserve">9.1759786605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
     <t xml:space="preserve">9.5653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98861122131348</t>
+    <t xml:space="preserve">9.98861217498779</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541835784912</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">9.71773433685303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1325159072876</t>
+    <t xml:space="preserve">10.1325149536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451475143433</t>
+    <t xml:space="preserve">10.9451484680176</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
@@ -719,25 +719,25 @@
     <t xml:space="preserve">16.0156364440918</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0517778396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443204879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173463821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009880065918</t>
+    <t xml:space="preserve">14.051775932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460294723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0940999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761619567871</t>
+    <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184869766235</t>
+    <t xml:space="preserve">13.5184860229492</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7639675140381</t>
+    <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
     <t xml:space="preserve">14.0094509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3057231903076</t>
+    <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
     <t xml:space="preserve">14.348048210144</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">14.6019954681396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512065887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596723556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088806152344</t>
+    <t xml:space="preserve">14.5512056350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088815689087</t>
   </si>
   <si>
     <t xml:space="preserve">14.5004167556763</t>
@@ -800,37 +800,37 @@
     <t xml:space="preserve">14.4157686233521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978267669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.984055519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994073867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385730743408</t>
+    <t xml:space="preserve">14.3311176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618194580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655462265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978277206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385721206665</t>
   </si>
   <si>
     <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397127151489</t>
+    <t xml:space="preserve">13.1290988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.782036781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397136688232</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175714492798</t>
+    <t xml:space="preserve">13.0175704956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.301872253418</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557321548462</t>
+    <t xml:space="preserve">12.6557312011719</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123390197754</t>
@@ -908,22 +908,22 @@
     <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501811981201</t>
+    <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314203262329</t>
+    <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834280014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.233588218689</t>
+    <t xml:space="preserve">12.4834289550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2335872650146</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369693756104</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474361419678</t>
+    <t xml:space="preserve">12.1474351882935</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597513198853</t>
+    <t xml:space="preserve">11.7597522735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769813537598</t>
+    <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511377334595</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182085037231</t>
+    <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785150527954</t>
+    <t xml:space="preserve">12.0785160064697</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157220840454</t>
+    <t xml:space="preserve">12.0871295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
@@ -1019,19 +1019,19 @@
     <t xml:space="preserve">12.6988077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591152191162</t>
+    <t xml:space="preserve">12.7591161727905</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231233596802</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">12.4661979675293</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628168106079</t>
+    <t xml:space="preserve">12.3628158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265054702759</t>
+    <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141893386841</t>
+    <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
     <t xml:space="preserve">12.8366527557373</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">12.8883428573608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8538837432861</t>
+    <t xml:space="preserve">12.8538827896118</t>
   </si>
   <si>
     <t xml:space="preserve">12.6471176147461</t>
@@ -1076,19 +1076,19 @@
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868110656738</t>
+    <t xml:space="preserve">12.5868120193481</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
+    <t xml:space="preserve">12.6126565933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8711128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917249679565</t>
+    <t xml:space="preserve">12.871111869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917259216309</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089569091797</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0778770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0951070785522</t>
+    <t xml:space="preserve">13.0778779983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0951080322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2674112319946</t>
+    <t xml:space="preserve">13.2674121856689</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550970077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7757081985474</t>
+    <t xml:space="preserve">13.6550960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7757091522217</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843246459961</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8618612289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240190505981</t>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8618621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240180969238</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547784805298</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.844630241394</t>
+    <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.111701965332</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929391860962</t>
+    <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206359863281</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292495727539</t>
+    <t xml:space="preserve">13.6292505264282</t>
   </si>
   <si>
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846422195435</t>
+    <t xml:space="preserve">13.2846431732178</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603294372559</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775594711304</t>
+    <t xml:space="preserve">13.5775604248047</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5086393356323</t>
+    <t xml:space="preserve">13.508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693746566772</t>
+    <t xml:space="preserve">13.9693737030029</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4219017028809</t>
+    <t xml:space="preserve">13.5278635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4219026565552</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402433395386</t>
+    <t xml:space="preserve">13.0686960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402423858643</t>
   </si>
   <si>
     <t xml:space="preserve">14.2872629165649</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985059738159</t>
+    <t xml:space="preserve">13.5985069274902</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1394,22 +1394,22 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452983856201</t>
+    <t xml:space="preserve">13.3512601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452993392944</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1746578216553</t>
+    <t xml:space="preserve">13.2276382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157136917114</t>
+    <t xml:space="preserve">13.0157127380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980535507202</t>
+    <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391103744507</t>
+    <t xml:space="preserve">12.8391094207764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099781036377</t>
+    <t xml:space="preserve">13.2099771499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2386560440063</t>
+    <t xml:space="preserve">12.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379764556885</t>
+    <t xml:space="preserve">11.267333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379755020142</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4262771606445</t>
+    <t xml:space="preserve">11.4262762069702</t>
   </si>
   <si>
     <t xml:space="preserve">11.0377492904663</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317874908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0730695724487</t>
+    <t xml:space="preserve">10.9317865371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0730686187744</t>
   </si>
   <si>
     <t xml:space="preserve">11.2849950790405</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728433609009</t>
+    <t xml:space="preserve">11.2496728897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549560546875</t>
+    <t xml:space="preserve">10.4549551010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
+    <t xml:space="preserve">10.1547298431396</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299152374268</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53661441802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7198629379272</t>
+    <t xml:space="preserve">9.5366153717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1370687484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551832199097</t>
+    <t xml:space="preserve">10.7551822662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2430305480957</t>
+    <t xml:space="preserve">10.24303150177</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902772903442</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.5079374313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5785789489746</t>
+    <t xml:space="preserve">10.5785779953003</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375221252441</t>
+    <t xml:space="preserve">10.7375211715698</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258247375488</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606906890869</t>
+    <t xml:space="preserve">10.5609178543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019756317139</t>
+    <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">10.84348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.896466255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554103851318</t>
+    <t xml:space="preserve">10.8964653015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -68079,7 +68079,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6911921296</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>8529</v>
@@ -68100,6 +68100,32 @@
         <v>900</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6911342593</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>14994</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>897</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414505004883</t>
+    <t xml:space="preserve">5.10414600372314</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394163131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169626235962</t>
+    <t xml:space="preserve">5.1539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169673919678</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16224145889282</t>
+    <t xml:space="preserve">5.16224098205566</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333089828491</t>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38632535934448</t>
+    <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
     <t xml:space="preserve">5.3489785194397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35312795639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972713470459</t>
+    <t xml:space="preserve">5.35312747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972665786743</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122388839722</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462566375732</t>
+    <t xml:space="preserve">5.39462518692017</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176956176758</t>
+    <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000337600708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9340877532959</t>
+    <t xml:space="preserve">5.93408823013306</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259099960327</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558498382568</t>
+    <t xml:space="preserve">5.85939264297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558450698853</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728563308716</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87599229812622</t>
+    <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
     <t xml:space="preserve">5.86769247055054</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05027961730957</t>
+    <t xml:space="preserve">6.05028009414673</t>
   </si>
   <si>
     <t xml:space="preserve">6.13327360153198</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36150789260864</t>
+    <t xml:space="preserve">6.47355079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36150884628296</t>
   </si>
   <si>
     <t xml:space="preserve">6.55239486694336</t>
@@ -182,67 +182,67 @@
     <t xml:space="preserve">6.43205308914185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53994607925415</t>
+    <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.5938925743103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559274673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953924179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80552673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321678161621</t>
+    <t xml:space="preserve">6.58559322357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804105758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953828811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8055272102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301336288452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02961158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05450963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920475006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948146820068</t>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920522689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948099136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6728982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648653030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573839187622</t>
+    <t xml:space="preserve">8.67289638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928676605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281770706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4279842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573934555054</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240262985229</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643712997437</t>
+    <t xml:space="preserve">7.43643665313721</t>
   </si>
   <si>
     <t xml:space="preserve">7.22058057785034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788383483887</t>
+    <t xml:space="preserve">7.20788431167603</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
@@ -266,37 +266,37 @@
     <t xml:space="preserve">6.72961521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356342315674</t>
+    <t xml:space="preserve">6.80156755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356294631958</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202919006348</t>
+    <t xml:space="preserve">6.77617311477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37294960021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676628112793</t>
+    <t xml:space="preserve">7.37295007705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676532745361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290559768677</t>
@@ -305,28 +305,28 @@
     <t xml:space="preserve">7.30523061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36448431015015</t>
+    <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
     <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28830051422119</t>
+    <t xml:space="preserve">7.28830003738403</t>
   </si>
   <si>
     <t xml:space="preserve">7.23751163482666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16132640838623</t>
+    <t xml:space="preserve">7.16132736206055</t>
   </si>
   <si>
     <t xml:space="preserve">7.06821298599243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351894378662</t>
+    <t xml:space="preserve">7.02588796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351942062378</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67036104202271</t>
+    <t xml:space="preserve">6.67036151885986</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
@@ -344,52 +344,52 @@
     <t xml:space="preserve">7.15286207199097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08514261245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96663284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99626111984253</t>
+    <t xml:space="preserve">7.08514213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96663331985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99626064300537</t>
   </si>
   <si>
     <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77194023132324</t>
+    <t xml:space="preserve">6.77193975448608</t>
   </si>
   <si>
     <t xml:space="preserve">6.84812450408936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621759414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053657531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016532897949</t>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1105375289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0936074256897</t>
+    <t xml:space="preserve">7.09360694885254</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705047607422</t>
+    <t xml:space="preserve">7.05974817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04704999923706</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086524963379</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03012132644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0639796257019</t>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398057937622</t>
   </si>
   <si>
     <t xml:space="preserve">7.0555157661438</t>
@@ -410,196 +410,196 @@
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00049304962158</t>
+    <t xml:space="preserve">7.00049352645874</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11900186538696</t>
+    <t xml:space="preserve">7.11900234222412</t>
   </si>
   <si>
     <t xml:space="preserve">7.008957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476945877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327875137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402362823486</t>
+    <t xml:space="preserve">7.11476898193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207223892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987970352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402458190918</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597644805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680980682373</t>
+    <t xml:space="preserve">7.24597692489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680932998657</t>
   </si>
   <si>
     <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49992322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42374038696289</t>
+    <t xml:space="preserve">7.49992370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373895645142</t>
   </si>
   <si>
     <t xml:space="preserve">7.38141441345215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28406810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490146636963</t>
+    <t xml:space="preserve">7.28406763076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490194320679</t>
   </si>
   <si>
     <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382648468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005571365356</t>
+    <t xml:space="preserve">7.47452831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005619049072</t>
   </si>
   <si>
     <t xml:space="preserve">7.65652465820312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457231521606</t>
+    <t xml:space="preserve">7.78349924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457374572754</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913482666016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53378248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
+    <t xml:space="preserve">7.53378343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843252182007</t>
   </si>
   <si>
     <t xml:space="preserve">7.58880615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229272842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88931035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9147047996521</t>
+    <t xml:space="preserve">7.65229225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8681492805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9316349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88930988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470623016357</t>
   </si>
   <si>
     <t xml:space="preserve">7.95279788970947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9485650062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332227706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020837783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45759963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685380935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30946350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40257692337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137041091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838804244995</t>
+    <t xml:space="preserve">7.94856452941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332370758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45760011672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694133758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3094630241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40257740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01205158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474880218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40990352630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45222759246826</t>
+    <t xml:space="preserve">8.01205253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474975585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097755432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023220062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40990257263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45222663879395</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
@@ -608,28 +608,28 @@
     <t xml:space="preserve">8.26599979400635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30832481384277</t>
+    <t xml:space="preserve">8.23214054107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
     <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027572631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040821075439</t>
+    <t xml:space="preserve">8.38027477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040916442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11672496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01514530181885</t>
+    <t xml:space="preserve">9.11672401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01514434814453</t>
   </si>
   <si>
     <t xml:space="preserve">8.998215675354</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290924072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17597961425781</t>
+    <t xml:space="preserve">9.19290828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5653657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861122131348</t>
+    <t xml:space="preserve">9.56536483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861217498779</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541845321655</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773433685303</t>
+    <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396213531494</t>
+    <t xml:space="preserve">9.90396118164062</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927799224854</t>
+    <t xml:space="preserve">10.7927808761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">10.9620771408081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191846847534</t>
+    <t xml:space="preserve">11.0551919937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">11.7662448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355449676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973886489868</t>
+    <t xml:space="preserve">11.9355459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741413116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973876953125</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2633991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0517749786377</t>
+    <t xml:space="preserve">14.2634000778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111598968506</t>
@@ -725,46 +725,46 @@
     <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009860992432</t>
+    <t xml:space="preserve">14.6443195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0940999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173473358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4169073104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438804626465</t>
+    <t xml:space="preserve">12.8243608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4169063568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.433837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438795089722</t>
   </si>
   <si>
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930906295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7639684677124</t>
+    <t xml:space="preserve">13.5184860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.493091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7639694213867</t>
   </si>
   <si>
     <t xml:space="preserve">14.0094509124756</t>
@@ -773,58 +773,58 @@
     <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480472564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596723556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004167556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618204116821</t>
+    <t xml:space="preserve">14.3480491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512065887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157686233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
     <t xml:space="preserve">13.8655462265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7978277206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.984058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994073867798</t>
+    <t xml:space="preserve">13.7978267669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994083404541</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031341552734</t>
+    <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.782036781311</t>
+    <t xml:space="preserve">12.7820377349854</t>
   </si>
   <si>
     <t xml:space="preserve">12.7397127151489</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523452758789</t>
+    <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5430994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2071056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0348024368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0434169769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.940034866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397163391113</t>
+    <t xml:space="preserve">13.543098449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.207106590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0348014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.043417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9400339126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397172927856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
@@ -890,52 +890,52 @@
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
+    <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123399734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277196884155</t>
+    <t xml:space="preserve">13.1123380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277177810669</t>
   </si>
   <si>
     <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501811981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0606470108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9314193725586</t>
+    <t xml:space="preserve">13.2501821517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0606479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9314203262329</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834280014038</t>
+    <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.035439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474361419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3542013168335</t>
+    <t xml:space="preserve">12.3369703292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0354385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3542003631592</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594327926636</t>
@@ -953,34 +953,34 @@
     <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8372888565063</t>
+    <t xml:space="preserve">11.837287902832</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166757583618</t>
+    <t xml:space="preserve">11.7166767120361</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286724090576</t>
+    <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8200588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7769813537598</t>
+    <t xml:space="preserve">11.8200578689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339067459106</t>
+    <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
@@ -989,49 +989,49 @@
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182085037231</t>
+    <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785150527954</t>
+    <t xml:space="preserve">12.0785140991211</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0440530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0871286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157220840454</t>
+    <t xml:space="preserve">12.0440540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0871295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5006589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815786361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7591152191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7160396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4231224060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4920444488525</t>
+    <t xml:space="preserve">12.6988096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.500659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815776824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7591161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7160406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4231233596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4920434951782</t>
   </si>
   <si>
     <t xml:space="preserve">12.4661989212036</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265054702759</t>
+    <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8366527557373</t>
+    <t xml:space="preserve">12.8366508483887</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883438110352</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7505006790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868101119995</t>
+    <t xml:space="preserve">12.7504997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7246561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
+    <t xml:space="preserve">12.7246541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917249679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089559555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520324707031</t>
+    <t xml:space="preserve">12.9917268753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520315170288</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0951070785522</t>
+    <t xml:space="preserve">13.0951080322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914064407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6550970077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7757081985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843246459961</t>
+    <t xml:space="preserve">13.4914073944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6550960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.775710105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843236923218</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
@@ -1145,28 +1145,28 @@
     <t xml:space="preserve">14.4907712936401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8618612289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1547775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443126678467</t>
+    <t xml:space="preserve">14.5166177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8618621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240180969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1547784805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.844630241394</t>
+    <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.1117010116577</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">13.7929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
+    <t xml:space="preserve">13.6637115478516</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1205,22 +1205,22 @@
     <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8360157012939</t>
+    <t xml:space="preserve">13.8360147476196</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7326326370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154026031494</t>
+    <t xml:space="preserve">13.7326335906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569473266602</t>
+    <t xml:space="preserve">13.4569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1229,52 +1229,52 @@
     <t xml:space="preserve">13.3535642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4052562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3191041946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3880243301392</t>
+    <t xml:space="preserve">13.405255317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3191032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3880252838135</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292505264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.370795249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2846422195435</t>
+    <t xml:space="preserve">13.6292514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3707942962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2846431732178</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3363332748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5775594711304</t>
+    <t xml:space="preserve">13.3363342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5775604248047</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5086393356323</t>
+    <t xml:space="preserve">13.5086374282837</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693746566772</t>
+    <t xml:space="preserve">13.8634128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693756103516</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340543746948</t>
+    <t xml:space="preserve">13.9340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
@@ -1295,31 +1295,31 @@
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219017028809</t>
+    <t xml:space="preserve">13.4219026565552</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982797622681</t>
+    <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686950683594</t>
+    <t xml:space="preserve">13.0686941146851</t>
   </si>
   <si>
     <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0046949386597</t>
+    <t xml:space="preserve">14.004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870347976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8457527160645</t>
+    <t xml:space="preserve">13.9870357513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8457517623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8104314804077</t>
+    <t xml:space="preserve">13.810432434082</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338262557983</t>
+    <t xml:space="preserve">13.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.6691484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
+    <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
+    <t xml:space="preserve">13.2276382446289</t>
   </si>
   <si>
     <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1746578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629594802856</t>
+    <t xml:space="preserve">13.174656867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629585266113</t>
   </si>
   <si>
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095247268677</t>
+    <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
     <t xml:space="preserve">12.5035619735718</t>
@@ -1424,22 +1424,22 @@
     <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3159399032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9097509384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0333738327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1569967269897</t>
+    <t xml:space="preserve">13.3159408569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9097499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1569957733154</t>
   </si>
   <si>
     <t xml:space="preserve">13.2099781036377</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.121675491333</t>
+    <t xml:space="preserve">13.1216764450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037891387939</t>
+    <t xml:space="preserve">12.8567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037881851196</t>
   </si>
   <si>
     <t xml:space="preserve">12.2386560440063</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379764556885</t>
+    <t xml:space="preserve">11.267333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379755020142</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790323257446</t>
+    <t xml:space="preserve">11.1790313720703</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
@@ -1493,34 +1493,34 @@
     <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0024280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143526077271</t>
+    <t xml:space="preserve">11.0024271011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143535614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317874908447</t>
+    <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494476318359</t>
+    <t xml:space="preserve">10.9494466781616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299152374268</t>
+    <t xml:space="preserve">10.154727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
     <t xml:space="preserve">9.44831275939941</t>
@@ -1586,37 +1586,37 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53661441802979</t>
+    <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198629379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966924667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551832199097</t>
+    <t xml:space="preserve">10.7198619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551822662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2783517837524</t>
+    <t xml:space="preserve">10.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785789489746</t>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785779953003</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8258247375488</t>
+    <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3313331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.3313322067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019756317139</t>
+    <t xml:space="preserve">10.4019737243652</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.84348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.896466255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141263961792</t>
+    <t xml:space="preserve">10.8434839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8964653015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141254425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.0554103851318</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069110870361</t>
+    <t xml:space="preserve">10.7069101333618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027923583984</t>
+    <t xml:space="preserve">9.84669780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846300125122</t>
+    <t xml:space="preserve">10.0663261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846290588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578388214111</t>
+    <t xml:space="preserve">10.139536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578397750854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055847167969</t>
+    <t xml:space="preserve">10.5055837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5238876342773</t>
+    <t xml:space="preserve">10.523886680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5604915618896</t>
+    <t xml:space="preserve">10.560492515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716335296631</t>
+    <t xml:space="preserve">10.8716325759888</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899354934692</t>
+    <t xml:space="preserve">10.6703062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899345397949</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193794250488</t>
+    <t xml:space="preserve">11.2193784713745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533306121826</t>
+    <t xml:space="preserve">11.1644716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252140045166</t>
+    <t xml:space="preserve">10.7252130508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944842338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461687088013</t>
+    <t xml:space="preserve">10.9448432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608589172363</t>
+    <t xml:space="preserve">8.23608493804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550094604492</t>
+    <t xml:space="preserve">8.17202663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550142288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234292984009</t>
+    <t xml:space="preserve">6.01234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00982332229614</t>
+    <t xml:space="preserve">7.0098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558013916016</t>
+    <t xml:space="preserve">7.055579662323</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531558990479</t>
+    <t xml:space="preserve">7.41247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531511306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568677902222</t>
+    <t xml:space="preserve">7.48568725585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038034439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303308486938</t>
+    <t xml:space="preserve">6.68038082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229118347168</t>
+    <t xml:space="preserve">7.52229166030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364643096924</t>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364547729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818161010742</t>
+    <t xml:space="preserve">8.96818256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62043571472168</t>
+    <t xml:space="preserve">8.620436668396</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003803253174</t>
+    <t xml:space="preserve">7.7968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003755569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6321063041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361755371094</t>
+    <t xml:space="preserve">7.77852535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63210582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236180305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642868041992</t>
+    <t xml:space="preserve">7.04642820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340475082397</t>
+    <t xml:space="preserve">6.86340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3509373664856</t>
+    <t xml:space="preserve">6.46075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35093688964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130807876587</t>
+    <t xml:space="preserve">6.02149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242116928101</t>
+    <t xml:space="preserve">5.47242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279235839844</t>
+    <t xml:space="preserve">5.25279188156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626070022583</t>
+    <t xml:space="preserve">5.36260652542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884069442749</t>
+    <t xml:space="preserve">5.61884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44908237457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324684143066</t>
+    <t xml:space="preserve">7.4490818977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324731826782</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55889654159546</t>
+    <t xml:space="preserve">7.5588960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062202453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452194213867</t>
+    <t xml:space="preserve">8.51062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452289581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025035858154</t>
+    <t xml:space="preserve">8.73025131225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176208496094</t>
+    <t xml:space="preserve">8.82176303863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308940887451</t>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179000854492</t>
+    <t xml:space="preserve">9.79179096221924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866195678711</t>
+    <t xml:space="preserve">10.3866186141968</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998676300049</t>
+    <t xml:space="preserve">9.37998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8949728012085</t>
+    <t xml:space="preserve">8.89497184753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833999633789</t>
+    <t xml:space="preserve">7.88833904266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4740161895752</t>
+    <t xml:space="preserve">8.47401714324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9249439239502</t>
+    <t xml:space="preserve">7.92494487762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735593795776</t>
+    <t xml:space="preserve">6.57056617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735641479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.53396081924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661451339722</t>
+    <t xml:space="preserve">6.93661403656006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -68128,7 +68128,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6911805556</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>5495</v>
@@ -68149,6 +68149,32 @@
         <v>896</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6913078704</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>17424</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>895</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414600372314</t>
+    <t xml:space="preserve">5.10414505004883</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169673919678</t>
+    <t xml:space="preserve">5.15394163131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16224098205566</t>
+    <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333137512207</t>
+    <t xml:space="preserve">5.30333089828491</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38632583618164</t>
+    <t xml:space="preserve">5.38632535934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.3489785194397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35312747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972665786743</t>
+    <t xml:space="preserve">5.35312795639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122388839722</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462518692017</t>
+    <t xml:space="preserve">5.39462566375732</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176908493042</t>
+    <t xml:space="preserve">5.48176956176758</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000337600708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93408823013306</t>
+    <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259099960327</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558450698853</t>
+    <t xml:space="preserve">5.85939359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728563308716</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87599182128906</t>
+    <t xml:space="preserve">5.87599229812622</t>
   </si>
   <si>
     <t xml:space="preserve">5.86769247055054</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05028009414673</t>
+    <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
     <t xml:space="preserve">6.13327360153198</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36150884628296</t>
+    <t xml:space="preserve">6.47355031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36150789260864</t>
   </si>
   <si>
     <t xml:space="preserve">6.55239486694336</t>
@@ -182,67 +182,67 @@
     <t xml:space="preserve">6.43205308914185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53994560241699</t>
+    <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.5938925743103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559322357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804105758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953828811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8055272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321630477905</t>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80552673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321678161621</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301336288452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02961206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034930229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948099136353</t>
+    <t xml:space="preserve">7.02961158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05450963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920475006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948146820068</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67289638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928676605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281770706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4279842376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573934555054</t>
+    <t xml:space="preserve">8.6728982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648653030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573839187622</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240262985229</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643665313721</t>
+    <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
     <t xml:space="preserve">7.22058057785034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788431167603</t>
+    <t xml:space="preserve">7.20788383483887</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
@@ -266,37 +266,37 @@
     <t xml:space="preserve">6.72961521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356294631958</t>
+    <t xml:space="preserve">6.80156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617311477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202823638916</t>
+    <t xml:space="preserve">6.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202919006348</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37295007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676532745361</t>
+    <t xml:space="preserve">7.37294960021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676628112793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290559768677</t>
@@ -305,28 +305,28 @@
     <t xml:space="preserve">7.30523061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3644847869873</t>
+    <t xml:space="preserve">7.36448431015015</t>
   </si>
   <si>
     <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28830003738403</t>
+    <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
     <t xml:space="preserve">7.23751163482666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16132736206055</t>
+    <t xml:space="preserve">7.16132640838623</t>
   </si>
   <si>
     <t xml:space="preserve">7.06821298599243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588796615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351942062378</t>
+    <t xml:space="preserve">7.02588748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351894378662</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67036151885986</t>
+    <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
@@ -344,52 +344,52 @@
     <t xml:space="preserve">7.15286207199097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08514213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96663331985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99626064300537</t>
+    <t xml:space="preserve">7.08514261245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96663284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
     <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77193975448608</t>
+    <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84812450408936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1105375289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016485214233</t>
+    <t xml:space="preserve">6.88621759414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016532897949</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09360694885254</t>
+    <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04704999923706</t>
+    <t xml:space="preserve">7.05974769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086524963379</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
+    <t xml:space="preserve">7.03012132644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0639796257019</t>
   </si>
   <si>
     <t xml:space="preserve">7.0555157661438</t>
@@ -410,196 +410,196 @@
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00049352645874</t>
+    <t xml:space="preserve">7.00049304962158</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11900234222412</t>
+    <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
     <t xml:space="preserve">7.008957862854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207223892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402458190918</t>
+    <t xml:space="preserve">7.11476945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402362823486</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680932998657</t>
+    <t xml:space="preserve">7.24597644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
     <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49992370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373895645142</t>
+    <t xml:space="preserve">7.49992322921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42374038696289</t>
   </si>
   <si>
     <t xml:space="preserve">7.38141441345215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28406763076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490194320679</t>
+    <t xml:space="preserve">7.28406810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490146636963</t>
   </si>
   <si>
     <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382696151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005619049072</t>
+    <t xml:space="preserve">7.47452926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382648468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
     <t xml:space="preserve">7.65652465820312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78349924087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457374572754</t>
+    <t xml:space="preserve">7.78349733352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457231521606</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913482666016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53378343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843252182007</t>
+    <t xml:space="preserve">7.53378248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
   </si>
   <si>
     <t xml:space="preserve">7.58880615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8681492805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9316349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88930988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470623016357</t>
+    <t xml:space="preserve">7.65229272842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540567398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8258228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9147047996521</t>
   </si>
   <si>
     <t xml:space="preserve">7.95279788970947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94856452941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332370758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45760011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694133758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3094630241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40257740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838851928711</t>
+    <t xml:space="preserve">7.9485650062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30946350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40257692337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137041091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838804244995</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01205253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097755432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023220062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40990257263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.01205158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474880218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707286834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40990352630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
@@ -608,28 +608,28 @@
     <t xml:space="preserve">8.26599979400635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23214054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30832386016846</t>
+    <t xml:space="preserve">8.23213958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30832481384277</t>
   </si>
   <si>
     <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027477264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040916442871</t>
+    <t xml:space="preserve">8.38027572631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
     <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11672401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01514434814453</t>
+    <t xml:space="preserve">9.11672496795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
     <t xml:space="preserve">8.998215675354</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290828704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1759786605835</t>
+    <t xml:space="preserve">9.19290924072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56536483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861217498779</t>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861122131348</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541845321655</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773338317871</t>
+    <t xml:space="preserve">9.71773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396118164062</t>
+    <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927808761597</t>
+    <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
@@ -680,10 +680,10 @@
     <t xml:space="preserve">10.9620771408081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0551919937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191837310791</t>
+    <t xml:space="preserve">11.0551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191846847534</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">11.7662448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741413116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973876953125</t>
+    <t xml:space="preserve">11.9355449676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973886489868</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
@@ -710,13 +710,13 @@
     <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156402587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.051775932312</t>
+    <t xml:space="preserve">14.2633991241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156383514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0517749786377</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111598968506</t>
@@ -725,46 +725,46 @@
     <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0940999984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009870529175</t>
+    <t xml:space="preserve">14.6443214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0941009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009860992432</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4169063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.433837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438795089722</t>
+    <t xml:space="preserve">12.8243618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4169073104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.493091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7639694213867</t>
+    <t xml:space="preserve">13.5184850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
     <t xml:space="preserve">14.0094509124756</t>
@@ -773,58 +773,58 @@
     <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019973754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512065887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596714019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.500415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311185836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618194580078</t>
+    <t xml:space="preserve">14.3480472564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512075424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596723556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004167556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157676696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618204116821</t>
   </si>
   <si>
     <t xml:space="preserve">13.8655462265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7978267669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840564727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994083404541</t>
+    <t xml:space="preserve">13.7978277206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.984058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031351089478</t>
+    <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7820377349854</t>
+    <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
     <t xml:space="preserve">12.7397127151489</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523462295532</t>
+    <t xml:space="preserve">13.5523452758789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.543098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.207106590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0348014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.043417930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9400339126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397172927856</t>
+    <t xml:space="preserve">13.5430994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2071056365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0348024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0434169769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.940034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
@@ -890,52 +890,52 @@
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228038787842</t>
+    <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123380661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277177810669</t>
+    <t xml:space="preserve">13.1123399734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277196884155</t>
   </si>
   <si>
     <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501821517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0606479644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9314203262329</t>
+    <t xml:space="preserve">13.2501811981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0606470108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834289550781</t>
+    <t xml:space="preserve">12.4834280014038</t>
   </si>
   <si>
     <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369703292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0354385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3542003631592</t>
+    <t xml:space="preserve">12.3369693756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.035439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975954055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474361419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3542013168335</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594327926636</t>
@@ -953,34 +953,34 @@
     <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.837287902832</t>
+    <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166767120361</t>
+    <t xml:space="preserve">11.7166757583618</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286733627319</t>
+    <t xml:space="preserve">11.8286724090576</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8200578689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7769823074341</t>
+    <t xml:space="preserve">11.8200588226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7769813537598</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339057922363</t>
+    <t xml:space="preserve">11.7339067459106</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
@@ -989,49 +989,49 @@
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182075500488</t>
+    <t xml:space="preserve">12.0182085037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785140991211</t>
+    <t xml:space="preserve">12.0785150527954</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0440540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0871295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157211303711</t>
+    <t xml:space="preserve">12.0440530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0871286392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157220840454</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988096237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.500659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815776824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7591161727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7160406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4231233596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4920434951782</t>
+    <t xml:space="preserve">12.6988086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5006589889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815786361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7591152191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7160396575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4231224060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
     <t xml:space="preserve">12.4661989212036</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
+    <t xml:space="preserve">12.5265054702759</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8366508483887</t>
+    <t xml:space="preserve">12.8366527557373</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883438110352</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7504997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868110656738</t>
+    <t xml:space="preserve">12.7505006790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868101119995</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7246541976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935762405396</t>
+    <t xml:space="preserve">12.7246561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935752868652</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917268753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520315170288</t>
+    <t xml:space="preserve">12.9917249679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089559555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0951080322266</t>
+    <t xml:space="preserve">13.0951070785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914073944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6550960540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.775710105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843236923218</t>
+    <t xml:space="preserve">13.4914064407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6550970077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7757081985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
@@ -1145,28 +1145,28 @@
     <t xml:space="preserve">14.4907712936401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166177749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8618621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1547784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443117141724</t>
+    <t xml:space="preserve">14.5166168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963212966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8618612289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1547775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8446311950684</t>
+    <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
     <t xml:space="preserve">14.1117010116577</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206359863281</t>
+    <t xml:space="preserve">13.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206369400024</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637115478516</t>
+    <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1205,22 +1205,22 @@
     <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8360147476196</t>
+    <t xml:space="preserve">13.8360157012939</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7326335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154035568237</t>
+    <t xml:space="preserve">13.7326326370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154026031494</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569463729858</t>
+    <t xml:space="preserve">13.4569473266602</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1229,52 +1229,52 @@
     <t xml:space="preserve">13.3535642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.405255317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3191032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3880252838135</t>
+    <t xml:space="preserve">13.4052562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3191041946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3880243301392</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292514801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3707942962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2846431732178</t>
+    <t xml:space="preserve">13.6292505264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.370795249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3363342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5775604248047</t>
+    <t xml:space="preserve">13.3363332748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5086374282837</t>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.951714515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693756103516</t>
+    <t xml:space="preserve">13.8634119033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9517154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693746566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340534210205</t>
+    <t xml:space="preserve">13.9340543746948</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
@@ -1295,31 +1295,31 @@
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219026565552</t>
+    <t xml:space="preserve">13.4219017028809</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982807159424</t>
+    <t xml:space="preserve">13.2982797622681</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686941146851</t>
+    <t xml:space="preserve">13.0686950683594</t>
   </si>
   <si>
     <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872619628906</t>
+    <t xml:space="preserve">14.2872629165649</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.004695892334</t>
+    <t xml:space="preserve">14.0046949386597</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753374099731</t>
+    <t xml:space="preserve">14.0753364562988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870357513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8457517623901</t>
+    <t xml:space="preserve">13.9870347976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8457527160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.810432434082</t>
+    <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338272094727</t>
+    <t xml:space="preserve">13.6338262557983</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691484451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102043151855</t>
+    <t xml:space="preserve">13.6691474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102052688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
+    <t xml:space="preserve">13.351261138916</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
+    <t xml:space="preserve">13.2276372909546</t>
   </si>
   <si>
     <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.174656867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629585266113</t>
+    <t xml:space="preserve">13.1746578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629594802856</t>
   </si>
   <si>
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095237731934</t>
+    <t xml:space="preserve">12.6095247268677</t>
   </si>
   <si>
     <t xml:space="preserve">12.5035619735718</t>
@@ -1424,22 +1424,22 @@
     <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3159408569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980525970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9097499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.033374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1569957733154</t>
+    <t xml:space="preserve">13.3159399032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980535507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9097509384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0333738327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
     <t xml:space="preserve">13.2099781036377</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1216764450073</t>
+    <t xml:space="preserve">13.121675491333</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037881851196</t>
+    <t xml:space="preserve">12.8567695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
     <t xml:space="preserve">12.2386560440063</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.2673349380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790313720703</t>
+    <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
@@ -1493,34 +1493,34 @@
     <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0024271011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143535614014</t>
+    <t xml:space="preserve">11.0024280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143526077271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
+    <t xml:space="preserve">10.9317874908447</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792585372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441654205322</t>
+    <t xml:space="preserve">11.2849950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441644668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439373016357</t>
+    <t xml:space="preserve">11.4439382553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494466781616</t>
+    <t xml:space="preserve">10.9494476318359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.154727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299247741699</t>
+    <t xml:space="preserve">10.1547288894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299152374268</t>
   </si>
   <si>
     <t xml:space="preserve">9.44831275939941</t>
@@ -1586,37 +1586,37 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
+    <t xml:space="preserve">9.53661441802979</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198619842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551822662354</t>
+    <t xml:space="preserve">10.7198629379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966924667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2783527374268</t>
+    <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785779953003</t>
+    <t xml:space="preserve">10.4902772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079374313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785789489746</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8258237838745</t>
+    <t xml:space="preserve">10.8258247375488</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3313322067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432567596436</t>
+    <t xml:space="preserve">10.3313331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432577133179</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019737243652</t>
+    <t xml:space="preserve">10.4019756317139</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8434839248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8964653015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141254425049</t>
+    <t xml:space="preserve">10.84348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.896466255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141263961792</t>
   </si>
   <si>
     <t xml:space="preserve">11.0554103851318</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069101333618</t>
+    <t xml:space="preserve">10.7069110870361</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027828216553</t>
+    <t xml:space="preserve">9.84669876098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027923583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846290588379</t>
+    <t xml:space="preserve">10.0663270950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846300125122</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.139536857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578397750854</t>
+    <t xml:space="preserve">10.1395359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578388214111</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055837631226</t>
+    <t xml:space="preserve">10.5055847167969</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.523886680603</t>
+    <t xml:space="preserve">10.5238876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.560492515564</t>
+    <t xml:space="preserve">10.5604915618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716325759888</t>
+    <t xml:space="preserve">10.8716335296631</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703062057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899345397949</t>
+    <t xml:space="preserve">10.6703052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984228134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899354934692</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193784713745</t>
+    <t xml:space="preserve">11.2193794250488</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644716262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533296585083</t>
+    <t xml:space="preserve">11.1644706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533306121826</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252130508423</t>
+    <t xml:space="preserve">10.7252140045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9448432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461696624756</t>
+    <t xml:space="preserve">10.944842338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109564781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461687088013</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608493804932</t>
+    <t xml:space="preserve">8.23608589172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550142288208</t>
+    <t xml:space="preserve">8.17202758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550094604492</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234245300293</t>
+    <t xml:space="preserve">6.01234292984009</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0098237991333</t>
+    <t xml:space="preserve">7.00982332229614</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.055579662323</t>
+    <t xml:space="preserve">7.05558013916016</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247749328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531511306763</t>
+    <t xml:space="preserve">7.41247701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531558990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568725585938</t>
+    <t xml:space="preserve">7.48568677902222</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303356170654</t>
+    <t xml:space="preserve">6.68038034439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303308486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229166030884</t>
+    <t xml:space="preserve">7.52229118347168</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364547729492</t>
+    <t xml:space="preserve">8.14457225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364643096924</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818256378174</t>
+    <t xml:space="preserve">8.96818161010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.620436668396</t>
+    <t xml:space="preserve">8.62043571472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7968282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003755569458</t>
+    <t xml:space="preserve">7.79682779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003803253174</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63210582733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7236180305481</t>
+    <t xml:space="preserve">7.77852582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6321063041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361755371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642820358276</t>
+    <t xml:space="preserve">7.04642868041992</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340427398682</t>
+    <t xml:space="preserve">6.86340475082397</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46075105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35093688964844</t>
+    <t xml:space="preserve">6.4607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3509373664856</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130760192871</t>
+    <t xml:space="preserve">6.02149391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130807876587</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242164611816</t>
+    <t xml:space="preserve">5.47242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279188156128</t>
+    <t xml:space="preserve">5.25279235839844</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36260652542114</t>
+    <t xml:space="preserve">5.3626070022583</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884021759033</t>
+    <t xml:space="preserve">5.61884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4490818977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324731826782</t>
+    <t xml:space="preserve">7.44908237457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324684143066</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5588960647583</t>
+    <t xml:space="preserve">7.55889654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452289581299</t>
+    <t xml:space="preserve">8.51062202453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847312927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452194213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025131225586</t>
+    <t xml:space="preserve">8.73025035858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176303863525</t>
+    <t xml:space="preserve">8.82176208496094</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0230884552002</t>
+    <t xml:space="preserve">9.13290309906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02308940887451</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179096221924</t>
+    <t xml:space="preserve">9.79179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866186141968</t>
+    <t xml:space="preserve">10.3866195678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998580932617</t>
+    <t xml:space="preserve">9.37998676300049</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89497184753418</t>
+    <t xml:space="preserve">8.8949728012085</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833904266357</t>
+    <t xml:space="preserve">7.88833999633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47401714324951</t>
+    <t xml:space="preserve">8.4740161895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92494487762451</t>
+    <t xml:space="preserve">7.9249439239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735641479492</t>
+    <t xml:space="preserve">6.57056570053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735593795776</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396081924438</t>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661403656006</t>
+    <t xml:space="preserve">6.93661451339722</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -68154,25 +68154,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6913078704</v>
+        <v>45967.6911226852</v>
       </c>
       <c r="B2505" t="n">
-        <v>17424</v>
+        <v>29643</v>
       </c>
       <c r="C2505" t="n">
-        <v>9.22000026702881</v>
+        <v>9.27999973297119</v>
       </c>
       <c r="D2505" t="n">
-        <v>9.14000034332275</v>
+        <v>9.11999988555908</v>
       </c>
       <c r="E2505" t="n">
-        <v>9.14000034332275</v>
+        <v>9.19999980926514</v>
       </c>
       <c r="F2505" t="n">
-        <v>9.22000026702881</v>
+        <v>9.11999988555908</v>
       </c>
       <c r="G2505" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -44,106 +44,106 @@
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394258499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169626235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14564275741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1165943145752</t>
+    <t xml:space="preserve">5.1539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14564228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18713998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958877563477</t>
+    <t xml:space="preserve">5.19958925247192</t>
   </si>
   <si>
     <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333185195923</t>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632535934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3489785194397</t>
+    <t xml:space="preserve">5.3157811164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897804260254</t>
   </si>
   <si>
     <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122436523438</t>
+    <t xml:space="preserve">5.36972618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122341156006</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761917114258</t>
+    <t xml:space="preserve">5.39462518692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7100043296814</t>
+    <t xml:space="preserve">5.71000337600708</t>
   </si>
   <si>
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259052276611</t>
+    <t xml:space="preserve">5.89259099960327</t>
   </si>
   <si>
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939359664917</t>
+    <t xml:space="preserve">5.85939311981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728563308716</t>
+    <t xml:space="preserve">5.96728610992432</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068693161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653701782227</t>
+    <t xml:space="preserve">5.96313524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653654098511</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86769247055054</t>
+    <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
     <t xml:space="preserve">6.05442953109741</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05027961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327360153198</t>
+    <t xml:space="preserve">6.05028009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
@@ -176,37 +176,37 @@
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56069421768188</t>
+    <t xml:space="preserve">6.5606951713562</t>
   </si>
   <si>
     <t xml:space="preserve">6.432053565979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53994607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5938925743103</t>
+    <t xml:space="preserve">6.53994560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
     <t xml:space="preserve">6.58559274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59804153442383</t>
+    <t xml:space="preserve">6.59804105758667</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63953924179077</t>
+    <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
     <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96321630477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301240921021</t>
+    <t xml:space="preserve">6.96321678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301288604736</t>
   </si>
   <si>
     <t xml:space="preserve">7.02961206436157</t>
@@ -215,55 +215,55 @@
     <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12920475006104</t>
+    <t xml:space="preserve">7.12920618057251</t>
   </si>
   <si>
     <t xml:space="preserve">7.3034930229187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46948099136353</t>
+    <t xml:space="preserve">7.46948146820068</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234485626221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6728982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928485870361</t>
+    <t xml:space="preserve">8.67289638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928581237793</t>
   </si>
   <si>
     <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38648653030396</t>
+    <t xml:space="preserve">7.38648748397827</t>
   </si>
   <si>
     <t xml:space="preserve">7.4279842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36573791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240310668945</t>
+    <t xml:space="preserve">7.36573886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240262985229</t>
   </si>
   <si>
     <t xml:space="preserve">7.21634817123413</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788383483887</t>
+    <t xml:space="preserve">7.43643569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22058057785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788478851318</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72961568832397</t>
+    <t xml:space="preserve">6.72961521148682</t>
   </si>
   <si>
     <t xml:space="preserve">6.80156755447388</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">6.77617311477661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97933101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.992027759552</t>
+    <t xml:space="preserve">6.97933149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37295007705688</t>
+    <t xml:space="preserve">7.37294912338257</t>
   </si>
   <si>
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2925329208374</t>
+    <t xml:space="preserve">7.29253244400024</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676532745361</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">7.26290559768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30523109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448526382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941854476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830051422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23751068115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588844299316</t>
+    <t xml:space="preserve">7.30523014068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3644847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1994194984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830099105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23751258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132688522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588796615601</t>
   </si>
   <si>
     <t xml:space="preserve">6.87351894378662</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56031703948975</t>
+    <t xml:space="preserve">6.5603175163269</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286159515381</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96663284301758</t>
+    <t xml:space="preserve">6.96663331985474</t>
   </si>
   <si>
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538328170776</t>
+    <t xml:space="preserve">6.72538280487061</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
@@ -362,46 +362,46 @@
     <t xml:space="preserve">6.84812498092651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128240585327</t>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128335952759</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360790252686</t>
+    <t xml:space="preserve">7.10630464553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705095291138</t>
+    <t xml:space="preserve">7.05974817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858470916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
+    <t xml:space="preserve">7.03858518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0639796257019</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">7.00049352645874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03435325622559</t>
+    <t xml:space="preserve">7.03435230255127</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900186538696</t>
@@ -425,25 +425,25 @@
     <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10207319259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
+    <t xml:space="preserve">7.10207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2036509513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402410507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597644805908</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680932998657</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42373991012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141536712646</t>
+    <t xml:space="preserve">7.42373943328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141489028931</t>
   </si>
   <si>
     <t xml:space="preserve">7.28406763076782</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">7.44490146636963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39834451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382696151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652513504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349828720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457231521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
+    <t xml:space="preserve">7.39834499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652561187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880519866943</t>
   </si>
   <si>
     <t xml:space="preserve">7.65229225158691</t>
@@ -506,76 +506,76 @@
     <t xml:space="preserve">7.69885015487671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74540662765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316913604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88931035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470575332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856595993042</t>
+    <t xml:space="preserve">7.74540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9316349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582330703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470527648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279884338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856452941895</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6141996383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
+    <t xml:space="preserve">7.70308303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.34332275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25020837783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45759963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694181442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685380935669</t>
+    <t xml:space="preserve">7.25020790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45760011672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685333251953</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40257692337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137136459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838899612427</t>
+    <t xml:space="preserve">7.4025764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702934265137</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097755432129</t>
+    <t xml:space="preserve">8.06707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097660064697</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
@@ -605,19 +605,19 @@
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599979400635</t>
+    <t xml:space="preserve">8.26600074768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30832386016846</t>
+    <t xml:space="preserve">8.30832481384277</t>
   </si>
   <si>
     <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027572631836</t>
+    <t xml:space="preserve">8.38027477264404</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514530181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99821662902832</t>
+    <t xml:space="preserve">9.01514434814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
@@ -641,31 +641,31 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290828704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17597961425781</t>
+    <t xml:space="preserve">9.19290924072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56536483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861122131348</t>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861217498779</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541826248169</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773433685303</t>
+    <t xml:space="preserve">9.71773242950439</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396213531494</t>
+    <t xml:space="preserve">9.90396118164062</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620771408081</t>
+    <t xml:space="preserve">10.9451475143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620780944824</t>
   </si>
   <si>
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191827774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884809494019</t>
+    <t xml:space="preserve">11.4191846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
@@ -695,40 +695,40 @@
     <t xml:space="preserve">11.7662448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355440139771</t>
+    <t xml:space="preserve">11.9355449676514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629590988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3491878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633991241455</t>
+    <t xml:space="preserve">12.6973876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3491868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634000778198</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0517768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111589431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460285186768</t>
+    <t xml:space="preserve">14.051775932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460275650024</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443195343018</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0941019058228</t>
+    <t xml:space="preserve">14.0941009521484</t>
   </si>
   <si>
     <t xml:space="preserve">14.5173463821411</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1206340789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8243608474731</t>
+    <t xml:space="preserve">13.1206350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8243618011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761610031128</t>
+    <t xml:space="preserve">13.4761619567871</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5100202560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184869766235</t>
+    <t xml:space="preserve">13.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184860229492</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930906295776</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7639675140381</t>
+    <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
     <t xml:space="preserve">14.0094509124756</t>
@@ -773,49 +773,49 @@
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512065887451</t>
+    <t xml:space="preserve">14.348048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.601996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512056350708</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004167556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618194580078</t>
+    <t xml:space="preserve">14.508882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.407301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157695770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618185043335</t>
   </si>
   <si>
     <t xml:space="preserve">13.8655471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7978267669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.984055519104</t>
+    <t xml:space="preserve">13.7978277206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385730743408</t>
+    <t xml:space="preserve">13.7385740280151</t>
   </si>
   <si>
     <t xml:space="preserve">13.6031351089478</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">12.7820377349854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0275192260742</t>
+    <t xml:space="preserve">12.7397127151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423017501831</t>
+    <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
@@ -857,46 +857,46 @@
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397163391113</t>
+    <t xml:space="preserve">13.4397172927856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175714492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3018732070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1640300750732</t>
+    <t xml:space="preserve">13.0175704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.301872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1640310287476</t>
   </si>
   <si>
     <t xml:space="preserve">13.1295690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8797273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2243366241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812601089478</t>
+    <t xml:space="preserve">12.8797283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901941299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2243375778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557331085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123399734497</t>
+    <t xml:space="preserve">12.9228038787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557321548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123380661011</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277196884155</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501811981201</t>
+    <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
     <t xml:space="preserve">13.0606470108032</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834280014038</t>
+    <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.233588218689</t>
@@ -926,25 +926,25 @@
     <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.035439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975954055786</t>
+    <t xml:space="preserve">12.0354385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
     <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3542013168335</t>
+    <t xml:space="preserve">12.3542003631592</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3197402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.3197393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286724090576</t>
@@ -974,55 +974,55 @@
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769813537598</t>
+    <t xml:space="preserve">11.7769832611084</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339067459106</t>
+    <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182085037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0785150527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388206481934</t>
+    <t xml:space="preserve">11.6305246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182065963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0785160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388216018677</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157220840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.103723526001</t>
+    <t xml:space="preserve">12.0871295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1037225723267</t>
   </si>
   <si>
     <t xml:space="preserve">12.6988086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591152191162</t>
+    <t xml:space="preserve">12.7591161727905</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920444488525</t>
+    <t xml:space="preserve">12.4920434951782</t>
   </si>
   <si>
     <t xml:space="preserve">12.4661989212036</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.535120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265054702759</t>
+    <t xml:space="preserve">12.5351209640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141893386841</t>
+    <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
     <t xml:space="preserve">12.8366527557373</t>
@@ -1073,37 +1073,37 @@
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868101119995</t>
+    <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280372619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7418851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8711128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917249679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089559555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572639465332</t>
+    <t xml:space="preserve">12.6126565933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280363082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7418842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.871111869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917268753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0951070785522</t>
+    <t xml:space="preserve">13.0951080322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
@@ -1124,34 +1124,34 @@
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914064407349</t>
+    <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757081985474</t>
+    <t xml:space="preserve">13.7757091522217</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498636245728</t>
+    <t xml:space="preserve">13.7498645782471</t>
   </si>
   <si>
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907712936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5166168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
+    <t xml:space="preserve">14.4907703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5166177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
   </si>
   <si>
     <t xml:space="preserve">13.8963212966919</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240190505981</t>
+    <t xml:space="preserve">13.7240171432495</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547775268555</t>
@@ -1169,22 +1169,22 @@
     <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9393978118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.844630241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1117010116577</t>
+    <t xml:space="preserve">14.0255498886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.939398765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8446311950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929391860962</t>
+    <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206369400024</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704767227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360157012939</t>
+    <t xml:space="preserve">13.870475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360147476196</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154026031494</t>
+    <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880243301392</t>
+    <t xml:space="preserve">13.3880252838135</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846422195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603294372559</t>
+    <t xml:space="preserve">13.2846431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603284835815</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5086393356323</t>
+    <t xml:space="preserve">13.508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
+    <t xml:space="preserve">13.8634128570557</t>
   </si>
   <si>
     <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693746566772</t>
+    <t xml:space="preserve">13.9693737030029</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1289,28 +1289,28 @@
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161670684814</t>
+    <t xml:space="preserve">13.6161661148071</t>
   </si>
   <si>
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219017028809</t>
+    <t xml:space="preserve">13.4219026565552</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982797622681</t>
+    <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402433395386</t>
+    <t xml:space="preserve">13.0686960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402423858643</t>
   </si>
   <si>
     <t xml:space="preserve">14.2872629165649</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1352,25 +1352,25 @@
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865823745728</t>
+    <t xml:space="preserve">13.3865814208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7221298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514873504639</t>
+    <t xml:space="preserve">13.722128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514883041382</t>
   </si>
   <si>
     <t xml:space="preserve">13.4748840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6868085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.580846786499</t>
+    <t xml:space="preserve">13.6868095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5808458328247</t>
   </si>
   <si>
     <t xml:space="preserve">13.6338262557983</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691474914551</t>
+    <t xml:space="preserve">13.6691484451294</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102052688599</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
+    <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">13.2276372909546</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3689222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1746578216553</t>
+    <t xml:space="preserve">13.3689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095247268677</t>
+    <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157136917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159399032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980535507202</t>
+    <t xml:space="preserve">13.0157127380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159408569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391103744507</t>
+    <t xml:space="preserve">12.8391084671021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099781036377</t>
+    <t xml:space="preserve">13.2099771499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8920907974243</t>
+    <t xml:space="preserve">12.8920917510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
@@ -1466,22 +1466,22 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2386560440063</t>
+    <t xml:space="preserve">12.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379764556885</t>
+    <t xml:space="preserve">11.267333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379755020142</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615983963013</t>
+    <t xml:space="preserve">11.461597442627</t>
   </si>
   <si>
     <t xml:space="preserve">11.1790323257446</t>
@@ -1502,25 +1502,25 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317874908447</t>
+    <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496738433838</t>
+    <t xml:space="preserve">11.1260509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496728897095</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549560546875</t>
+    <t xml:space="preserve">10.4549551010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1577,25 +1577,25 @@
     <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41299152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831275939941</t>
+    <t xml:space="preserve">9.41299247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831371307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53661441802979</t>
+    <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198629379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966924667358</t>
+    <t xml:space="preserve">10.7198610305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966934204102</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551832199097</t>
@@ -1607,25 +1607,25 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2430305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785789489746</t>
+    <t xml:space="preserve">10.24303150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785779953003</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258247375488</t>
+    <t xml:space="preserve">10.7375211715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
@@ -1634,34 +1634,34 @@
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606906890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3313331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432577133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4196348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4019756317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.437294960022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.84348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.896466255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554103851318</t>
+    <t xml:space="preserve">10.2606916427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3313322067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432567596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4196357727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4019746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4372959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8434839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8964653015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069110870361</t>
+    <t xml:space="preserve">10.7069101333618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027923583984</t>
+    <t xml:space="preserve">9.84669780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846300125122</t>
+    <t xml:space="preserve">10.0663261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846290588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578388214111</t>
+    <t xml:space="preserve">10.139536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578397750854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055847167969</t>
+    <t xml:space="preserve">10.5055837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5238876342773</t>
+    <t xml:space="preserve">10.523886680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5604915618896</t>
+    <t xml:space="preserve">10.560492515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716335296631</t>
+    <t xml:space="preserve">10.8716325759888</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899354934692</t>
+    <t xml:space="preserve">10.6703062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899345397949</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193794250488</t>
+    <t xml:space="preserve">11.2193784713745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533306121826</t>
+    <t xml:space="preserve">11.1644716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252140045166</t>
+    <t xml:space="preserve">10.7252130508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944842338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461687088013</t>
+    <t xml:space="preserve">10.9448432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608589172363</t>
+    <t xml:space="preserve">8.23608493804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550094604492</t>
+    <t xml:space="preserve">8.17202663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550142288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234292984009</t>
+    <t xml:space="preserve">6.01234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00982332229614</t>
+    <t xml:space="preserve">7.0098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558013916016</t>
+    <t xml:space="preserve">7.055579662323</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531558990479</t>
+    <t xml:space="preserve">7.41247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531511306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568677902222</t>
+    <t xml:space="preserve">7.48568725585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038034439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303308486938</t>
+    <t xml:space="preserve">6.68038082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229118347168</t>
+    <t xml:space="preserve">7.52229166030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364643096924</t>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364547729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818161010742</t>
+    <t xml:space="preserve">8.96818256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62043571472168</t>
+    <t xml:space="preserve">8.620436668396</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003803253174</t>
+    <t xml:space="preserve">7.7968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003755569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6321063041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361755371094</t>
+    <t xml:space="preserve">7.77852535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63210582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236180305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642868041992</t>
+    <t xml:space="preserve">7.04642820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340475082397</t>
+    <t xml:space="preserve">6.86340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3509373664856</t>
+    <t xml:space="preserve">6.46075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35093688964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130807876587</t>
+    <t xml:space="preserve">6.02149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242116928101</t>
+    <t xml:space="preserve">5.47242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279235839844</t>
+    <t xml:space="preserve">5.25279188156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626070022583</t>
+    <t xml:space="preserve">5.36260652542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884069442749</t>
+    <t xml:space="preserve">5.61884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44908237457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324684143066</t>
+    <t xml:space="preserve">7.4490818977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324731826782</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55889654159546</t>
+    <t xml:space="preserve">7.5588960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062202453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452194213867</t>
+    <t xml:space="preserve">8.51062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452289581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025035858154</t>
+    <t xml:space="preserve">8.73025131225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176208496094</t>
+    <t xml:space="preserve">8.82176303863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308940887451</t>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179000854492</t>
+    <t xml:space="preserve">9.79179096221924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866195678711</t>
+    <t xml:space="preserve">10.3866186141968</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998676300049</t>
+    <t xml:space="preserve">9.37998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8949728012085</t>
+    <t xml:space="preserve">8.89497184753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833999633789</t>
+    <t xml:space="preserve">7.88833904266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4740161895752</t>
+    <t xml:space="preserve">8.47401714324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9249439239502</t>
+    <t xml:space="preserve">7.92494487762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735593795776</t>
+    <t xml:space="preserve">6.57056617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735641479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.53396081924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661451339722</t>
+    <t xml:space="preserve">6.93661403656006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -68339,7 +68339,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6912268518</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>15384</v>
@@ -68360,6 +68360,32 @@
         <v>899</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6873263889</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>6292</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">5.09169673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564228057861</t>
+    <t xml:space="preserve">5.14564180374146</t>
   </si>
   <si>
     <t xml:space="preserve">5.18713998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659479141235</t>
+    <t xml:space="preserve">5.1165943145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224098205566</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31163120269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3157811164856</t>
+    <t xml:space="preserve">5.31163167953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31578159332275</t>
   </si>
   <si>
     <t xml:space="preserve">5.34482908248901</t>
@@ -83,31 +83,31 @@
     <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34897804260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122341156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462518692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761964797974</t>
+    <t xml:space="preserve">5.34897899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972665786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122484207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067964553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761917114258</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000337600708</t>
+    <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
     <t xml:space="preserve">5.9340877532959</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939311981201</t>
+    <t xml:space="preserve">5.85939264297485</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728610992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9008903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96313524246216</t>
+    <t xml:space="preserve">5.96728563308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90089082717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96313619613647</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653654098511</t>
+    <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8676929473877</t>
+    <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
     <t xml:space="preserve">6.05442953109741</t>
@@ -155,28 +155,28 @@
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05028009414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137001037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47355079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239534378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57314348220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5606951713562</t>
+    <t xml:space="preserve">6.05027914047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327360153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19136953353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47354984283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36150789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239486694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57314395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
     <t xml:space="preserve">6.432053565979</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559274673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804105758667</t>
+    <t xml:space="preserve">6.58559226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804153442383</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464023590088</t>
@@ -200,103 +200,103 @@
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8055272102356</t>
+    <t xml:space="preserve">6.80552673339844</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301288604736</t>
+    <t xml:space="preserve">7.01301240921021</t>
   </si>
   <si>
     <t xml:space="preserve">7.02961206436157</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920618057251</t>
+    <t xml:space="preserve">7.05451059341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920475006104</t>
   </si>
   <si>
     <t xml:space="preserve">7.3034930229187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46948146820068</t>
+    <t xml:space="preserve">7.46948099136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234485626221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67289638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648748397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4279842376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573886871338</t>
+    <t xml:space="preserve">8.67289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3864860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573839187622</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240262985229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21634817123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22058057785034</t>
+    <t xml:space="preserve">7.21634864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
     <t xml:space="preserve">7.20788478851318</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89468193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617311477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202823638916</t>
+    <t xml:space="preserve">6.89468240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356342315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123888015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933053970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202871322632</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37294912338257</t>
+    <t xml:space="preserve">7.37295007705688</t>
   </si>
   <si>
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676532745361</t>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676580429077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290559768677</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">7.30523014068604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3644847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994194984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830099105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23751258850098</t>
+    <t xml:space="preserve">7.36448526382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2375111579895</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821346282959</t>
+    <t xml:space="preserve">7.06821250915527</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588796615601</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5603175163269</t>
+    <t xml:space="preserve">6.56031656265259</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286159515381</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96663331985474</t>
+    <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538280487061</t>
+    <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">6.84812498092651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621664047241</t>
+    <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
     <t xml:space="preserve">7.18672132492065</t>
@@ -371,97 +371,97 @@
     <t xml:space="preserve">7.11053657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128335952759</t>
+    <t xml:space="preserve">7.05128288269043</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630464553833</t>
+    <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
     <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937501907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974817276001</t>
+    <t xml:space="preserve">7.08937454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974769592285</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086524963379</t>
+    <t xml:space="preserve">6.97086572647095</t>
   </si>
   <si>
     <t xml:space="preserve">7.03858518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0639796257019</t>
+    <t xml:space="preserve">7.03012037277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398057937622</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09783935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00049352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900186538696</t>
+    <t xml:space="preserve">7.09784030914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0004940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11900234222412</t>
   </si>
   <si>
     <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476945877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2036509513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402410507202</t>
+    <t xml:space="preserve">7.11476993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207223892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987970352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402458190918</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597644805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680932998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.432204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373943328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406763076782</t>
+    <t xml:space="preserve">7.24597597122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40681076049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373991012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406810760498</t>
   </si>
   <si>
     <t xml:space="preserve">7.44490146636963</t>
@@ -470,28 +470,28 @@
     <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382743835449</t>
+    <t xml:space="preserve">7.47452926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382696151733</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65652561187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349924087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457326889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913482666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378391265869</t>
+    <t xml:space="preserve">7.6565260887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7834997177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457279205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.449134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378295898438</t>
   </si>
   <si>
     <t xml:space="preserve">7.61843299865723</t>
@@ -500,22 +500,22 @@
     <t xml:space="preserve">7.58880519866943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9316349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316961288452</t>
+    <t xml:space="preserve">7.6522912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540567398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.82582330703735</t>
@@ -524,58 +524,58 @@
     <t xml:space="preserve">7.88931083679199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91470527648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856452941895</t>
+    <t xml:space="preserve">7.91470575332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9485650062561</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45760011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536262512207</t>
+    <t xml:space="preserve">7.70308256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020885467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536214828491</t>
   </si>
   <si>
     <t xml:space="preserve">7.73694229125977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51685333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30946254730225</t>
+    <t xml:space="preserve">7.51685428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3094630241394</t>
   </si>
   <si>
     <t xml:space="preserve">7.4025764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838851928711</t>
+    <t xml:space="preserve">7.34755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838899612427</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702934265137</t>
@@ -584,49 +584,49 @@
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474880218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023220062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40990352630615</t>
+    <t xml:space="preserve">8.02474975585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707286834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097755432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40990447998047</t>
   </si>
   <si>
     <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40567111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26600074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23214054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30832481384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32525444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027477264404</t>
+    <t xml:space="preserve">8.40567016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26599979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23213958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30832386016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3252534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970542907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11672496795654</t>
+    <t xml:space="preserve">8.87970638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11672401428223</t>
   </si>
   <si>
     <t xml:space="preserve">9.01514434814453</t>
@@ -644,46 +644,46 @@
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1759786605835</t>
+    <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5653657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861217498779</t>
+    <t xml:space="preserve">9.56536483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861122131348</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541826248169</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773242950439</t>
+    <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496506690979</t>
+    <t xml:space="preserve">9.90396213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965076446533</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451475143433</t>
+    <t xml:space="preserve">10.9451484680176</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191846847534</t>
+    <t xml:space="preserve">11.0551919937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
@@ -692,22 +692,22 @@
     <t xml:space="preserve">11.7239217758179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7662448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355449676514</t>
+    <t xml:space="preserve">11.7662467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3491868972778</t>
+    <t xml:space="preserve">12.6973886489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3491888046265</t>
   </si>
   <si>
     <t xml:space="preserve">14.2634000778198</t>
@@ -719,28 +719,28 @@
     <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443195343018</t>
+    <t xml:space="preserve">12.5111589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460294723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443185806274</t>
   </si>
   <si>
     <t xml:space="preserve">14.0941009521484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173463821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009870529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8243618011475</t>
+    <t xml:space="preserve">14.5173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206331253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169073104858</t>
@@ -749,22 +749,22 @@
     <t xml:space="preserve">13.4761619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338369369507</t>
+    <t xml:space="preserve">13.4338359832764</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5100212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930906295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7639684677124</t>
+    <t xml:space="preserve">13.5100202560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930896759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7639694213867</t>
   </si>
   <si>
     <t xml:space="preserve">14.0094509124756</t>
@@ -773,25 +773,25 @@
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348048210144</t>
+    <t xml:space="preserve">14.3480491638184</t>
   </si>
   <si>
     <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512056350708</t>
+    <t xml:space="preserve">14.5512075424194</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.508882522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.500415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.407301902771</t>
+    <t xml:space="preserve">14.5088815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004177093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073028564453</t>
   </si>
   <si>
     <t xml:space="preserve">14.4157695770264</t>
@@ -800,31 +800,31 @@
     <t xml:space="preserve">14.3311185836792</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1618185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978277206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840564727783</t>
+    <t xml:space="preserve">14.1618194580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655462265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978286743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840574264526</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385740280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031351089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820377349854</t>
+    <t xml:space="preserve">13.7385721206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290998458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
     <t xml:space="preserve">12.7397127151489</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523462295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5430994033813</t>
+    <t xml:space="preserve">13.5523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423017501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.543098449707</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348024368286</t>
+    <t xml:space="preserve">13.0348014831543</t>
   </si>
   <si>
     <t xml:space="preserve">13.0434169769287</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">13.301872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1640310287476</t>
+    <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
     <t xml:space="preserve">13.1295690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8797283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901941299438</t>
+    <t xml:space="preserve">12.8797273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243375778198</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228038787842</t>
+    <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557321548462</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">13.1123380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276026725769</t>
+    <t xml:space="preserve">13.3277177810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0606470108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9314193725586</t>
+    <t xml:space="preserve">13.0606479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9314203262329</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
@@ -920,19 +920,19 @@
     <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.233588218689</t>
+    <t xml:space="preserve">12.2335872650146</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0354385375977</t>
+    <t xml:space="preserve">12.0354375839233</t>
   </si>
   <si>
     <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474361419678</t>
+    <t xml:space="preserve">12.1474370956421</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3197393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1302051544189</t>
+    <t xml:space="preserve">12.3197402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7855978012085</t>
+    <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166767120361</t>
@@ -965,16 +965,16 @@
     <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286724090576</t>
+    <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8200588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7769832611084</t>
+    <t xml:space="preserve">11.8200578689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6046781539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6305246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0785160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388216018677</t>
+    <t xml:space="preserve">11.6046772003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6305236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612840652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0785140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037225723267</t>
+    <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.6988086700439</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6815786361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7591161727905</t>
+    <t xml:space="preserve">12.6815776824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
@@ -1031,19 +1031,19 @@
     <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4661989212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.4920444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4661979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5351209640503</t>
+    <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
     <t xml:space="preserve">12.5265045166016</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8366527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883438110352</t>
+    <t xml:space="preserve">12.9141893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.836651802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883428573608</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7505006790161</t>
+    <t xml:space="preserve">12.7505016326904</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
@@ -1079,25 +1079,25 @@
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126565933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935762405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280363082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7418842315674</t>
+    <t xml:space="preserve">12.6126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280372619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.871111869812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917268753052</t>
+    <t xml:space="preserve">12.9917259216309</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089569091797</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520324707031</t>
+    <t xml:space="preserve">13.0520315170288</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2674112319946</t>
+    <t xml:space="preserve">13.1984891891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2674121856689</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914073944092</t>
@@ -1136,22 +1136,22 @@
     <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498645782471</t>
+    <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907703399658</t>
+    <t xml:space="preserve">14.4907712936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.5166177749634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.8963212966919</t>
@@ -1160,25 +1160,25 @@
     <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240171432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1547775268555</t>
+    <t xml:space="preserve">13.7240190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1547784805298</t>
   </si>
   <si>
     <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255498886108</t>
+    <t xml:space="preserve">14.0255517959595</t>
   </si>
   <si>
     <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8446311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.111701965332</t>
+    <t xml:space="preserve">13.844630241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1117010116577</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
@@ -1187,28 +1187,28 @@
     <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6206369400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5517129898071</t>
+    <t xml:space="preserve">13.6206350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5517139434814</t>
   </si>
   <si>
     <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8187866210938</t>
+    <t xml:space="preserve">13.8187856674194</t>
   </si>
   <si>
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.870475769043</t>
+    <t xml:space="preserve">13.8704776763916</t>
   </si>
   <si>
     <t xml:space="preserve">13.8360147476196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8015556335449</t>
+    <t xml:space="preserve">13.8015546798706</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
@@ -1220,19 +1220,19 @@
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6120204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3535652160645</t>
+    <t xml:space="preserve">13.4569463729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.612021446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3535642623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3191041946411</t>
+    <t xml:space="preserve">13.3191032409668</t>
   </si>
   <si>
     <t xml:space="preserve">13.3880252838135</t>
@@ -1241,25 +1241,25 @@
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292505264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.370795249939</t>
+    <t xml:space="preserve">13.6292495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3707942962646</t>
   </si>
   <si>
     <t xml:space="preserve">13.2846431732178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603284835815</t>
+    <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258684158325</t>
+    <t xml:space="preserve">13.5775604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258674621582</t>
   </si>
   <si>
     <t xml:space="preserve">13.508638381958</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634128570557</t>
+    <t xml:space="preserve">13.8634119033813</t>
   </si>
   <si>
     <t xml:space="preserve">13.9517154693604</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161661148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5278644561768</t>
+    <t xml:space="preserve">13.6161670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5278635025024</t>
   </si>
   <si>
     <t xml:space="preserve">13.4219026565552</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982807159424</t>
+    <t xml:space="preserve">13.2982797622681</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753374099731</t>
+    <t xml:space="preserve">14.0753364562988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1349,28 +1349,28 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985059738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3865814208984</t>
+    <t xml:space="preserve">13.5985069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3865823745728</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.722128868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514883041382</t>
+    <t xml:space="preserve">13.7221298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514873504639</t>
   </si>
   <si>
     <t xml:space="preserve">13.4748840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6868095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5808458328247</t>
+    <t xml:space="preserve">13.6868085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
     <t xml:space="preserve">13.6338262557983</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691484451294</t>
+    <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102052688599</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2452983856201</t>
+    <t xml:space="preserve">13.2452993392944</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
+    <t xml:space="preserve">13.2276382446289</t>
   </si>
   <si>
     <t xml:space="preserve">13.3689212799072</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095237731934</t>
+    <t xml:space="preserve">12.6095247268677</t>
   </si>
   <si>
     <t xml:space="preserve">12.5035619735718</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">13.0157127380371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3159408569336</t>
+    <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
     <t xml:space="preserve">12.9980525970459</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391084671021</t>
+    <t xml:space="preserve">12.8391094207764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">12.9274120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8920917510986</t>
+    <t xml:space="preserve">12.8920907974243</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">11.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.461597442627</t>
+    <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
     <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4262771606445</t>
+    <t xml:space="preserve">11.4262762069702</t>
   </si>
   <si>
     <t xml:space="preserve">11.0377492904663</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0730695724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792585372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441654205322</t>
+    <t xml:space="preserve">11.0730686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2849950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441644668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1260509490967</t>
+    <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
     <t xml:space="preserve">11.2496728897095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7728433609009</t>
+    <t xml:space="preserve">10.7728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831371307373</t>
+    <t xml:space="preserve">10.1547298431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299152374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831275939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7198610305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966934204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551832199097</t>
+    <t xml:space="preserve">10.1370687484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7198619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966924667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551822662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">10.24303150177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079364776611</t>
+    <t xml:space="preserve">10.4902772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079374313354</t>
   </si>
   <si>
     <t xml:space="preserve">10.5785779953003</t>
@@ -1625,34 +1625,34 @@
     <t xml:space="preserve">10.7375211715698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8258237838745</t>
+    <t xml:space="preserve">10.8258247375488</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609188079834</t>
+    <t xml:space="preserve">10.5609178543091</t>
   </si>
   <si>
     <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3313322067261</t>
+    <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
     <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4196357727051</t>
+    <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
     <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4372959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8434839248657</t>
+    <t xml:space="preserve">10.437294960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.84348487854</t>
   </si>
   <si>
     <t xml:space="preserve">10.8964653015137</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069101333618</t>
+    <t xml:space="preserve">10.7069110870361</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027828216553</t>
+    <t xml:space="preserve">9.84669876098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027923583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846290588379</t>
+    <t xml:space="preserve">10.0663270950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846300125122</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.139536857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578397750854</t>
+    <t xml:space="preserve">10.1395359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578388214111</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055837631226</t>
+    <t xml:space="preserve">10.5055847167969</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.523886680603</t>
+    <t xml:space="preserve">10.5238876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.560492515564</t>
+    <t xml:space="preserve">10.5604915618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716325759888</t>
+    <t xml:space="preserve">10.8716335296631</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703062057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899345397949</t>
+    <t xml:space="preserve">10.6703052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984228134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899354934692</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193784713745</t>
+    <t xml:space="preserve">11.2193794250488</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644716262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533296585083</t>
+    <t xml:space="preserve">11.1644706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533306121826</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252130508423</t>
+    <t xml:space="preserve">10.7252140045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9448432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461696624756</t>
+    <t xml:space="preserve">10.944842338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109564781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461687088013</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608493804932</t>
+    <t xml:space="preserve">8.23608589172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550142288208</t>
+    <t xml:space="preserve">8.17202758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550094604492</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234245300293</t>
+    <t xml:space="preserve">6.01234292984009</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0098237991333</t>
+    <t xml:space="preserve">7.00982332229614</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.055579662323</t>
+    <t xml:space="preserve">7.05558013916016</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247749328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531511306763</t>
+    <t xml:space="preserve">7.41247701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531558990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568725585938</t>
+    <t xml:space="preserve">7.48568677902222</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303356170654</t>
+    <t xml:space="preserve">6.68038034439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303308486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229166030884</t>
+    <t xml:space="preserve">7.52229118347168</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364547729492</t>
+    <t xml:space="preserve">8.14457225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364643096924</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818256378174</t>
+    <t xml:space="preserve">8.96818161010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.620436668396</t>
+    <t xml:space="preserve">8.62043571472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7968282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003755569458</t>
+    <t xml:space="preserve">7.79682779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003803253174</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63210582733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7236180305481</t>
+    <t xml:space="preserve">7.77852582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6321063041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361755371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642820358276</t>
+    <t xml:space="preserve">7.04642868041992</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340427398682</t>
+    <t xml:space="preserve">6.86340475082397</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46075105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35093688964844</t>
+    <t xml:space="preserve">6.4607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3509373664856</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130760192871</t>
+    <t xml:space="preserve">6.02149391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130807876587</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242164611816</t>
+    <t xml:space="preserve">5.47242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279188156128</t>
+    <t xml:space="preserve">5.25279235839844</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36260652542114</t>
+    <t xml:space="preserve">5.3626070022583</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884021759033</t>
+    <t xml:space="preserve">5.61884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4490818977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324731826782</t>
+    <t xml:space="preserve">7.44908237457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324684143066</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5588960647583</t>
+    <t xml:space="preserve">7.55889654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452289581299</t>
+    <t xml:space="preserve">8.51062202453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847312927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452194213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025131225586</t>
+    <t xml:space="preserve">8.73025035858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176303863525</t>
+    <t xml:space="preserve">8.82176208496094</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0230884552002</t>
+    <t xml:space="preserve">9.13290309906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02308940887451</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179096221924</t>
+    <t xml:space="preserve">9.79179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866186141968</t>
+    <t xml:space="preserve">10.3866195678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998580932617</t>
+    <t xml:space="preserve">9.37998676300049</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89497184753418</t>
+    <t xml:space="preserve">8.8949728012085</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833904266357</t>
+    <t xml:space="preserve">7.88833999633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47401714324951</t>
+    <t xml:space="preserve">8.4740161895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92494487762451</t>
+    <t xml:space="preserve">7.9249439239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735641479492</t>
+    <t xml:space="preserve">6.57056570053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735593795776</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396081924438</t>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661403656006</t>
+    <t xml:space="preserve">6.93661451339722</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -68365,7 +68365,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6873263889</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>6292</v>
@@ -68386,6 +68386,32 @@
         <v>888</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6913078704</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>7607</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>894</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="904">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414552688599</t>
+    <t xml:space="preserve">5.10414505004883</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1539421081543</t>
+    <t xml:space="preserve">5.15394163131714</t>
   </si>
   <si>
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18713998794556</t>
+    <t xml:space="preserve">5.14564180374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18713903427124</t>
   </si>
   <si>
     <t xml:space="preserve">5.11659479141235</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24523544311523</t>
+    <t xml:space="preserve">5.24523639678955</t>
   </si>
   <si>
     <t xml:space="preserve">5.30333185195923</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3863263130188</t>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
     <t xml:space="preserve">5.3489785194397</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122436523438</t>
+    <t xml:space="preserve">5.41122341156006</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">5.48176956176758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9340877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89259099960327</t>
+    <t xml:space="preserve">5.71000385284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93408823013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89259052276611</t>
   </si>
   <si>
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558450698853</t>
+    <t xml:space="preserve">5.85939311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728563308716</t>
@@ -134,34 +134,34 @@
     <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95068645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8759913444519</t>
+    <t xml:space="preserve">5.95068693161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653654098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
     <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05443000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198026657104</t>
+    <t xml:space="preserve">6.05442953109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
     <t xml:space="preserve">6.05857992172241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05027961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327360153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137001037598</t>
+    <t xml:space="preserve">6.05028009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19137048721313</t>
   </si>
   <si>
     <t xml:space="preserve">6.47355031967163</t>
@@ -173,37 +173,37 @@
     <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57314348220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5606951713562</t>
+    <t xml:space="preserve">6.57314395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
     <t xml:space="preserve">6.43205308914185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53994607925415</t>
+    <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8055272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321725845337</t>
+    <t xml:space="preserve">6.63953924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80552673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321678161621</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301288604736</t>
@@ -212,373 +212,373 @@
     <t xml:space="preserve">7.02961158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920570373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034930229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928581237793</t>
+    <t xml:space="preserve">7.05450963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920475006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349254608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234533309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6728982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
   </si>
   <si>
     <t xml:space="preserve">7.67281675338745</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38648653030396</t>
+    <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
     <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36573886871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240310668945</t>
+    <t xml:space="preserve">7.36573839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634912490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9835638999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123792648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617311477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3644847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1994194984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23751163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351942062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729114532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45027303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036104202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56031656265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15286207199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96663284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99626111984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77194023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84812450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672227859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016485214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04704999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858423233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398010253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05551528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00049352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11900186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.008957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402410507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40681028366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373943328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141489028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490194320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652418136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457279205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.449134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378295898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880567550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229272842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163585662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8258228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88930988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470575332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279836654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694181442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30946350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40257692337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137041091919</t>
   </si>
   <si>
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617311477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37295055389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676485061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448526382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830003738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2375111579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588796615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351942062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729066848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45027303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036151885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56031703948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15286159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96663284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99626111984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77194023132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84812498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016485214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858423233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05551528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09783983230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435373306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900186538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00895833969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476945877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207319259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211719512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680932998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43220376968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373991012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141584396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406763076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843252182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814832687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88930940628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470575332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279836654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856548309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61419916152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332323074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020837783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45759916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30946254730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40257692337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137136459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634769439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838804244995</t>
+    <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702981948853</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40567111968994</t>
+    <t xml:space="preserve">8.40567207336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.26599979400635</t>
@@ -614,43 +614,43 @@
     <t xml:space="preserve">8.23213958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30832386016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32525444030762</t>
+    <t xml:space="preserve">8.30832481384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32525539398193</t>
   </si>
   <si>
     <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71040725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.71040916442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514530181885</t>
+    <t xml:space="preserve">9.01514625549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.99821662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04054069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02361106872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19290924072266</t>
+    <t xml:space="preserve">9.04053974151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02360916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19290828704834</t>
   </si>
   <si>
     <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448699951172</t>
+    <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
     <t xml:space="preserve">9.5653657913208</t>
@@ -659,16 +659,16 @@
     <t xml:space="preserve">9.98861217498779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4541826248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773529052734</t>
+    <t xml:space="preserve">10.4541835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325149536133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396308898926</t>
+    <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
@@ -677,25 +677,25 @@
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451494216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620771408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884819030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239217758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7662448883057</t>
+    <t xml:space="preserve">10.9451484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620780944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.055193901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884828567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
     <t xml:space="preserve">11.9355440139771</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973896026611</t>
+    <t xml:space="preserve">12.6973886489868</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
@@ -719,28 +719,28 @@
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.051775932312</t>
+    <t xml:space="preserve">14.0517749786377</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111589431763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460294723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0941009521484</t>
+    <t xml:space="preserve">13.1460285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443185806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0940999984741</t>
   </si>
   <si>
     <t xml:space="preserve">14.5173463821411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206340789795</t>
+    <t xml:space="preserve">14.0009870529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206331253052</t>
   </si>
   <si>
     <t xml:space="preserve">12.8243608474731</t>
@@ -749,40 +749,40 @@
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338359832764</t>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338350296021</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5100212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184860229492</t>
+    <t xml:space="preserve">13.5100202560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184869766235</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7639684677124</t>
+    <t xml:space="preserve">13.7639694213867</t>
   </si>
   <si>
     <t xml:space="preserve">14.0094509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3057231903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3480491638184</t>
+    <t xml:space="preserve">14.3057241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.348048210144</t>
   </si>
   <si>
     <t xml:space="preserve">14.6019954681396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512056350708</t>
+    <t xml:space="preserve">14.5512084960938</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">14.5088815689087</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5004167556763</t>
+    <t xml:space="preserve">14.500415802002</t>
   </si>
   <si>
     <t xml:space="preserve">14.4073038101196</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9840564727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994083404541</t>
+    <t xml:space="preserve">13.984058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994064331055</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385730743408</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">13.1290988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7820377349854</t>
+    <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
     <t xml:space="preserve">12.7397117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0275192260742</t>
+    <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
@@ -848,34 +848,34 @@
     <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071056365967</t>
+    <t xml:space="preserve">13.2071046829224</t>
   </si>
   <si>
     <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0434169769287</t>
+    <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1726446151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0175704956055</t>
+    <t xml:space="preserve">13.439715385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1726455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0175714492798</t>
   </si>
   <si>
     <t xml:space="preserve">13.301872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.1640291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2243375778198</t>
+    <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812601089478</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557321548462</t>
+    <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276026725769</t>
+    <t xml:space="preserve">13.3277187347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8194217681885</t>
+    <t xml:space="preserve">12.8194208145142</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">12.2335872650146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369693756104</t>
+    <t xml:space="preserve">12.3369703292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.0354385375977</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3542013168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2594327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3197393417358</t>
+    <t xml:space="preserve">12.3542003631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
     <t xml:space="preserve">12.1302051544189</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837474822998</t>
+    <t xml:space="preserve">11.9837465286255</t>
   </si>
   <si>
     <t xml:space="preserve">11.8372888565063</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339067459106</t>
+    <t xml:space="preserve">11.7511367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
@@ -992,28 +992,28 @@
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182075500488</t>
+    <t xml:space="preserve">12.0182085037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388206481934</t>
+    <t xml:space="preserve">12.0785150527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.138819694519</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871286392212</t>
+    <t xml:space="preserve">12.0871295928955</t>
   </si>
   <si>
     <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037225723267</t>
+    <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.6988086700439</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591161727905</t>
+    <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231214523315</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7849597930908</t>
+    <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
     <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8366527557373</t>
+    <t xml:space="preserve">12.836651802063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883438110352</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643486022949</t>
+    <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.707423210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126565933228</t>
+    <t xml:space="preserve">12.5868101119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7074241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246551513672</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917259216309</t>
+    <t xml:space="preserve">12.8711128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089559555054</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520324707031</t>
+    <t xml:space="preserve">13.0520315170288</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984901428223</t>
+    <t xml:space="preserve">13.1984910964966</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
@@ -1142,28 +1142,28 @@
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289310455322</t>
+    <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963212966919</t>
+    <t xml:space="preserve">14.5166177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963222503662</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240171432495</t>
+    <t xml:space="preserve">13.7240180969238</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547775268555</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8446311950684</t>
+    <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
     <t xml:space="preserve">14.1117010116577</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
+    <t xml:space="preserve">13.6637115478516</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154035568237</t>
+    <t xml:space="preserve">13.7154026031494</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569473266602</t>
+    <t xml:space="preserve">13.4569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846431732178</t>
+    <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603284835815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3363332748413</t>
+    <t xml:space="preserve">13.3363342285156</t>
   </si>
   <si>
     <t xml:space="preserve">13.5775594711304</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">13.8634128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7751111984253</t>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.775110244751</t>
   </si>
   <si>
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340543746948</t>
+    <t xml:space="preserve">13.9340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219026565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0863542556763</t>
+    <t xml:space="preserve">13.4219017028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0863552093506</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2806196212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">13.2806205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870347976685</t>
+    <t xml:space="preserve">13.9870357513428</t>
   </si>
   <si>
     <t xml:space="preserve">13.8457527160645</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">13.4395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.722128868103</t>
+    <t xml:space="preserve">13.7221298217773</t>
   </si>
   <si>
     <t xml:space="preserve">13.6514883041382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6868095397949</t>
+    <t xml:space="preserve">13.4748849868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6868085861206</t>
   </si>
   <si>
     <t xml:space="preserve">13.5808458328247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338262557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4572229385376</t>
+    <t xml:space="preserve">13.6338272094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4572238922119</t>
   </si>
   <si>
     <t xml:space="preserve">13.4925441741943</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">13.6691484451294</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">13.2276372909546</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3689212799072</t>
+    <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
     <t xml:space="preserve">13.174656867981</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5035619735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0157127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159408569336</t>
+    <t xml:space="preserve">12.5035629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0157136917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
     <t xml:space="preserve">12.9980525970459</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569967269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9274120330811</t>
+    <t xml:space="preserve">13.1569957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9274110794067</t>
   </si>
   <si>
     <t xml:space="preserve">12.8920917510986</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.8567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037881851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">11.267333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.461597442627</t>
+    <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
     <t xml:space="preserve">11.1790323257446</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
+    <t xml:space="preserve">10.9317855834961</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">11.7794857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7618246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7265043258667</t>
+    <t xml:space="preserve">11.7618255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.726505279541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2077102661133</t>
+    <t xml:space="preserve">10.2077112197876</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0200881958008</t>
+    <t xml:space="preserve">11.0200872421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9494476318359</t>
@@ -1577,40 +1577,40 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
+    <t xml:space="preserve">10.154727935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44831371307373</t>
+    <t xml:space="preserve">9.44831275939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
+    <t xml:space="preserve">9.53661441802979</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198610305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966934204102</t>
+    <t xml:space="preserve">10.7198619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.666880607605</t>
+    <t xml:space="preserve">10.6668796539307</t>
   </si>
   <si>
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
+    <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902763366699</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4196357727051</t>
+    <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
     <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4372959136963</t>
+    <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434839248657</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.984766960144</t>
+    <t xml:space="preserve">10.9847679138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.3203153610229</t>
@@ -2721,6 +2721,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.18000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26000022888184</t>
   </si>
 </sst>
 </file>
@@ -68423,7 +68426,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6910185185</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>9064</v>
@@ -68444,6 +68447,32 @@
         <v>902</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6912384259</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>44816</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>903</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414600372314</t>
+    <t xml:space="preserve">5.10414505004883</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1539421081543</t>
+    <t xml:space="preserve">5.15394163131714</t>
   </si>
   <si>
     <t xml:space="preserve">5.09169626235962</t>
@@ -59,37 +59,37 @@
     <t xml:space="preserve">5.1165943145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16224098205566</t>
+    <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24523591995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31163167953491</t>
+    <t xml:space="preserve">5.24523639678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
     <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3489785194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972665786743</t>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632535934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897804260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122388839722</t>
@@ -98,25 +98,25 @@
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462471008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47762012481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48176908493042</t>
+    <t xml:space="preserve">5.39462614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48176956176758</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9340877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89259099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71415328979492</t>
+    <t xml:space="preserve">5.93408823013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89259052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71415376663208</t>
   </si>
   <si>
     <t xml:space="preserve">5.85939359664917</t>
@@ -125,55 +125,55 @@
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728563308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90088987350464</t>
+    <t xml:space="preserve">5.96728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
     <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95068645477295</t>
+    <t xml:space="preserve">5.95068693161011</t>
   </si>
   <si>
     <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87599229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8676929473877</t>
+    <t xml:space="preserve">5.87599182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
     <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04198026657104</t>
+    <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05027961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327360153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137048721313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47355079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36150789260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239534378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57314300537109</t>
+    <t xml:space="preserve">6.05028009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1332745552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19137001037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47355031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5523943901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57314395904541</t>
   </si>
   <si>
     <t xml:space="preserve">6.56069469451904</t>
@@ -182,64 +182,64 @@
     <t xml:space="preserve">6.43205308914185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53994607925415</t>
+    <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559274673462</t>
+    <t xml:space="preserve">6.58559322357178</t>
   </si>
   <si>
     <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61464071273804</t>
+    <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80552673339844</t>
+    <t xml:space="preserve">6.80552768707275</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301288604736</t>
+    <t xml:space="preserve">7.01301336288452</t>
   </si>
   <si>
     <t xml:space="preserve">7.02961158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05451011657715</t>
+    <t xml:space="preserve">7.05450963973999</t>
   </si>
   <si>
     <t xml:space="preserve">7.12920475006104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30349349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234580993652</t>
+    <t xml:space="preserve">7.30349254608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234533309937</t>
   </si>
   <si>
     <t xml:space="preserve">8.67289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798519134521</t>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648653030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
     <t xml:space="preserve">7.3657374382019</t>
@@ -251,67 +251,67 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643760681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22058010101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961521148682</t>
+    <t xml:space="preserve">7.43643712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
     <t xml:space="preserve">6.80156755447388</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98356342315674</t>
+    <t xml:space="preserve">6.98356294631958</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617263793945</t>
+    <t xml:space="preserve">6.77617216110229</t>
   </si>
   <si>
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202823638916</t>
+    <t xml:space="preserve">6.99202871322632</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145889282227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37294960021973</t>
+    <t xml:space="preserve">7.37295055389404</t>
   </si>
   <si>
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290607452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523061752319</t>
+    <t xml:space="preserve">7.29253244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523109436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830051422119</t>
+    <t xml:space="preserve">7.19941854476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830099105835</t>
   </si>
   <si>
     <t xml:space="preserve">7.2375111579895</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821298599243</t>
+    <t xml:space="preserve">7.06821250915527</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588796615601</t>
@@ -332,85 +332,85 @@
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036104202271</t>
+    <t xml:space="preserve">6.45027256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036151885986</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286207199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514261245728</t>
+    <t xml:space="preserve">7.15286159515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626064300537</t>
+    <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
     <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77193975448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84812498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621759414673</t>
+    <t xml:space="preserve">6.77194023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84812450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
     <t xml:space="preserve">7.18672132492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11053705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128240585327</t>
+    <t xml:space="preserve">7.11053657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128288269043</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360694885254</t>
+    <t xml:space="preserve">7.10630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360790252686</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04704999923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0555157661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09783983230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00049352645874</t>
+    <t xml:space="preserve">7.05974769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858423233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011989593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398105621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05551528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0004940032959</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
@@ -419,37 +419,37 @@
     <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00895738601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476945877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207223892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402410507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597644805908</t>
+    <t xml:space="preserve">7.00895833969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476898193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987970352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402505874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597692489624</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43220472335815</t>
+    <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
     <t xml:space="preserve">7.49992370605469</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">7.28406763076782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44490146636963</t>
+    <t xml:space="preserve">7.44490242004395</t>
   </si>
   <si>
     <t xml:space="preserve">7.39834451675415</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">7.64382743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83005571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349828720093</t>
+    <t xml:space="preserve">7.83005619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349781036377</t>
   </si>
   <si>
     <t xml:space="preserve">7.58457279205322</t>
@@ -491,121 +491,121 @@
     <t xml:space="preserve">7.449134349823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53378391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229272842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540662765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814880371094</t>
+    <t xml:space="preserve">7.53378248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880662918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
   </si>
   <si>
     <t xml:space="preserve">7.93163442611694</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92316913604736</t>
+    <t xml:space="preserve">7.92317008972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.8258228302002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88931035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470575332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856405258179</t>
+    <t xml:space="preserve">7.88930988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470670700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856452941895</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6141996383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332275390625</t>
+    <t xml:space="preserve">7.70308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332227706909</t>
   </si>
   <si>
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45759963989258</t>
+    <t xml:space="preserve">7.45760011672974</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73694229125977</t>
+    <t xml:space="preserve">7.73694181442261</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30946350097656</t>
+    <t xml:space="preserve">7.30946254730225</t>
   </si>
   <si>
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137041091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702934265137</t>
+    <t xml:space="preserve">7.34755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702886581421</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474784851074</t>
+    <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707286834717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21097850799561</t>
+    <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40990257263184</t>
+    <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
     <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40567016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26599979400635</t>
+    <t xml:space="preserve">8.40567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26599884033203</t>
   </si>
   <si>
     <t xml:space="preserve">8.23214054107666</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027667999268</t>
+    <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99821662902832</t>
+    <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
@@ -650,28 +650,28 @@
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56536674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861217498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773338317871</t>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773433685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396213531494</t>
+    <t xml:space="preserve">9.90396308898926</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927799224854</t>
+    <t xml:space="preserve">10.7927808761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191846847534</t>
+    <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7239208221436</t>
+    <t xml:space="preserve">11.7239227294922</t>
   </si>
   <si>
     <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741422653198</t>
+    <t xml:space="preserve">11.9355440139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.6973886489868</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633991241455</t>
+    <t xml:space="preserve">13.3491878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633981704712</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
@@ -722,58 +722,58 @@
     <t xml:space="preserve">12.5111598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0940999984741</t>
+    <t xml:space="preserve">13.1460294723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443185806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0941009521484</t>
   </si>
   <si>
     <t xml:space="preserve">14.5173473358154</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009870529175</t>
+    <t xml:space="preserve">14.0009880065918</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4169063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438795089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5100202560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930906295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7639694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0094499588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057241439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.348048210144</t>
+    <t xml:space="preserve">12.8243608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4169073104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184869766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930896759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7639684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0094509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057231903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3480501174927</t>
   </si>
   <si>
     <t xml:space="preserve">14.601996421814</t>
@@ -785,31 +785,31 @@
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088815689087</t>
+    <t xml:space="preserve">14.5088806152344</t>
   </si>
   <si>
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311185836792</t>
+    <t xml:space="preserve">14.4073038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157676696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311195373535</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8655471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978277206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840564727783</t>
+    <t xml:space="preserve">13.8655462265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978267669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840574264526</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290988922119</t>
+    <t xml:space="preserve">13.1290979385376</t>
   </si>
   <si>
     <t xml:space="preserve">12.7820377349854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397127151489</t>
+    <t xml:space="preserve">12.7397117614746</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275192260742</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523452758789</t>
+    <t xml:space="preserve">13.5523443222046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0348014831543</t>
+    <t xml:space="preserve">13.2071046829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.03480052948</t>
   </si>
   <si>
     <t xml:space="preserve">13.043417930603</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1726446151733</t>
+    <t xml:space="preserve">13.4397163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1726455688477</t>
   </si>
   <si>
     <t xml:space="preserve">13.0175714492798</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">13.1640291213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6901922225952</t>
+    <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243366241455</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123390197754</t>
+    <t xml:space="preserve">13.1123380661011</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277187347412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.276026725769</t>
+    <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314203262329</t>
+    <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">12.3369703292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.035439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975954055786</t>
+    <t xml:space="preserve">12.0354385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975963592529</t>
   </si>
   <si>
     <t xml:space="preserve">12.1474370956421</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">12.3542003631592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2594327926636</t>
+    <t xml:space="preserve">12.2594337463379</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837474822998</t>
+    <t xml:space="preserve">11.9837465286255</t>
   </si>
   <si>
     <t xml:space="preserve">11.837287902832</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286724090576</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511377334595</t>
+    <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339057922363</t>
@@ -986,22 +986,22 @@
     <t xml:space="preserve">11.604679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182085037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612840652466</t>
+    <t xml:space="preserve">11.6305236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612831115723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0785140991211</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1388216018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440540313721</t>
+    <t xml:space="preserve">12.1388206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
     <t xml:space="preserve">12.0871295928955</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231233596802</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.4661989212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">12.5351209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265054702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7849607467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9141893386841</t>
+    <t xml:space="preserve">12.5265045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
     <t xml:space="preserve">12.836651802063</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7074241638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
+    <t xml:space="preserve">12.7074251174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126585006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.871111869812</t>
+    <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
     <t xml:space="preserve">12.9917259216309</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">13.0089569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572658538818</t>
+    <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984901428223</t>
+    <t xml:space="preserve">13.1984910964966</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">13.6550960540771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757081985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843236923218</t>
+    <t xml:space="preserve">13.7757091522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498626708984</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907712936401</t>
+    <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
     <t xml:space="preserve">14.5166168212891</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8963222503662</t>
+    <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618621826172</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255508422852</t>
+    <t xml:space="preserve">14.0255498886108</t>
   </si>
   <si>
     <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8446311950684</t>
+    <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
     <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9221677780151</t>
+    <t xml:space="preserve">13.9221668243408</t>
   </si>
   <si>
     <t xml:space="preserve">13.7929391860962</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637115478516</t>
+    <t xml:space="preserve">13.6637125015259</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704776763916</t>
+    <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
     <t xml:space="preserve">13.8360157012939</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6809415817261</t>
+    <t xml:space="preserve">13.6809425354004</t>
   </si>
   <si>
     <t xml:space="preserve">13.4569463729858</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1106586456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9340543746948</t>
+    <t xml:space="preserve">14.1106576919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278654098511</t>
+    <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
     <t xml:space="preserve">13.4219026565552</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982797622681</t>
+    <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870347976685</t>
+    <t xml:space="preserve">13.9870357513428</t>
   </si>
   <si>
     <t xml:space="preserve">13.8457517623901</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8104314804077</t>
+    <t xml:space="preserve">13.810432434082</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691474914551</t>
+    <t xml:space="preserve">13.6691484451294</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102043151855</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
+    <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1400,25 +1400,25 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
+    <t xml:space="preserve">13.2276382446289</t>
   </si>
   <si>
     <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1746578216553</t>
+    <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629585266113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.980393409729</t>
+    <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
     <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5035610198975</t>
+    <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
     <t xml:space="preserve">13.0157136917114</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">13.3159408569336</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9097509384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0333738327026</t>
+    <t xml:space="preserve">12.9980525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9097499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033374786377</t>
   </si>
   <si>
     <t xml:space="preserve">13.1569957733154</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.121675491333</t>
+    <t xml:space="preserve">13.1216764450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037891387939</t>
+    <t xml:space="preserve">12.8567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037881851196</t>
   </si>
   <si>
     <t xml:space="preserve">12.2386560440063</t>
@@ -1490,19 +1490,19 @@
     <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.037748336792</t>
+    <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
     <t xml:space="preserve">11.0024271011353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2143526077271</t>
+    <t xml:space="preserve">11.2143535614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">11.7618246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7265033721924</t>
+    <t xml:space="preserve">11.7265043258667</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1574,13 +1574,13 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
+    <t xml:space="preserve">10.154727935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44831371307373</t>
+    <t xml:space="preserve">9.44831275939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1966924667358</t>
+    <t xml:space="preserve">11.1966915130615</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551822662354</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2783517837524</t>
+    <t xml:space="preserve">10.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430305480957</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">10.5079364776611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5785789489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6845407485962</t>
+    <t xml:space="preserve">10.5785779953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
     <t xml:space="preserve">10.7375221252441</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
-    <t xml:space="preserve">10.613899230957</t>
+    <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
     <t xml:space="preserve">10.5609188079834</t>
@@ -1637,16 +1637,16 @@
     <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3313331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.3313322067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019746780396</t>
+    <t xml:space="preserve">10.4019737243652</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">10.8964653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9141263961792</t>
+    <t xml:space="preserve">10.9141254425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.0554103851318</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069110870361</t>
+    <t xml:space="preserve">10.7069101333618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027923583984</t>
+    <t xml:space="preserve">9.84669780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846300125122</t>
+    <t xml:space="preserve">10.0663261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846290588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578388214111</t>
+    <t xml:space="preserve">10.139536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578397750854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055847167969</t>
+    <t xml:space="preserve">10.5055837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5238876342773</t>
+    <t xml:space="preserve">10.523886680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5604915618896</t>
+    <t xml:space="preserve">10.560492515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716335296631</t>
+    <t xml:space="preserve">10.8716325759888</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899354934692</t>
+    <t xml:space="preserve">10.6703062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899345397949</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193794250488</t>
+    <t xml:space="preserve">11.2193784713745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533306121826</t>
+    <t xml:space="preserve">11.1644716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252140045166</t>
+    <t xml:space="preserve">10.7252130508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944842338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461687088013</t>
+    <t xml:space="preserve">10.9448432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608589172363</t>
+    <t xml:space="preserve">8.23608493804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550094604492</t>
+    <t xml:space="preserve">8.17202663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550142288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234292984009</t>
+    <t xml:space="preserve">6.01234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00982332229614</t>
+    <t xml:space="preserve">7.0098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558013916016</t>
+    <t xml:space="preserve">7.055579662323</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531558990479</t>
+    <t xml:space="preserve">7.41247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531511306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568677902222</t>
+    <t xml:space="preserve">7.48568725585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038034439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303308486938</t>
+    <t xml:space="preserve">6.68038082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229118347168</t>
+    <t xml:space="preserve">7.52229166030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364643096924</t>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364547729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818161010742</t>
+    <t xml:space="preserve">8.96818256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62043571472168</t>
+    <t xml:space="preserve">8.620436668396</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003803253174</t>
+    <t xml:space="preserve">7.7968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003755569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6321063041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361755371094</t>
+    <t xml:space="preserve">7.77852535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63210582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236180305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642868041992</t>
+    <t xml:space="preserve">7.04642820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340475082397</t>
+    <t xml:space="preserve">6.86340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3509373664856</t>
+    <t xml:space="preserve">6.46075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35093688964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130807876587</t>
+    <t xml:space="preserve">6.02149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242116928101</t>
+    <t xml:space="preserve">5.47242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279235839844</t>
+    <t xml:space="preserve">5.25279188156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626070022583</t>
+    <t xml:space="preserve">5.36260652542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884069442749</t>
+    <t xml:space="preserve">5.61884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44908237457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324684143066</t>
+    <t xml:space="preserve">7.4490818977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324731826782</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55889654159546</t>
+    <t xml:space="preserve">7.5588960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062202453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452194213867</t>
+    <t xml:space="preserve">8.51062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452289581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025035858154</t>
+    <t xml:space="preserve">8.73025131225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176208496094</t>
+    <t xml:space="preserve">8.82176303863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308940887451</t>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179000854492</t>
+    <t xml:space="preserve">9.79179096221924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866195678711</t>
+    <t xml:space="preserve">10.3866186141968</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998676300049</t>
+    <t xml:space="preserve">9.37998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8949728012085</t>
+    <t xml:space="preserve">8.89497184753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833999633789</t>
+    <t xml:space="preserve">7.88833904266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4740161895752</t>
+    <t xml:space="preserve">8.47401714324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9249439239502</t>
+    <t xml:space="preserve">7.92494487762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735593795776</t>
+    <t xml:space="preserve">6.57056617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735641479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.53396081924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661451339722</t>
+    <t xml:space="preserve">6.93661403656006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -68475,7 +68475,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6909722222</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>6997</v>
@@ -68496,6 +68496,32 @@
         <v>896</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6912037037</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>6115</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>894</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414505004883</t>
+    <t xml:space="preserve">5.10414552688599</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394163131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169626235962</t>
+    <t xml:space="preserve">5.1539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169673919678</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1165943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523639678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333185195923</t>
+    <t xml:space="preserve">5.18713998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958925247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523591995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
@@ -80,73 +80,73 @@
     <t xml:space="preserve">5.34482908248901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38632535934448</t>
+    <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
     <t xml:space="preserve">5.34897804260254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35312843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122388839722</t>
+    <t xml:space="preserve">5.35312795639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122341156006</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48176956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71000385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93408823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89259052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71415376663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939359664917</t>
+    <t xml:space="preserve">5.39462518692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48176908493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71000337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9340877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89259099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939311981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728515625</t>
+    <t xml:space="preserve">5.96728610992432</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068693161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653701782227</t>
+    <t xml:space="preserve">5.96313524246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653654098511</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86769247055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05443000793457</t>
+    <t xml:space="preserve">5.8676929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
@@ -158,28 +158,28 @@
     <t xml:space="preserve">6.05028009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1332745552063</t>
+    <t xml:space="preserve">6.13327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355031967163</t>
+    <t xml:space="preserve">6.47355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5523943901062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57314395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205308914185</t>
+    <t xml:space="preserve">6.55239534378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57314348220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5606951713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.432053565979</t>
   </si>
   <si>
     <t xml:space="preserve">6.53994560241699</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559322357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804201126099</t>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804105758667</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464023590088</t>
@@ -200,70 +200,70 @@
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80552768707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321630477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301336288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05450963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920475006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234533309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281675338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648653030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3657374382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961568832397</t>
+    <t xml:space="preserve">6.8055272102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234485626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67289638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648748397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4279842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634817123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22058057785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788478851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961521148682</t>
   </si>
   <si>
     <t xml:space="preserve">6.80156755447388</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37295055389404</t>
+    <t xml:space="preserve">6.77617311477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37294912338257</t>
   </si>
   <si>
     <t xml:space="preserve">7.27983617782593</t>
@@ -299,28 +299,28 @@
     <t xml:space="preserve">7.29676532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523109436035</t>
+    <t xml:space="preserve">7.26290559768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523014068604</t>
   </si>
   <si>
     <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941854476929</t>
+    <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2375111579895</t>
+    <t xml:space="preserve">7.23751258850098</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821250915527</t>
+    <t xml:space="preserve">7.06821346282959</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588796615601</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027256011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036151885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56031703948975</t>
+    <t xml:space="preserve">6.45027303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036104202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5603175163269</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286159515381</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96663284301758</t>
+    <t xml:space="preserve">6.96663331985474</t>
   </si>
   <si>
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538328170776</t>
+    <t xml:space="preserve">6.72538280487061</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84812450408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621711730957</t>
+    <t xml:space="preserve">6.84812498092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621664047241</t>
   </si>
   <si>
     <t xml:space="preserve">7.18672132492065</t>
@@ -371,37 +371,37 @@
     <t xml:space="preserve">7.11053657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128288269043</t>
+    <t xml:space="preserve">7.05128335952759</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360790252686</t>
+    <t xml:space="preserve">7.10630464553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974769592285</t>
+    <t xml:space="preserve">7.05974817276001</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858423233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03011989593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398105621338</t>
+    <t xml:space="preserve">6.97086524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0639796257019</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">7.09783935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435325622559</t>
+    <t xml:space="preserve">7.00049352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435230255127</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900186538696</t>
@@ -422,37 +422,37 @@
     <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476898193359</t>
+    <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
     <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402505874634</t>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2036509513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402410507202</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680980682373</t>
+    <t xml:space="preserve">7.24597644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680932998657</t>
   </si>
   <si>
     <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49992370605469</t>
+    <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373943328857</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.28406763076782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44490242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834451675415</t>
+    <t xml:space="preserve">7.44490146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
     <t xml:space="preserve">7.47452878952026</t>
@@ -476,58 +476,58 @@
     <t xml:space="preserve">7.64382743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83005619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652513504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880662918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229177474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69884967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540710449219</t>
+    <t xml:space="preserve">7.83005571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652561187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540615081787</t>
   </si>
   <si>
     <t xml:space="preserve">7.86814785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88930988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279741287231</t>
+    <t xml:space="preserve">7.9316349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582330703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470527648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279884338379</t>
   </si>
   <si>
     <t xml:space="preserve">7.94856452941895</t>
@@ -536,49 +536,49 @@
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420011520386</t>
+    <t xml:space="preserve">7.70308303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420059204102</t>
   </si>
   <si>
     <t xml:space="preserve">7.42797183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34332227706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020837783813</t>
+    <t xml:space="preserve">7.34332275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">7.45760011672974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63536310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694181442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685380935669</t>
+    <t xml:space="preserve">7.63536262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685333251953</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40257692337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137088775635</t>
+    <t xml:space="preserve">7.4025764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137184143066</t>
   </si>
   <si>
     <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702886581421</t>
+    <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097755432129</t>
+    <t xml:space="preserve">8.06707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097660064697</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
@@ -605,31 +605,31 @@
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599884033203</t>
+    <t xml:space="preserve">8.26600074768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30832386016846</t>
+    <t xml:space="preserve">8.30832481384277</t>
   </si>
   <si>
     <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027572631836</t>
+    <t xml:space="preserve">8.38027477264404</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.87970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514530181885</t>
+    <t xml:space="preserve">9.01514434814453</t>
   </si>
   <si>
     <t xml:space="preserve">8.998215675354</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17597961425781</t>
+    <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
@@ -653,28 +653,28 @@
     <t xml:space="preserve">9.5653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98861312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773433685303</t>
+    <t xml:space="preserve">9.98861217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541826248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773242950439</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396308898926</t>
+    <t xml:space="preserve">9.90396118164062</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927808761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9451484680176</t>
+    <t xml:space="preserve">10.7927799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9451475143433</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
@@ -683,34 +683,34 @@
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191837310791</t>
+    <t xml:space="preserve">11.4191846847534</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7239227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.76624584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355440139771</t>
+    <t xml:space="preserve">11.7239217758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7662448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355449676514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629590988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3491878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633981704712</t>
+    <t xml:space="preserve">12.6973876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3491868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634000778198</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
@@ -722,34 +722,34 @@
     <t xml:space="preserve">12.5111598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460294723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443185806274</t>
+    <t xml:space="preserve">13.1460275650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443195343018</t>
   </si>
   <si>
     <t xml:space="preserve">14.0941009521484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206340789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8243608474731</t>
+    <t xml:space="preserve">14.5173463821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009870529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8243618011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338359832764</t>
+    <t xml:space="preserve">13.4761619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338369369507</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">13.5100212097168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184869766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930896759033</t>
+    <t xml:space="preserve">13.5184860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930906295776</t>
   </si>
   <si>
     <t xml:space="preserve">13.7639684677124</t>
@@ -773,49 +773,49 @@
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480501174927</t>
+    <t xml:space="preserve">14.348048210144</t>
   </si>
   <si>
     <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512075424194</t>
+    <t xml:space="preserve">14.5512056350708</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004167556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655462265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978267669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840574264526</t>
+    <t xml:space="preserve">14.508882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.407301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157695770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978277206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385730743408</t>
+    <t xml:space="preserve">13.7385740280151</t>
   </si>
   <si>
     <t xml:space="preserve">13.6031351089478</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">12.7820377349854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0275192260742</t>
+    <t xml:space="preserve">12.7397127151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523443222046</t>
+    <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
@@ -845,64 +845,64 @@
     <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071046829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.03480052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.043417930603</t>
+    <t xml:space="preserve">13.2071056365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0348024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0434169769287</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1726455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0175714492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3018732070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1640291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1295680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8797273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2243366241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812601089478</t>
+    <t xml:space="preserve">13.4397172927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1726446151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0175704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.301872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1640310287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1295690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8797283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901941299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2243375778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557331085205</t>
+    <t xml:space="preserve">12.9228038787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557321548462</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277187347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2760276794434</t>
+    <t xml:space="preserve">13.3277196884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
@@ -923,40 +923,40 @@
     <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369703292847</t>
+    <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.0354385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8975963592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474370956421</t>
+    <t xml:space="preserve">11.8975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2594337463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3197402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.2594327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3197393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837465286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.837287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7855968475342</t>
+    <t xml:space="preserve">11.9837474822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8372888565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166767120361</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769823074341</t>
+    <t xml:space="preserve">11.7769832611084</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.604679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182075500488</t>
+    <t xml:space="preserve">11.6046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6305246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182065963745</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388206481934</t>
+    <t xml:space="preserve">12.0785160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388216018677</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.103723526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6988077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">13.1037225723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6988086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920444488525</t>
+    <t xml:space="preserve">12.4920434951782</t>
   </si>
   <si>
     <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628168106079</t>
+    <t xml:space="preserve">12.3628158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7849617004395</t>
+    <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
     <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
-    <t xml:space="preserve">12.836651802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883428573608</t>
+    <t xml:space="preserve">12.8366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883438110352</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1067,37 +1067,37 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7504997253418</t>
+    <t xml:space="preserve">12.6643476486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7074251174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126585006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246541976929</t>
+    <t xml:space="preserve">12.7074241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126565933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246551513672</t>
   </si>
   <si>
     <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8280372619629</t>
+    <t xml:space="preserve">12.8280363082886</t>
   </si>
   <si>
     <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8711128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917259216309</t>
+    <t xml:space="preserve">12.871111869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917268753052</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089569091797</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984910964966</t>
+    <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550960540771</t>
+    <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
     <t xml:space="preserve">13.7757091522217</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498626708984</t>
+    <t xml:space="preserve">13.7498645782471</t>
   </si>
   <si>
     <t xml:space="preserve">14.1289319992065</t>
@@ -1145,28 +1145,28 @@
     <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
+    <t xml:space="preserve">14.5166177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
   </si>
   <si>
     <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8618621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1547784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443117141724</t>
+    <t xml:space="preserve">13.8618612289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240171432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1547775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255498886108</t>
@@ -1175,25 +1175,25 @@
     <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.844630241394</t>
+    <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9221668243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206359863281</t>
+    <t xml:space="preserve">13.9221677780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206369400024</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637125015259</t>
+    <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704767227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8015546798706</t>
+    <t xml:space="preserve">13.870475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360147476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6809425354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4569463729858</t>
+    <t xml:space="preserve">13.6809415817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4569473266602</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3191032409668</t>
+    <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
     <t xml:space="preserve">13.3880252838135</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846422195435</t>
+    <t xml:space="preserve">13.2846431732178</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603284835815</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5258693695068</t>
+    <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
     <t xml:space="preserve">13.508638381958</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">13.8634128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.951714515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693756103516</t>
+    <t xml:space="preserve">13.9517154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693737030029</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340534210205</t>
+    <t xml:space="preserve">13.9340543746948</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161670684814</t>
+    <t xml:space="preserve">13.6161661148071</t>
   </si>
   <si>
     <t xml:space="preserve">13.5278644561768</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686941146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402433395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872619628906</t>
+    <t xml:space="preserve">13.0686960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872629165649</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.004695892334</t>
+    <t xml:space="preserve">14.0046949386597</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1337,43 +1337,43 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870357513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8457517623901</t>
+    <t xml:space="preserve">13.9870347976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8457527160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.810432434082</t>
+    <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865823745728</t>
+    <t xml:space="preserve">13.3865814208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7221298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514873504639</t>
+    <t xml:space="preserve">13.722128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514883041382</t>
   </si>
   <si>
     <t xml:space="preserve">13.4748840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6868085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.580846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6338272094727</t>
+    <t xml:space="preserve">13.6868095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5808458328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6338262557983</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">13.6691484451294</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102043151855</t>
+    <t xml:space="preserve">13.5102052688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689222335815</t>
+    <t xml:space="preserve">13.2276372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689212799072</t>
   </si>
   <si>
     <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629585266113</t>
+    <t xml:space="preserve">13.2629594802856</t>
   </si>
   <si>
     <t xml:space="preserve">12.9803924560547</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157136917114</t>
+    <t xml:space="preserve">13.0157127380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159408569336</t>
@@ -1430,43 +1430,43 @@
     <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9097499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.033374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1569957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099781036377</t>
+    <t xml:space="preserve">12.9097509384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391084671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0333738327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1569967269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099771499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8920907974243</t>
+    <t xml:space="preserve">12.8920917510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1216764450073</t>
+    <t xml:space="preserve">13.121675491333</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037881851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2386560440063</t>
+    <t xml:space="preserve">12.8567695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037891387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1481,10 +1481,10 @@
     <t xml:space="preserve">11.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615983963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1790313720703</t>
+    <t xml:space="preserve">11.461597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0024271011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143535614014</t>
+    <t xml:space="preserve">11.0024280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143526077271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496738433838</t>
+    <t xml:space="preserve">11.1260509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496728897095</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549560546875</t>
+    <t xml:space="preserve">10.4549551010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439373016357</t>
+    <t xml:space="preserve">11.4439382553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494466781616</t>
+    <t xml:space="preserve">10.9494476318359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.154727935791</t>
+    <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44831275939941</t>
+    <t xml:space="preserve">9.44831371307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
@@ -1592,22 +1592,22 @@
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198619842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551822662354</t>
+    <t xml:space="preserve">10.7198610305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966934204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2783527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2430305480957</t>
+    <t xml:space="preserve">10.2783517837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.24303150177</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902763366699</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375221252441</t>
+    <t xml:space="preserve">10.7375211715698</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258237838745</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606906890869</t>
+    <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313322067261</t>
@@ -1643,13 +1643,13 @@
     <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4196348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4019737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.437294960022</t>
+    <t xml:space="preserve">10.4196357727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4019746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4372959136963</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434839248657</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">10.9141254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554103851318</t>
+    <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -68501,7 +68501,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6912037037</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>6115</v>
@@ -68522,6 +68522,32 @@
         <v>894</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6912962963</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>34540</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169673919678</t>
+    <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">5.18713998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11659479141235</t>
+    <t xml:space="preserve">5.1165943145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224098205566</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482908248901</t>
+    <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
     <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34897804260254</t>
+    <t xml:space="preserve">5.3489785194397</t>
   </si>
   <si>
     <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122341156006</t>
+    <t xml:space="preserve">5.36972665786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122484207153</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
@@ -104,40 +104,40 @@
     <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71000337600708</t>
+    <t xml:space="preserve">5.48176956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259099960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939311981201</t>
+    <t xml:space="preserve">5.89259052276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71415376663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939264297485</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728610992432</t>
+    <t xml:space="preserve">5.96728563308716</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313524246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653654098511</t>
+    <t xml:space="preserve">5.96313571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068693161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599182128906</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0419807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05857944488525</t>
+    <t xml:space="preserve">6.04198026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05857992172241</t>
   </si>
   <si>
     <t xml:space="preserve">6.05028009414673</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355079650879</t>
+    <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
     <t xml:space="preserve">6.3615083694458</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5606951713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.432053565979</t>
+    <t xml:space="preserve">6.56069469451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43205308914185</t>
   </si>
   <si>
     <t xml:space="preserve">6.53994560241699</t>
@@ -200,58 +200,58 @@
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8055272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321678161621</t>
+    <t xml:space="preserve">6.80552768707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301288604736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02961206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920618057251</t>
+    <t xml:space="preserve">7.02961254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451059341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920522689819</t>
   </si>
   <si>
     <t xml:space="preserve">7.3034930229187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46948146820068</t>
+    <t xml:space="preserve">7.46948099136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234485626221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67289638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648748397827</t>
+    <t xml:space="preserve">8.67289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
     <t xml:space="preserve">7.4279842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36573886871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240262985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634817123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643569946289</t>
+    <t xml:space="preserve">7.36573839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643617630005</t>
   </si>
   <si>
     <t xml:space="preserve">7.22058057785034</t>
@@ -260,61 +260,61 @@
     <t xml:space="preserve">7.20788478851318</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89468193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617311477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933149337769</t>
+    <t xml:space="preserve">6.89468145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9835638999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123888015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933053970337</t>
   </si>
   <si>
     <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49145936965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37294912338257</t>
+    <t xml:space="preserve">7.49145984649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37294960021973</t>
   </si>
   <si>
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676532745361</t>
+    <t xml:space="preserve">7.29253339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676485061646</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290559768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30523014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3644847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994194984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830099105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23751258850098</t>
+    <t xml:space="preserve">7.30523061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36448526382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23751163482666</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132688522339</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">7.06821346282959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588796615601</t>
+    <t xml:space="preserve">7.02588844299316</t>
   </si>
   <si>
     <t xml:space="preserve">6.87351894378662</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538280487061</t>
+    <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
@@ -365,31 +365,31 @@
     <t xml:space="preserve">6.88621664047241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18672132492065</t>
+    <t xml:space="preserve">7.1867208480835</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128335952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016485214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0936074256897</t>
+    <t xml:space="preserve">7.05128288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016437530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360694885254</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705047607422</t>
+    <t xml:space="preserve">7.05974769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04704999923706</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086524963379</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">7.03858518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0639796257019</t>
+    <t xml:space="preserve">7.03012037277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398010253906</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
@@ -413,16 +413,16 @@
     <t xml:space="preserve">7.00049352645874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03435230255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900186538696</t>
+    <t xml:space="preserve">7.03435277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1190013885498</t>
   </si>
   <si>
     <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476945877075</t>
+    <t xml:space="preserve">7.11476993560791</t>
   </si>
   <si>
     <t xml:space="preserve">7.10207271575928</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">7.2036509513855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402410507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597644805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680932998657</t>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597597122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
     <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49992322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373943328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406763076782</t>
+    <t xml:space="preserve">7.49992370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373991012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406858444214</t>
   </si>
   <si>
     <t xml:space="preserve">7.44490146636963</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452878952026</t>
+    <t xml:space="preserve">7.47452926635742</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382743835449</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.65652561187744</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78349924087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457326889038</t>
+    <t xml:space="preserve">7.78349828720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457279205322</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913482666016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53378391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
+    <t xml:space="preserve">7.53378343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843204498291</t>
   </si>
   <si>
     <t xml:space="preserve">7.58880519866943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
+    <t xml:space="preserve">7.65229177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
   </si>
   <si>
     <t xml:space="preserve">7.74540615081787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86814785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9316349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316961288452</t>
+    <t xml:space="preserve">7.86814832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.82582330703735</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">7.88931083679199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91470527648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856452941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553863525391</t>
+    <t xml:space="preserve">7.91470575332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856405258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553958892822</t>
   </si>
   <si>
     <t xml:space="preserve">7.70308303833008</t>
@@ -542,25 +542,25 @@
     <t xml:space="preserve">7.61420059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45760011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685333251953</t>
+    <t xml:space="preserve">7.42797136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536214828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694133758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946254730225</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">7.34755563735962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27137184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702934265137</t>
+    <t xml:space="preserve">7.27137136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838899612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95703029632568</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023220062256</t>
+    <t xml:space="preserve">8.06707286834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097755432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023315429688</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990352630615</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30832481384277</t>
+    <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
     <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027477264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87970542907715</t>
+    <t xml:space="preserve">8.38027572631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290924072266</t>
+    <t xml:space="preserve">9.19290828704834</t>
   </si>
   <si>
     <t xml:space="preserve">9.1759786605835</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">10.4541826248169</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773242950439</t>
+    <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
@@ -668,70 +668,70 @@
     <t xml:space="preserve">9.90396118164062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.496506690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7927799224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9451475143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620780944824</t>
+    <t xml:space="preserve">10.4965085983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7927808761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9451484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620790481567</t>
   </si>
   <si>
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191846847534</t>
+    <t xml:space="preserve">11.4191827774048</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7239217758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7662448883057</t>
+    <t xml:space="preserve">11.7239227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
     <t xml:space="preserve">11.9355449676514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2741413116455</t>
+    <t xml:space="preserve">12.2741422653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.6973876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1629581451416</t>
+    <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
     <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634000778198</t>
+    <t xml:space="preserve">14.2634010314941</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.051775932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173463821411</t>
+    <t xml:space="preserve">14.0517768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443204879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0940999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173473358154</t>
   </si>
   <si>
     <t xml:space="preserve">14.0009870529175</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">13.1206350326538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4169073104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761619567871</t>
+    <t xml:space="preserve">12.8243627548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4169082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5100212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184860229492</t>
+    <t xml:space="preserve">13.5100202560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184850692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930906295776</t>
@@ -767,28 +767,28 @@
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094509124756</t>
+    <t xml:space="preserve">14.0094518661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348048210144</t>
+    <t xml:space="preserve">14.3480491638184</t>
   </si>
   <si>
     <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512056350708</t>
+    <t xml:space="preserve">14.5512075424194</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.508882522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.500415802002</t>
+    <t xml:space="preserve">14.5088815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
     <t xml:space="preserve">14.407301902771</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">14.4157695770264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3311185836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618185043335</t>
+    <t xml:space="preserve">14.3311195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
     <t xml:space="preserve">13.8655471801758</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385740280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031351089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290979385376</t>
+    <t xml:space="preserve">13.7385730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290988922119</t>
   </si>
   <si>
     <t xml:space="preserve">12.7820377349854</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523462295532</t>
+    <t xml:space="preserve">13.5523452758789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5430994033813</t>
+    <t xml:space="preserve">13.543098449707</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071056365967</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">13.301872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1640310287476</t>
+    <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
     <t xml:space="preserve">13.1295690536499</t>
@@ -893,25 +893,25 @@
     <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557321548462</t>
+    <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276026725769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2501821517944</t>
+    <t xml:space="preserve">13.3277177810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2760276794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2501811981201</t>
   </si>
   <si>
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314193725586</t>
+    <t xml:space="preserve">12.9314203262329</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0354385375977</t>
+    <t xml:space="preserve">12.0354375839233</t>
   </si>
   <si>
     <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474361419678</t>
+    <t xml:space="preserve">12.1474370956421</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3197393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1302051544189</t>
+    <t xml:space="preserve">12.3197402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837474822998</t>
+    <t xml:space="preserve">11.9837465286255</t>
   </si>
   <si>
     <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7855978012085</t>
+    <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166767120361</t>
@@ -965,16 +965,16 @@
     <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286724090576</t>
+    <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8200588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7769832611084</t>
+    <t xml:space="preserve">11.8200578689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6046781539917</t>
+    <t xml:space="preserve">11.6046772003174</t>
   </si>
   <si>
     <t xml:space="preserve">11.6305246353149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0785160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388216018677</t>
+    <t xml:space="preserve">12.0182075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612840652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0785140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037225723267</t>
+    <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.6988086700439</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6815786361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7591161727905</t>
+    <t xml:space="preserve">12.6815776824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920434951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4661989212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.4920444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4661979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">12.5351209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
+    <t xml:space="preserve">12.5265035629272</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8366527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883438110352</t>
+    <t xml:space="preserve">12.9141893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.836651802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883428573608</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1070,22 +1070,22 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7505006790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868110656738</t>
+    <t xml:space="preserve">12.7505016326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868101119995</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126565933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935762405396</t>
+    <t xml:space="preserve">12.6126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935771942139</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280363082886</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.871111869812</t>
+    <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
     <t xml:space="preserve">12.9917268753052</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550970077515</t>
+    <t xml:space="preserve">13.6550979614258</t>
   </si>
   <si>
     <t xml:space="preserve">13.7757091522217</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498645782471</t>
+    <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
     <t xml:space="preserve">14.1289319992065</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166177749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
+    <t xml:space="preserve">14.5166187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.8963212966919</t>
@@ -1160,25 +1160,25 @@
     <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240171432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1547775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0255498886108</t>
+    <t xml:space="preserve">13.7240180969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1547784805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443117141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
     <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8446311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.111701965332</t>
+    <t xml:space="preserve">13.844630241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1117010116577</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
@@ -1187,31 +1187,31 @@
     <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6206369400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5517129898071</t>
+    <t xml:space="preserve">13.6206359863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5517139434814</t>
   </si>
   <si>
     <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8187866210938</t>
+    <t xml:space="preserve">13.8187856674194</t>
   </si>
   <si>
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.870475769043</t>
+    <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
     <t xml:space="preserve">13.8360147476196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8015556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7326326370239</t>
+    <t xml:space="preserve">13.8015546798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">13.7154035568237</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6120204925537</t>
+    <t xml:space="preserve">13.4569463729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.612021446228</t>
   </si>
   <si>
     <t xml:space="preserve">13.3535652160645</t>
@@ -1235,28 +1235,28 @@
     <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880252838135</t>
+    <t xml:space="preserve">13.3880243301392</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292505264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.370795249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2846431732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3363332748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5775594711304</t>
+    <t xml:space="preserve">13.6292495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3707942962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2846422195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603294372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5775604248047</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258684158325</t>
@@ -68527,7 +68527,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6912962963</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>34540</v>
@@ -68548,6 +68548,32 @@
         <v>888</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6913078704</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>10914</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>902</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414600372314</t>
+    <t xml:space="preserve">5.10414505004883</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169673919678</t>
+    <t xml:space="preserve">5.15394163131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">5.1165943145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16224098205566</t>
+    <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24523544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333137512207</t>
+    <t xml:space="preserve">5.24523639678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333185195923</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">5.38632535934448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3489785194397</t>
+    <t xml:space="preserve">5.34897804260254</t>
   </si>
   <si>
     <t xml:space="preserve">5.35312843322754</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">5.41122388839722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34067964553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462518692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761964797974</t>
+    <t xml:space="preserve">5.34067916870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462614059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761917114258</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176956176758</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9340877532959</t>
+    <t xml:space="preserve">5.93408823013306</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259052276611</t>
@@ -119,19 +119,19 @@
     <t xml:space="preserve">5.71415376663208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939311981201</t>
+    <t xml:space="preserve">5.85939359664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728610992432</t>
+    <t xml:space="preserve">5.96728515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313619613647</t>
+    <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068693161011</t>
@@ -143,22 +143,22 @@
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86769199371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05442953109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198026657104</t>
+    <t xml:space="preserve">5.86769247055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05443000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05027961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327407836914</t>
+    <t xml:space="preserve">6.05028009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1332745552063</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
@@ -170,28 +170,28 @@
     <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55239534378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57314348220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56069421768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205404281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994607925415</t>
+    <t xml:space="preserve">6.5523943901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57314395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56069469451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43205308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
+    <t xml:space="preserve">6.58559322357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464023590088</t>
@@ -200,31 +200,31 @@
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80552673339844</t>
+    <t xml:space="preserve">6.80552768707275</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920570373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034930229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234580993652</t>
+    <t xml:space="preserve">7.01301336288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05450963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920475006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349254608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234533309937</t>
   </si>
   <si>
     <t xml:space="preserve">8.67289733886719</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">8.12928485870361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3864860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798328399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573839187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240262985229</t>
+    <t xml:space="preserve">7.67281675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648653030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3657374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240310668945</t>
   </si>
   <si>
     <t xml:space="preserve">7.21634864807129</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156707763672</t>
+    <t xml:space="preserve">6.80156755447388</t>
   </si>
   <si>
     <t xml:space="preserve">6.98356294631958</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617263793945</t>
+    <t xml:space="preserve">6.77617216110229</t>
   </si>
   <si>
     <t xml:space="preserve">6.97933101654053</t>
@@ -284,46 +284,46 @@
     <t xml:space="preserve">6.99202871322632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49145936965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37295007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925329208374</t>
+    <t xml:space="preserve">7.49145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253244400024</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290607452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30522966384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448431015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830003738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23751163482666</t>
+    <t xml:space="preserve">7.26290512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523109436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3644847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941854476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830099105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2375111579895</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821298599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588748931885</t>
+    <t xml:space="preserve">7.06821250915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588796615601</t>
   </si>
   <si>
     <t xml:space="preserve">6.87351894378662</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">6.45027256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67036104202271</t>
+    <t xml:space="preserve">6.67036151885986</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
@@ -350,25 +350,25 @@
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538280487061</t>
+    <t xml:space="preserve">6.99626111984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84812498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621759414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053705215454</t>
+    <t xml:space="preserve">6.84812450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053657531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.05128288269043</t>
@@ -380,37 +380,37 @@
     <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0936074256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04704999923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086572647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398010253906</t>
+    <t xml:space="preserve">7.09360790252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858423233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011989593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398105621338</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09784030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00049352645874</t>
+    <t xml:space="preserve">7.09783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0004940032959</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
@@ -422,28 +422,28 @@
     <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207223892212</t>
+    <t xml:space="preserve">7.11476898193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
     <t xml:space="preserve">7.38987970352173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20365142822266</t>
+    <t xml:space="preserve">7.20365190505981</t>
   </si>
   <si>
     <t xml:space="preserve">7.23327922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17402458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
+    <t xml:space="preserve">7.17402505874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597692489624</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680980682373</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">7.49992370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42373991012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141536712646</t>
+    <t xml:space="preserve">7.42373943328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141489028931</t>
   </si>
   <si>
     <t xml:space="preserve">7.28406763076782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44490194320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834499359131</t>
+    <t xml:space="preserve">7.44490242004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834451675415</t>
   </si>
   <si>
     <t xml:space="preserve">7.47452878952026</t>
@@ -476,55 +476,55 @@
     <t xml:space="preserve">7.64382743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83005571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6565260887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349876403809</t>
+    <t xml:space="preserve">7.83005619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349781036377</t>
   </si>
   <si>
     <t xml:space="preserve">7.58457279205322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913482666016</t>
+    <t xml:space="preserve">7.449134349823</t>
   </si>
   <si>
     <t xml:space="preserve">7.53378248214722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61843347549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6522912979126</t>
+    <t xml:space="preserve">7.61843204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880662918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229177474976</t>
   </si>
   <si>
     <t xml:space="preserve">7.69884967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74540615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8681492805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163537979126</t>
+    <t xml:space="preserve">7.74540710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163442611694</t>
   </si>
   <si>
     <t xml:space="preserve">7.92317008972168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82582378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88930940628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470575332642</t>
+    <t xml:space="preserve">7.8258228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88930988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470670700073</t>
   </si>
   <si>
     <t xml:space="preserve">7.95279741287231</t>
@@ -536,37 +536,37 @@
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6141996383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332370758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45759868621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694133758545</t>
+    <t xml:space="preserve">7.70308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45760011672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694181442261</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30946350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4025764465332</t>
+    <t xml:space="preserve">7.30946254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
     <t xml:space="preserve">7.34755516052246</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702981948853</t>
+    <t xml:space="preserve">7.95702886581421</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707382202148</t>
+    <t xml:space="preserve">8.06707286834717</t>
   </si>
   <si>
     <t xml:space="preserve">8.21097755432129</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40567016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26600074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23213958740234</t>
+    <t xml:space="preserve">8.40567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26599884033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.30832386016846</t>
@@ -638,25 +638,25 @@
     <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02360916137695</t>
+    <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1759786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29448699951172</t>
+    <t xml:space="preserve">9.17597961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
     <t xml:space="preserve">9.5653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98861217498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541826248169</t>
+    <t xml:space="preserve">9.98861312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541835784912</t>
   </si>
   <si>
     <t xml:space="preserve">9.71773433685303</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4965076446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7927799224854</t>
+    <t xml:space="preserve">9.90396308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.496506690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7927808761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884809494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239217758179</t>
+    <t xml:space="preserve">11.5884819030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239227294922</t>
   </si>
   <si>
     <t xml:space="preserve">11.76624584198</t>
@@ -707,34 +707,34 @@
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633991241455</t>
+    <t xml:space="preserve">13.3491878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633981704712</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0517749786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111589431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460285186768</t>
+    <t xml:space="preserve">14.051775932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460294723511</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443185806274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0940999984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009870529175</t>
+    <t xml:space="preserve">14.0941009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173473358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009880065918</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
@@ -743,22 +743,22 @@
     <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338369369507</t>
+    <t xml:space="preserve">13.4169073104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338359832764</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5100202560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184860229492</t>
+    <t xml:space="preserve">13.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184869766235</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930896759033</t>
@@ -773,40 +773,40 @@
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512056350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004177093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073028564453</t>
+    <t xml:space="preserve">14.3480501174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.601996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512075424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596723556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004167556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073038101196</t>
   </si>
   <si>
     <t xml:space="preserve">14.4157676696777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3311176300049</t>
+    <t xml:space="preserve">14.3311195373535</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8655471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978277206421</t>
+    <t xml:space="preserve">13.8655462265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978267669678</t>
   </si>
   <si>
     <t xml:space="preserve">13.9840574264526</t>
@@ -818,61 +818,61 @@
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031341552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290988922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.782036781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397127151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0275201797485</t>
+    <t xml:space="preserve">13.6031351089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290979385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0275192260742</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423017501831</t>
+    <t xml:space="preserve">13.5523443222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071056365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0348024368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0434169769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9400358200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1726446151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.301872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.2071046829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.03480052948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.043417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.940034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1726455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3018732070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1640291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2243375778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812610626221</t>
+    <t xml:space="preserve">13.2243366241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123390197754</t>
+    <t xml:space="preserve">12.6557331085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123380661011</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277187347412</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0606479644775</t>
+    <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
     <t xml:space="preserve">12.9314193725586</t>
@@ -920,40 +920,40 @@
     <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2335872650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3369693756104</t>
+    <t xml:space="preserve">12.233588218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3369703292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.0354385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8975944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474361419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3542013168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2594327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3197393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1302051544189</t>
+    <t xml:space="preserve">11.8975963592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3542003631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3197402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8372888565063</t>
+    <t xml:space="preserve">11.9837465286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.837287902832</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855968475342</t>
@@ -965,25 +965,25 @@
     <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286733627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7597522735596</t>
+    <t xml:space="preserve">11.8286724090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769813537598</t>
+    <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339067459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6046781539917</t>
+    <t xml:space="preserve">11.7339057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.604679107666</t>
   </si>
   <si>
     <t xml:space="preserve">11.6305236816406</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">12.0612831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785150527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388216018677</t>
+    <t xml:space="preserve">12.0785140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871286392212</t>
+    <t xml:space="preserve">12.0871295928955</t>
   </si>
   <si>
     <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037225723267</t>
+    <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.6988077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500659942627</t>
+    <t xml:space="preserve">12.5006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
@@ -1037,19 +1037,19 @@
     <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5351190567017</t>
+    <t xml:space="preserve">12.5351209640503</t>
   </si>
   <si>
     <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7849607467651</t>
+    <t xml:space="preserve">12.7849617004395</t>
   </si>
   <si>
     <t xml:space="preserve">12.9141883850098</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643476486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7505016326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868120193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7074241638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126575469971</t>
+    <t xml:space="preserve">12.6643486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7504997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868110656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7074251174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126585006714</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246541976929</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.871111869812</t>
+    <t xml:space="preserve">12.7418842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
     <t xml:space="preserve">12.9917259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0089559555054</t>
+    <t xml:space="preserve">13.0089569091797</t>
   </si>
   <si>
     <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520315170288</t>
+    <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2674121856689</t>
+    <t xml:space="preserve">13.1984910964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914073944092</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">13.7757091522217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7843236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7498636245728</t>
+    <t xml:space="preserve">13.7843246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7498626708984</t>
   </si>
   <si>
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907712936401</t>
+    <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
     <t xml:space="preserve">14.5166168212891</t>
@@ -1160,55 +1160,55 @@
     <t xml:space="preserve">13.8618621826172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240190505981</t>
+    <t xml:space="preserve">13.7240180969238</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547784805298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3443126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0255508422852</t>
+    <t xml:space="preserve">14.3443117141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0255498886108</t>
   </si>
   <si>
     <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8446311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1117010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9221677780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206350326538</t>
+    <t xml:space="preserve">13.844630241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.111701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9221668243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
+    <t xml:space="preserve">13.6637125015259</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8877086639404</t>
+    <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8360147476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8015556335449</t>
+    <t xml:space="preserve">13.8360157012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8015546798706</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6809415817261</t>
+    <t xml:space="preserve">13.6809425354004</t>
   </si>
   <si>
     <t xml:space="preserve">13.4569463729858</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
+    <t xml:space="preserve">13.3535652160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.405255317688</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">13.3191032409668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880262374878</t>
+    <t xml:space="preserve">13.3880252838135</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
@@ -1247,19 +1247,19 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846431732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.336332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5775604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258674621582</t>
+    <t xml:space="preserve">13.2846422195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603284835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363332748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5775594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258693695068</t>
   </si>
   <si>
     <t xml:space="preserve">13.508638381958</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693737030029</t>
+    <t xml:space="preserve">13.8634128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693756103516</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340543746948</t>
+    <t xml:space="preserve">13.9340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278635025024</t>
+    <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
     <t xml:space="preserve">13.4219026565552</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982797622681</t>
+    <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">13.0686941146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0046949386597</t>
+    <t xml:space="preserve">14.004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870347976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8457527160645</t>
+    <t xml:space="preserve">13.9870357513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8457517623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8104314804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5985069274902</t>
+    <t xml:space="preserve">13.810432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338262557983</t>
+    <t xml:space="preserve">13.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.6691484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2452993392944</t>
+    <t xml:space="preserve">13.2452983856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
@@ -1403,46 +1403,46 @@
     <t xml:space="preserve">13.2276382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3689212799072</t>
+    <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
     <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629594802856</t>
+    <t xml:space="preserve">13.2629585266113</t>
   </si>
   <si>
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095247268677</t>
+    <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159399032593</t>
+    <t xml:space="preserve">13.0157136917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159408569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9097509384155</t>
+    <t xml:space="preserve">12.9097499847412</t>
   </si>
   <si>
     <t xml:space="preserve">12.8391094207764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0333738327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1569967269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099771499634</t>
+    <t xml:space="preserve">13.033374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1569957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1454,19 +1454,19 @@
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.121675491333</t>
+    <t xml:space="preserve">13.1216764450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.8567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037881851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1484,19 +1484,19 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790323257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4262762069702</t>
+    <t xml:space="preserve">11.1790313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
     <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0024280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143526077271</t>
+    <t xml:space="preserve">11.0024271011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143535614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0730686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">11.0730695724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496728897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728424072266</t>
+    <t xml:space="preserve">11.2496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494476318359</t>
+    <t xml:space="preserve">10.9494466781616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547298431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299152374268</t>
+    <t xml:space="preserve">10.154727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
     <t xml:space="preserve">9.44831275939941</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1370687484741</t>
+    <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
     <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1966924667358</t>
+    <t xml:space="preserve">11.1966915130615</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551822662354</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2783517837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.24303150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
+    <t xml:space="preserve">10.2783527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2430305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
   </si>
   <si>
     <t xml:space="preserve">10.5785779953003</t>
@@ -1622,22 +1622,22 @@
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375211715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258247375488</t>
+    <t xml:space="preserve">10.7375221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609178543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606916427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3313331604004</t>
+    <t xml:space="preserve">10.5609188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606906890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3313322067261</t>
   </si>
   <si>
     <t xml:space="preserve">10.5432567596436</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019746780396</t>
+    <t xml:space="preserve">10.4019737243652</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.84348487854</t>
+    <t xml:space="preserve">10.8434839248657</t>
   </si>
   <si>
     <t xml:space="preserve">10.8964653015137</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">10.9141254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554094314575</t>
+    <t xml:space="preserve">11.0554103851318</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069110870361</t>
+    <t xml:space="preserve">10.7069101333618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027923583984</t>
+    <t xml:space="preserve">9.84669780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846300125122</t>
+    <t xml:space="preserve">10.0663261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846290588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578388214111</t>
+    <t xml:space="preserve">10.139536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578397750854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055847167969</t>
+    <t xml:space="preserve">10.5055837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5238876342773</t>
+    <t xml:space="preserve">10.523886680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5604915618896</t>
+    <t xml:space="preserve">10.560492515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716335296631</t>
+    <t xml:space="preserve">10.8716325759888</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899354934692</t>
+    <t xml:space="preserve">10.6703062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899345397949</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193794250488</t>
+    <t xml:space="preserve">11.2193784713745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533306121826</t>
+    <t xml:space="preserve">11.1644716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252140045166</t>
+    <t xml:space="preserve">10.7252130508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944842338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461687088013</t>
+    <t xml:space="preserve">10.9448432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608589172363</t>
+    <t xml:space="preserve">8.23608493804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550094604492</t>
+    <t xml:space="preserve">8.17202663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550142288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234292984009</t>
+    <t xml:space="preserve">6.01234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00982332229614</t>
+    <t xml:space="preserve">7.0098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558013916016</t>
+    <t xml:space="preserve">7.055579662323</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531558990479</t>
+    <t xml:space="preserve">7.41247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531511306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568677902222</t>
+    <t xml:space="preserve">7.48568725585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038034439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303308486938</t>
+    <t xml:space="preserve">6.68038082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229118347168</t>
+    <t xml:space="preserve">7.52229166030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364643096924</t>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364547729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818161010742</t>
+    <t xml:space="preserve">8.96818256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62043571472168</t>
+    <t xml:space="preserve">8.620436668396</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003803253174</t>
+    <t xml:space="preserve">7.7968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003755569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6321063041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361755371094</t>
+    <t xml:space="preserve">7.77852535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63210582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236180305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642868041992</t>
+    <t xml:space="preserve">7.04642820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340475082397</t>
+    <t xml:space="preserve">6.86340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3509373664856</t>
+    <t xml:space="preserve">6.46075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35093688964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130807876587</t>
+    <t xml:space="preserve">6.02149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242116928101</t>
+    <t xml:space="preserve">5.47242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279235839844</t>
+    <t xml:space="preserve">5.25279188156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626070022583</t>
+    <t xml:space="preserve">5.36260652542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884069442749</t>
+    <t xml:space="preserve">5.61884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44908237457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324684143066</t>
+    <t xml:space="preserve">7.4490818977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324731826782</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55889654159546</t>
+    <t xml:space="preserve">7.5588960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062202453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452194213867</t>
+    <t xml:space="preserve">8.51062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452289581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025035858154</t>
+    <t xml:space="preserve">8.73025131225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176208496094</t>
+    <t xml:space="preserve">8.82176303863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308940887451</t>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179000854492</t>
+    <t xml:space="preserve">9.79179096221924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866195678711</t>
+    <t xml:space="preserve">10.3866186141968</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998676300049</t>
+    <t xml:space="preserve">9.37998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8949728012085</t>
+    <t xml:space="preserve">8.89497184753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833999633789</t>
+    <t xml:space="preserve">7.88833904266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4740161895752</t>
+    <t xml:space="preserve">8.47401714324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9249439239502</t>
+    <t xml:space="preserve">7.92494487762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735593795776</t>
+    <t xml:space="preserve">6.57056617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735641479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.53396081924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661451339722</t>
+    <t xml:space="preserve">6.93661403656006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -68608,7 +68608,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6910416667</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>20194</v>
@@ -68629,6 +68629,32 @@
         <v>901</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6911689815</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>82388</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>9.27999973297119</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="905">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394163131714</t>
+    <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564228057861</t>
+    <t xml:space="preserve">5.14564180374146</t>
   </si>
   <si>
     <t xml:space="preserve">5.1871395111084</t>
@@ -65,46 +65,46 @@
     <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24523639678955</t>
+    <t xml:space="preserve">5.24523544311523</t>
   </si>
   <si>
     <t xml:space="preserve">5.30333185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31163120269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3157811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482908248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632535934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34897804260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122388839722</t>
+    <t xml:space="preserve">5.31163167953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31578063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482955932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3863263130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312795639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972665786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122436523438</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462614059448</t>
+    <t xml:space="preserve">5.39462566375732</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176956176758</t>
+    <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000385284424</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">5.89259052276611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71415376663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558498382568</t>
+    <t xml:space="preserve">5.71415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558450698853</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9008903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96313571929932</t>
+    <t xml:space="preserve">5.90089082717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96313619613647</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068693161011</t>
@@ -146,19 +146,19 @@
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05443000793457</t>
+    <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05857944488525</t>
+    <t xml:space="preserve">6.05857992172241</t>
   </si>
   <si>
     <t xml:space="preserve">6.05028009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1332745552063</t>
+    <t xml:space="preserve">6.13327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5523943901062</t>
+    <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314395904541</t>
@@ -179,52 +179,52 @@
     <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43205308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994560241699</t>
+    <t xml:space="preserve">6.432053565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559322357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804201126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80552768707275</t>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301336288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05450963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920475006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234533309937</t>
+    <t xml:space="preserve">7.01301240921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451059341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920522689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.67289733886719</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">8.12928485870361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67281675338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648653030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3657374382019</t>
+    <t xml:space="preserve">7.67281770706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798280715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573934555054</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240310668945</t>
@@ -251,31 +251,31 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468240737915</t>
+    <t xml:space="preserve">7.43643617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22058010101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788478851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468193054199</t>
   </si>
   <si>
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356294631958</t>
+    <t xml:space="preserve">6.80156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617216110229</t>
+    <t xml:space="preserve">6.77617311477661</t>
   </si>
   <si>
     <t xml:space="preserve">6.97933101654053</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">7.49145889282227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37295055389404</t>
+    <t xml:space="preserve">7.37294960021973</t>
   </si>
   <si>
     <t xml:space="preserve">7.27983617782593</t>
@@ -299,28 +299,28 @@
     <t xml:space="preserve">7.29676532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523109436035</t>
+    <t xml:space="preserve">7.26290559768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523061752319</t>
   </si>
   <si>
     <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941854476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830099105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2375111579895</t>
+    <t xml:space="preserve">7.19941902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23751211166382</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821250915527</t>
+    <t xml:space="preserve">7.06821346282959</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588796615601</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027256011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036151885986</t>
+    <t xml:space="preserve">6.45027303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514213562012</t>
+    <t xml:space="preserve">7.15286207199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77194023132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84812450408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053657531738</t>
+    <t xml:space="preserve">6.72538280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7719407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84812498092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1867208480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053609848022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05128288269043</t>
@@ -380,40 +380,40 @@
     <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09360790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937501907349</t>
+    <t xml:space="preserve">7.09360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937454223633</t>
   </si>
   <si>
     <t xml:space="preserve">7.05974769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04705047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858423233032</t>
+    <t xml:space="preserve">7.04704999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
     <t xml:space="preserve">7.03011989593506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06398105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05551528930664</t>
+    <t xml:space="preserve">7.06398057937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0555157661438</t>
   </si>
   <si>
     <t xml:space="preserve">7.09783935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435325622559</t>
+    <t xml:space="preserve">7.00049352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435277938843</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900186538696</t>
@@ -422,37 +422,37 @@
     <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476898193359</t>
+    <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
     <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402505874634</t>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402410507202</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.432204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992370605469</t>
+    <t xml:space="preserve">7.24597644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373943328857</t>
@@ -461,28 +461,28 @@
     <t xml:space="preserve">7.38141489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28406763076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452878952026</t>
+    <t xml:space="preserve">7.28406810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452831268311</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83005619049072</t>
+    <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
     <t xml:space="preserve">7.65652513504028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78349781036377</t>
+    <t xml:space="preserve">7.78349876403809</t>
   </si>
   <si>
     <t xml:space="preserve">7.58457279205322</t>
@@ -491,28 +491,28 @@
     <t xml:space="preserve">7.449134349823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53378248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880662918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229177474976</t>
+    <t xml:space="preserve">7.53378391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880472183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229272842407</t>
   </si>
   <si>
     <t xml:space="preserve">7.69884967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74540710449219</t>
+    <t xml:space="preserve">7.74540615081787</t>
   </si>
   <si>
     <t xml:space="preserve">7.86814785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93163442611694</t>
+    <t xml:space="preserve">7.93163537979126</t>
   </si>
   <si>
     <t xml:space="preserve">7.92317008972168</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">7.8258228302002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88930988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279741287231</t>
+    <t xml:space="preserve">7.88931083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470575332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279836654663</t>
   </si>
   <si>
     <t xml:space="preserve">7.94856452941895</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308208465576</t>
+    <t xml:space="preserve">7.70308303833008</t>
   </si>
   <si>
     <t xml:space="preserve">7.61420011520386</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">7.42797183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34332227706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020837783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45760011672974</t>
+    <t xml:space="preserve">7.34332275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020742416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45760059356689</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">7.34755516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27137088775635</t>
+    <t xml:space="preserve">7.27137136459351</t>
   </si>
   <si>
     <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702886581421</t>
+    <t xml:space="preserve">7.95702981948853</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097755432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023220062256</t>
+    <t xml:space="preserve">8.06707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023124694824</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990352630615</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599884033203</t>
+    <t xml:space="preserve">8.26600074768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.23214054107666</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.87970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02361011505127</t>
+    <t xml:space="preserve">9.02360916137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17597961425781</t>
+    <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
@@ -653,28 +653,28 @@
     <t xml:space="preserve">9.5653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98861312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773433685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1325159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90396308898926</t>
+    <t xml:space="preserve">9.98861217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541826248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1325149536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927808761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9451484680176</t>
+    <t xml:space="preserve">10.7927799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9451475143433</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884819030762</t>
+    <t xml:space="preserve">11.4191846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884828567505</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239227294922</t>
   </si>
   <si>
-    <t xml:space="preserve">11.76624584198</t>
+    <t xml:space="preserve">11.7662448883057</t>
   </si>
   <si>
     <t xml:space="preserve">11.9355440139771</t>
@@ -701,16 +701,16 @@
     <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629590988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3491878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633981704712</t>
+    <t xml:space="preserve">12.6973867416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3491868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634000778198</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
@@ -719,22 +719,22 @@
     <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460294723511</t>
+    <t xml:space="preserve">12.5111589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460275650024</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443185806274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009880065918</t>
+    <t xml:space="preserve">14.0940999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173463821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
@@ -749,16 +749,16 @@
     <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438804626465</t>
+    <t xml:space="preserve">13.4338350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438814163208</t>
   </si>
   <si>
     <t xml:space="preserve">13.5100212097168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184869766235</t>
+    <t xml:space="preserve">13.5184860229492</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930896759033</t>
@@ -767,43 +767,43 @@
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094509124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057231903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3480501174927</t>
+    <t xml:space="preserve">14.0094518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.348048210144</t>
   </si>
   <si>
     <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512075424194</t>
+    <t xml:space="preserve">14.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004167556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655462265015</t>
+    <t xml:space="preserve">14.508882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004148483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157695770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655471801758</t>
   </si>
   <si>
     <t xml:space="preserve">13.7978267669678</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">13.9840574264526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8994073867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031351089478</t>
+    <t xml:space="preserve">13.8994064331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385740280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290979385376</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">12.7397117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0275192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5269498825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5523443222046</t>
+    <t xml:space="preserve">13.0275201797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5269508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">13.2071046829224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.03480052948</t>
+    <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
     <t xml:space="preserve">13.043417930603</t>
@@ -866,31 +866,31 @@
     <t xml:space="preserve">13.0175714492798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3018732070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1640291213989</t>
+    <t xml:space="preserve">13.301872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
     <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8797273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901931762695</t>
+    <t xml:space="preserve">12.8797283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901941299438</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812601089478</t>
+    <t xml:space="preserve">13.1812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
+    <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557331085205</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8194217681885</t>
+    <t xml:space="preserve">12.8194208145142</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">12.0354385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8975963592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3542003631592</t>
+    <t xml:space="preserve">11.8975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474361419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3541994094849</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594337463379</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">11.9837465286255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.837287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7855968475342</t>
+    <t xml:space="preserve">11.8372888565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166767120361</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769823074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7511367797852</t>
+    <t xml:space="preserve">11.7769832611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7511358261108</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.604679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6305236816406</t>
+    <t xml:space="preserve">11.6046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6305246353149</t>
   </si>
   <si>
     <t xml:space="preserve">12.0182075500488</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">12.0612831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785140991211</t>
+    <t xml:space="preserve">12.0785150527954</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871295928955</t>
+    <t xml:space="preserve">12.0871305465698</t>
   </si>
   <si>
     <t xml:space="preserve">13.2157211303711</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">12.6988086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591161727905</t>
+    <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231224060059</t>
+    <t xml:space="preserve">12.4231233596802</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628168106079</t>
+    <t xml:space="preserve">12.3628158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">12.836651802063</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8883428573608</t>
+    <t xml:space="preserve">12.8883438110352</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1067,28 +1067,28 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7504997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868110656738</t>
+    <t xml:space="preserve">12.6643466949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7505006790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868101119995</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074251174927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126585006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246541976929</t>
+    <t xml:space="preserve">12.6126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246551513672</t>
   </si>
   <si>
     <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8280372619629</t>
+    <t xml:space="preserve">12.8280363082886</t>
   </si>
   <si>
     <t xml:space="preserve">12.7418842315674</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520324707031</t>
+    <t xml:space="preserve">13.0520315170288</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550960540771</t>
+    <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
     <t xml:space="preserve">13.7757091522217</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498626708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1289319992065</t>
+    <t xml:space="preserve">13.7498636245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1289329528809</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166168212891</t>
+    <t xml:space="preserve">14.5166187286377</t>
   </si>
   <si>
     <t xml:space="preserve">14.2150850296021</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8963212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8618621826172</t>
+    <t xml:space="preserve">13.8963222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
     <t xml:space="preserve">13.7240180969238</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1547784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443117141724</t>
+    <t xml:space="preserve">14.1547775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255498886108</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9221668243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929391860962</t>
+    <t xml:space="preserve">13.9221677780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206359863281</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637125015259</t>
+    <t xml:space="preserve">13.6637115478516</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704767227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8015546798706</t>
+    <t xml:space="preserve">13.870475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360147476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154035568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6809425354004</t>
+    <t xml:space="preserve">13.7154026031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
     <t xml:space="preserve">13.4569463729858</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3191032409668</t>
+    <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
     <t xml:space="preserve">13.3880252838135</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">13.5603284835815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3363332748413</t>
+    <t xml:space="preserve">13.3363342285156</t>
   </si>
   <si>
     <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5258693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5258684158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">13.951714515686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693756103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7751111984253</t>
+    <t xml:space="preserve">13.9693746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.775110244751</t>
   </si>
   <si>
     <t xml:space="preserve">14.1106576919556</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161670684814</t>
+    <t xml:space="preserve">13.6161661148071</t>
   </si>
   <si>
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219026565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0863542556763</t>
+    <t xml:space="preserve">13.4219017028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0863552093506</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2806196212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0686941146851</t>
+    <t xml:space="preserve">13.2806205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0686950683594</t>
   </si>
   <si>
     <t xml:space="preserve">14.3402433395386</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.004695892334</t>
+    <t xml:space="preserve">14.0046949386597</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">13.9870357513428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8457517623901</t>
+    <t xml:space="preserve">13.8457527160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.810432434082</t>
+    <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865823745728</t>
+    <t xml:space="preserve">13.3865814208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
@@ -1361,22 +1361,22 @@
     <t xml:space="preserve">13.7221298217773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6514873504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4748840332031</t>
+    <t xml:space="preserve">13.6514883041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4748849868774</t>
   </si>
   <si>
     <t xml:space="preserve">13.6868085861206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.580846786499</t>
+    <t xml:space="preserve">13.5808458328247</t>
   </si>
   <si>
     <t xml:space="preserve">13.6338272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4572229385376</t>
+    <t xml:space="preserve">13.4572238922119</t>
   </si>
   <si>
     <t xml:space="preserve">13.4925441741943</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
+    <t xml:space="preserve">13.2276372909546</t>
   </si>
   <si>
     <t xml:space="preserve">13.3689222335815</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629585266113</t>
+    <t xml:space="preserve">13.2629594802856</t>
   </si>
   <si>
     <t xml:space="preserve">12.9803924560547</t>
@@ -1418,25 +1418,25 @@
     <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5035619735718</t>
+    <t xml:space="preserve">12.5035629272461</t>
   </si>
   <si>
     <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3159408569336</t>
+    <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
     <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9097499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.033374786377</t>
+    <t xml:space="preserve">12.9097509384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391084671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
     <t xml:space="preserve">13.1569957733154</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9274120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8920907974243</t>
+    <t xml:space="preserve">12.9274110794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8920917510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1216764450073</t>
+    <t xml:space="preserve">13.121675491333</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">11.267333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790313720703</t>
+    <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0024271011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143535614014</t>
+    <t xml:space="preserve">11.0024280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143526077271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
+    <t xml:space="preserve">10.9317855834961</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
@@ -1526,25 +1526,25 @@
     <t xml:space="preserve">11.7794857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7618246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7265043258667</t>
+    <t xml:space="preserve">11.7618255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.726505279541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496738433838</t>
+    <t xml:space="preserve">11.1260509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496728897095</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2077102661133</t>
+    <t xml:space="preserve">10.2077112197876</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843145370483</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">11.3026552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0200881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9494466781616</t>
+    <t xml:space="preserve">11.0200872421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9494476318359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
+    <t xml:space="preserve">9.53661441802979</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
@@ -1595,16 +1595,16 @@
     <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1966915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551822662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.666880607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2783527374268</t>
+    <t xml:space="preserve">11.1966924667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551832199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668796539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430305480957</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375221252441</t>
+    <t xml:space="preserve">10.7375211715698</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258237838745</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606906890869</t>
+    <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313322067261</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019737243652</t>
+    <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">10.9141254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554103851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.984766960144</t>
+    <t xml:space="preserve">11.0554094314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9847679138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.3203153610229</t>
@@ -2724,6 +2724,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.23999977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42000007629395</t>
   </si>
 </sst>
 </file>
@@ -68634,7 +68637,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.6911689815</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>82388</v>
@@ -68643,7 +68646,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="D2523" t="n">
-        <v>9.15999984741211</v>
+        <v>9.11999988555908</v>
       </c>
       <c r="E2523" t="n">
         <v>9.22000026702881</v>
@@ -68655,6 +68658,32 @@
         <v>888</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.6912731481</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>32341</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>9.64000034332275</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>904</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="906">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414505004883</t>
+    <t xml:space="preserve">5.10414600372314</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1539421081543</t>
+    <t xml:space="preserve">5.15394258499146</t>
   </si>
   <si>
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564180374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1165943145752</t>
+    <t xml:space="preserve">5.14564228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18713998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224145889282</t>
@@ -65,52 +65,52 @@
     <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24523544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333185195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31163167953491</t>
+    <t xml:space="preserve">5.24523591995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
     <t xml:space="preserve">5.31578063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3863263130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34897899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972665786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067916870117</t>
+    <t xml:space="preserve">5.34482860565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632535934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3489785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122388839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067964553833</t>
   </si>
   <si>
     <t xml:space="preserve">5.39462566375732</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47761917114258</t>
+    <t xml:space="preserve">5.47762012481689</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93408823013306</t>
+    <t xml:space="preserve">5.71000337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93408727645874</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259052276611</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">5.97558450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90089082717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96313619613647</t>
+    <t xml:space="preserve">5.96728610992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9008903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068693161011</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442953109741</t>
+    <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05857992172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05028009414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327407836914</t>
+    <t xml:space="preserve">6.05857944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05027914047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355031967163</t>
+    <t xml:space="preserve">6.47355079650879</t>
   </si>
   <si>
     <t xml:space="preserve">6.3615083694458</t>
@@ -173,52 +173,52 @@
     <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57314395904541</t>
+    <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
     <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.432053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59389209747314</t>
+    <t xml:space="preserve">6.43205308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994512557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59389162063599</t>
   </si>
   <si>
     <t xml:space="preserve">6.58559274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59804153442383</t>
+    <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464071273804</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63953924179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8055272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321630477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301240921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451059341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349349975586</t>
+    <t xml:space="preserve">6.63953876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80552673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321725845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920475006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349254608154</t>
   </si>
   <si>
     <t xml:space="preserve">7.46948051452637</t>
@@ -227,52 +227,52 @@
     <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67289733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928485870361</t>
+    <t xml:space="preserve">8.6728982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928581237793</t>
   </si>
   <si>
     <t xml:space="preserve">7.67281770706177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38648700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798280715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573934555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240310668945</t>
+    <t xml:space="preserve">7.3864860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4279842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240262985229</t>
   </si>
   <si>
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643617630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22058010101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788478851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468193054199</t>
+    <t xml:space="preserve">7.43643665313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468145370483</t>
   </si>
   <si>
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156707763672</t>
+    <t xml:space="preserve">6.80156755447388</t>
   </si>
   <si>
     <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94123840332031</t>
+    <t xml:space="preserve">6.94123792648315</t>
   </si>
   <si>
     <t xml:space="preserve">6.77617311477661</t>
@@ -284,19 +284,19 @@
     <t xml:space="preserve">6.99202871322632</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37294960021973</t>
+    <t xml:space="preserve">7.49145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37295007705688</t>
   </si>
   <si>
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676532745361</t>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676628112793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290559768677</t>
@@ -305,19 +305,19 @@
     <t xml:space="preserve">7.30523061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3644847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941902160645</t>
+    <t xml:space="preserve">7.36448431015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23751211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132688522339</t>
+    <t xml:space="preserve">7.23751163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132640838623</t>
   </si>
   <si>
     <t xml:space="preserve">7.06821346282959</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">7.02588796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87351894378662</t>
+    <t xml:space="preserve">6.87351942062378</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67036104202271</t>
+    <t xml:space="preserve">6.67036056518555</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286207199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514261245728</t>
+    <t xml:space="preserve">7.15286159515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
@@ -356,61 +356,61 @@
     <t xml:space="preserve">6.72538280487061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7719407081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84812498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1867208480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128288269043</t>
+    <t xml:space="preserve">6.77194023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84812450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672227859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053705215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128240585327</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630512237549</t>
+    <t xml:space="preserve">7.10630559921265</t>
   </si>
   <si>
     <t xml:space="preserve">7.09360694885254</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04704999923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086572647095</t>
+    <t xml:space="preserve">7.0893759727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086524963379</t>
   </si>
   <si>
     <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03011989593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0555157661438</t>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0639796257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05551528930664</t>
   </si>
   <si>
     <t xml:space="preserve">7.09783935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00049352645874</t>
+    <t xml:space="preserve">7.00049304962158</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435277938843</t>
@@ -419,61 +419,61 @@
     <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00895833969116</t>
+    <t xml:space="preserve">7.008957862854</t>
   </si>
   <si>
     <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10207271575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327875137329</t>
+    <t xml:space="preserve">7.10207319259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987970352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327827453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.17402410507202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21211624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597644805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680932998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43220376968384</t>
+    <t xml:space="preserve">7.21211671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597597122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40681028366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
     <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42373943328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490146636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834499359131</t>
+    <t xml:space="preserve">7.42373991012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406763076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490194320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834451675415</t>
   </si>
   <si>
     <t xml:space="preserve">7.47452831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64382743835449</t>
+    <t xml:space="preserve">7.64382696151733</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
@@ -482,31 +482,31 @@
     <t xml:space="preserve">7.65652513504028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78349876403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880472183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229272842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69884967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540615081787</t>
+    <t xml:space="preserve">7.78349828720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457231521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880567550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540662765503</t>
   </si>
   <si>
     <t xml:space="preserve">7.86814785003662</t>
@@ -515,43 +515,43 @@
     <t xml:space="preserve">7.93163537979126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88931083679199</t>
+    <t xml:space="preserve">7.92316913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931035995483</t>
   </si>
   <si>
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279836654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856452941895</t>
+    <t xml:space="preserve">7.95279788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856595993042</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020742416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45760059356689</t>
+    <t xml:space="preserve">7.70308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
@@ -560,25 +560,25 @@
     <t xml:space="preserve">7.73694181442261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51685380935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30946254730225</t>
+    <t xml:space="preserve">7.51685476303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137136459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702981948853</t>
+    <t xml:space="preserve">7.34755611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137041091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838899612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023124694824</t>
+    <t xml:space="preserve">8.06707286834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023220062256</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990352630615</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26600074768066</t>
+    <t xml:space="preserve">8.26599979400635</t>
   </si>
   <si>
     <t xml:space="preserve">8.23214054107666</t>
@@ -629,43 +629,43 @@
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514530181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.998215675354</t>
+    <t xml:space="preserve">9.01514625549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99821662902832</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02360916137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19290924072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1759786605835</t>
+    <t xml:space="preserve">9.02361011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19290828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5653657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861217498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541826248169</t>
+    <t xml:space="preserve">9.56536483764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541835784912</t>
   </si>
   <si>
     <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1325149536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90396213531494</t>
+    <t xml:space="preserve">10.1325159072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90396118164062</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451475143433</t>
+    <t xml:space="preserve">10.9451484680176</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191846847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884828567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7662448883057</t>
+    <t xml:space="preserve">11.4191837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884819030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239217758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
     <t xml:space="preserve">11.9355440139771</t>
@@ -701,16 +701,16 @@
     <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973867416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3491868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634000778198</t>
+    <t xml:space="preserve">12.6973886489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629590988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3491878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633991241455</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">12.5111589431763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443185806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0940999984741</t>
+    <t xml:space="preserve">13.1460285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0941009521484</t>
   </si>
   <si>
     <t xml:space="preserve">14.5173463821411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009870529175</t>
+    <t xml:space="preserve">14.0009860992432</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
@@ -749,64 +749,64 @@
     <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438814163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5100212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930896759033</t>
+    <t xml:space="preserve">13.4338369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5100202560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184869766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930906295776</t>
   </si>
   <si>
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094518661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057241439819</t>
+    <t xml:space="preserve">14.0094509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
     <t xml:space="preserve">14.348048210144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.601996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512065887451</t>
+    <t xml:space="preserve">14.6019954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512075424194</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.508882522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004148483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157695770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311185836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978267669678</t>
+    <t xml:space="preserve">14.5088806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004167556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157676696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618194580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655462265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
     <t xml:space="preserve">13.9840574264526</t>
@@ -815,16 +815,16 @@
     <t xml:space="preserve">13.8994064331055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385740280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031341552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820377349854</t>
+    <t xml:space="preserve">13.7385730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031351089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
     <t xml:space="preserve">12.7397117614746</t>
@@ -833,25 +833,25 @@
     <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5269508361816</t>
+    <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
     <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423007965088</t>
+    <t xml:space="preserve">13.4423017501831</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071046829224</t>
+    <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
     <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.043417930603</t>
+    <t xml:space="preserve">13.0434169769287</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
@@ -860,52 +860,52 @@
     <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1726455688477</t>
+    <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
     <t xml:space="preserve">13.0175714492798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.301872253418</t>
+    <t xml:space="preserve">13.3018732070923</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8797283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901941299438</t>
+    <t xml:space="preserve">13.1295690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8797273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812610626221</t>
+    <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228038787842</t>
+    <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123380661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277187347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2760276794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2501821517944</t>
+    <t xml:space="preserve">13.1123399734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277196884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276026725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2501811981201</t>
   </si>
   <si>
     <t xml:space="preserve">13.0606470108032</t>
@@ -914,43 +914,43 @@
     <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8194208145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4834289550781</t>
+    <t xml:space="preserve">12.8194217681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4834280014038</t>
   </si>
   <si>
     <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369703292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0354385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975944519043</t>
+    <t xml:space="preserve">12.3369693756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.035439491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975954055786</t>
   </si>
   <si>
     <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3541994094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2594337463379</t>
+    <t xml:space="preserve">12.3542013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302051544189</t>
+    <t xml:space="preserve">12.1302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837465286255</t>
+    <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
     <t xml:space="preserve">11.8372888565063</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114433288574</t>
+    <t xml:space="preserve">11.7166757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286724090576</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769832611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7511358261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339057922363</t>
+    <t xml:space="preserve">11.7769813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7511367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339067459106</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612831115723</t>
+    <t xml:space="preserve">11.6305236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182085037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
     <t xml:space="preserve">12.0785150527954</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871305465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157211303711</t>
+    <t xml:space="preserve">12.0871286392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157220840454</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">12.6988086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500659942627</t>
+    <t xml:space="preserve">12.5006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231233596802</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5351209640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7849617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9141883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.836651802063</t>
+    <t xml:space="preserve">12.535120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265054702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7849607467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9141893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8366527557373</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883438110352</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643466949463</t>
+    <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
     <t xml:space="preserve">12.7505006790161</t>
@@ -1076,61 +1076,61 @@
     <t xml:space="preserve">12.5868101119995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7074251174927</t>
+    <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
     <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7246551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935762405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280363082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7418842315674</t>
+    <t xml:space="preserve">12.7246561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280372619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520315170288</t>
+    <t xml:space="preserve">12.9917249679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089559555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0951080322266</t>
+    <t xml:space="preserve">13.0951070785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984910964966</t>
+    <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914073944092</t>
+    <t xml:space="preserve">13.4914064407349</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757091522217</t>
+    <t xml:space="preserve">13.7757081985474</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843246459961</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289329528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4907703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5166187286377</t>
+    <t xml:space="preserve">14.1289319992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4907712936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
     <t xml:space="preserve">14.2150850296021</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8963222503662</t>
+    <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240180969238</t>
+    <t xml:space="preserve">13.7240190505981</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547775268555</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255498886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.939398765564</t>
+    <t xml:space="preserve">14.0255508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
     <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.111701965332</t>
+    <t xml:space="preserve">14.1117010116577</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206359863281</t>
+    <t xml:space="preserve">13.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206369400024</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637115478516</t>
+    <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.870475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360147476196</t>
+    <t xml:space="preserve">13.8704767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360157012939</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
@@ -1220,22 +1220,22 @@
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569463729858</t>
+    <t xml:space="preserve">13.4569473266602</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.405255317688</t>
+    <t xml:space="preserve">13.3535642623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880252838135</t>
+    <t xml:space="preserve">13.3880243301392</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3363342285156</t>
+    <t xml:space="preserve">13.5603294372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
     <t xml:space="preserve">13.5775594711304</t>
@@ -1268,28 +1268,28 @@
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.951714515686</t>
+    <t xml:space="preserve">13.8634119033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
     <t xml:space="preserve">13.9693746566772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.775110244751</t>
+    <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340534210205</t>
+    <t xml:space="preserve">13.9340543746948</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161661148071</t>
+    <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
     <t xml:space="preserve">13.5278644561768</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">13.4219017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0863552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2982807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2806205749512</t>
+    <t xml:space="preserve">13.0863542556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2982797622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
     <t xml:space="preserve">13.0686950683594</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872619628906</t>
+    <t xml:space="preserve">14.2872629165649</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753374099731</t>
+    <t xml:space="preserve">14.0753364562988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870357513428</t>
+    <t xml:space="preserve">13.9870347976685</t>
   </si>
   <si>
     <t xml:space="preserve">13.8457527160645</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865814208984</t>
+    <t xml:space="preserve">13.3865823745728</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
@@ -1361,37 +1361,37 @@
     <t xml:space="preserve">13.7221298217773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6514883041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4748849868774</t>
+    <t xml:space="preserve">13.6514873504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4748840332031</t>
   </si>
   <si>
     <t xml:space="preserve">13.6868085861206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5808458328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6338272094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4572238922119</t>
+    <t xml:space="preserve">13.580846786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6338262557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4572229385376</t>
   </si>
   <si>
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691484451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102043151855</t>
+    <t xml:space="preserve">13.6691474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102052688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
+    <t xml:space="preserve">13.351261138916</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.174656867981</t>
+    <t xml:space="preserve">13.1746578216553</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5035629272461</t>
+    <t xml:space="preserve">12.6095247268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
     <t xml:space="preserve">13.0157136917114</t>
@@ -1427,28 +1427,28 @@
     <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980525970459</t>
+    <t xml:space="preserve">12.9980535507202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391084671021</t>
+    <t xml:space="preserve">12.8391103744507</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569957733154</t>
+    <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
     <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9274110794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8920917510986</t>
+    <t xml:space="preserve">12.9274120330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8920907974243</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037881851196</t>
+    <t xml:space="preserve">12.8567695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
     <t xml:space="preserve">12.2386560440063</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267333984375</t>
+    <t xml:space="preserve">11.2673349380493</t>
   </si>
   <si>
     <t xml:space="preserve">11.3379764556885</t>
@@ -1502,49 +1502,49 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317855834961</t>
+    <t xml:space="preserve">10.9317874908447</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792585372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441654205322</t>
+    <t xml:space="preserve">11.2849950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441644668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7618255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.726505279541</t>
+    <t xml:space="preserve">11.7618246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7265043258667</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1260509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496728897095</t>
+    <t xml:space="preserve">11.126051902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496738433838</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2077112197876</t>
+    <t xml:space="preserve">10.2077102661133</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843145370483</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439373016357</t>
+    <t xml:space="preserve">11.4439382553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0200872421265</t>
+    <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
     <t xml:space="preserve">10.9494476318359</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.154727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299247741699</t>
+    <t xml:space="preserve">10.1547288894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299152374268</t>
   </si>
   <si>
     <t xml:space="preserve">9.44831275939941</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198619842529</t>
+    <t xml:space="preserve">10.7198629379272</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6668796539307</t>
+    <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
     <t xml:space="preserve">10.2783517837524</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785779953003</t>
+    <t xml:space="preserve">10.4902772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079374313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785789489746</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375211715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258237838745</t>
+    <t xml:space="preserve">10.7375221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258247375488</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
@@ -1634,37 +1634,37 @@
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606916427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3313322067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432567596436</t>
+    <t xml:space="preserve">10.2606906890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3313331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432577133179</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019746780396</t>
+    <t xml:space="preserve">10.4019756317139</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8434839248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8964653015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554094314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9847679138184</t>
+    <t xml:space="preserve">10.84348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.896466255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.984766960144</t>
   </si>
   <si>
     <t xml:space="preserve">11.3203153610229</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069101333618</t>
+    <t xml:space="preserve">10.7069110870361</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027828216553</t>
+    <t xml:space="preserve">9.84669876098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027923583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846290588379</t>
+    <t xml:space="preserve">10.0663270950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846300125122</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.139536857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578397750854</t>
+    <t xml:space="preserve">10.1395359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578388214111</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055837631226</t>
+    <t xml:space="preserve">10.5055847167969</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.523886680603</t>
+    <t xml:space="preserve">10.5238876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.560492515564</t>
+    <t xml:space="preserve">10.5604915618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716325759888</t>
+    <t xml:space="preserve">10.8716335296631</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703062057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899345397949</t>
+    <t xml:space="preserve">10.6703052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984228134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899354934692</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193784713745</t>
+    <t xml:space="preserve">11.2193794250488</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644716262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533296585083</t>
+    <t xml:space="preserve">11.1644706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533306121826</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252130508423</t>
+    <t xml:space="preserve">10.7252140045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9448432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461696624756</t>
+    <t xml:space="preserve">10.944842338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109564781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461687088013</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608493804932</t>
+    <t xml:space="preserve">8.23608589172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550142288208</t>
+    <t xml:space="preserve">8.17202758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550094604492</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234245300293</t>
+    <t xml:space="preserve">6.01234292984009</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0098237991333</t>
+    <t xml:space="preserve">7.00982332229614</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.055579662323</t>
+    <t xml:space="preserve">7.05558013916016</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247749328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531511306763</t>
+    <t xml:space="preserve">7.41247701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531558990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568725585938</t>
+    <t xml:space="preserve">7.48568677902222</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303356170654</t>
+    <t xml:space="preserve">6.68038034439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303308486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229166030884</t>
+    <t xml:space="preserve">7.52229118347168</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364547729492</t>
+    <t xml:space="preserve">8.14457225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364643096924</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818256378174</t>
+    <t xml:space="preserve">8.96818161010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.620436668396</t>
+    <t xml:space="preserve">8.62043571472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7968282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003755569458</t>
+    <t xml:space="preserve">7.79682779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003803253174</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63210582733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7236180305481</t>
+    <t xml:space="preserve">7.77852582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6321063041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361755371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642820358276</t>
+    <t xml:space="preserve">7.04642868041992</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340427398682</t>
+    <t xml:space="preserve">6.86340475082397</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46075105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35093688964844</t>
+    <t xml:space="preserve">6.4607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3509373664856</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130760192871</t>
+    <t xml:space="preserve">6.02149391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130807876587</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242164611816</t>
+    <t xml:space="preserve">5.47242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279188156128</t>
+    <t xml:space="preserve">5.25279235839844</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36260652542114</t>
+    <t xml:space="preserve">5.3626070022583</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884021759033</t>
+    <t xml:space="preserve">5.61884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4490818977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324731826782</t>
+    <t xml:space="preserve">7.44908237457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324684143066</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5588960647583</t>
+    <t xml:space="preserve">7.55889654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452289581299</t>
+    <t xml:space="preserve">8.51062202453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847312927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452194213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025131225586</t>
+    <t xml:space="preserve">8.73025035858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176303863525</t>
+    <t xml:space="preserve">8.82176208496094</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0230884552002</t>
+    <t xml:space="preserve">9.13290309906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02308940887451</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179096221924</t>
+    <t xml:space="preserve">9.79179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866186141968</t>
+    <t xml:space="preserve">10.3866195678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998580932617</t>
+    <t xml:space="preserve">9.37998676300049</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89497184753418</t>
+    <t xml:space="preserve">8.8949728012085</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833904266357</t>
+    <t xml:space="preserve">7.88833999633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47401714324951</t>
+    <t xml:space="preserve">8.4740161895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92494487762451</t>
+    <t xml:space="preserve">7.9249439239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735641479492</t>
+    <t xml:space="preserve">6.57056570053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735593795776</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396081924438</t>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661403656006</t>
+    <t xml:space="preserve">6.93661451339722</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -2727,6 +2727,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.42000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46000003814697</t>
   </si>
 </sst>
 </file>
@@ -68663,7 +68666,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6912731481</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>32341</v>
@@ -68684,6 +68687,32 @@
         <v>904</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.691099537</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>15240</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>9.57999992370605</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>9.31999969482422</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>9.46000003814697</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>905</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="907">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394258499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169626235962</t>
+    <t xml:space="preserve">5.1539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169673919678</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18713998794556</t>
+    <t xml:space="preserve">5.1871395111084</t>
   </si>
   <si>
     <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16224145889282</t>
+    <t xml:space="preserve">5.16224098205566</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
@@ -68,70 +68,70 @@
     <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333137512207</t>
+    <t xml:space="preserve">5.30333185195923</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632535934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3489785194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312843322754</t>
+    <t xml:space="preserve">5.3157811164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122388839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067964553833</t>
+    <t xml:space="preserve">5.41122484207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
     <t xml:space="preserve">5.39462566375732</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47762012481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48176908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71000337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93408727645874</t>
+    <t xml:space="preserve">5.47761964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48176956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71000385284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259052276611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558450698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96728610992432</t>
+    <t xml:space="preserve">5.71415376663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939264297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96728563308716</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313571929932</t>
+    <t xml:space="preserve">5.96313619613647</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068693161011</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86769247055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05443000793457</t>
+    <t xml:space="preserve">5.8676929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05442953109741</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
@@ -155,16 +155,16 @@
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05027914047241</t>
+    <t xml:space="preserve">6.05028009414673</t>
   </si>
   <si>
     <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19137001037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47355079650879</t>
+    <t xml:space="preserve">6.19136953353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
     <t xml:space="preserve">6.3615083694458</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994512557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59389162063599</t>
+    <t xml:space="preserve">6.56069421768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.432053565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
     <t xml:space="preserve">6.58559274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59804201126099</t>
+    <t xml:space="preserve">6.59804153442383</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464071273804</t>
@@ -203,85 +203,85 @@
     <t xml:space="preserve">6.80552673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96321725845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451011657715</t>
+    <t xml:space="preserve">6.96321630477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301240921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451059341431</t>
   </si>
   <si>
     <t xml:space="preserve">7.12920475006104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30349254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948051452637</t>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948146820068</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6728982925415</t>
+    <t xml:space="preserve">8.67289638519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.12928581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67281770706177</t>
+    <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
     <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4279842376709</t>
+    <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
     <t xml:space="preserve">7.36573839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16240262985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634864807129</t>
+    <t xml:space="preserve">7.16240310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634817123413</t>
   </si>
   <si>
     <t xml:space="preserve">7.43643665313721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468145370483</t>
+    <t xml:space="preserve">7.22058057785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788478851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468193054199</t>
   </si>
   <si>
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156755447388</t>
+    <t xml:space="preserve">6.80156707763672</t>
   </si>
   <si>
     <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94123792648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617311477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202871322632</t>
+    <t xml:space="preserve">6.94123888015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933053970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -290,25 +290,25 @@
     <t xml:space="preserve">7.37295007705688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27983617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448431015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994194984436</t>
+    <t xml:space="preserve">7.27983570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523109436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36448574066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941902160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830051422119</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">7.23751163482666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821346282959</t>
+    <t xml:space="preserve">7.16132688522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821298599243</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588796615601</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036056518555</t>
+    <t xml:space="preserve">6.45027351379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96663284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99626111984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538280487061</t>
+    <t xml:space="preserve">6.96663331985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99626064300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538375854492</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
@@ -362,46 +362,46 @@
     <t xml:space="preserve">6.84812450408936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672227859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016485214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360694885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0893759727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858470916748</t>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1867208480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016437530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0936074256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04704999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858518600464</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0639796257019</t>
+    <t xml:space="preserve">7.06398010253906</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">7.09783935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00049304962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435277938843</t>
+    <t xml:space="preserve">7.0004940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435230255127</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.008957862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476945877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207319259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402410507202</t>
+    <t xml:space="preserve">7.00895833969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476993560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402458190918</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211671829224</t>
@@ -446,136 +446,136 @@
     <t xml:space="preserve">7.24597597122192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40681028366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.432204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373991012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406763076782</t>
+    <t xml:space="preserve">7.40680932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992275238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373943328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406810760498</t>
   </si>
   <si>
     <t xml:space="preserve">7.44490194320679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39834451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452831268311</t>
+    <t xml:space="preserve">7.39834403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47453022003174</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382696151733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83005571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652513504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349828720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457231521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843204498291</t>
+    <t xml:space="preserve">7.83005666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457279205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843252182007</t>
   </si>
   <si>
     <t xml:space="preserve">7.58880567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229225158691</t>
+    <t xml:space="preserve">7.65229177474976</t>
   </si>
   <si>
     <t xml:space="preserve">7.69885015487671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74540662765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316913604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88931035995483</t>
+    <t xml:space="preserve">7.74540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582330703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931083679199</t>
   </si>
   <si>
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332180023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020837783813</t>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9485650062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553958892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797088623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63536310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694181442261</t>
+    <t xml:space="preserve">7.63536262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694276809692</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685476303101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30946350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40257692337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137041091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838899612427</t>
+    <t xml:space="preserve">7.30946254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40257740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702934265137</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474880218506</t>
+    <t xml:space="preserve">8.02474784851074</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707286834717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21097850799561</t>
+    <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222759246826</t>
+    <t xml:space="preserve">8.45222854614258</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
@@ -614,49 +614,49 @@
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32525444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027572631836</t>
+    <t xml:space="preserve">8.3252534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027667999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970542907715</t>
+    <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514625549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99821662902832</t>
+    <t xml:space="preserve">9.01514434814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02361011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19290828704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17597961425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29448795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56536483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541835784912</t>
+    <t xml:space="preserve">9.02361106872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19291019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1759786605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29448699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541826248169</t>
   </si>
   <si>
     <t xml:space="preserve">9.71773338317871</t>
@@ -665,16 +665,16 @@
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496506690979</t>
+    <t xml:space="preserve">9.90396213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965076446533</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451484680176</t>
+    <t xml:space="preserve">10.9451494216919</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191837310791</t>
+    <t xml:space="preserve">11.4191827774048</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2741413116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973886489868</t>
+    <t xml:space="preserve">12.2741403579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973876953125</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633991241455</t>
+    <t xml:space="preserve">13.3491868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634010314941</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
@@ -728,28 +728,28 @@
     <t xml:space="preserve">14.6443195343018</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173463821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009860992432</t>
+    <t xml:space="preserve">14.0940999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173473358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009880065918</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4169073104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338369369507</t>
+    <t xml:space="preserve">12.8243618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4169082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338359832764</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184869766235</t>
+    <t xml:space="preserve">13.5184850692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930906295776</t>
@@ -767,67 +767,67 @@
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094509124756</t>
+    <t xml:space="preserve">14.0094518661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348048210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019954681396</t>
+    <t xml:space="preserve">14.3480491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
     <t xml:space="preserve">14.5512075424194</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5596723556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004167556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157676696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655462265015</t>
+    <t xml:space="preserve">14.5596714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157695770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655471801758</t>
   </si>
   <si>
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9840574264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994064331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031351089478</t>
+    <t xml:space="preserve">13.9840564727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994073867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385740280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.782036781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397117614746</t>
+    <t xml:space="preserve">12.7820377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397127151489</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523462295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423017501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5430994033813</t>
+    <t xml:space="preserve">13.5523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.543098449707</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071056365967</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0434169769287</t>
+    <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175714492798</t>
+    <t xml:space="preserve">13.0175704956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.3018732070923</t>
@@ -872,16 +872,16 @@
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8797273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2243366241455</t>
+    <t xml:space="preserve">13.1295700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8797283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901941299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2243375778198</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812601089478</t>
@@ -890,19 +890,19 @@
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
+    <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123399734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276026725769</t>
+    <t xml:space="preserve">13.1123380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277177810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501811981201</t>
@@ -911,31 +911,31 @@
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314193725586</t>
+    <t xml:space="preserve">12.9314203262329</t>
   </si>
   <si>
     <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834280014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.233588218689</t>
+    <t xml:space="preserve">12.4834289550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2335872650146</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.035439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975954055786</t>
+    <t xml:space="preserve">12.0354375839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
     <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3542013168335</t>
+    <t xml:space="preserve">12.3542003631592</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594327926636</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166757583618</t>
+    <t xml:space="preserve">11.7166767120361</t>
   </si>
   <si>
     <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286724090576</t>
+    <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597513198853</t>
@@ -974,52 +974,52 @@
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769813537598</t>
+    <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
     <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339067459106</t>
+    <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182085037231</t>
+    <t xml:space="preserve">11.6305246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785150527954</t>
+    <t xml:space="preserve">12.0785140991211</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0440530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0871286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157220840454</t>
+    <t xml:space="preserve">12.0440540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0871305465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5006589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815786361694</t>
+    <t xml:space="preserve">12.6988096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5006608963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815776824951</t>
   </si>
   <si>
     <t xml:space="preserve">12.7591152191162</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920444488525</t>
+    <t xml:space="preserve">12.4920434951782</t>
   </si>
   <si>
     <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265054702759</t>
+    <t xml:space="preserve">12.5265035629272</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8366527557373</t>
+    <t xml:space="preserve">12.8366508483887</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883438110352</t>
@@ -1073,19 +1073,19 @@
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868101119995</t>
+    <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
+    <t xml:space="preserve">12.6126565933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917249679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089559555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520324707031</t>
+    <t xml:space="preserve">12.9917259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520315170288</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">13.0951070785522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1381845474243</t>
+    <t xml:space="preserve">13.13818359375</t>
   </si>
   <si>
     <t xml:space="preserve">13.1984901428223</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914064407349</t>
+    <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757081985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843246459961</t>
+    <t xml:space="preserve">13.7757091522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843236923218</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
@@ -1145,28 +1145,28 @@
     <t xml:space="preserve">14.4907712936401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963212966919</t>
+    <t xml:space="preserve">14.5166177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963203430176</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240190505981</t>
+    <t xml:space="preserve">13.7240180969238</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547775268555</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3443126678467</t>
+    <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.844630241394</t>
+    <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.1117010116577</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">13.7929410934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
@@ -1196,31 +1196,31 @@
     <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8187866210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8877077102661</t>
+    <t xml:space="preserve">13.8187856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8877086639404</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8360157012939</t>
+    <t xml:space="preserve">13.8360147476196</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7326326370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154026031494</t>
+    <t xml:space="preserve">13.7326335906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569473266602</t>
+    <t xml:space="preserve">13.4569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">13.3535642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4052562713623</t>
+    <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880243301392</t>
+    <t xml:space="preserve">13.3880252838135</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">13.6292505264282</t>
   </si>
   <si>
-    <t xml:space="preserve">13.370795249939</t>
+    <t xml:space="preserve">13.3707942962646</t>
   </si>
   <si>
     <t xml:space="preserve">13.2846422195435</t>
@@ -1253,43 +1253,43 @@
     <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3363332748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5775594711304</t>
+    <t xml:space="preserve">13.3363342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5775604248047</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5086393356323</t>
+    <t xml:space="preserve">13.508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9517154693604</t>
+    <t xml:space="preserve">13.8634128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951714515686</t>
   </si>
   <si>
     <t xml:space="preserve">13.9693746566772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7751111984253</t>
+    <t xml:space="preserve">13.775110244751</t>
   </si>
   <si>
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340543746948</t>
+    <t xml:space="preserve">13.9340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161670684814</t>
+    <t xml:space="preserve">13.6161661148071</t>
   </si>
   <si>
     <t xml:space="preserve">13.5278644561768</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">13.4219017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0863542556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2982797622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2806196212769</t>
+    <t xml:space="preserve">13.0863552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2982807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2806205749512</t>
   </si>
   <si>
     <t xml:space="preserve">13.0686950683594</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870347976685</t>
+    <t xml:space="preserve">13.9870357513428</t>
   </si>
   <si>
     <t xml:space="preserve">13.8457527160645</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865823745728</t>
+    <t xml:space="preserve">13.3865814208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
@@ -1361,37 +1361,37 @@
     <t xml:space="preserve">13.7221298217773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6514873504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4748840332031</t>
+    <t xml:space="preserve">13.6514883041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4748849868774</t>
   </si>
   <si>
     <t xml:space="preserve">13.6868085861206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.580846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6338262557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4572229385376</t>
+    <t xml:space="preserve">13.5808458328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6338272094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4572238922119</t>
   </si>
   <si>
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.6691484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
+    <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1746578216553</t>
+    <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095247268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5035619735718</t>
+    <t xml:space="preserve">12.6095237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5035629272461</t>
   </si>
   <si>
     <t xml:space="preserve">13.0157136917114</t>
@@ -1427,28 +1427,28 @@
     <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980535507202</t>
+    <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391103744507</t>
+    <t xml:space="preserve">12.8391084671021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569967269897</t>
+    <t xml:space="preserve">13.1569957733154</t>
   </si>
   <si>
     <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9274120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8920907974243</t>
+    <t xml:space="preserve">12.9274110794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8920917510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037891387939</t>
+    <t xml:space="preserve">12.8567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037881851196</t>
   </si>
   <si>
     <t xml:space="preserve">12.2386560440063</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673349380493</t>
+    <t xml:space="preserve">11.267333984375</t>
   </si>
   <si>
     <t xml:space="preserve">11.3379764556885</t>
@@ -1502,49 +1502,49 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317874908447</t>
+    <t xml:space="preserve">10.9317855834961</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7618246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7265043258667</t>
+    <t xml:space="preserve">11.7618255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.726505279541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496738433838</t>
+    <t xml:space="preserve">11.1260509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496728897095</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2077102661133</t>
+    <t xml:space="preserve">10.2077112197876</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843145370483</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0200881958008</t>
+    <t xml:space="preserve">11.0200872421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9494476318359</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299152374268</t>
+    <t xml:space="preserve">10.154727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
     <t xml:space="preserve">9.44831275939941</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198629379272</t>
+    <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.666880607605</t>
+    <t xml:space="preserve">10.6668796539307</t>
   </si>
   <si>
     <t xml:space="preserve">10.2783517837524</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785789489746</t>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785779953003</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258247375488</t>
+    <t xml:space="preserve">10.7375211715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
@@ -1634,37 +1634,37 @@
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606906890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3313331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.2606916427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3313322067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019756317139</t>
+    <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.84348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.896466255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554103851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.984766960144</t>
+    <t xml:space="preserve">10.8434839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8964653015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554094314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9847679138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.3203153610229</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069110870361</t>
+    <t xml:space="preserve">10.7069101333618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027923583984</t>
+    <t xml:space="preserve">9.84669780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846300125122</t>
+    <t xml:space="preserve">10.0663261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846290588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578388214111</t>
+    <t xml:space="preserve">10.139536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578397750854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055847167969</t>
+    <t xml:space="preserve">10.5055837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5238876342773</t>
+    <t xml:space="preserve">10.523886680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5604915618896</t>
+    <t xml:space="preserve">10.560492515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716335296631</t>
+    <t xml:space="preserve">10.8716325759888</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899354934692</t>
+    <t xml:space="preserve">10.6703062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899345397949</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193794250488</t>
+    <t xml:space="preserve">11.2193784713745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533306121826</t>
+    <t xml:space="preserve">11.1644716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252140045166</t>
+    <t xml:space="preserve">10.7252130508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944842338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461687088013</t>
+    <t xml:space="preserve">10.9448432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608589172363</t>
+    <t xml:space="preserve">8.23608493804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550094604492</t>
+    <t xml:space="preserve">8.17202663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550142288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234292984009</t>
+    <t xml:space="preserve">6.01234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00982332229614</t>
+    <t xml:space="preserve">7.0098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558013916016</t>
+    <t xml:space="preserve">7.055579662323</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531558990479</t>
+    <t xml:space="preserve">7.41247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531511306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568677902222</t>
+    <t xml:space="preserve">7.48568725585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038034439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303308486938</t>
+    <t xml:space="preserve">6.68038082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229118347168</t>
+    <t xml:space="preserve">7.52229166030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364643096924</t>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364547729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818161010742</t>
+    <t xml:space="preserve">8.96818256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62043571472168</t>
+    <t xml:space="preserve">8.620436668396</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003803253174</t>
+    <t xml:space="preserve">7.7968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003755569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6321063041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361755371094</t>
+    <t xml:space="preserve">7.77852535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63210582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236180305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642868041992</t>
+    <t xml:space="preserve">7.04642820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340475082397</t>
+    <t xml:space="preserve">6.86340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3509373664856</t>
+    <t xml:space="preserve">6.46075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35093688964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130807876587</t>
+    <t xml:space="preserve">6.02149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242116928101</t>
+    <t xml:space="preserve">5.47242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279235839844</t>
+    <t xml:space="preserve">5.25279188156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626070022583</t>
+    <t xml:space="preserve">5.36260652542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884069442749</t>
+    <t xml:space="preserve">5.61884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44908237457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324684143066</t>
+    <t xml:space="preserve">7.4490818977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324731826782</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55889654159546</t>
+    <t xml:space="preserve">7.5588960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062202453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452194213867</t>
+    <t xml:space="preserve">8.51062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452289581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025035858154</t>
+    <t xml:space="preserve">8.73025131225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176208496094</t>
+    <t xml:space="preserve">8.82176303863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308940887451</t>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179000854492</t>
+    <t xml:space="preserve">9.79179096221924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866195678711</t>
+    <t xml:space="preserve">10.3866186141968</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998676300049</t>
+    <t xml:space="preserve">9.37998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8949728012085</t>
+    <t xml:space="preserve">8.89497184753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833999633789</t>
+    <t xml:space="preserve">7.88833904266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4740161895752</t>
+    <t xml:space="preserve">8.47401714324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9249439239502</t>
+    <t xml:space="preserve">7.92494487762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735593795776</t>
+    <t xml:space="preserve">6.57056617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735641479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.53396081924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661451339722</t>
+    <t xml:space="preserve">6.93661403656006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -2730,6 +2730,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.46000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64000034332275</t>
   </si>
 </sst>
 </file>
@@ -68692,7 +68695,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.691099537</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>15240</v>
@@ -68713,6 +68716,32 @@
         <v>905</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6910300926</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>29246</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>9.77999973297119</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>9.64000034332275</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>906</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="908">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414600372314</t>
+    <t xml:space="preserve">5.10414505004883</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169673919678</t>
+    <t xml:space="preserve">5.09169578552246</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
@@ -59,13 +59,13 @@
     <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16224098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523591995239</t>
+    <t xml:space="preserve">5.16224193572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958829879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523639678955</t>
   </si>
   <si>
     <t xml:space="preserve">5.30333185195923</t>
@@ -74,37 +74,37 @@
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3157811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482908248901</t>
+    <t xml:space="preserve">5.31578063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
     <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34897899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
+    <t xml:space="preserve">5.3489785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122484207153</t>
+    <t xml:space="preserve">5.41122388839722</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462566375732</t>
+    <t xml:space="preserve">5.39462518692017</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176956176758</t>
+    <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000385284424</t>
@@ -113,28 +113,28 @@
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71415376663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96728563308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9008903503418</t>
+    <t xml:space="preserve">5.89259099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558546066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96728610992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90089082717896</t>
   </si>
   <si>
     <t xml:space="preserve">5.96313619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95068693161011</t>
+    <t xml:space="preserve">5.95068597793579</t>
   </si>
   <si>
     <t xml:space="preserve">5.94653701782227</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442953109741</t>
+    <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
@@ -158,103 +158,103 @@
     <t xml:space="preserve">6.05028009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327360153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19136953353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47355031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239486694336</t>
+    <t xml:space="preserve">6.13327407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19137048721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47355079650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36150741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239534378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56069421768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.432053565979</t>
+    <t xml:space="preserve">6.5606951713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43205308914185</t>
   </si>
   <si>
     <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59389209747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58559274673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80552673339844</t>
+    <t xml:space="preserve">6.59389162063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58559226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301240921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451059341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920475006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034930229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234580993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3864860534668</t>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920522689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349254608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234533309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648748397827</t>
   </si>
   <si>
     <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36573839187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634817123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22058057785034</t>
+    <t xml:space="preserve">7.36573886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22058010101318</t>
   </si>
   <si>
     <t xml:space="preserve">7.20788478851318</t>
@@ -272,40 +272,40 @@
     <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94123888015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49145936965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37295007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29253339767456</t>
+    <t xml:space="preserve">6.94123840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617311477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37294960021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253244400024</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290607452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448574066162</t>
+    <t xml:space="preserve">7.26290559768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
     <t xml:space="preserve">7.19941902160645</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23751163482666</t>
+    <t xml:space="preserve">7.23751211166382</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821298599243</t>
+    <t xml:space="preserve">7.06821346282959</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87351942062378</t>
+    <t xml:space="preserve">6.87351894378662</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027351379395</t>
+    <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.67036104202271</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96663331985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538375854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77194023132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84812450408936</t>
+    <t xml:space="preserve">7.15286207199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96663284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99626111984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7719407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84812498092651</t>
   </si>
   <si>
     <t xml:space="preserve">6.88621664047241</t>
@@ -368,22 +368,22 @@
     <t xml:space="preserve">7.1867208480835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11053657531738</t>
+    <t xml:space="preserve">7.11053609848022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05128288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14016437530518</t>
+    <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0936074256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937501907349</t>
+    <t xml:space="preserve">7.09360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937454223633</t>
   </si>
   <si>
     <t xml:space="preserve">7.05974769592285</t>
@@ -395,25 +395,25 @@
     <t xml:space="preserve">6.97086572647095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398010253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05551528930664</t>
+    <t xml:space="preserve">7.03858470916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011989593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398057937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0555157661438</t>
   </si>
   <si>
     <t xml:space="preserve">7.09783935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435230255127</t>
+    <t xml:space="preserve">7.00049352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435277938843</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900186538696</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476993560791</t>
+    <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
     <t xml:space="preserve">7.10207271575928</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">7.23327875137329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17402458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
+    <t xml:space="preserve">7.17402410507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597644805908</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680932998657</t>
@@ -452,73 +452,73 @@
     <t xml:space="preserve">7.43220376968384</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49992275238037</t>
+    <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373943328857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38141536712646</t>
+    <t xml:space="preserve">7.38141489028931</t>
   </si>
   <si>
     <t xml:space="preserve">7.28406810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44490194320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47453022003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382696151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349924087524</t>
+    <t xml:space="preserve">7.44490146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349876403809</t>
   </si>
   <si>
     <t xml:space="preserve">7.58457279205322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913482666016</t>
+    <t xml:space="preserve">7.449134349823</t>
   </si>
   <si>
     <t xml:space="preserve">7.53378391265869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61843252182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229177474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880472183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229272842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
   </si>
   <si>
     <t xml:space="preserve">7.74540615081787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86814832687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163537979126</t>
   </si>
   <si>
     <t xml:space="preserve">7.92317008972168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82582330703735</t>
+    <t xml:space="preserve">7.8258228302002</t>
   </si>
   <si>
     <t xml:space="preserve">7.88931083679199</t>
@@ -527,85 +527,85 @@
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9485650062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308256149292</t>
+    <t xml:space="preserve">7.95279836654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856452941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308303833008</t>
   </si>
   <si>
     <t xml:space="preserve">7.61420011520386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42797088623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332227706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45759963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694276809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685476303101</t>
+    <t xml:space="preserve">7.42797183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020742416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45760059356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694181442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40257740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137088775635</t>
+    <t xml:space="preserve">7.40257692337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137136459351</t>
   </si>
   <si>
     <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702934265137</t>
+    <t xml:space="preserve">7.95702981948853</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097755432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023220062256</t>
+    <t xml:space="preserve">8.02474880218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023124694824</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222854614258</t>
+    <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599979400635</t>
+    <t xml:space="preserve">8.26600074768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.23214054107666</t>
@@ -614,22 +614,22 @@
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3252534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027667999268</t>
+    <t xml:space="preserve">8.32525444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.87970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514434814453</t>
+    <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
     <t xml:space="preserve">8.998215675354</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02361106872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19291019439697</t>
+    <t xml:space="preserve">9.02360916137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
     <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448699951172</t>
+    <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
     <t xml:space="preserve">9.5653657913208</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1325159072876</t>
+    <t xml:space="preserve">10.1325149536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4965076446533</t>
+    <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451494216919</t>
+    <t xml:space="preserve">10.9451475143433</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
@@ -683,34 +683,34 @@
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191827774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884819030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239217758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.76624584198</t>
+    <t xml:space="preserve">11.4191846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884828567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7662448883057</t>
   </si>
   <si>
     <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2741403579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629590988159</t>
+    <t xml:space="preserve">12.2741413116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973867416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629581451416</t>
   </si>
   <si>
     <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2634010314941</t>
+    <t xml:space="preserve">14.2634000778198</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
@@ -722,46 +722,46 @@
     <t xml:space="preserve">12.5111589431763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443195343018</t>
+    <t xml:space="preserve">13.1460275650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443185806274</t>
   </si>
   <si>
     <t xml:space="preserve">14.0940999984741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009880065918</t>
+    <t xml:space="preserve">14.5173463821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4169082641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5100202560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930906295776</t>
+    <t xml:space="preserve">12.8243608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4169073104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438814163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
     <t xml:space="preserve">13.7639684677124</t>
@@ -770,25 +770,25 @@
     <t xml:space="preserve">14.0094518661499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3057231903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3480491638184</t>
+    <t xml:space="preserve">14.3057241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.348048210144</t>
   </si>
   <si>
     <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596714019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.500415802002</t>
+    <t xml:space="preserve">14.5512065887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596723556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.508882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004148483276</t>
   </si>
   <si>
     <t xml:space="preserve">14.4073028564453</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">13.8655471801758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7978277206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840564727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994073867798</t>
+    <t xml:space="preserve">13.7978267669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994064331055</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385740280151</t>
@@ -821,31 +821,31 @@
     <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290988922119</t>
+    <t xml:space="preserve">13.1290979385376</t>
   </si>
   <si>
     <t xml:space="preserve">12.7820377349854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397127151489</t>
+    <t xml:space="preserve">12.7397117614746</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5269498825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5523452758789</t>
+    <t xml:space="preserve">13.5269508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.543098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2071056365967</t>
+    <t xml:space="preserve">13.5430994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2071046829224</t>
   </si>
   <si>
     <t xml:space="preserve">13.0348024368286</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1726446151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3018732070923</t>
+    <t xml:space="preserve">13.1726455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.301872253418</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295700073242</t>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797283172607</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">12.6901941299438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2243375778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812601089478</t>
+    <t xml:space="preserve">13.2243366241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
@@ -899,34 +899,34 @@
     <t xml:space="preserve">13.1123380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277177810669</t>
+    <t xml:space="preserve">13.3277187347412</t>
   </si>
   <si>
     <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501811981201</t>
+    <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8194217681885</t>
+    <t xml:space="preserve">12.9314193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8194208145142</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2335872650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3369693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0354375839233</t>
+    <t xml:space="preserve">12.233588218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3369703292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0354385375977</t>
   </si>
   <si>
     <t xml:space="preserve">11.8975944519043</t>
@@ -935,22 +935,22 @@
     <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3542003631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2594327926636</t>
+    <t xml:space="preserve">12.3541994094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2594337463379</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837474822998</t>
+    <t xml:space="preserve">11.9837465286255</t>
   </si>
   <si>
     <t xml:space="preserve">11.8372888565063</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">11.7166767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114423751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8286733627319</t>
+    <t xml:space="preserve">11.8114433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8286724090576</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597513198853</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769823074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7511367797852</t>
+    <t xml:space="preserve">11.7769832611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7511358261108</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339057922363</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0612840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0785140991211</t>
+    <t xml:space="preserve">12.0612831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0785150527954</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0440540313721</t>
+    <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
     <t xml:space="preserve">12.0871305465698</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988096237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5006608963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815776824951</t>
+    <t xml:space="preserve">12.6988086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.500659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
     <t xml:space="preserve">12.7591152191162</t>
@@ -1028,34 +1028,34 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231224060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4920434951782</t>
+    <t xml:space="preserve">12.4231233596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
     <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628168106079</t>
+    <t xml:space="preserve">12.3628158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.535120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265035629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7849607467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9141893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8366508483887</t>
+    <t xml:space="preserve">12.5351209640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9141883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.836651802063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883438110352</t>
@@ -1067,31 +1067,31 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643476486206</t>
+    <t xml:space="preserve">12.6643466949463</t>
   </si>
   <si>
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7074241638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126565933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246541976929</t>
+    <t xml:space="preserve">12.5868101119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7074251174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246551513672</t>
   </si>
   <si>
     <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8280372619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7418851852417</t>
+    <t xml:space="preserve">12.8280363082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
     <t xml:space="preserve">12.8711128234863</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">13.0089569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572658538818</t>
+    <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520315170288</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0951070785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.13818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1984901428223</t>
+    <t xml:space="preserve">13.0951080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1381845474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1984910964966</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
@@ -1133,28 +1133,28 @@
     <t xml:space="preserve">13.7757091522217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7843236923218</t>
+    <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289319992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4907712936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5166177749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963203430176</t>
+    <t xml:space="preserve">14.1289329528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4907703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5166187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963222503662</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618612289429</t>
@@ -1166,25 +1166,25 @@
     <t xml:space="preserve">14.1547775268555</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3443117141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0255508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9393978118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8446311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1117010116577</t>
+    <t xml:space="preserve">14.3443126678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0255498886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.939398765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.844630241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929410934448</t>
+    <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206359863281</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8187856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8877086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8704767227173</t>
+    <t xml:space="preserve">13.6637115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8187866210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8877077102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.870475769043</t>
   </si>
   <si>
     <t xml:space="preserve">13.8360147476196</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7326335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154035568237</t>
+    <t xml:space="preserve">13.7326326370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154026031494</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
+    <t xml:space="preserve">13.3535652160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.405255317688</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">13.6292505264282</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3707942962646</t>
+    <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
     <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603294372559</t>
+    <t xml:space="preserve">13.5603284835815</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363342285156</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775604248047</t>
+    <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -2733,6 +2733,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.64000034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80000019073486</t>
   </si>
 </sst>
 </file>
@@ -68721,7 +68724,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.6910300926</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>29246</v>
@@ -68742,6 +68745,32 @@
         <v>906</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.6912152778</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>26899</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>9.77999973297119</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>907</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="911">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414552688599</t>
+    <t xml:space="preserve">5.10414600372314</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">5.15394258499146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169626235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14564228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18713998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11659479141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958925247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523591995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333089828491</t>
+    <t xml:space="preserve">5.09169673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14564180374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1165943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333185195923</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632583618164</t>
+    <t xml:space="preserve">5.34482955932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632535934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.3489785194397</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972665786743</t>
+    <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122436523438</t>
@@ -98,76 +98,76 @@
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462566375732</t>
+    <t xml:space="preserve">5.39462518692017</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48176908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71000337600708</t>
+    <t xml:space="preserve">5.48176956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259099960327</t>
+    <t xml:space="preserve">5.89259052276611</t>
   </si>
   <si>
     <t xml:space="preserve">5.71415376663208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558450698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96728515625</t>
+    <t xml:space="preserve">5.85939311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96728610992432</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068693161011</t>
+    <t xml:space="preserve">5.96313571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068645477295</t>
   </si>
   <si>
     <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87599182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8676929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05443000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0419807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05857944488525</t>
+    <t xml:space="preserve">5.87599229812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86769247055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05442953109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04198026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0585789680481</t>
   </si>
   <si>
     <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327360153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137048721313</t>
+    <t xml:space="preserve">6.13327407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19136953353882</t>
   </si>
   <si>
     <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36150789260864</t>
+    <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
     <t xml:space="preserve">6.55239486694336</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205308914185</t>
+    <t xml:space="preserve">6.56069421768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.432053565979</t>
   </si>
   <si>
     <t xml:space="preserve">6.53994607925415</t>
@@ -188,43 +188,43 @@
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559274673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804201126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464071273804</t>
+    <t xml:space="preserve">6.58559226989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61463975906372</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80552768707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321535110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301336288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05450916290283</t>
+    <t xml:space="preserve">6.8055272102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321630477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301240921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">7.12920522689819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30349397659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
+    <t xml:space="preserve">7.30349254608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.67289733886719</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">8.12928581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648748397827</t>
+    <t xml:space="preserve">7.67281770706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
     <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36573839187622</t>
+    <t xml:space="preserve">7.36573791503906</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240310668945</t>
@@ -257,64 +257,64 @@
     <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788478851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617263793945</t>
+    <t xml:space="preserve">7.20788431167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123888015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617311477661</t>
   </si>
   <si>
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49145889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37294960021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983522415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29253339767456</t>
+    <t xml:space="preserve">6.99202871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37295007705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2925329208374</t>
   </si>
   <si>
     <t xml:space="preserve">7.29676580429077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26290512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448383331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994194984436</t>
+    <t xml:space="preserve">7.26290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523014068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3644847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941902160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830003738403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2375111579895</t>
+    <t xml:space="preserve">7.23751163482666</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132688522339</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">7.06821298599243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351894378662</t>
+    <t xml:space="preserve">7.02588796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351942062378</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">7.15286207199097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08514261245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96663284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99626111984253</t>
+    <t xml:space="preserve">7.08514213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96663331985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99626064300537</t>
   </si>
   <si>
     <t xml:space="preserve">6.72538328170776</t>
@@ -365,25 +365,25 @@
     <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18672132492065</t>
+    <t xml:space="preserve">7.18672180175781</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128192901611</t>
+    <t xml:space="preserve">7.05128288269043</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360647201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937501907349</t>
+    <t xml:space="preserve">7.10630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360790252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937454223633</t>
   </si>
   <si>
     <t xml:space="preserve">7.05974817276001</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">7.04704999923706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086572647095</t>
+    <t xml:space="preserve">6.97086524963379</t>
   </si>
   <si>
     <t xml:space="preserve">7.03858470916748</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">7.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06398057937622</t>
+    <t xml:space="preserve">7.06398010253906</t>
   </si>
   <si>
     <t xml:space="preserve">7.0555157661438</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435277938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900186538696</t>
+    <t xml:space="preserve">7.00049352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11900234222412</t>
   </si>
   <si>
     <t xml:space="preserve">7.008957862854</t>
@@ -425,94 +425,94 @@
     <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10207176208496</t>
+    <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
     <t xml:space="preserve">7.38987970352173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402458190918</t>
+    <t xml:space="preserve">7.20365142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402410507202</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597692489624</t>
+    <t xml:space="preserve">7.24597644805908</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43220520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373943328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834547042847</t>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373991012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406763076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490194320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
     <t xml:space="preserve">7.47452831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64382648468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652513504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457374572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69884967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540662765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
+    <t xml:space="preserve">7.64382696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6565260887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349876403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843395233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880472183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6522912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163537979126</t>
   </si>
   <si>
     <t xml:space="preserve">7.92317008972168</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9485650062561</t>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856548309326</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
@@ -539,58 +539,58 @@
     <t xml:space="preserve">7.70308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61419916152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332323074341</t>
+    <t xml:space="preserve">7.6141996383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332370758057</t>
   </si>
   <si>
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45759916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536310195923</t>
+    <t xml:space="preserve">7.45759868621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536214828491</t>
   </si>
   <si>
     <t xml:space="preserve">7.73694229125977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51685380935669</t>
+    <t xml:space="preserve">7.51685428619385</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40257692337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755516052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137088775635</t>
+    <t xml:space="preserve">7.4025764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137136459351</t>
   </si>
   <si>
     <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01205158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474784851074</t>
+    <t xml:space="preserve">7.95702981948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01205253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707382202148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21097755432129</t>
+    <t xml:space="preserve">8.21097660064697</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599884033203</t>
+    <t xml:space="preserve">8.26600074768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.23213958740234</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">8.3252534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027667999268</t>
+    <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.87970733642578</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99821662902832</t>
+    <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02361011505127</t>
+    <t xml:space="preserve">9.02360916137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17597961425781</t>
+    <t xml:space="preserve">9.1759786605835</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">9.98861217498779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4541845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1325168609619</t>
+    <t xml:space="preserve">10.4541835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773433685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1325149536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927808761597</t>
+    <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">10.9620780944824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0551929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191846847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884828567505</t>
+    <t xml:space="preserve">11.0551919937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884809494019</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355449676514</t>
+    <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973886489868</t>
+    <t xml:space="preserve">12.6973876953125</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">14.2633991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0156383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0517768859863</t>
+    <t xml:space="preserve">16.0156364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111589431763</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">13.1460294723511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443185806274</t>
+    <t xml:space="preserve">14.6443195343018</t>
   </si>
   <si>
     <t xml:space="preserve">14.0940999984741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009880065918</t>
+    <t xml:space="preserve">14.5173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761619567871</t>
+    <t xml:space="preserve">13.4169073104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">13.5184860229492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.493091583252</t>
+    <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
     <t xml:space="preserve">13.7639684677124</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.601996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596704483032</t>
+    <t xml:space="preserve">14.348048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512056350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596733093262</t>
   </si>
   <si>
     <t xml:space="preserve">14.5088815689087</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4073038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157695770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311195373535</t>
+    <t xml:space="preserve">14.4073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157686233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311176300049</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
@@ -809,37 +809,37 @@
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9840564727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994073867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031341552734</t>
+    <t xml:space="preserve">13.9840574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385721206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7820377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397117614746</t>
+    <t xml:space="preserve">12.782036781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397136688232</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5269508361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5523452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423007965088</t>
+    <t xml:space="preserve">13.5269498825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5523462295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423017501831</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348014831543</t>
+    <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
     <t xml:space="preserve">13.043417930603</t>
@@ -857,52 +857,52 @@
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397172927856</t>
+    <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175714492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3018732070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1640291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.0175704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.301872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1640300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6901922225952</t>
+    <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812601089478</t>
+    <t xml:space="preserve">13.1812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557331085205</t>
+    <t xml:space="preserve">12.9228038787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557312011719</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277187347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276026725769</t>
+    <t xml:space="preserve">13.3277196884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
@@ -911,28 +911,28 @@
     <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9314203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8194217681885</t>
+    <t xml:space="preserve">12.9314193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8194227218628</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.233588218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3369703292847</t>
+    <t xml:space="preserve">12.2335872650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.035439491272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8975954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474370956421</t>
+    <t xml:space="preserve">11.8975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474351882935</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.837287902832</t>
+    <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8286724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7597513198853</t>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8286733627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7597522735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.8200588226318</t>
@@ -980,28 +980,28 @@
     <t xml:space="preserve">11.7511377334595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.604679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6305246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182085037231</t>
+    <t xml:space="preserve">11.7339067459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6305236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388216018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440540313721</t>
+    <t xml:space="preserve">12.0785160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
     <t xml:space="preserve">12.0871295928955</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">12.6988077163696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231233596802</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661998748779</t>
+    <t xml:space="preserve">12.4661979675293</t>
   </si>
   <si>
     <t xml:space="preserve">12.3628158569336</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">12.6298875808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5351209640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5265054702759</t>
+    <t xml:space="preserve">12.535120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.836651802063</t>
+    <t xml:space="preserve">12.9141883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8366527557373</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883428573608</t>
@@ -1067,31 +1067,31 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7504997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868110656738</t>
+    <t xml:space="preserve">12.6643476486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7505006790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868120193481</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126575469971</t>
+    <t xml:space="preserve">12.6126565933228</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7935752868652</t>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418842315674</t>
+    <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.871111869812</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">13.0089569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572658538818</t>
+    <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2674112319946</t>
+    <t xml:space="preserve">13.2674121856689</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914073944092</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">13.6550960540771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757081985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843236923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7498626708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1289319992065</t>
+    <t xml:space="preserve">13.7757091522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7498636245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1289329528809</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907712936401</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963222503662</t>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963203430176</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618621826172</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">14.1547784805298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3443117141724</t>
+    <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929391860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">13.7929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637115478516</t>
+    <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704776763916</t>
+    <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
     <t xml:space="preserve">13.8360157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8015546798706</t>
+    <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1247,19 +1247,19 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846422195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603284835815</t>
+    <t xml:space="preserve">13.2846431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258693695068</t>
+    <t xml:space="preserve">13.5775604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
     <t xml:space="preserve">13.508638381958</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.951714515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693756103516</t>
+    <t xml:space="preserve">13.8634119033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9517154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693737030029</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1106586456299</t>
+    <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
     <t xml:space="preserve">13.9340543746948</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278654098511</t>
+    <t xml:space="preserve">13.5278635025024</t>
   </si>
   <si>
     <t xml:space="preserve">13.4219026565552</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686941146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402433395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872619628906</t>
+    <t xml:space="preserve">13.0686960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872629165649</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.004695892334</t>
+    <t xml:space="preserve">14.0046949386597</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753374099731</t>
+    <t xml:space="preserve">14.0753364562988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.9870347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8457517623901</t>
+    <t xml:space="preserve">13.8457527160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985059738159</t>
+    <t xml:space="preserve">13.5985069274902</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338272094727</t>
+    <t xml:space="preserve">13.6338262557983</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1385,64 +1385,64 @@
     <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102043151855</t>
+    <t xml:space="preserve">13.5102052688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452983856201</t>
+    <t xml:space="preserve">13.3512601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452993392944</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1746578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629585266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.980393409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6095237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5035610198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0157136917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159408569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980535507202</t>
+    <t xml:space="preserve">13.2276382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.174656867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629594802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9803924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6095247268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5035619735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0157127380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159399032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391103744507</t>
+    <t xml:space="preserve">12.8391094207764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099781036377</t>
+    <t xml:space="preserve">13.1569967269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099771499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2386560440063</t>
+    <t xml:space="preserve">12.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790313720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4262771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.037748336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0024271011353</t>
+    <t xml:space="preserve">11.1790323257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4262762069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0377492904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0024280548096</t>
   </si>
   <si>
     <t xml:space="preserve">11.2143526077271</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0730695724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792585372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441654205322</t>
+    <t xml:space="preserve">11.0730686187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2849950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441644668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">11.7618246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7265033721924</t>
+    <t xml:space="preserve">11.7265043258667</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728433609009</t>
+    <t xml:space="preserve">11.2496728897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439373016357</t>
+    <t xml:space="preserve">11.4439382553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494466781616</t>
+    <t xml:space="preserve">10.9494476318359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831371307373</t>
+    <t xml:space="preserve">10.1547298431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299152374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831275939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1370677947998</t>
+    <t xml:space="preserve">10.1370687484741</t>
   </si>
   <si>
     <t xml:space="preserve">10.7198619842529</t>
@@ -1607,40 +1607,40 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2430305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785789489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6845407485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7375221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258237838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.613899230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606906890869</t>
+    <t xml:space="preserve">10.24303150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079374313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785779953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6845417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7375211715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258247375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6139001846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5609178543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8434839248657</t>
+    <t xml:space="preserve">10.84348487854</t>
   </si>
   <si>
     <t xml:space="preserve">10.8964653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9141263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554103851318</t>
+    <t xml:space="preserve">10.9141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -2742,6 +2742,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.72000026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89999961853027</t>
   </si>
 </sst>
 </file>
@@ -68808,7 +68811,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6911226852</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>29689</v>
@@ -68829,6 +68832,32 @@
         <v>909</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6912152778</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>25809</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>9.97999954223633</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>9.72000026702881</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>9.89999961853027</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>910</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="912">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414600372314</t>
+    <t xml:space="preserve">5.10414552688599</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394258499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14564180374146</t>
+    <t xml:space="preserve">5.1539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14564275741577</t>
   </si>
   <si>
     <t xml:space="preserve">5.1871395111084</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">5.16224098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333185195923</t>
+    <t xml:space="preserve">5.19958925247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523591995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
@@ -77,97 +77,97 @@
     <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632535934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3489785194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312843322754</t>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122436523438</t>
+    <t xml:space="preserve">5.41122484207153</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462518692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761964797974</t>
+    <t xml:space="preserve">5.39462566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761917114258</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176956176758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9340877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89259052276611</t>
+    <t xml:space="preserve">5.71000337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93408727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89259099960327</t>
   </si>
   <si>
     <t xml:space="preserve">5.71415376663208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939311981201</t>
+    <t xml:space="preserve">5.85939264297485</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728610992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9008903503418</t>
+    <t xml:space="preserve">5.96728563308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90089082717896</t>
   </si>
   <si>
     <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95068645477295</t>
+    <t xml:space="preserve">5.95068693161011</t>
   </si>
   <si>
     <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87599229812622</t>
+    <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442953109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0585789680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05027961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19136953353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47355031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3615083694458</t>
+    <t xml:space="preserve">6.05443000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0419807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05857944488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05028009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327360153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19137001037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47354984283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36150789260864</t>
   </si>
   <si>
     <t xml:space="preserve">6.55239486694336</t>
@@ -179,37 +179,37 @@
     <t xml:space="preserve">6.56069421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.432053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994607925415</t>
+    <t xml:space="preserve">6.43205404281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559226989746</t>
+    <t xml:space="preserve">6.58559274673462</t>
   </si>
   <si>
     <t xml:space="preserve">6.59804153442383</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61463975906372</t>
+    <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8055272102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321630477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301240921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961206436157</t>
+    <t xml:space="preserve">6.80552673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961254119873</t>
   </si>
   <si>
     <t xml:space="preserve">7.05451011657715</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">7.12920522689819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30349254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948146820068</t>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948099136353</t>
   </si>
   <si>
     <t xml:space="preserve">7.99234580993652</t>
@@ -233,91 +233,91 @@
     <t xml:space="preserve">8.12928581237793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67281770706177</t>
+    <t xml:space="preserve">7.67281675338745</t>
   </si>
   <si>
     <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42798376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573791503906</t>
+    <t xml:space="preserve">7.42798471450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573839187622</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240310668945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21634864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643712997437</t>
+    <t xml:space="preserve">7.21634817123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643665313721</t>
   </si>
   <si>
     <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468193054199</t>
+    <t xml:space="preserve">7.20788478851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468145370483</t>
   </si>
   <si>
     <t xml:space="preserve">6.72961521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123888015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617311477661</t>
+    <t xml:space="preserve">6.80156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356342315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617216110229</t>
   </si>
   <si>
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202871322632</t>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37295007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290607452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3644847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941902160645</t>
+    <t xml:space="preserve">7.37294960021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983522415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253339767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290559768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523109436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36448431015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830003738403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23751163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132688522339</t>
+    <t xml:space="preserve">7.2375111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132640838623</t>
   </si>
   <si>
     <t xml:space="preserve">7.06821298599243</t>
@@ -329,16 +329,16 @@
     <t xml:space="preserve">6.87351942062378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68729114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45027256011963</t>
+    <t xml:space="preserve">6.68729066848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
     <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56031703948975</t>
+    <t xml:space="preserve">6.56031656265259</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286207199097</t>
@@ -356,52 +356,52 @@
     <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77194023132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84812498092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053705215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128288269043</t>
+    <t xml:space="preserve">6.7719407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84812450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128192901611</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974817276001</t>
+    <t xml:space="preserve">7.10630559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974769592285</t>
   </si>
   <si>
     <t xml:space="preserve">7.04704999923706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858470916748</t>
+    <t xml:space="preserve">6.97086572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858518600464</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06398010253906</t>
+    <t xml:space="preserve">7.06398057937622</t>
   </si>
   <si>
     <t xml:space="preserve">7.0555157661438</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">7.03435325622559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11900234222412</t>
+    <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
     <t xml:space="preserve">7.008957862854</t>
@@ -425,22 +425,22 @@
     <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10207271575928</t>
+    <t xml:space="preserve">7.10207176208496</t>
   </si>
   <si>
     <t xml:space="preserve">7.38987970352173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20365142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402410507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211671829224</t>
+    <t xml:space="preserve">7.20365238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402505874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211624145508</t>
   </si>
   <si>
     <t xml:space="preserve">7.24597644805908</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">7.40680980682373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43220376968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992322921753</t>
+    <t xml:space="preserve">7.43220472335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992370605469</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373991012573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38141536712646</t>
+    <t xml:space="preserve">7.38141489028931</t>
   </si>
   <si>
     <t xml:space="preserve">7.28406763076782</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452831268311</t>
+    <t xml:space="preserve">7.47452878952026</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382696151733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83005571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6565260887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349876403809</t>
+    <t xml:space="preserve">7.83005666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349828720093</t>
   </si>
   <si>
     <t xml:space="preserve">7.58457326889038</t>
@@ -491,22 +491,22 @@
     <t xml:space="preserve">7.44913482666016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53378248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843395233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880472183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6522912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540615081787</t>
+    <t xml:space="preserve">7.53378391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540567398071</t>
   </si>
   <si>
     <t xml:space="preserve">7.86814832687378</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">7.93163537979126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88931035995483</t>
+    <t xml:space="preserve">7.92316913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582330703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88930988311768</t>
   </si>
   <si>
     <t xml:space="preserve">7.91470575332642</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">7.95279741287231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94856548309326</t>
+    <t xml:space="preserve">7.9485650062561</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
@@ -545,52 +545,52 @@
     <t xml:space="preserve">7.42797136306763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34332370758057</t>
+    <t xml:space="preserve">7.34332323074341</t>
   </si>
   <si>
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45759868621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536214828491</t>
+    <t xml:space="preserve">7.45759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536357879639</t>
   </si>
   <si>
     <t xml:space="preserve">7.73694229125977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51685428619385</t>
+    <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4025764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137136459351</t>
+    <t xml:space="preserve">7.40257692337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137088775635</t>
   </si>
   <si>
     <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702981948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01205253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02474880218506</t>
+    <t xml:space="preserve">7.95702934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01205158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02474784851074</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707382202148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21097660064697</t>
+    <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222759246826</t>
+    <t xml:space="preserve">8.45222663879395</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26600074768066</t>
+    <t xml:space="preserve">8.26599979400635</t>
   </si>
   <si>
     <t xml:space="preserve">8.23213958740234</t>
@@ -617,19 +617,19 @@
     <t xml:space="preserve">8.3252534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027572631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87970733642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11672496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01514530181885</t>
+    <t xml:space="preserve">8.38027667999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040916442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87970638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11672401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01514434814453</t>
   </si>
   <si>
     <t xml:space="preserve">8.998215675354</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1759786605835</t>
+    <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.29448795318604</t>
@@ -659,16 +659,16 @@
     <t xml:space="preserve">10.4541835784912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773433685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1325149536133</t>
+    <t xml:space="preserve">9.71773338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.496506690979</t>
+    <t xml:space="preserve">10.4965076446533</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">10.9451484680176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620780944824</t>
+    <t xml:space="preserve">10.9620771408081</t>
   </si>
   <si>
     <t xml:space="preserve">11.0551919937134</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884809494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239217758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.76624584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355440139771</t>
+    <t xml:space="preserve">11.5884828567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7662467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355449676514</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741413116455</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">14.2633991241455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0156364440918</t>
+    <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
     <t xml:space="preserve">14.051775932312</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">14.0940999984741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173454284668</t>
+    <t xml:space="preserve">14.5173482894897</t>
   </si>
   <si>
     <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1206340789795</t>
+    <t xml:space="preserve">13.1206331253052</t>
   </si>
   <si>
     <t xml:space="preserve">12.8243608474731</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761610031128</t>
+    <t xml:space="preserve">13.4761619567871</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5438804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5100202560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930896759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7639684677124</t>
+    <t xml:space="preserve">13.5438814163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7639694213867</t>
   </si>
   <si>
     <t xml:space="preserve">14.0094509124756</t>
@@ -773,91 +773,91 @@
     <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348048210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512056350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088815689087</t>
+    <t xml:space="preserve">14.3480501174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.601996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512075424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596704483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.508882522583</t>
   </si>
   <si>
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311176300049</t>
+    <t xml:space="preserve">14.4073047637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157695770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311185836792</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8655462265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978277206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840574264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994083404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385721206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031351089478</t>
+    <t xml:space="preserve">13.8655471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978267669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994073867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.782036781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397136688232</t>
+    <t xml:space="preserve">12.7820386886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397127151489</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5269498825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5523462295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423017501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5430994033813</t>
+    <t xml:space="preserve">13.5269508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5523443222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.543098449707</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348024368286</t>
+    <t xml:space="preserve">13.03480052948</t>
   </si>
   <si>
     <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.940034866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397163391113</t>
+    <t xml:space="preserve">12.9400339126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397172927856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">13.0175704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.301872253418</t>
+    <t xml:space="preserve">13.3018732070923</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295680999756</t>
+    <t xml:space="preserve">13.1295690536499</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812610626221</t>
+    <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
@@ -893,28 +893,28 @@
     <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557312011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123390197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2760276794434</t>
+    <t xml:space="preserve">12.6557331085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277187347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0606470108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9314193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8194227218628</t>
+    <t xml:space="preserve">13.0606479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9314203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
@@ -923,28 +923,28 @@
     <t xml:space="preserve">12.2335872650146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.035439491272</t>
+    <t xml:space="preserve">12.3369703292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0354385375977</t>
   </si>
   <si>
     <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474351882935</t>
+    <t xml:space="preserve">12.1474370956421</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2594327926636</t>
+    <t xml:space="preserve">12.2594337463379</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302051544189</t>
+    <t xml:space="preserve">12.1302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8372888565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7855968475342</t>
+    <t xml:space="preserve">11.837287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166767120361</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8200588226318</t>
+    <t xml:space="preserve">11.7597513198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8200578689575</t>
   </si>
   <si>
     <t xml:space="preserve">11.7769823074341</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">11.7511377334595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339067459106</t>
+    <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305236816406</t>
+    <t xml:space="preserve">11.6305227279663</t>
   </si>
   <si>
     <t xml:space="preserve">12.0182075500488</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785160064697</t>
+    <t xml:space="preserve">12.0785140991211</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.500659942627</t>
+    <t xml:space="preserve">12.6988096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231224060059</t>
+    <t xml:space="preserve">12.4231233596802</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">12.4661979675293</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1046,58 +1046,58 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
+    <t xml:space="preserve">12.5265054702759</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8366527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883428573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8538827896118</t>
+    <t xml:space="preserve">12.9141893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8366508483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8538837432861</t>
   </si>
   <si>
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643476486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7505006790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868120193481</t>
+    <t xml:space="preserve">12.6643486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7504997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126565933228</t>
+    <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7935762405396</t>
+    <t xml:space="preserve">12.7935771942139</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917259216309</t>
+    <t xml:space="preserve">12.7418842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8711128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917268753052</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089569091797</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520324707031</t>
+    <t xml:space="preserve">13.0520315170288</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
@@ -1118,16 +1118,16 @@
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2674121856689</t>
+    <t xml:space="preserve">13.1984910964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550960540771</t>
+    <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
     <t xml:space="preserve">13.7757091522217</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289329528809</t>
+    <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907712936401</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">13.6981716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8963203430176</t>
+    <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618621826172</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">14.1547784805298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3443126678467</t>
+    <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">13.939398765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8446311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.111701965332</t>
+    <t xml:space="preserve">13.9393978118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.844630241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1117010116577</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8187866210938</t>
+    <t xml:space="preserve">13.6637115478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8187856674194</t>
   </si>
   <si>
     <t xml:space="preserve">13.8877077102661</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8360157012939</t>
+    <t xml:space="preserve">13.8360147476196</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7326326370239</t>
+    <t xml:space="preserve">13.7326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">13.7154035568237</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535652160645</t>
+    <t xml:space="preserve">13.3535642623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.405255317688</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">13.3880252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7670936584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6292505264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.370795249939</t>
+    <t xml:space="preserve">13.7670946121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6292514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3707942962646</t>
   </si>
   <si>
     <t xml:space="preserve">13.2846431732178</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5086374282837</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693737030029</t>
+    <t xml:space="preserve">13.8634128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693756103516</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1106576919556</t>
+    <t xml:space="preserve">14.1106586456299</t>
   </si>
   <si>
     <t xml:space="preserve">13.9340543746948</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278635025024</t>
+    <t xml:space="preserve">13.5278654098511</t>
   </si>
   <si>
     <t xml:space="preserve">13.4219026565552</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">13.0686941146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0046949386597</t>
+    <t xml:space="preserve">14.004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.9870347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8457527160645</t>
+    <t xml:space="preserve">13.8457517623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985069274902</t>
+    <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338262557983</t>
+    <t xml:space="preserve">13.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1385,64 +1385,64 @@
     <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452993392944</t>
+    <t xml:space="preserve">13.351261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452983856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.174656867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629594802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9803924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6095247268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5035619735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0157127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159399032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980525970459</t>
+    <t xml:space="preserve">13.2276372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1746578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.980393409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6095237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5035610198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0157136917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159408569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980535507202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391094207764</t>
+    <t xml:space="preserve">12.8391103744507</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569967269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099771499634</t>
+    <t xml:space="preserve">13.1569957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790323257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4262762069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0377492904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0024280548096</t>
+    <t xml:space="preserve">11.1790313720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4262771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.037748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0024271011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.2143526077271</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0730686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">11.0730695724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">11.7618246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7265043258667</t>
+    <t xml:space="preserve">11.7265033721924</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496728897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728424072266</t>
+    <t xml:space="preserve">11.2496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494476318359</t>
+    <t xml:space="preserve">10.9494466781616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547298431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831275939941</t>
+    <t xml:space="preserve">10.1547288894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831371307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1370687484741</t>
+    <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
     <t xml:space="preserve">10.7198619842529</t>
@@ -1607,40 +1607,40 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785779953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6845417022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7375211715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258247375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6139001846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5609178543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606916427612</t>
+    <t xml:space="preserve">10.2430305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785789489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6845407485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7375221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258237838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.613899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5609188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432567596436</t>
+    <t xml:space="preserve">10.5432577133179</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.84348487854</t>
+    <t xml:space="preserve">10.8434839248657</t>
   </si>
   <si>
     <t xml:space="preserve">10.8964653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554094314575</t>
+    <t xml:space="preserve">10.9141263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554103851318</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -2745,6 +2745,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.89999961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69999980926514</t>
   </si>
 </sst>
 </file>
@@ -68837,7 +68840,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.6912152778</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>25809</v>
@@ -68858,6 +68861,32 @@
         <v>910</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.69125</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>21111</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>9.96000003814697</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>9.65999984741211</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>911</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="914">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14564275741577</t>
+    <t xml:space="preserve">5.15394163131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14564180374146</t>
   </si>
   <si>
     <t xml:space="preserve">5.1871395111084</t>
@@ -59,34 +59,34 @@
     <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958925247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333137512207</t>
+    <t xml:space="preserve">5.16224193572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958829879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523591995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333185195923</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3157811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482860565186</t>
+    <t xml:space="preserve">5.31578063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482908248901</t>
   </si>
   <si>
     <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34897899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
+    <t xml:space="preserve">5.34897804260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972665786743</t>
@@ -95,79 +95,79 @@
     <t xml:space="preserve">5.41122388839722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34067964553833</t>
+    <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
     <t xml:space="preserve">5.39462518692017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47762012481689</t>
+    <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93408823013306</t>
+    <t xml:space="preserve">5.71000385284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259052276611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939311981201</t>
+    <t xml:space="preserve">5.71415281295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939359664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728610992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90088987350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96313571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068693161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599182128906</t>
+    <t xml:space="preserve">5.96728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90089082717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96313619613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599229812622</t>
   </si>
   <si>
     <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442953109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0419807434082</t>
+    <t xml:space="preserve">6.05443000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04198026657104</t>
   </si>
   <si>
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05027961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327360153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137048721313</t>
+    <t xml:space="preserve">6.05028009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
     <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36150789260864</t>
+    <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
     <t xml:space="preserve">6.55239486694336</t>
@@ -179,154 +179,154 @@
     <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43205261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994512557983</t>
+    <t xml:space="preserve">6.43205308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
     <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80552673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321725845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301336288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034930229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6728982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798328399658</t>
+    <t xml:space="preserve">6.63953924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8055272102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961111068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451107025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920570373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349254608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3864860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
     <t xml:space="preserve">7.36573839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16240310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634912490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22058153152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468193054199</t>
+    <t xml:space="preserve">7.16240358352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634864807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468240737915</t>
   </si>
   <si>
     <t xml:space="preserve">6.72961521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123792648315</t>
+    <t xml:space="preserve">6.80156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356342315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
     <t xml:space="preserve">6.77617311477661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97933149337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49146032333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37295007705688</t>
+    <t xml:space="preserve">6.97933101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49145889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37295055389404</t>
   </si>
   <si>
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3644847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994194984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830099105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23751163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132593154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821298599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351942062378</t>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36448526382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941854476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2375111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821250915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351894378662</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
@@ -335,85 +335,85 @@
     <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67036104202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56031703948975</t>
+    <t xml:space="preserve">6.67036151885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56031656265259</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286207199097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08514165878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96663331985474</t>
+    <t xml:space="preserve">7.08514261245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538280487061</t>
+    <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84812450408936</t>
+    <t xml:space="preserve">6.84812498092651</t>
   </si>
   <si>
     <t xml:space="preserve">6.88621664047241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18672180175781</t>
+    <t xml:space="preserve">7.18672132492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630464553833</t>
+    <t xml:space="preserve">7.05128288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016485214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
     <t xml:space="preserve">7.09360790252686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937549591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974817276001</t>
+    <t xml:space="preserve">7.08937454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974721908569</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858470916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012132644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0639796257019</t>
+    <t xml:space="preserve">6.97086572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858423233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03011989593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398105621338</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09783983230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00049352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435277938843</t>
+    <t xml:space="preserve">7.09783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0004940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435373306274</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900186538696</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10207319259644</t>
+    <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
     <t xml:space="preserve">7.38987922668457</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">7.20365190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23327827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402410507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211719512939</t>
+    <t xml:space="preserve">7.23327922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
     <t xml:space="preserve">7.24597549438477</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">7.40680932998657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.432204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992370605469</t>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373943328857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38141489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406763076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452878952026</t>
+    <t xml:space="preserve">7.38141584396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452831268311</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83005571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349828720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457326889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913482666016</t>
+    <t xml:space="preserve">7.83005619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652418136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457279205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.449134349823</t>
   </si>
   <si>
     <t xml:space="preserve">7.53378295898438</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">7.61843299865723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58880615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229225158691</t>
+    <t xml:space="preserve">7.58880567550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229272842407</t>
   </si>
   <si>
     <t xml:space="preserve">7.69885015487671</t>
@@ -509,25 +509,25 @@
     <t xml:space="preserve">7.74540615081787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86814785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163585662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582330703735</t>
+    <t xml:space="preserve">7.86814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8258228302002</t>
   </si>
   <si>
     <t xml:space="preserve">7.88930988311768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91470527648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279788970947</t>
+    <t xml:space="preserve">7.91470575332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279836654663</t>
   </si>
   <si>
     <t xml:space="preserve">7.94856548309326</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">8.07553768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420059204102</t>
+    <t xml:space="preserve">7.70308113098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61419916152954</t>
   </si>
   <si>
     <t xml:space="preserve">7.42797183990479</t>
@@ -548,40 +548,40 @@
     <t xml:space="preserve">7.34332275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25020885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45760011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30946350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4025764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755563735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634817123413</t>
+    <t xml:space="preserve">7.25020790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694181442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30946254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40257692337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634769439697</t>
   </si>
   <si>
     <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95703029632568</t>
+    <t xml:space="preserve">7.95702981948853</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">8.40567207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26600074768066</t>
+    <t xml:space="preserve">8.26599979400635</t>
   </si>
   <si>
     <t xml:space="preserve">8.23213958740234</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">8.30832481384277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32525444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027477264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040916442871</t>
+    <t xml:space="preserve">8.32525539398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027572631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
     <t xml:space="preserve">8.87970542907715</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.998215675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04054069519043</t>
+    <t xml:space="preserve">8.99821662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04053974151611</t>
   </si>
   <si>
     <t xml:space="preserve">9.02361011505127</t>
@@ -656,19 +656,19 @@
     <t xml:space="preserve">9.5653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98861122131348</t>
+    <t xml:space="preserve">9.98861217498779</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541826248169</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773242950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1325159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90396118164062</t>
+    <t xml:space="preserve">9.71773529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1325149536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90396308898926</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">10.9451484680176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9620780944824</t>
+    <t xml:space="preserve">10.9620771408081</t>
   </si>
   <si>
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191846847534</t>
+    <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7239217758179</t>
+    <t xml:space="preserve">11.7239227294922</t>
   </si>
   <si>
     <t xml:space="preserve">11.7662448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9355449676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741422653198</t>
+    <t xml:space="preserve">11.9355440139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.6973886489868</t>
@@ -713,22 +713,22 @@
     <t xml:space="preserve">13.3491878509521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2633991241455</t>
+    <t xml:space="preserve">14.2633981704712</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0517749786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460275650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443195343018</t>
+    <t xml:space="preserve">14.051775932312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443185806274</t>
   </si>
   <si>
     <t xml:space="preserve">14.0941009521484</t>
@@ -737,34 +737,34 @@
     <t xml:space="preserve">14.5173463821411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009870529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206340789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8243618011475</t>
+    <t xml:space="preserve">14.0009880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206331253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338369369507</t>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338350296021</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5100202560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930906295776</t>
+    <t xml:space="preserve">13.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184869766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
     <t xml:space="preserve">13.7639684677124</t>
@@ -776,64 +776,64 @@
     <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348048210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.601996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512056350708</t>
+    <t xml:space="preserve">14.3480491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004177093506</t>
+    <t xml:space="preserve">14.5088815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500415802002</t>
   </si>
   <si>
     <t xml:space="preserve">14.4073038101196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4157686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311185836792</t>
+    <t xml:space="preserve">14.4157676696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311195373535</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8655462265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978277206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840574264526</t>
+    <t xml:space="preserve">13.8655481338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978267669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385740280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031351089478</t>
+    <t xml:space="preserve">13.7385730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290979385376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.782036781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397136688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0275201797485</t>
+    <t xml:space="preserve">12.7820377349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0275192260742</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
@@ -848,34 +848,34 @@
     <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2071056365967</t>
+    <t xml:space="preserve">13.2071046829224</t>
   </si>
   <si>
     <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0434169769287</t>
+    <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1726446151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0175704956055</t>
+    <t xml:space="preserve">13.439715385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1726455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0175714492798</t>
   </si>
   <si>
     <t xml:space="preserve">13.301872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1640300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.1640291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2243375778198</t>
+    <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812601089478</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557321548462</t>
+    <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.276026725769</t>
+    <t xml:space="preserve">13.3277187347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8194217681885</t>
+    <t xml:space="preserve">12.8194208145142</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">12.2335872650146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369693756104</t>
+    <t xml:space="preserve">12.3369703292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.0354385375977</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3542013168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2594327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3197393417358</t>
+    <t xml:space="preserve">12.3542003631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2594337463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
     <t xml:space="preserve">12.1302051544189</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837474822998</t>
+    <t xml:space="preserve">11.9837465286255</t>
   </si>
   <si>
     <t xml:space="preserve">11.8372888565063</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339067459106</t>
+    <t xml:space="preserve">11.7511367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
@@ -992,28 +992,28 @@
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182075500488</t>
+    <t xml:space="preserve">12.0182085037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612831115723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388206481934</t>
+    <t xml:space="preserve">12.0785150527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.138819694519</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871286392212</t>
+    <t xml:space="preserve">12.0871295928955</t>
   </si>
   <si>
     <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1037225723267</t>
+    <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.6988086700439</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591161727905</t>
+    <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231214523315</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7849597930908</t>
+    <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
     <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8366527557373</t>
+    <t xml:space="preserve">12.836651802063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883438110352</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643486022949</t>
+    <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.707423210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126565933228</t>
+    <t xml:space="preserve">12.5868101119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7074241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246551513672</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917259216309</t>
+    <t xml:space="preserve">12.8711128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089559555054</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520324707031</t>
+    <t xml:space="preserve">13.0520315170288</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984901428223</t>
+    <t xml:space="preserve">13.1984910964966</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
@@ -1142,28 +1142,28 @@
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289310455322</t>
+    <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963212966919</t>
+    <t xml:space="preserve">14.5166177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963222503662</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240171432495</t>
+    <t xml:space="preserve">13.7240180969238</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547775268555</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8446311950684</t>
+    <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
     <t xml:space="preserve">14.1117010116577</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6206369400024</t>
+    <t xml:space="preserve">13.6206359863281</t>
   </si>
   <si>
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
+    <t xml:space="preserve">13.6637115478516</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154035568237</t>
+    <t xml:space="preserve">13.7154026031494</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569473266602</t>
+    <t xml:space="preserve">13.4569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846431732178</t>
+    <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603284835815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3363332748413</t>
+    <t xml:space="preserve">13.3363342285156</t>
   </si>
   <si>
     <t xml:space="preserve">13.5775594711304</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">13.8634128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7751111984253</t>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.775110244751</t>
   </si>
   <si>
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340543746948</t>
+    <t xml:space="preserve">13.9340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219026565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0863542556763</t>
+    <t xml:space="preserve">13.4219017028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0863552093506</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2806196212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">13.2806205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870347976685</t>
+    <t xml:space="preserve">13.9870357513428</t>
   </si>
   <si>
     <t xml:space="preserve">13.8457527160645</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">13.4395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.722128868103</t>
+    <t xml:space="preserve">13.7221298217773</t>
   </si>
   <si>
     <t xml:space="preserve">13.6514883041382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4748840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6868095397949</t>
+    <t xml:space="preserve">13.4748849868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6868085861206</t>
   </si>
   <si>
     <t xml:space="preserve">13.5808458328247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338262557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4572229385376</t>
+    <t xml:space="preserve">13.6338272094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4572238922119</t>
   </si>
   <si>
     <t xml:space="preserve">13.4925441741943</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">13.6691484451294</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">13.2276372909546</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3689212799072</t>
+    <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
     <t xml:space="preserve">13.174656867981</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5035619735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0157127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159408569336</t>
+    <t xml:space="preserve">12.5035629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0157136917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
     <t xml:space="preserve">12.9980525970459</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569967269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9274120330811</t>
+    <t xml:space="preserve">13.1569957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9274110794067</t>
   </si>
   <si>
     <t xml:space="preserve">12.8920917510986</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.8567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037881851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">11.267333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.461597442627</t>
+    <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
     <t xml:space="preserve">11.1790323257446</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
+    <t xml:space="preserve">10.9317855834961</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">11.7794857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7618246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7265043258667</t>
+    <t xml:space="preserve">11.7618255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.726505279541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2077102661133</t>
+    <t xml:space="preserve">10.2077112197876</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0200881958008</t>
+    <t xml:space="preserve">11.0200872421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9494476318359</t>
@@ -1577,40 +1577,40 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
+    <t xml:space="preserve">10.154727935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44831371307373</t>
+    <t xml:space="preserve">9.44831275939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
+    <t xml:space="preserve">9.53661441802979</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198610305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966934204102</t>
+    <t xml:space="preserve">10.7198619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.666880607605</t>
+    <t xml:space="preserve">10.6668796539307</t>
   </si>
   <si>
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
+    <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902763366699</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4196357727051</t>
+    <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
     <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4372959136963</t>
+    <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434839248657</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.984766960144</t>
+    <t xml:space="preserve">10.9847679138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.3203153610229</t>
@@ -2751,6 +2751,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.69999980926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76000022888184</t>
   </si>
 </sst>
 </file>
@@ -68895,7 +68898,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6909837963</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>23700</v>
@@ -68916,6 +68919,32 @@
         <v>912</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6912268518</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>9505</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>9.89999961853027</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>9.72000026702881</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>9.76000022888184</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>913</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414552688599</t>
+    <t xml:space="preserve">5.10414505004883</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394258499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09169673919678</t>
+    <t xml:space="preserve">5.1539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18713998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11659479141235</t>
+    <t xml:space="preserve">5.1871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659383773804</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224098205566</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24523544311523</t>
+    <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
     <t xml:space="preserve">5.30333185195923</t>
@@ -77,19 +77,19 @@
     <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34897899627686</t>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632535934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3489785194397</t>
   </si>
   <si>
     <t xml:space="preserve">5.35312795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972665786743</t>
+    <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122436523438</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462518692017</t>
+    <t xml:space="preserve">5.39462614059448</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9340877532959</t>
+    <t xml:space="preserve">5.93408823013306</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259052276611</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728563308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90089082717896</t>
+    <t xml:space="preserve">5.96728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
     <t xml:space="preserve">5.96313571929932</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">5.95068645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86769247055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05442953109741</t>
+    <t xml:space="preserve">5.94653701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86769199371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">6.04198026657104</t>
@@ -164,85 +164,85 @@
     <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3615083694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239534378052</t>
+    <t xml:space="preserve">6.47355031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36150789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5523943901062</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56069374084473</t>
+    <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
     <t xml:space="preserve">6.43205308914185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53994607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5938925743103</t>
+    <t xml:space="preserve">6.53994560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
     <t xml:space="preserve">6.58559274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61463975906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8055272102356</t>
+    <t xml:space="preserve">6.59804201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80552768707275</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301240921021</t>
+    <t xml:space="preserve">7.01301288604736</t>
   </si>
   <si>
     <t xml:space="preserve">7.02961158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05451059341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349206924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
+    <t xml:space="preserve">7.05450963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920427322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948099136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234533309937</t>
   </si>
   <si>
     <t xml:space="preserve">8.67289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281770706177</t>
   </si>
   <si>
     <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42798471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573886871338</t>
+    <t xml:space="preserve">7.4279842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573791503906</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240310668945</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961521148682</t>
+    <t xml:space="preserve">7.20788383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
     <t xml:space="preserve">6.80156755447388</t>
@@ -275,67 +275,67 @@
     <t xml:space="preserve">6.94123888015747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617311477661</t>
+    <t xml:space="preserve">6.77617263793945</t>
   </si>
   <si>
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.992027759552</t>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37295007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676580429077</t>
+    <t xml:space="preserve">7.37295055389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676532745361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290512084961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30523061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448431015015</t>
+    <t xml:space="preserve">7.30523109436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3644847869873</t>
   </si>
   <si>
     <t xml:space="preserve">7.19941854476929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28830003738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23751068115234</t>
+    <t xml:space="preserve">7.28830099105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2375111579895</t>
   </si>
   <si>
     <t xml:space="preserve">7.16132640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821298599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588891983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351894378662</t>
+    <t xml:space="preserve">7.06821250915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351942062378</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036104202271</t>
+    <t xml:space="preserve">6.45027256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036151885986</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">7.08514213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96663331985474</t>
+    <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
     <t xml:space="preserve">6.99626111984253</t>
@@ -356,25 +356,25 @@
     <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77194023132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84812498092651</t>
+    <t xml:space="preserve">6.7719407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8481240272522</t>
   </si>
   <si>
     <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18672180175781</t>
+    <t xml:space="preserve">7.18672132492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016532897949</t>
+    <t xml:space="preserve">7.05128288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">7.09360790252686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937501907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974769592285</t>
+    <t xml:space="preserve">7.08937454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974721908569</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97086572647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858470916748</t>
+    <t xml:space="preserve">6.97086620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858423233032</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012037277222</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">7.06398057937622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0555157661438</t>
+    <t xml:space="preserve">7.05551528930664</t>
   </si>
   <si>
     <t xml:space="preserve">7.09783983230591</t>
@@ -413,37 +413,37 @@
     <t xml:space="preserve">7.0004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03435277938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900234222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.008957862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476898193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207319259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327922821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402410507202</t>
+    <t xml:space="preserve">7.03435325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11900186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00895833969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38988018035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327875137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402505874634</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597644805908</t>
+    <t xml:space="preserve">7.24597692489624</t>
   </si>
   <si>
     <t xml:space="preserve">7.40680932998657</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49992322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373991012573</t>
+    <t xml:space="preserve">7.49992418289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373943328857</t>
   </si>
   <si>
     <t xml:space="preserve">7.38141536712646</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">7.44490194320679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39834499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652513504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349924087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457326889038</t>
+    <t xml:space="preserve">7.39834403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382839202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65652418136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457183837891</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913387298584</t>
@@ -500,49 +500,49 @@
     <t xml:space="preserve">7.58880567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540662765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82582378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88931035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470575332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6141996383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
+    <t xml:space="preserve">7.65229177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8258228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88930988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91470670700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279836654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856452941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420106887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797088623047</t>
   </si>
   <si>
     <t xml:space="preserve">7.34332227706909</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45760011672974</t>
+    <t xml:space="preserve">7.45760059356689</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73694276809692</t>
+    <t xml:space="preserve">7.73694181442261</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685380935669</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">7.34755563735962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27137184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50838899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01205253601074</t>
+    <t xml:space="preserve">7.27137088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50838851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702981948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
     <t xml:space="preserve">8.02474880218506</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.45222854614258</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26599979400635</t>
+    <t xml:space="preserve">8.26599884033203</t>
   </si>
   <si>
     <t xml:space="preserve">8.23214054107666</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38027667999268</t>
+    <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514625549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.998215675354</t>
+    <t xml:space="preserve">9.01514530181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99821662902832</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
@@ -647,25 +647,25 @@
     <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448890686035</t>
+    <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
     <t xml:space="preserve">9.5653657913208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98861122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773433685303</t>
+    <t xml:space="preserve">9.98861217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541826248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773529052734</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396213531494</t>
+    <t xml:space="preserve">9.90396308898926</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451475143433</t>
+    <t xml:space="preserve">10.9451484680176</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0551919937134</t>
+    <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884809494019</t>
+    <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">13.3491878509521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2633991241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156364440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0517778396606</t>
+    <t xml:space="preserve">14.2633981704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156383514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443204879761</t>
+    <t xml:space="preserve">13.1460294723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443195343018</t>
   </si>
   <si>
     <t xml:space="preserve">14.0941009521484</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5173463821411</t>
+    <t xml:space="preserve">14.5173473358154</t>
   </si>
   <si>
     <t xml:space="preserve">14.0009880065918</t>
@@ -743,16 +743,16 @@
     <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169073104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438804626465</t>
+    <t xml:space="preserve">13.4169082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438814163208</t>
   </si>
   <si>
     <t xml:space="preserve">13.5100202560425</t>
@@ -764,25 +764,25 @@
     <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7639675140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0094509124756</t>
+    <t xml:space="preserve">13.7639684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0094499588013</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348048210144</t>
+    <t xml:space="preserve">14.3480501174927</t>
   </si>
   <si>
     <t xml:space="preserve">14.6019954681396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512065887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596723556519</t>
+    <t xml:space="preserve">14.5512075424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596733093262</t>
   </si>
   <si>
     <t xml:space="preserve">14.5088806152344</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1618204116821</t>
+    <t xml:space="preserve">14.4073038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157676696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311185836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
     <t xml:space="preserve">13.8655471801758</t>
@@ -809,10 +809,10 @@
     <t xml:space="preserve">13.7978267669678</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984055519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994073867798</t>
+    <t xml:space="preserve">13.9840564727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994064331055</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385730743408</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">12.7397127151489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0275201797485</t>
+    <t xml:space="preserve">13.0275192260742</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523462295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423017501831</t>
+    <t xml:space="preserve">13.5523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348024368286</t>
+    <t xml:space="preserve">13.0348014831543</t>
   </si>
   <si>
     <t xml:space="preserve">13.043417930603</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397163391113</t>
+    <t xml:space="preserve">13.4397172927856</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -884,55 +884,55 @@
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812610626221</t>
+    <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228038787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123390197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277196884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2760276794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2501811981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0606470108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9314203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8194227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4834280014038</t>
+    <t xml:space="preserve">12.9228048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557331085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277187347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276026725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2501821517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0606479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9314193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8194217681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.035439491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474361419678</t>
+    <t xml:space="preserve">12.3369703292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0354385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975954055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474370956421</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
@@ -944,58 +944,58 @@
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9837474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8372888565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7855968475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8286733627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7597513198853</t>
+    <t xml:space="preserve">11.9837465286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.837287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7855978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8286724090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7597522735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7511377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339067459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6046781539917</t>
+    <t xml:space="preserve">11.7769823074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7511367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.604679107666</t>
   </si>
   <si>
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182085037231</t>
+    <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785150527954</t>
+    <t xml:space="preserve">12.0785140991211</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1004,25 +1004,25 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157220840454</t>
+    <t xml:space="preserve">12.0871295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988077163696</t>
+    <t xml:space="preserve">12.6988086700439</t>
   </si>
   <si>
     <t xml:space="preserve">12.5006589889526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6815786361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7591152191162</t>
+    <t xml:space="preserve">12.6815776824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7591161727905</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3628168106079</t>
+    <t xml:space="preserve">12.4661989212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3628158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1046,22 +1046,22 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265054702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7849607467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9141893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8366527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883428573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8538837432861</t>
+    <t xml:space="preserve">12.5265045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9141883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8366508483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883438110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8538827896118</t>
   </si>
   <si>
     <t xml:space="preserve">12.6471176147461</t>
@@ -1070,55 +1070,55 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7505006790161</t>
+    <t xml:space="preserve">12.7504997253418</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7074241638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
+    <t xml:space="preserve">12.7074251174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126585006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8711128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917249679565</t>
+    <t xml:space="preserve">12.7418842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.871111869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917259216309</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0778770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0951070785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1381845474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1984901428223</t>
+    <t xml:space="preserve">12.9572639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520315170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0778789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0951080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1381855010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1984910964966</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674112319946</t>
@@ -1127,55 +1127,55 @@
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550970077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7757081985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843246459961</t>
+    <t xml:space="preserve">13.6550960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7757091522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843236923218</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289329528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4907712936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5166168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
+    <t xml:space="preserve">14.1289319992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4907703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5166177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
   </si>
   <si>
     <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8618612289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240190505981</t>
+    <t xml:space="preserve">13.8618621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240180969238</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547784805298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3443126678467</t>
+    <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">13.939398765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.844630241394</t>
+    <t xml:space="preserve">13.9393978118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.111701965332</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
+    <t xml:space="preserve">13.6637115478516</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8877077102661</t>
+    <t xml:space="preserve">13.8877067565918</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704767227173</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6809415817261</t>
+    <t xml:space="preserve">13.6809425354004</t>
   </si>
   <si>
     <t xml:space="preserve">13.4569463729858</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1241,40 +1241,40 @@
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292495727539</t>
+    <t xml:space="preserve">13.6292514801025</t>
   </si>
   <si>
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846422195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3363332748413</t>
+    <t xml:space="preserve">13.2846431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603284835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363342285156</t>
   </si>
   <si>
     <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5258684158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5086393356323</t>
+    <t xml:space="preserve">13.5258693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5086374282837</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693746566772</t>
+    <t xml:space="preserve">13.8634128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693756103516</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340543746948</t>
+    <t xml:space="preserve">13.9340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
@@ -1295,31 +1295,31 @@
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219017028809</t>
+    <t xml:space="preserve">13.4219026565552</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982797622681</t>
+    <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686950683594</t>
+    <t xml:space="preserve">13.0686941146851</t>
   </si>
   <si>
     <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0046949386597</t>
+    <t xml:space="preserve">14.004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870347976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8457527160645</t>
+    <t xml:space="preserve">13.9870357513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8457517623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8104314804077</t>
+    <t xml:space="preserve">13.810432434082</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338262557983</t>
+    <t xml:space="preserve">13.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.6691484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
+    <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
+    <t xml:space="preserve">13.2276382446289</t>
   </si>
   <si>
     <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1746578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629594802856</t>
+    <t xml:space="preserve">13.174656867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629585266113</t>
   </si>
   <si>
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095247268677</t>
+    <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
     <t xml:space="preserve">12.5035619735718</t>
@@ -1424,22 +1424,22 @@
     <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3159399032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9097509384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0333738327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1569967269897</t>
+    <t xml:space="preserve">13.3159408569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9097499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1569957733154</t>
   </si>
   <si>
     <t xml:space="preserve">13.2099781036377</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.121675491333</t>
+    <t xml:space="preserve">13.1216764450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037891387939</t>
+    <t xml:space="preserve">12.8567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037881851196</t>
   </si>
   <si>
     <t xml:space="preserve">12.2386560440063</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379764556885</t>
+    <t xml:space="preserve">11.267333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379755020142</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790323257446</t>
+    <t xml:space="preserve">11.1790313720703</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
@@ -1493,34 +1493,34 @@
     <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0024280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143526077271</t>
+    <t xml:space="preserve">11.0024271011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143535614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317874908447</t>
+    <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494476318359</t>
+    <t xml:space="preserve">10.9494466781616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299152374268</t>
+    <t xml:space="preserve">10.154727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
     <t xml:space="preserve">9.44831275939941</t>
@@ -1586,37 +1586,37 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53661441802979</t>
+    <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198629379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966924667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551832199097</t>
+    <t xml:space="preserve">10.7198619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551822662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2783517837524</t>
+    <t xml:space="preserve">10.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785789489746</t>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785779953003</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8258247375488</t>
+    <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3313331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.3313322067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019756317139</t>
+    <t xml:space="preserve">10.4019737243652</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.84348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.896466255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141263961792</t>
+    <t xml:space="preserve">10.8434839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8964653015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141254425049</t>
   </si>
   <si>
     <t xml:space="preserve">11.0554103851318</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069110870361</t>
+    <t xml:space="preserve">10.7069101333618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027923583984</t>
+    <t xml:space="preserve">9.84669780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846300125122</t>
+    <t xml:space="preserve">10.0663261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846290588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578388214111</t>
+    <t xml:space="preserve">10.139536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578397750854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055847167969</t>
+    <t xml:space="preserve">10.5055837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5238876342773</t>
+    <t xml:space="preserve">10.523886680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5604915618896</t>
+    <t xml:space="preserve">10.560492515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716335296631</t>
+    <t xml:space="preserve">10.8716325759888</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899354934692</t>
+    <t xml:space="preserve">10.6703062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899345397949</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193794250488</t>
+    <t xml:space="preserve">11.2193784713745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533306121826</t>
+    <t xml:space="preserve">11.1644716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252140045166</t>
+    <t xml:space="preserve">10.7252130508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944842338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461687088013</t>
+    <t xml:space="preserve">10.9448432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608589172363</t>
+    <t xml:space="preserve">8.23608493804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550094604492</t>
+    <t xml:space="preserve">8.17202663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550142288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234292984009</t>
+    <t xml:space="preserve">6.01234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00982332229614</t>
+    <t xml:space="preserve">7.0098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558013916016</t>
+    <t xml:space="preserve">7.055579662323</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531558990479</t>
+    <t xml:space="preserve">7.41247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531511306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568677902222</t>
+    <t xml:space="preserve">7.48568725585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038034439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303308486938</t>
+    <t xml:space="preserve">6.68038082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229118347168</t>
+    <t xml:space="preserve">7.52229166030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364643096924</t>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364547729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818161010742</t>
+    <t xml:space="preserve">8.96818256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62043571472168</t>
+    <t xml:space="preserve">8.620436668396</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003803253174</t>
+    <t xml:space="preserve">7.7968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003755569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6321063041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361755371094</t>
+    <t xml:space="preserve">7.77852535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63210582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236180305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642868041992</t>
+    <t xml:space="preserve">7.04642820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340475082397</t>
+    <t xml:space="preserve">6.86340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3509373664856</t>
+    <t xml:space="preserve">6.46075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35093688964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130807876587</t>
+    <t xml:space="preserve">6.02149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242116928101</t>
+    <t xml:space="preserve">5.47242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279235839844</t>
+    <t xml:space="preserve">5.25279188156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626070022583</t>
+    <t xml:space="preserve">5.36260652542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884069442749</t>
+    <t xml:space="preserve">5.61884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44908237457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324684143066</t>
+    <t xml:space="preserve">7.4490818977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324731826782</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55889654159546</t>
+    <t xml:space="preserve">7.5588960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062202453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452194213867</t>
+    <t xml:space="preserve">8.51062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452289581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025035858154</t>
+    <t xml:space="preserve">8.73025131225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176208496094</t>
+    <t xml:space="preserve">8.82176303863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308940887451</t>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179000854492</t>
+    <t xml:space="preserve">9.79179096221924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866195678711</t>
+    <t xml:space="preserve">10.3866186141968</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998676300049</t>
+    <t xml:space="preserve">9.37998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8949728012085</t>
+    <t xml:space="preserve">8.89497184753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833999633789</t>
+    <t xml:space="preserve">7.88833904266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4740161895752</t>
+    <t xml:space="preserve">8.47401714324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9249439239502</t>
+    <t xml:space="preserve">7.92494487762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735593795776</t>
+    <t xml:space="preserve">6.57056617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735641479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.53396081924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661451339722</t>
+    <t xml:space="preserve">6.93661403656006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -68950,7 +68950,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6911574074</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>23262</v>
@@ -68971,6 +68971,32 @@
         <v>913</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6912615741</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>21436</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>9.89999961853027</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>9.57999992370605</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>9.72000026702881</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>9.72000026702881</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>909</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="915">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414505004883</t>
+    <t xml:space="preserve">5.10414552688599</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
@@ -50,16 +50,16 @@
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11659383773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224098205566</t>
+    <t xml:space="preserve">5.14564275741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18713998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1165943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333185195923</t>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
@@ -83,22 +83,22 @@
     <t xml:space="preserve">5.38632535934448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3489785194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972713470459</t>
+    <t xml:space="preserve">5.34897899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972665786743</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122436523438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34067916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462614059448</t>
+    <t xml:space="preserve">5.34067869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462471008301</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93408823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89259052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71415376663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939359664917</t>
+    <t xml:space="preserve">5.71000337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9340877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89259099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939264297485</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9008903503418</t>
+    <t xml:space="preserve">5.96728610992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90089082717896</t>
   </si>
   <si>
     <t xml:space="preserve">5.96313571929932</t>
@@ -137,28 +137,28 @@
     <t xml:space="preserve">5.95068645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653701782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86769199371338</t>
+    <t xml:space="preserve">5.94653654098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599229812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
     <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04198026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05857944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05028009414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327407836914</t>
+    <t xml:space="preserve">6.0419807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0585789680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05027961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">6.36150789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5523943901062</t>
+    <t xml:space="preserve">6.55239534378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">6.56069469451904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43205308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994560241699</t>
+    <t xml:space="preserve">6.432053565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.59389209747314</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953924179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80552768707275</t>
+    <t xml:space="preserve">6.61464023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80552673339844</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321678161621</t>
@@ -212,52 +212,52 @@
     <t xml:space="preserve">7.02961158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05450963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920427322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3034930229187</t>
+    <t xml:space="preserve">7.05451011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920570373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30349254608154</t>
   </si>
   <si>
     <t xml:space="preserve">7.46948099136353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99234533309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289733886719</t>
+    <t xml:space="preserve">7.99234580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6728982925415</t>
   </si>
   <si>
     <t xml:space="preserve">8.12928485870361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67281770706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3864860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4279842376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240310668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643712997437</t>
+    <t xml:space="preserve">7.67281723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634817123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643665313721</t>
   </si>
   <si>
     <t xml:space="preserve">7.2205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20788383483887</t>
+    <t xml:space="preserve">7.20788431167603</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356294631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123888015747</t>
+    <t xml:space="preserve">6.80156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356342315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123840332031</t>
   </si>
   <si>
     <t xml:space="preserve">6.77617263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97933101654053</t>
+    <t xml:space="preserve">6.97933053970337</t>
   </si>
   <si>
     <t xml:space="preserve">6.99202823638916</t>
@@ -287,22 +287,22 @@
     <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37295055389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523109436035</t>
+    <t xml:space="preserve">7.37294960021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676485061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523061752319</t>
   </si>
   <si>
     <t xml:space="preserve">7.3644847869873</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">7.19941854476929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28830099105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2375111579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821250915527</t>
+    <t xml:space="preserve">7.28830051422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23751163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132736206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821346282959</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87351942062378</t>
+    <t xml:space="preserve">6.87351894378662</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">6.45027256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67036151885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56031703948975</t>
+    <t xml:space="preserve">6.67036104202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5603175163269</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08514213562012</t>
+    <t xml:space="preserve">7.08514261245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
@@ -353,55 +353,55 @@
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7719407081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8481240272522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621711730957</t>
+    <t xml:space="preserve">6.72538280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77194023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84812498092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621759414673</t>
   </si>
   <si>
     <t xml:space="preserve">7.18672132492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11053705215454</t>
+    <t xml:space="preserve">7.11053657531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.05128288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14016485214233</t>
+    <t xml:space="preserve">7.14016437530518</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09360790252686</t>
+    <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05974721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858423233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
+    <t xml:space="preserve">7.05974769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04704999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086572647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398010253906</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">7.09783983230591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435325622559</t>
+    <t xml:space="preserve">7.00049304962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435277938843</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900186538696</t>
@@ -422,85 +422,85 @@
     <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11476945877075</t>
+    <t xml:space="preserve">7.11476993560791</t>
   </si>
   <si>
     <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38988018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327875137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402505874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211671829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40680932998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.432204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992418289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373943328857</t>
+    <t xml:space="preserve">7.38987874984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211719512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597597122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680980682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373991012573</t>
   </si>
   <si>
     <t xml:space="preserve">7.38141536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28406763076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490194320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382839202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83005619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65652418136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229177474976</t>
+    <t xml:space="preserve">7.28406810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83005571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6565260887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349876403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457279205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.449134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843252182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6522912979126</t>
   </si>
   <si>
     <t xml:space="preserve">7.69884967803955</t>
@@ -509,40 +509,40 @@
     <t xml:space="preserve">7.74540615081787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86814785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92316913604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88930988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279836654663</t>
+    <t xml:space="preserve">7.86814832687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92317008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931035995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9147047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279741287231</t>
   </si>
   <si>
     <t xml:space="preserve">7.94856452941895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07553768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70308208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420106887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797088623047</t>
+    <t xml:space="preserve">8.07553958892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70308303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61420059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797136306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.34332227706909</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">7.25020837783813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45760059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536310195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694181442261</t>
+    <t xml:space="preserve">7.45759916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694229125977</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30946254730225</t>
+    <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
     <t xml:space="preserve">7.4025764465332</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">7.34755563735962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27137088775635</t>
+    <t xml:space="preserve">7.27137136459351</t>
   </si>
   <si>
     <t xml:space="preserve">7.50838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702981948853</t>
+    <t xml:space="preserve">7.95703077316284</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -587,25 +587,25 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707286834717</t>
+    <t xml:space="preserve">8.06707382202148</t>
   </si>
   <si>
     <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27023315429688</t>
+    <t xml:space="preserve">8.27023220062256</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222854614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40567111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26599884033203</t>
+    <t xml:space="preserve">8.45222759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40567016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26600074768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.23214054107666</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32525444030762</t>
+    <t xml:space="preserve">8.32525539398193</t>
   </si>
   <si>
     <t xml:space="preserve">8.38027572631836</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">9.01514530181885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99821662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04054069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02361011505127</t>
+    <t xml:space="preserve">8.998215675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04054164886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02361106872559</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448795318604</t>
+    <t xml:space="preserve">9.29448699951172</t>
   </si>
   <si>
     <t xml:space="preserve">9.5653657913208</t>
@@ -659,19 +659,19 @@
     <t xml:space="preserve">10.4541826248169</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773529052734</t>
+    <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
     <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90396308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.496506690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7927799224854</t>
+    <t xml:space="preserve">9.90396213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965076446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7927808761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">10.9620780944824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0551929473877</t>
+    <t xml:space="preserve">11.055193901062</t>
   </si>
   <si>
     <t xml:space="preserve">11.4191837310791</t>
@@ -704,97 +704,97 @@
     <t xml:space="preserve">12.6973876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1629590988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3491878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633981704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156383514404</t>
+    <t xml:space="preserve">13.1629581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3491868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2634000778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156364440918</t>
   </si>
   <si>
     <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460294723511</t>
+    <t xml:space="preserve">12.511157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443195343018</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206340789795</t>
+    <t xml:space="preserve">14.0940999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173463821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009860992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206350326538</t>
   </si>
   <si>
     <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169082641602</t>
+    <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
     <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438814163208</t>
+    <t xml:space="preserve">13.4338369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184869766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930896759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7639684677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0094499588013</t>
+    <t xml:space="preserve">13.5184860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7639675140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0094518661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480501174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088806152344</t>
+    <t xml:space="preserve">14.3480491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.601996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512065887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596723556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088815689087</t>
   </si>
   <si>
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4073038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157676696777</t>
+    <t xml:space="preserve">14.4073028564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157686233521</t>
   </si>
   <si>
     <t xml:space="preserve">14.3311185836792</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8655471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978267669678</t>
+    <t xml:space="preserve">13.8655462265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
     <t xml:space="preserve">13.9840564727783</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8994064331055</t>
+    <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031351089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1290979385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7820377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7397127151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0275192260742</t>
+    <t xml:space="preserve">13.6031341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1290988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.782036781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7397117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
     <t xml:space="preserve">13.5269498825073</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">13.5523452758789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423007965088</t>
+    <t xml:space="preserve">13.4423017501831</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.043417930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.940034866333</t>
+    <t xml:space="preserve">13.0348033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0434169769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9400358200073</t>
   </si>
   <si>
     <t xml:space="preserve">13.4397172927856</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175714492798</t>
+    <t xml:space="preserve">13.0175704956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.301872253418</t>
@@ -872,43 +872,43 @@
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8797273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2243366241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812601089478</t>
+    <t xml:space="preserve">13.1295690536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8797283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901941299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2243375778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
+    <t xml:space="preserve">12.9228038787842</t>
   </si>
   <si>
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123380661011</t>
+    <t xml:space="preserve">13.1123390197754</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277187347412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.276026725769</t>
+    <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0606479644775</t>
+    <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
     <t xml:space="preserve">12.9314193725586</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369703292847</t>
+    <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
     <t xml:space="preserve">12.0354385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8975954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3542003631592</t>
+    <t xml:space="preserve">11.8975944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474361419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3542013168335</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3197402954102</t>
+    <t xml:space="preserve">12.3197393417358</t>
   </si>
   <si>
     <t xml:space="preserve">12.1302051544189</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">11.9837465286255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.837287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7855978012085</t>
+    <t xml:space="preserve">11.8372888565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7855968475342</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166767120361</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">11.8114433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286724090576</t>
+    <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597522735596</t>
@@ -980,46 +980,46 @@
     <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7339057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.604679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6305236816406</t>
+    <t xml:space="preserve">11.7339067459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6305246353149</t>
   </si>
   <si>
     <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0612840652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0785140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388206481934</t>
+    <t xml:space="preserve">12.0612831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0785150527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388216018677</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871295928955</t>
+    <t xml:space="preserve">12.0871286392212</t>
   </si>
   <si>
     <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.103723526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6988086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5006589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815776824951</t>
+    <t xml:space="preserve">13.1037225723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6988077163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.500659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
     <t xml:space="preserve">12.7591161727905</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231233596802</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7849617004395</t>
+    <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
     <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8366508483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883438110352</t>
+    <t xml:space="preserve">12.836651802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883428573608</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1070,16 +1070,16 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7504997253418</t>
+    <t xml:space="preserve">12.7505016326904</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7074251174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126585006714</t>
+    <t xml:space="preserve">12.7074241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246541976929</t>
@@ -1088,34 +1088,34 @@
     <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8280372619629</t>
+    <t xml:space="preserve">12.8280363082886</t>
   </si>
   <si>
     <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
-    <t xml:space="preserve">12.871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520315170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0778789520264</t>
+    <t xml:space="preserve">12.8711128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917268753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089559555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
     <t xml:space="preserve">13.0951080322266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1381855010986</t>
+    <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
     <t xml:space="preserve">13.1984910964966</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550960540771</t>
+    <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
     <t xml:space="preserve">13.7757091522217</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">14.5166177749634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.8963212966919</t>
@@ -1169,22 +1169,22 @@
     <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9393978118896</t>
+    <t xml:space="preserve">14.0255498886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.939398765564</t>
   </si>
   <si>
     <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
-    <t xml:space="preserve">14.111701965332</t>
+    <t xml:space="preserve">14.1117010116577</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929391860962</t>
+    <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206359863281</t>
@@ -1193,31 +1193,31 @@
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637115478516</t>
+    <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8704767227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360157012939</t>
+    <t xml:space="preserve">13.8877086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.870475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360147476196</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7326326370239</t>
+    <t xml:space="preserve">13.7326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6809425354004</t>
+    <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
     <t xml:space="preserve">13.4569463729858</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3191032409668</t>
+    <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
     <t xml:space="preserve">13.3880252838135</t>
@@ -1241,28 +1241,28 @@
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292514801025</t>
+    <t xml:space="preserve">13.6292505264282</t>
   </si>
   <si>
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846431732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3363342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5775594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5086374282837</t>
+    <t xml:space="preserve">13.2846422195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603294372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363332748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5775604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258684158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">13.8634128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.951714515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693756103516</t>
+    <t xml:space="preserve">13.9517154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693737030029</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340534210205</t>
+    <t xml:space="preserve">13.9340543746948</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161670684814</t>
+    <t xml:space="preserve">13.6161661148071</t>
   </si>
   <si>
     <t xml:space="preserve">13.5278644561768</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686941146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402433395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872619628906</t>
+    <t xml:space="preserve">13.0686960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872629165649</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.004695892334</t>
+    <t xml:space="preserve">14.0046949386597</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1337,43 +1337,43 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870357513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8457517623901</t>
+    <t xml:space="preserve">13.9870347976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8457527160645</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.810432434082</t>
+    <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865823745728</t>
+    <t xml:space="preserve">13.3865814208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7221298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514873504639</t>
+    <t xml:space="preserve">13.722128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514883041382</t>
   </si>
   <si>
     <t xml:space="preserve">13.4748840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6868085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.580846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6338272094727</t>
+    <t xml:space="preserve">13.6868095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5808458328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6338262557983</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">13.6691484451294</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102043151855</t>
+    <t xml:space="preserve">13.5102052688599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689222335815</t>
+    <t xml:space="preserve">13.2276372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689212799072</t>
   </si>
   <si>
     <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629585266113</t>
+    <t xml:space="preserve">13.2629594802856</t>
   </si>
   <si>
     <t xml:space="preserve">12.9803924560547</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157136917114</t>
+    <t xml:space="preserve">13.0157127380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159408569336</t>
@@ -1430,43 +1430,43 @@
     <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9097499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.033374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1569957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099781036377</t>
+    <t xml:space="preserve">12.9097509384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391084671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0333738327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1569967269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099771499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8920907974243</t>
+    <t xml:space="preserve">12.8920917510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1216764450073</t>
+    <t xml:space="preserve">13.121675491333</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037881851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2386560440063</t>
+    <t xml:space="preserve">12.8567695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037891387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1481,10 +1481,10 @@
     <t xml:space="preserve">11.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4615983963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1790313720703</t>
+    <t xml:space="preserve">11.461597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0024271011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143535614014</t>
+    <t xml:space="preserve">11.0024280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143526077271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496738433838</t>
+    <t xml:space="preserve">11.1260509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496728897095</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549560546875</t>
+    <t xml:space="preserve">10.4549551010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439373016357</t>
+    <t xml:space="preserve">11.4439382553101</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494466781616</t>
+    <t xml:space="preserve">10.9494476318359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.154727935791</t>
+    <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44831275939941</t>
+    <t xml:space="preserve">9.44831371307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
@@ -1592,22 +1592,22 @@
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198619842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551822662354</t>
+    <t xml:space="preserve">10.7198610305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966934204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2783527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2430305480957</t>
+    <t xml:space="preserve">10.2783517837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.24303150177</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902763366699</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375221252441</t>
+    <t xml:space="preserve">10.7375211715698</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258237838745</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606906890869</t>
+    <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313322067261</t>
@@ -1643,13 +1643,13 @@
     <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4196348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4019737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.437294960022</t>
+    <t xml:space="preserve">10.4196357727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4019746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4372959136963</t>
   </si>
   <si>
     <t xml:space="preserve">10.8434839248657</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">10.9141254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554103851318</t>
+    <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -2754,6 +2754,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.65999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84000015258789</t>
   </si>
 </sst>
 </file>
@@ -68976,7 +68979,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6912615741</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>21436</v>
@@ -68997,6 +69000,32 @@
         <v>909</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.691099537</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>3190</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>9.88000011444092</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>9.72000026702881</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>914</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">5.15394258499146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14564228057861</t>
+    <t xml:space="preserve">5.09169626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14564275741577</t>
   </si>
   <si>
     <t xml:space="preserve">5.18713998794556</t>
@@ -59,46 +59,46 @@
     <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16224145889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19958925247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333089828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31163167953491</t>
+    <t xml:space="preserve">5.16224098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19958877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523591995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
     <t xml:space="preserve">5.31578063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482908248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3489785194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
+    <t xml:space="preserve">5.34482860565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632535934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34897899627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122388839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462518692017</t>
+    <t xml:space="preserve">5.41122436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067964553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462566375732</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">5.48176908493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71000289916992</t>
+    <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
     <t xml:space="preserve">5.9340877532959</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939264297485</t>
+    <t xml:space="preserve">5.85939311981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">5.90088987350464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313571929932</t>
+    <t xml:space="preserve">5.96313619613647</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068693161011</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198026657104</t>
+    <t xml:space="preserve">6.05442953109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
     <t xml:space="preserve">6.05857944488525</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">6.05027914047241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137048721313</t>
+    <t xml:space="preserve">6.13327360153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
     <t xml:space="preserve">6.47355031967163</t>
@@ -173,19 +173,19 @@
     <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57314395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5606951713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205308914185</t>
+    <t xml:space="preserve">6.57314348220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56069421768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.432053565979</t>
   </si>
   <si>
     <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59389209747314</t>
+    <t xml:space="preserve">6.5938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">6.58559274673462</t>
@@ -197,49 +197,49 @@
     <t xml:space="preserve">6.61464071273804</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63953876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8055272102356</t>
+    <t xml:space="preserve">6.63953924179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80552673339844</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301336288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961158752441</t>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
   </si>
   <si>
     <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12920522689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30349254608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46948146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234580993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281675338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648700714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798280715942</t>
+    <t xml:space="preserve">7.12920475006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3034930229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948194503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234485626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6728982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38648653030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798328399658</t>
   </si>
   <si>
     <t xml:space="preserve">7.36573839187622</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643712997437</t>
+    <t xml:space="preserve">7.43643665313721</t>
   </si>
   <si>
     <t xml:space="preserve">7.2205810546875</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">7.20788383483887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89468193054199</t>
+    <t xml:space="preserve">6.89468145370483</t>
   </si>
   <si>
     <t xml:space="preserve">6.72961568832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80156707763672</t>
+    <t xml:space="preserve">6.80156755447388</t>
   </si>
   <si>
     <t xml:space="preserve">6.98356342315674</t>
@@ -281,25 +281,25 @@
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49145984649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37295055389404</t>
+    <t xml:space="preserve">6.99202871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49145936965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37295007705688</t>
   </si>
   <si>
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290607452393</t>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290559768677</t>
   </si>
   <si>
     <t xml:space="preserve">7.30523061752319</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28830003738403</t>
+    <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
     <t xml:space="preserve">7.23751163482666</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">7.16132640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06821298599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588748931885</t>
+    <t xml:space="preserve">7.06821346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588796615601</t>
   </si>
   <si>
     <t xml:space="preserve">6.87351942062378</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67036104202271</t>
+    <t xml:space="preserve">6.67036056518555</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286207199097</t>
+    <t xml:space="preserve">7.15286159515381</t>
   </si>
   <si>
     <t xml:space="preserve">7.08514213562012</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">6.72538280487061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7719407081604</t>
+    <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84812450408936</t>
@@ -365,37 +365,37 @@
     <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18672180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053657531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05128192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14016532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360790252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937501907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04704999923706</t>
+    <t xml:space="preserve">7.18672227859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053705215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05128240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14016485214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0893759727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858423233032</t>
+    <t xml:space="preserve">7.03858470916748</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012084960938</t>
@@ -404,22 +404,22 @@
     <t xml:space="preserve">7.0639796257019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0555157661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09784030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00049352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435325622559</t>
+    <t xml:space="preserve">7.05551528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00049304962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435277938843</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00895833969116</t>
+    <t xml:space="preserve">7.008957862854</t>
   </si>
   <si>
     <t xml:space="preserve">7.11476945877075</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.10207319259644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38987874984741</t>
+    <t xml:space="preserve">7.38987970352173</t>
   </si>
   <si>
     <t xml:space="preserve">7.20365190505981</t>
@@ -440,25 +440,25 @@
     <t xml:space="preserve">7.17402410507202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21211767196655</t>
+    <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
     <t xml:space="preserve">7.24597597122192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40680932998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43220376968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992418289185</t>
+    <t xml:space="preserve">7.40681028366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.432204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373991012573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38141489028931</t>
+    <t xml:space="preserve">7.38141441345215</t>
   </si>
   <si>
     <t xml:space="preserve">7.28406763076782</t>
@@ -467,100 +467,100 @@
     <t xml:space="preserve">7.44490194320679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39834499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382743835449</t>
+    <t xml:space="preserve">7.39834451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382696151733</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65652465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843252182007</t>
+    <t xml:space="preserve">7.65652513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349828720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457231521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843204498291</t>
   </si>
   <si>
     <t xml:space="preserve">7.58880567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65229320526123</t>
+    <t xml:space="preserve">7.65229225158691</t>
   </si>
   <si>
     <t xml:space="preserve">7.69885015487671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74540615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814737319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163633346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88930940628052</t>
+    <t xml:space="preserve">7.74540662765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316913604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82582378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931035995483</t>
   </si>
   <si>
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94856548309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553768157959</t>
+    <t xml:space="preserve">7.95279788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
     <t xml:space="preserve">7.70308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61420011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332323074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45760011672974</t>
+    <t xml:space="preserve">7.61420059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73694229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685333251953</t>
+    <t xml:space="preserve">7.73694181442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685476303101</t>
   </si>
   <si>
     <t xml:space="preserve">7.30946350097656</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755516052246</t>
+    <t xml:space="preserve">7.34755611419678</t>
   </si>
   <si>
     <t xml:space="preserve">7.27137041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50838804244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95703077316284</t>
+    <t xml:space="preserve">7.50838899612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702934265137</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097755432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27023124694824</t>
+    <t xml:space="preserve">8.06707286834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27023220062256</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990352630615</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26600074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23213958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30832290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3252534866333</t>
+    <t xml:space="preserve">8.26599979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23214054107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30832386016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32525444030762</t>
   </si>
   <si>
     <t xml:space="preserve">8.38027572631836</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970638275146</t>
+    <t xml:space="preserve">8.87970542907715</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
@@ -632,40 +632,40 @@
     <t xml:space="preserve">9.01514625549316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.998215675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04054164886475</t>
+    <t xml:space="preserve">8.99821662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290924072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1759786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29448699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5653657913208</t>
+    <t xml:space="preserve">9.19290828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17597961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29448795318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56536483764648</t>
   </si>
   <si>
     <t xml:space="preserve">9.98861122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4541826248169</t>
+    <t xml:space="preserve">10.4541835784912</t>
   </si>
   <si>
     <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1325149536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90396213531494</t>
+    <t xml:space="preserve">10.1325159072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90396118164062</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451494216919</t>
+    <t xml:space="preserve">10.9451484680176</t>
   </si>
   <si>
     <t xml:space="preserve">10.9620780944824</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4191846847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884828567505</t>
+    <t xml:space="preserve">11.4191837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884819030762</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7662448883057</t>
+    <t xml:space="preserve">11.76624584198</t>
   </si>
   <si>
     <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2741422653198</t>
+    <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
     <t xml:space="preserve">12.6973886489868</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0517749786377</t>
+    <t xml:space="preserve">14.051775932312</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111589431763</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">14.6443195343018</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0940999984741</t>
+    <t xml:space="preserve">14.0941009521484</t>
   </si>
   <si>
     <t xml:space="preserve">14.5173463821411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009870529175</t>
+    <t xml:space="preserve">14.0009860992432</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
@@ -746,31 +746,31 @@
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438814163208</t>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438804626465</t>
   </si>
   <si>
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930896759033</t>
+    <t xml:space="preserve">13.5184869766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930906295776</t>
   </si>
   <si>
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094518661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057241439819</t>
+    <t xml:space="preserve">14.0094509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057231903076</t>
   </si>
   <si>
     <t xml:space="preserve">14.348048210144</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">14.6019954681396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5512056350708</t>
+    <t xml:space="preserve">14.5512075424194</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">14.5088806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5004177093506</t>
+    <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
     <t xml:space="preserve">14.4073038101196</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">14.4157676696777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3311185836792</t>
+    <t xml:space="preserve">14.3311195373535</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994073867798</t>
+    <t xml:space="preserve">13.9840574264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994064331055</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031341552734</t>
+    <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397127151489</t>
+    <t xml:space="preserve">12.7397117614746</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">13.1726446151733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.301872253418</t>
+    <t xml:space="preserve">13.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3018732070923</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
@@ -881,22 +881,22 @@
     <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2243375778198</t>
+    <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1209545135498</t>
+    <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
     <t xml:space="preserve">12.9228048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6557321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123390197754</t>
+    <t xml:space="preserve">12.6557331085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123399734497</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277196884155</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501821517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0606479644775</t>
+    <t xml:space="preserve">13.2501811981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
     <t xml:space="preserve">12.9314193725586</t>
@@ -917,16 +917,16 @@
     <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4834289550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2335872650146</t>
+    <t xml:space="preserve">12.4834280014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369693756104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0354385375977</t>
+    <t xml:space="preserve">12.035439491272</t>
   </si>
   <si>
     <t xml:space="preserve">11.8975954055786</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3197393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1302051544189</t>
+    <t xml:space="preserve">12.3197402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114433288574</t>
+    <t xml:space="preserve">11.7166757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286724090576</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769823074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7511377334595</t>
+    <t xml:space="preserve">11.7769813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339067459106</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">11.6305236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0182075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0612831115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0785160064697</t>
+    <t xml:space="preserve">12.0182085037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0612840652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0785150527954</t>
   </si>
   <si>
     <t xml:space="preserve">12.1388206481934</t>
@@ -1007,28 +1007,28 @@
     <t xml:space="preserve">12.0871286392212</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2157211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1037225723267</t>
+    <t xml:space="preserve">13.2157220840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.6988086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500659942627</t>
+    <t xml:space="preserve">12.5006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591161727905</t>
+    <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
     <t xml:space="preserve">12.7160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4231214523315</t>
+    <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
     <t xml:space="preserve">12.4920444488525</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7849597930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9141883850098</t>
+    <t xml:space="preserve">12.5265054702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7849607467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
     <t xml:space="preserve">12.8366527557373</t>
@@ -1067,43 +1067,43 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643486022949</t>
+    <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
     <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5868110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.707423210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6126565933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935762405396</t>
+    <t xml:space="preserve">12.5868101119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7074241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6126575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246561050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935752868652</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.871111869812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917259216309</t>
+    <t xml:space="preserve">12.7418851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8711128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089559555054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572649002075</t>
+    <t xml:space="preserve">12.9572639465332</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0951080322266</t>
+    <t xml:space="preserve">13.0951070785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914073944092</t>
+    <t xml:space="preserve">13.4914064407349</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550970077515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757091522217</t>
+    <t xml:space="preserve">13.7757081985474</t>
   </si>
   <si>
     <t xml:space="preserve">13.7843246459961</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">13.7498636245728</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1289310455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4907703399658</t>
+    <t xml:space="preserve">14.1289319992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4907712936401</t>
   </si>
   <si>
     <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150840759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981716156006</t>
+    <t xml:space="preserve">14.2150850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.8963212966919</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240171432495</t>
+    <t xml:space="preserve">13.7240190505981</t>
   </si>
   <si>
     <t xml:space="preserve">14.1547775268555</t>
@@ -1169,22 +1169,22 @@
     <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255498886108</t>
+    <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
     <t xml:space="preserve">13.9393978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8446311950684</t>
+    <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
     <t xml:space="preserve">14.1117010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9221668243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929401397705</t>
+    <t xml:space="preserve">13.9221677780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929391860962</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206369400024</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8360147476196</t>
+    <t xml:space="preserve">13.8360157012939</t>
   </si>
   <si>
     <t xml:space="preserve">13.8015556335449</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154035568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6809425354004</t>
+    <t xml:space="preserve">13.7154026031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
     <t xml:space="preserve">13.4569473266602</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">13.3535642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.405255317688</t>
+    <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3880252838135</t>
+    <t xml:space="preserve">13.3880243301392</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846431732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603284835815</t>
+    <t xml:space="preserve">13.2846422195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634128570557</t>
+    <t xml:space="preserve">13.8634119033813</t>
   </si>
   <si>
     <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693737030029</t>
+    <t xml:space="preserve">13.9693746566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1289,28 +1289,28 @@
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161661148071</t>
+    <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219026565552</t>
+    <t xml:space="preserve">13.4219017028809</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2982807159424</t>
+    <t xml:space="preserve">13.2982797622681</t>
   </si>
   <si>
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
+    <t xml:space="preserve">13.0686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
     <t xml:space="preserve">14.2872629165649</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753374099731</t>
+    <t xml:space="preserve">14.0753364562988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1352,25 +1352,25 @@
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865814208984</t>
+    <t xml:space="preserve">13.3865823745728</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.722128868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514883041382</t>
+    <t xml:space="preserve">13.7221298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514873504639</t>
   </si>
   <si>
     <t xml:space="preserve">13.4748840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6868095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5808458328247</t>
+    <t xml:space="preserve">13.6868085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
     <t xml:space="preserve">13.6338262557983</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691484451294</t>
+    <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102052688599</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
+    <t xml:space="preserve">13.351261138916</t>
   </si>
   <si>
     <t xml:space="preserve">13.2452983856201</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">13.2276372909546</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.174656867981</t>
+    <t xml:space="preserve">13.3689222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1746578216553</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095237731934</t>
+    <t xml:space="preserve">12.6095247268677</t>
   </si>
   <si>
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3159408569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9980525970459</t>
+    <t xml:space="preserve">13.0157136917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3159399032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9980535507202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391084671021</t>
+    <t xml:space="preserve">12.8391103744507</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099771499634</t>
+    <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8920917510986</t>
+    <t xml:space="preserve">12.8920907974243</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
@@ -1466,22 +1466,22 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.2673349380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.461597442627</t>
+    <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
     <t xml:space="preserve">11.1790323257446</t>
@@ -1502,25 +1502,25 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
+    <t xml:space="preserve">10.9317874908447</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792585372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441654205322</t>
+    <t xml:space="preserve">11.2849950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441644668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1260509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496728897095</t>
+    <t xml:space="preserve">11.126051902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496738433838</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1577,25 +1577,25 @@
     <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41299247741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831371307373</t>
+    <t xml:space="preserve">9.41299152374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831275939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
+    <t xml:space="preserve">9.53661441802979</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198610305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1966934204102</t>
+    <t xml:space="preserve">10.7198629379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551832199097</t>
@@ -1607,25 +1607,25 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785779953003</t>
+    <t xml:space="preserve">10.2430305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079374313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785789489746</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375211715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8258237838745</t>
+    <t xml:space="preserve">10.7375221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8258247375488</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
@@ -1634,34 +1634,34 @@
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606916427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3313322067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5432567596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4196357727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4019746780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4372959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8434839248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8964653015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554094314575</t>
+    <t xml:space="preserve">10.2606906890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3313331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5432577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4196348190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4019756317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.437294960022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.84348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.896466255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554103851318</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069101333618</t>
+    <t xml:space="preserve">10.7069110870361</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027828216553</t>
+    <t xml:space="preserve">9.84669876098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027923583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846290588379</t>
+    <t xml:space="preserve">10.0663270950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846300125122</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.139536857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578397750854</t>
+    <t xml:space="preserve">10.1395359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578388214111</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055837631226</t>
+    <t xml:space="preserve">10.5055847167969</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.523886680603</t>
+    <t xml:space="preserve">10.5238876342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.560492515564</t>
+    <t xml:space="preserve">10.5604915618896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716325759888</t>
+    <t xml:space="preserve">10.8716335296631</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703062057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899345397949</t>
+    <t xml:space="preserve">10.6703052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984228134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899354934692</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193784713745</t>
+    <t xml:space="preserve">11.2193794250488</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644716262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533296585083</t>
+    <t xml:space="preserve">11.1644706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533306121826</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252130508423</t>
+    <t xml:space="preserve">10.7252140045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9448432922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461696624756</t>
+    <t xml:space="preserve">10.944842338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109564781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461687088013</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608493804932</t>
+    <t xml:space="preserve">8.23608589172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550142288208</t>
+    <t xml:space="preserve">8.17202758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550094604492</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234245300293</t>
+    <t xml:space="preserve">6.01234292984009</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0098237991333</t>
+    <t xml:space="preserve">7.00982332229614</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.055579662323</t>
+    <t xml:space="preserve">7.05558013916016</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247749328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531511306763</t>
+    <t xml:space="preserve">7.41247701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531558990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568725585938</t>
+    <t xml:space="preserve">7.48568677902222</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303356170654</t>
+    <t xml:space="preserve">6.68038034439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303308486938</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229166030884</t>
+    <t xml:space="preserve">7.52229118347168</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364547729492</t>
+    <t xml:space="preserve">8.14457225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364643096924</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818256378174</t>
+    <t xml:space="preserve">8.96818161010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.620436668396</t>
+    <t xml:space="preserve">8.62043571472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7968282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003755569458</t>
+    <t xml:space="preserve">7.79682779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003803253174</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63210582733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7236180305481</t>
+    <t xml:space="preserve">7.77852582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6321063041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72361755371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2099,13 +2099,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642820358276</t>
+    <t xml:space="preserve">7.04642868041992</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340427398682</t>
+    <t xml:space="preserve">6.86340475082397</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46075105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35093688964844</t>
+    <t xml:space="preserve">6.4607515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3509373664856</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2138,13 +2138,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130760192871</t>
+    <t xml:space="preserve">6.02149391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130807876587</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2168,25 +2168,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242164611816</t>
+    <t xml:space="preserve">5.47242116928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279188156128</t>
+    <t xml:space="preserve">5.25279235839844</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36260652542114</t>
+    <t xml:space="preserve">5.3626070022583</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884021759033</t>
+    <t xml:space="preserve">5.61884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4490818977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324731826782</t>
+    <t xml:space="preserve">7.44908237457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324684143066</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5588960647583</t>
+    <t xml:space="preserve">7.55889654159546</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062107086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987964630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452289581299</t>
+    <t xml:space="preserve">8.51062202453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847312927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452194213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025131225586</t>
+    <t xml:space="preserve">8.73025035858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176303863525</t>
+    <t xml:space="preserve">8.82176208496094</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0230884552002</t>
+    <t xml:space="preserve">9.13290309906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02308940887451</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179096221924</t>
+    <t xml:space="preserve">9.79179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866186141968</t>
+    <t xml:space="preserve">10.3866195678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998580932617</t>
+    <t xml:space="preserve">9.37998676300049</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89497184753418</t>
+    <t xml:space="preserve">8.8949728012085</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833904266357</t>
+    <t xml:space="preserve">7.88833999633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47401714324951</t>
+    <t xml:space="preserve">8.4740161895752</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92494487762451</t>
+    <t xml:space="preserve">7.9249439239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735641479492</t>
+    <t xml:space="preserve">6.57056570053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735593795776</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396081924438</t>
+    <t xml:space="preserve">6.53396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661403656006</t>
+    <t xml:space="preserve">6.93661451339722</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414552688599</t>
+    <t xml:space="preserve">5.10414600372314</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
@@ -50,55 +50,55 @@
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564275741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18713998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11659479141235</t>
+    <t xml:space="preserve">5.14564228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1165943145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.16224098205566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19958877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24523591995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333137512207</t>
+    <t xml:space="preserve">5.19958925247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24523639678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333089828491</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31578063964844</t>
+    <t xml:space="preserve">5.3157811164856</t>
   </si>
   <si>
     <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38632535934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34897899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067964553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462566375732</t>
+    <t xml:space="preserve">5.38632583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3489785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312795639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972665786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122388839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462518692017</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
@@ -125,16 +125,16 @@
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728610992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90088987350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96313619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068693161011</t>
+    <t xml:space="preserve">5.96728563308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9008903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96313571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068597793579</t>
   </si>
   <si>
     <t xml:space="preserve">5.94653701782227</t>
@@ -143,34 +143,34 @@
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86769247055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05442953109741</t>
+    <t xml:space="preserve">5.8676929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05857944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05027914047241</t>
+    <t xml:space="preserve">6.05857992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05028009414673</t>
   </si>
   <si>
     <t xml:space="preserve">6.13327360153198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19137001037598</t>
+    <t xml:space="preserve">6.19137048721313</t>
   </si>
   <si>
     <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36150789260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239486694336</t>
+    <t xml:space="preserve">6.3615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239534378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
@@ -191,19 +191,19 @@
     <t xml:space="preserve">6.58559274673462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464071273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953924179077</t>
+    <t xml:space="preserve">6.59804201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
     <t xml:space="preserve">6.80552673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96321678161621</t>
+    <t xml:space="preserve">6.96321582794189</t>
   </si>
   <si>
     <t xml:space="preserve">7.01301288604736</t>
@@ -212,37 +212,37 @@
     <t xml:space="preserve">7.02961206436157</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920475006104</t>
+    <t xml:space="preserve">7.05450963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920522689819</t>
   </si>
   <si>
     <t xml:space="preserve">7.3034930229187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46948194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6728982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928485870361</t>
+    <t xml:space="preserve">7.46948146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67289638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928581237793</t>
   </si>
   <si>
     <t xml:space="preserve">7.67281723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38648653030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798328399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573839187622</t>
+    <t xml:space="preserve">7.38648748397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798471450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573791503906</t>
   </si>
   <si>
     <t xml:space="preserve">7.16240310668945</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43643665313721</t>
+    <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
     <t xml:space="preserve">7.2205810546875</t>
@@ -260,43 +260,43 @@
     <t xml:space="preserve">7.20788383483887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89468145370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961568832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156755447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123792648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617311477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933101654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202871322632</t>
+    <t xml:space="preserve">6.89468193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933053970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37295007705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27983617782593</t>
+    <t xml:space="preserve">7.37294960021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27983570098877</t>
   </si>
   <si>
     <t xml:space="preserve">7.2925329208374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29676628112793</t>
+    <t xml:space="preserve">7.29676580429077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290559768677</t>
@@ -308,55 +308,55 @@
     <t xml:space="preserve">7.36448431015015</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1994194984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28830051422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23751163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132640838623</t>
+    <t xml:space="preserve">7.19941902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28830003738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2375111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132688522339</t>
   </si>
   <si>
     <t xml:space="preserve">7.06821346282959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588796615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351942062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729114532471</t>
+    <t xml:space="preserve">7.02588891983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351894378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729066848755</t>
   </si>
   <si>
     <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67036056518555</t>
+    <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15286159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514213562012</t>
+    <t xml:space="preserve">7.15286207199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
   </si>
   <si>
     <t xml:space="preserve">6.96663284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99626111984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72538280487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77194023132324</t>
+    <t xml:space="preserve">6.99626064300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72538328170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77193975448608</t>
   </si>
   <si>
     <t xml:space="preserve">6.84812450408936</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18672227859497</t>
+    <t xml:space="preserve">7.1867208480835</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053705215454</t>
@@ -377,61 +377,61 @@
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360694885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0893759727478</t>
+    <t xml:space="preserve">7.1063060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0936074256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937501907349</t>
   </si>
   <si>
     <t xml:space="preserve">7.05974817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04705047607422</t>
+    <t xml:space="preserve">7.04704999923706</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086524963379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858470916748</t>
+    <t xml:space="preserve">7.03858518600464</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0639796257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05551528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09783935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00049304962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435277938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900186538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.008957862854</t>
+    <t xml:space="preserve">7.06398057937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0555157661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09783983230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00049352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11900234222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00895833969116</t>
   </si>
   <si>
     <t xml:space="preserve">7.11476945877075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10207319259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365190505981</t>
+    <t xml:space="preserve">7.10207223892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365142822266</t>
   </si>
   <si>
     <t xml:space="preserve">7.23327827453613</t>
@@ -443,25 +443,25 @@
     <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597597122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40681028366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.432204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373991012573</t>
+    <t xml:space="preserve">7.24597692489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43220472335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42373943328857</t>
   </si>
   <si>
     <t xml:space="preserve">7.38141441345215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28406763076782</t>
+    <t xml:space="preserve">7.28406715393066</t>
   </si>
   <si>
     <t xml:space="preserve">7.44490194320679</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">7.39834451675415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64382696151733</t>
+    <t xml:space="preserve">7.47452878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64382791519165</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
@@ -482,55 +482,55 @@
     <t xml:space="preserve">7.65652513504028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78349828720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457231521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880567550659</t>
+    <t xml:space="preserve">7.78349924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.449134349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843252182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880615234375</t>
   </si>
   <si>
     <t xml:space="preserve">7.65229225158691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69885015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540662765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814785003662</t>
+    <t xml:space="preserve">7.69884872436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540567398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814880371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.93163537979126</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92316913604736</t>
+    <t xml:space="preserve">7.92317008972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.82582378387451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88931035995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91470575332642</t>
+    <t xml:space="preserve">7.88930940628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9147047996521</t>
   </si>
   <si>
     <t xml:space="preserve">7.95279788970947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94856595993042</t>
+    <t xml:space="preserve">7.9485650062561</t>
   </si>
   <si>
     <t xml:space="preserve">8.07553863525391</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">7.70308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61420059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332180023193</t>
+    <t xml:space="preserve">7.6141996383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332275390625</t>
   </si>
   <si>
     <t xml:space="preserve">7.25020837783813</t>
@@ -557,28 +557,28 @@
     <t xml:space="preserve">7.63536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73694181442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685476303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30946350097656</t>
+    <t xml:space="preserve">7.73694229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3094630241394</t>
   </si>
   <si>
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27137041091919</t>
+    <t xml:space="preserve">7.34755563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27137088775635</t>
   </si>
   <si>
     <t xml:space="preserve">7.50838899612427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702934265137</t>
+    <t xml:space="preserve">7.95703029632568</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707286834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21097850799561</t>
+    <t xml:space="preserve">8.06707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
     <t xml:space="preserve">8.27023220062256</t>
@@ -599,40 +599,40 @@
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40567111968994</t>
+    <t xml:space="preserve">8.45222663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40567016601562</t>
   </si>
   <si>
     <t xml:space="preserve">8.26599979400635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23214054107666</t>
+    <t xml:space="preserve">8.23213958740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32525444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027572631836</t>
+    <t xml:space="preserve">8.3252534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027667999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87970542907715</t>
+    <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514625549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99821662902832</t>
+    <t xml:space="preserve">9.01514530181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
     <t xml:space="preserve">9.04054069519043</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19290828704834</t>
+    <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
     <t xml:space="preserve">9.17597961425781</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">9.29448795318604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56536483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861122131348</t>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861217498779</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541835784912</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1325159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90396118164062</t>
+    <t xml:space="preserve">10.1325168609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90396213531494</t>
   </si>
   <si>
     <t xml:space="preserve">10.496506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7927799224854</t>
+    <t xml:space="preserve">10.7927808761597</t>
   </si>
   <si>
     <t xml:space="preserve">10.9451484680176</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884819030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239217758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.76624584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355440139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741413116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973886489868</t>
+    <t xml:space="preserve">11.5884828567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7662448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355449676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973876953125</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491878509521</t>
+    <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
     <t xml:space="preserve">14.2633991241455</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.051775932312</t>
+    <t xml:space="preserve">14.0517778396606</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111589431763</t>
@@ -728,37 +728,37 @@
     <t xml:space="preserve">14.6443195343018</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0941009521484</t>
+    <t xml:space="preserve">14.0940999984741</t>
   </si>
   <si>
     <t xml:space="preserve">14.5173463821411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009860992432</t>
+    <t xml:space="preserve">14.0009870529175</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8243608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4169073104858</t>
+    <t xml:space="preserve">12.8243618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4169063568115</t>
   </si>
   <si>
     <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438804626465</t>
+    <t xml:space="preserve">13.4338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438795089722</t>
   </si>
   <si>
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184869766235</t>
+    <t xml:space="preserve">13.5184850692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930906295776</t>
@@ -770,34 +770,34 @@
     <t xml:space="preserve">14.0094509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3057231903076</t>
+    <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
     <t xml:space="preserve">14.348048210144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6019954681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5596723556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5088806152344</t>
+    <t xml:space="preserve">14.601996421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512065887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5596714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5088815689087</t>
   </si>
   <si>
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4073038101196</t>
+    <t xml:space="preserve">14.4073028564453</t>
   </si>
   <si>
     <t xml:space="preserve">14.4157676696777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3311195373535</t>
+    <t xml:space="preserve">14.3311185836792</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">13.8655462265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7978277206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840574264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8994064331055</t>
+    <t xml:space="preserve">13.7978267669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
     <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6031351089478</t>
+    <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397117614746</t>
+    <t xml:space="preserve">12.7397127151489</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
@@ -836,22 +836,22 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523462295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423017501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5430994033813</t>
+    <t xml:space="preserve">13.5523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.543098449707</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348024368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0434169769287</t>
+    <t xml:space="preserve">13.0348014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
@@ -896,37 +896,37 @@
     <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123399734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277196884155</t>
+    <t xml:space="preserve">13.1123390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277187347412</t>
   </si>
   <si>
     <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501811981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0606470108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9314193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8194217681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4834280014038</t>
+    <t xml:space="preserve">13.2501821517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0606479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9314203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8194227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3369693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.035439491272</t>
+    <t xml:space="preserve">12.3369703292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0354385375977</t>
   </si>
   <si>
     <t xml:space="preserve">11.8975954055786</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">12.3542013168335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2594327926636</t>
+    <t xml:space="preserve">12.2594337463379</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">11.9837474822998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8372888565063</t>
+    <t xml:space="preserve">11.837287902832</t>
   </si>
   <si>
     <t xml:space="preserve">11.7855978012085</t>
@@ -965,22 +965,22 @@
     <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8286724090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7597513198853</t>
+    <t xml:space="preserve">11.8286733627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7597522735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7769813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7511367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339067459106</t>
+    <t xml:space="preserve">11.7769823074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7511377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
     <t xml:space="preserve">11.6046781539917</t>
@@ -995,19 +995,19 @@
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785150527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388206481934</t>
+    <t xml:space="preserve">12.0785140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388216018677</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2157220840454</t>
+    <t xml:space="preserve">12.0871295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2157211303711</t>
   </si>
   <si>
     <t xml:space="preserve">13.103723526001</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">12.6988086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">12.5006580352783</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591152191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7160396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4231224060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4920444488525</t>
+    <t xml:space="preserve">12.7591161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7160406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4231233596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4920434951782</t>
   </si>
   <si>
     <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8366527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883438110352</t>
+    <t xml:space="preserve">12.836651802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883428573608</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">12.6471176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6643476486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7505006790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5868101119995</t>
+    <t xml:space="preserve">12.6643486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7504997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5868110656738</t>
   </si>
   <si>
     <t xml:space="preserve">12.7074241638184</t>
@@ -1082,37 +1082,37 @@
     <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7246561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280372619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7418851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8711128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9917249679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089559555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572639465332</t>
+    <t xml:space="preserve">12.7246551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280382156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7418842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.871111869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9917259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0778779983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0951070785522</t>
+    <t xml:space="preserve">13.0778770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0951080322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2674112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4914064407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6550970077515</t>
+    <t xml:space="preserve">13.2674121856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4914073944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6550960540771</t>
   </si>
   <si>
     <t xml:space="preserve">13.7757081985474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7843246459961</t>
+    <t xml:space="preserve">13.7843236923218</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
@@ -1157,16 +1157,16 @@
     <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8618612289429</t>
+    <t xml:space="preserve">13.8618621826172</t>
   </si>
   <si>
     <t xml:space="preserve">13.7240190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1547775268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443126678467</t>
+    <t xml:space="preserve">14.1547784805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443117141724</t>
   </si>
   <si>
     <t xml:space="preserve">14.0255508422852</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1117010116577</t>
+    <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6637105941772</t>
+    <t xml:space="preserve">13.6637115478516</t>
   </si>
   <si>
     <t xml:space="preserve">13.8187866210938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8877077102661</t>
+    <t xml:space="preserve">13.8877067565918</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704767227173</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7326326370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154026031494</t>
+    <t xml:space="preserve">13.7326335906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154035568237</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569473266602</t>
+    <t xml:space="preserve">13.4569463729858</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3191041946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3880243301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7670936584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6292505264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.370795249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2846422195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5603294372559</t>
+    <t xml:space="preserve">13.3191032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3880252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7670946121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6292514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3707942962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2846431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5603284835815</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
@@ -1259,28 +1259,28 @@
     <t xml:space="preserve">13.5775594711304</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5258684158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5086393356323</t>
+    <t xml:space="preserve">13.5258693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693746566772</t>
+    <t xml:space="preserve">13.8634128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693756103516</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1106576919556</t>
+    <t xml:space="preserve">14.1106586456299</t>
   </si>
   <si>
     <t xml:space="preserve">13.9340543746948</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4219017028809</t>
+    <t xml:space="preserve">13.5278654098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4219026565552</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686950683594</t>
+    <t xml:space="preserve">13.0686941146851</t>
   </si>
   <si>
     <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0046949386597</t>
+    <t xml:space="preserve">14.004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.9870347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8457527160645</t>
+    <t xml:space="preserve">13.8457517623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6338262557983</t>
+    <t xml:space="preserve">13.6338272094727</t>
   </si>
   <si>
     <t xml:space="preserve">13.4572229385376</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">13.6691474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">13.1746578216553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629594802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9803924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6095247268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5035619735718</t>
+    <t xml:space="preserve">13.2629585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.980393409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6095237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5035610198975</t>
   </si>
   <si>
     <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3159399032593</t>
+    <t xml:space="preserve">13.3159408569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.9980535507202</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569967269897</t>
+    <t xml:space="preserve">13.1569957733154</t>
   </si>
   <si>
     <t xml:space="preserve">13.2099781036377</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379764556885</t>
+    <t xml:space="preserve">11.267333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379755020142</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790323257446</t>
+    <t xml:space="preserve">11.1790313720703</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0377492904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0024280548096</t>
+    <t xml:space="preserve">11.037748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0024271011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.2143526077271</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317874908447</t>
+    <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">11.7618246078491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7265043258667</t>
+    <t xml:space="preserve">11.7265033721924</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549560546875</t>
+    <t xml:space="preserve">10.4549551010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">11.0200881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9494476318359</t>
+    <t xml:space="preserve">10.9494466781616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
@@ -1577,28 +1577,28 @@
     <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41299152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44831275939941</t>
+    <t xml:space="preserve">9.41299247741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44831371307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53661441802979</t>
+    <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7198629379272</t>
+    <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551832199097</t>
+    <t xml:space="preserve">10.7551822662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1610,25 +1610,25 @@
     <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
   </si>
   <si>
     <t xml:space="preserve">10.5785789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6845417022705</t>
+    <t xml:space="preserve">10.6845407485962</t>
   </si>
   <si>
     <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8258247375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6139001846313</t>
+    <t xml:space="preserve">10.8258237838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.613899230957</t>
   </si>
   <si>
     <t xml:space="preserve">10.5609188079834</t>
@@ -1646,16 +1646,16 @@
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019756317139</t>
+    <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.84348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.896466255188</t>
+    <t xml:space="preserve">10.8434839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8964653015137</t>
   </si>
   <si>
     <t xml:space="preserve">10.9141263961792</t>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="919">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414552688599</t>
+    <t xml:space="preserve">5.10414600372314</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169721603394</t>
+    <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564275741577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18713998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1165943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224098205566</t>
+    <t xml:space="preserve">5.1871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958925247192</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">5.24523639678955</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333185195923</t>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">5.38632583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34897899627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36972618103027</t>
+    <t xml:space="preserve">5.3489785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36972713470459</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122436523438</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48176908493042</t>
+    <t xml:space="preserve">5.39462518692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47762012481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48177003860474</t>
   </si>
   <si>
     <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9340877532959</t>
+    <t xml:space="preserve">5.93408727645874</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259052276611</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728563308716</t>
+    <t xml:space="preserve">5.96728610992432</t>
   </si>
   <si>
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653701782227</t>
+    <t xml:space="preserve">5.96313571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068693161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653654098511</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599182128906</t>
@@ -146,31 +146,31 @@
     <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05442905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0419807434082</t>
+    <t xml:space="preserve">6.05442953109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04198026657104</t>
   </si>
   <si>
     <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05027914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137001037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47354984283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36150741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55239486694336</t>
+    <t xml:space="preserve">6.05028009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327360153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19136953353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47355031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55239534378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">6.53994607925415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59389209747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63953876495361</t>
+    <t xml:space="preserve">6.5938925743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63953924179077</t>
   </si>
   <si>
     <t xml:space="preserve">6.8055272102356</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">6.96321630477905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301240921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05451107025146</t>
+    <t xml:space="preserve">7.01301288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">7.12920522689819</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">7.3034930229187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46948099136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
+    <t xml:space="preserve">7.46948146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234580993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.67289733886719</t>
@@ -239,28 +239,28 @@
     <t xml:space="preserve">7.3864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42798471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573839187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240215301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634912490845</t>
+    <t xml:space="preserve">7.4279842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634817123413</t>
   </si>
   <si>
     <t xml:space="preserve">7.43643617630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2205810546875</t>
+    <t xml:space="preserve">7.22058057785034</t>
   </si>
   <si>
     <t xml:space="preserve">7.20788478851318</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89468240737915</t>
+    <t xml:space="preserve">6.89468193054199</t>
   </si>
   <si>
     <t xml:space="preserve">6.72961568832397</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">6.77617263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97933053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202871322632</t>
+    <t xml:space="preserve">6.97933101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523014068604</t>
+    <t xml:space="preserve">7.29253244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676485061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523061752319</t>
   </si>
   <si>
     <t xml:space="preserve">7.36448526382446</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941902160645</t>
+    <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830051422119</t>
@@ -317,64 +317,64 @@
     <t xml:space="preserve">7.2375111579895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16132688522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588796615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351894378662</t>
+    <t xml:space="preserve">7.16132736206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821298599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351942062378</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45027303695679</t>
+    <t xml:space="preserve">6.45027351379395</t>
   </si>
   <si>
     <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56031656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15286159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96663284301758</t>
+    <t xml:space="preserve">6.56031703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15286207199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96663331985474</t>
   </si>
   <si>
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538328170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77194023132324</t>
+    <t xml:space="preserve">6.72538375854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7719407081604</t>
   </si>
   <si>
     <t xml:space="preserve">6.84812498092651</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88621711730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11053657531738</t>
+    <t xml:space="preserve">6.88621664047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1867208480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11053609848022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05128288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14016485214233</t>
+    <t xml:space="preserve">7.14016437530518</t>
   </si>
   <si>
     <t xml:space="preserve">7.10630512237549</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04705047607422</t>
+    <t xml:space="preserve">7.08937501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04704999923706</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086572647095</t>
@@ -398,25 +398,25 @@
     <t xml:space="preserve">7.03858518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03012037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398010253906</t>
   </si>
   <si>
     <t xml:space="preserve">7.05551528930664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09784030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0004940032959</t>
+    <t xml:space="preserve">7.09783935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00049352645874</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435277938843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11900234222412</t>
+    <t xml:space="preserve">7.11900186538696</t>
   </si>
   <si>
     <t xml:space="preserve">7.00895833969116</t>
@@ -428,25 +428,25 @@
     <t xml:space="preserve">7.10207223892212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20365142822266</t>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2036509513855</t>
   </si>
   <si>
     <t xml:space="preserve">7.23327875137329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17402458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40681076049805</t>
+    <t xml:space="preserve">7.17402410507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211671829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680932998657</t>
   </si>
   <si>
     <t xml:space="preserve">7.43220376968384</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.49992370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42373991012573</t>
+    <t xml:space="preserve">7.42373943328857</t>
   </si>
   <si>
     <t xml:space="preserve">7.38141536712646</t>
@@ -464,58 +464,58 @@
     <t xml:space="preserve">7.28406810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44490146636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834499359131</t>
+    <t xml:space="preserve">7.44490194320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834403991699</t>
   </si>
   <si>
     <t xml:space="preserve">7.47452926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64382696151733</t>
+    <t xml:space="preserve">7.64382791519165</t>
   </si>
   <si>
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6565260887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7834997177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
+    <t xml:space="preserve">7.65652561187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349828720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913482666016</t>
   </si>
   <si>
     <t xml:space="preserve">7.53378295898438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6522912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69884967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814832687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93163537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
+    <t xml:space="preserve">7.61843252182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880472183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69885015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316913604736</t>
   </si>
   <si>
     <t xml:space="preserve">7.82582330703735</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9485650062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553863525391</t>
+    <t xml:space="preserve">7.95279836654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553958892822</t>
   </si>
   <si>
     <t xml:space="preserve">7.70308256149292</t>
@@ -542,34 +542,34 @@
     <t xml:space="preserve">7.61420011520386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42797136306763</t>
+    <t xml:space="preserve">7.42797183990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.34332227706909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25020885467529</t>
+    <t xml:space="preserve">7.25020790100098</t>
   </si>
   <si>
     <t xml:space="preserve">7.45759963989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63536214828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51685428619385</t>
+    <t xml:space="preserve">7.63536262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694181442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51685380935669</t>
   </si>
   <si>
     <t xml:space="preserve">7.3094630241394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4025764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755516052246</t>
+    <t xml:space="preserve">7.40257740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755659103394</t>
   </si>
   <si>
     <t xml:space="preserve">7.27137136459351</t>
@@ -578,49 +578,49 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50838899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702934265137</t>
+    <t xml:space="preserve">7.50838851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95703029632568</t>
   </si>
   <si>
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06707286834717</t>
+    <t xml:space="preserve">8.02474784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06707382202148</t>
   </si>
   <si>
     <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27023124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40990447998047</t>
+    <t xml:space="preserve">8.27023220062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
     <t xml:space="preserve">8.45222759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40567016601562</t>
+    <t xml:space="preserve">8.40567111968994</t>
   </si>
   <si>
     <t xml:space="preserve">8.26599979400635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23213958740234</t>
+    <t xml:space="preserve">8.23214054107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3252534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027572631836</t>
+    <t xml:space="preserve">8.32525444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027667999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.71040821075439</t>
@@ -638,34 +638,34 @@
     <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04054069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02361011505127</t>
+    <t xml:space="preserve">9.04053974151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02361106872559</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17597961425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29448795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56536483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541826248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1325159072876</t>
+    <t xml:space="preserve">9.1759786605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29448699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1325149536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620780944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0551919937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4191837310791</t>
+    <t xml:space="preserve">10.9451494216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620790481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4191827774048</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884819030762</t>
@@ -695,22 +695,22 @@
     <t xml:space="preserve">11.7239217758179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7662467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355440139771</t>
+    <t xml:space="preserve">11.76624584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355430603027</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3491888046265</t>
+    <t xml:space="preserve">12.6973876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629590988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3491878509521</t>
   </si>
   <si>
     <t xml:space="preserve">14.2634000778198</t>
@@ -719,82 +719,82 @@
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.051775932312</t>
+    <t xml:space="preserve">14.0517768859863</t>
   </si>
   <si>
     <t xml:space="preserve">12.5111589431763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1460294723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443185806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0941009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206331253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8243608474731</t>
+    <t xml:space="preserve">13.1460285186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0940999984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173473358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009870529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206340789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8243618011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.4169073104858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4761619567871</t>
+    <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5438804626465</t>
+    <t xml:space="preserve">13.5438814163208</t>
   </si>
   <si>
     <t xml:space="preserve">13.5100202560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4930896759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7639694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0094509124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057231903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.601996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512075424194</t>
+    <t xml:space="preserve">13.5184841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4930906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7639684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0094518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.348048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019973754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004177093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073028564453</t>
+    <t xml:space="preserve">14.508882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500415802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.407301902771</t>
   </si>
   <si>
     <t xml:space="preserve">14.4157695770264</t>
@@ -803,31 +803,31 @@
     <t xml:space="preserve">14.3311185836792</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1618194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8655462265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840574264526</t>
+    <t xml:space="preserve">14.1618185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8655471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978277206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385721206665</t>
+    <t xml:space="preserve">13.7385740280151</t>
   </si>
   <si>
     <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290998458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.782036781311</t>
+    <t xml:space="preserve">13.1290988922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7820377349854</t>
   </si>
   <si>
     <t xml:space="preserve">12.7397127151489</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0434169769287</t>
+    <t xml:space="preserve">13.0348024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.043417930603</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397172927856</t>
+    <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726446151733</t>
@@ -869,34 +869,34 @@
     <t xml:space="preserve">13.0175704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.301872253418</t>
+    <t xml:space="preserve">13.3018732070923</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295690536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8797273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6901931762695</t>
+    <t xml:space="preserve">13.1295700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8797283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6901941299438</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812610626221</t>
+    <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557321548462</t>
+    <t xml:space="preserve">12.9228038787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557331085205</t>
   </si>
   <si>
     <t xml:space="preserve">13.1123380661011</t>
@@ -908,10 +908,10 @@
     <t xml:space="preserve">13.2760276794434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2501821517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0606479644775</t>
+    <t xml:space="preserve">13.2501811981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0606470108032</t>
   </si>
   <si>
     <t xml:space="preserve">12.9314203262329</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">11.8975944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474370956421</t>
+    <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542003631592</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7855968475342</t>
+    <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.7166767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8114433288574</t>
+    <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286733627319</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">11.7597513198853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8200578689575</t>
+    <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
     <t xml:space="preserve">11.7769823074341</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">11.7339057922363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6046772003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6305236816406</t>
+    <t xml:space="preserve">11.6046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6305246353149</t>
   </si>
   <si>
     <t xml:space="preserve">12.0182075500488</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0440530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0871295928955</t>
+    <t xml:space="preserve">12.0440540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0871305465698</t>
   </si>
   <si>
     <t xml:space="preserve">13.2157211303711</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">13.103723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6988086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.500659942627</t>
+    <t xml:space="preserve">12.6988096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5006608963013</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815776824951</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">12.4231224060059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4920444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4661979675293</t>
+    <t xml:space="preserve">12.4920434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
     <t xml:space="preserve">12.3628168106079</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
+    <t xml:space="preserve">12.5265035629272</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.836651802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8883428573608</t>
+    <t xml:space="preserve">12.8366508483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8883438110352</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7505016326904</t>
+    <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126575469971</t>
+    <t xml:space="preserve">12.6126565933228</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246541976929</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7935771942139</t>
+    <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280372619629</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.871111869812</t>
+    <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
     <t xml:space="preserve">12.9917259216309</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">13.0089569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572649002075</t>
+    <t xml:space="preserve">12.9572658538818</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520315170288</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">13.0778779983521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0951080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1381845474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1984891891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2674121856689</t>
+    <t xml:space="preserve">13.0951070785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.13818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1984901428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
     <t xml:space="preserve">13.4914073944092</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">13.7757091522217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7843246459961</t>
+    <t xml:space="preserve">13.7843236923218</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
@@ -1151,34 +1151,34 @@
     <t xml:space="preserve">14.5166177749634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963212966919</t>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963203430176</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618612289429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7240190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1547784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3443126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0255517959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.939398765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.844630241394</t>
+    <t xml:space="preserve">13.7240180969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1547775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3443117141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0255508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9393978118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8446311950684</t>
   </si>
   <si>
     <t xml:space="preserve">14.1117010116577</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5517139434814</t>
+    <t xml:space="preserve">13.7929410934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206359863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
     <t xml:space="preserve">13.6637105941772</t>
@@ -1202,19 +1202,19 @@
     <t xml:space="preserve">13.8187856674194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8877077102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8704776763916</t>
+    <t xml:space="preserve">13.8877086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8704767227173</t>
   </si>
   <si>
     <t xml:space="preserve">13.8360147476196</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8015546798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7326326370239</t>
+    <t xml:space="preserve">13.8015556335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">13.7154035568237</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">13.4569463729858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.612021446228</t>
+    <t xml:space="preserve">13.6120204925537</t>
   </si>
   <si>
     <t xml:space="preserve">13.3535642623901</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">13.405255317688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3191032409668</t>
+    <t xml:space="preserve">13.3191041946411</t>
   </si>
   <si>
     <t xml:space="preserve">13.3880252838135</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292495727539</t>
+    <t xml:space="preserve">13.6292505264282</t>
   </si>
   <si>
     <t xml:space="preserve">13.3707942962646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2846431732178</t>
+    <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
     <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3363332748413</t>
+    <t xml:space="preserve">13.3363342285156</t>
   </si>
   <si>
     <t xml:space="preserve">13.5775604248047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5258674621582</t>
+    <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
     <t xml:space="preserve">13.508638381958</t>
@@ -1271,52 +1271,52 @@
     <t xml:space="preserve">14.0223560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8634119033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9517154693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9693737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7751111984253</t>
+    <t xml:space="preserve">13.8634128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951714515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9693746566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.775110244751</t>
   </si>
   <si>
     <t xml:space="preserve">14.1106576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9340543746948</t>
+    <t xml:space="preserve">13.9340534210205</t>
   </si>
   <si>
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5278635025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4219026565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0863542556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2982797622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2806196212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2872629165649</t>
+    <t xml:space="preserve">13.6161661148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5278644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4219017028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0863552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2982807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2806205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2872619628906</t>
   </si>
   <si>
     <t xml:space="preserve">14.0929975509644</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">13.8810729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0753364562988</t>
+    <t xml:space="preserve">14.0753374099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576772689819</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">13.8987331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9870347976685</t>
+    <t xml:space="preserve">13.9870357513428</t>
   </si>
   <si>
     <t xml:space="preserve">13.8457527160645</t>
@@ -1352,10 +1352,10 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3865823745728</t>
+    <t xml:space="preserve">13.5985059738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3865814208984</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
@@ -1364,31 +1364,31 @@
     <t xml:space="preserve">13.7221298217773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6514873504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4748840332031</t>
+    <t xml:space="preserve">13.6514883041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4748849868774</t>
   </si>
   <si>
     <t xml:space="preserve">13.6868085861206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.580846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6338262557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4572229385376</t>
+    <t xml:space="preserve">13.5808458328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6338272094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4572238922119</t>
   </si>
   <si>
     <t xml:space="preserve">13.4925441741943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6691474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102052688599</t>
+    <t xml:space="preserve">13.6691484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102043151855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5455255508423</t>
@@ -1397,16 +1397,16 @@
     <t xml:space="preserve">13.3512601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2452993392944</t>
+    <t xml:space="preserve">13.2452983856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689212799072</t>
+    <t xml:space="preserve">13.2276372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689222335815</t>
   </si>
   <si>
     <t xml:space="preserve">13.174656867981</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">12.9803924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6095247268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5035619735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0157127380371</t>
+    <t xml:space="preserve">12.6095237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5035629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159399032593</t>
@@ -1436,22 +1436,22 @@
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391094207764</t>
+    <t xml:space="preserve">12.8391084671021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1569967269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2099771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9274120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8920907974243</t>
+    <t xml:space="preserve">13.1569957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2099781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9274110794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8920917510986</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">12.7684679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8567695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8037891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.8567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8037881851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">11.267333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4262762069702</t>
+    <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
     <t xml:space="preserve">11.0377492904663</t>
@@ -1511,49 +1511,49 @@
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0730686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4792594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7441644668579</t>
+    <t xml:space="preserve">10.9317855834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0730695724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2849941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4792585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7441654205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7794857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7618246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7265043258667</t>
+    <t xml:space="preserve">11.7618255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.726505279541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126051902771</t>
+    <t xml:space="preserve">11.1260509490967</t>
   </si>
   <si>
     <t xml:space="preserve">11.2496728897095</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2077102661133</t>
+    <t xml:space="preserve">10.7728433609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2077112197876</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">10.9671077728271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4439382553101</t>
+    <t xml:space="preserve">11.4439373016357</t>
   </si>
   <si>
     <t xml:space="preserve">11.3026552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0200881958008</t>
+    <t xml:space="preserve">11.0200872421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9494476318359</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547298431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41299152374268</t>
+    <t xml:space="preserve">10.154727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41299247741699</t>
   </si>
   <si>
     <t xml:space="preserve">9.44831275939941</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1370687484741</t>
+    <t xml:space="preserve">9.53661441802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1370677947998</t>
   </si>
   <si>
     <t xml:space="preserve">10.7198619842529</t>
@@ -1601,22 +1601,22 @@
     <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551822662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.666880607605</t>
+    <t xml:space="preserve">10.7551832199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668796539307</t>
   </si>
   <si>
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079374313354</t>
+    <t xml:space="preserve">10.2430305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079364776611</t>
   </si>
   <si>
     <t xml:space="preserve">10.5785779953003</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">10.7375211715698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8258247375488</t>
+    <t xml:space="preserve">10.8258237838745</t>
   </si>
   <si>
     <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609178543091</t>
+    <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
     <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3313331604004</t>
+    <t xml:space="preserve">10.3313322067261</t>
   </si>
   <si>
     <t xml:space="preserve">10.5432567596436</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">10.437294960022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.84348487854</t>
+    <t xml:space="preserve">10.8434839248657</t>
   </si>
   <si>
     <t xml:space="preserve">10.8964653015137</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
-    <t xml:space="preserve">10.984766960144</t>
+    <t xml:space="preserve">10.9847679138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.3203153610229</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">11.2559833526611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7069110870361</t>
+    <t xml:space="preserve">10.7069101333618</t>
   </si>
   <si>
     <t xml:space="preserve">10.9631443023682</t>
@@ -1709,19 +1709,19 @@
     <t xml:space="preserve">9.91990756988525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84669876098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70027923583984</t>
+    <t xml:space="preserve">9.84669780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70027828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.97481441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0663270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0846300125122</t>
+    <t xml:space="preserve">10.0663261413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0846290588379</t>
   </si>
   <si>
     <t xml:space="preserve">9.93820953369141</t>
@@ -1739,10 +1739,10 @@
     <t xml:space="preserve">10.0114192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1578388214111</t>
+    <t xml:space="preserve">10.139536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1578397750854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2127456665039</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">10.4323749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5055847167969</t>
+    <t xml:space="preserve">10.5055837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.3225593566895</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">10.3774681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5238876342773</t>
+    <t xml:space="preserve">10.523886680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.267653465271</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">10.6520042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5604915618896</t>
+    <t xml:space="preserve">10.560492515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.7435159683228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8716335296631</t>
+    <t xml:space="preserve">10.8716325759888</t>
   </si>
   <si>
     <t xml:space="preserve">10.9082374572754</t>
@@ -1802,13 +1802,13 @@
     <t xml:space="preserve">10.68860912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6703052520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7984228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8899354934692</t>
+    <t xml:space="preserve">10.6703062057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7984237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8899345397949</t>
   </si>
   <si>
     <t xml:space="preserve">10.9814472198486</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">11.2925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2193794250488</t>
+    <t xml:space="preserve">11.2193784713745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3108901977539</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">11.2742853164673</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1644706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8533306121826</t>
+    <t xml:space="preserve">11.1644716262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8533296585083</t>
   </si>
   <si>
     <t xml:space="preserve">10.7618188858032</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">10.6337013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7252140045166</t>
+    <t xml:space="preserve">10.7252130508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7801208496094</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">10.8350276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.944842338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.109564781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1461687088013</t>
+    <t xml:space="preserve">10.9448432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1461696624756</t>
   </si>
   <si>
     <t xml:space="preserve">11.0363550186157</t>
@@ -1901,16 +1901,16 @@
     <t xml:space="preserve">9.33423042297363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23608589172363</t>
+    <t xml:space="preserve">8.23608493804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.21778297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17202758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59550094604492</t>
+    <t xml:space="preserve">8.17202663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59550142288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.6895318031311</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">6.69868326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01234292984009</t>
+    <t xml:space="preserve">6.01234245300293</t>
   </si>
   <si>
     <t xml:space="preserve">6.63462448120117</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">7.22030162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00982332229614</t>
+    <t xml:space="preserve">7.0098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.32096481323242</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">7.31181335449219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05558013916016</t>
+    <t xml:space="preserve">7.055579662323</t>
   </si>
   <si>
     <t xml:space="preserve">7.10133600234985</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">7.6504077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41247701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70531558990479</t>
+    <t xml:space="preserve">7.41247749328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70531511306763</t>
   </si>
   <si>
     <t xml:space="preserve">7.46738386154175</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">7.35756969451904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48568677902222</t>
+    <t xml:space="preserve">7.48568725585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26605749130249</t>
@@ -1994,10 +1994,10 @@
     <t xml:space="preserve">7.21115064620972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68038034439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08303308486938</t>
+    <t xml:space="preserve">6.68038082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">7.19284820556641</t>
@@ -2006,28 +2006,28 @@
     <t xml:space="preserve">7.66871070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52229118347168</t>
+    <t xml:space="preserve">7.52229166030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.54059362411499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69364643096924</t>
+    <t xml:space="preserve">8.14457321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69364547729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.05969333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96818161010742</t>
+    <t xml:space="preserve">8.96818256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.56552886962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62043571472168</t>
+    <t xml:space="preserve">8.620436668396</t>
   </si>
   <si>
     <t xml:space="preserve">7.9981541633606</t>
@@ -2057,25 +2057,25 @@
     <t xml:space="preserve">7.96154928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79682779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87003803253174</t>
+    <t xml:space="preserve">7.7968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87003755569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.76022243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6321063041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74192047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72361755371094</t>
+    <t xml:space="preserve">7.77852535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63210582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74192094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7236180305481</t>
   </si>
   <si>
     <t xml:space="preserve">7.81512975692749</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">7.1745457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04642868041992</t>
+    <t xml:space="preserve">7.04642820358276</t>
   </si>
   <si>
     <t xml:space="preserve">7.02812623977661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86340475082397</t>
+    <t xml:space="preserve">6.86340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.77189302444458</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">6.60717058181763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4607515335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31433200836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3509373664856</t>
+    <t xml:space="preserve">6.46075105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31433248519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35093688964844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11300563812256</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">5.96658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02149391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13130807876587</t>
+    <t xml:space="preserve">6.02149343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94828367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13130760192871</t>
   </si>
   <si>
     <t xml:space="preserve">6.22282028198242</t>
@@ -2171,25 +2171,25 @@
     <t xml:space="preserve">5.50902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47242116928101</t>
+    <t xml:space="preserve">5.47242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.21618747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25279235839844</t>
+    <t xml:space="preserve">5.25279188156128</t>
   </si>
   <si>
     <t xml:space="preserve">5.10637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3626070022583</t>
+    <t xml:space="preserve">5.36260652542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.63714265823364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61884069442749</t>
+    <t xml:space="preserve">5.61884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">5.69204998016357</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">6.18621587753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44908237457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94324684143066</t>
+    <t xml:space="preserve">7.4490818977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324731826782</t>
   </si>
   <si>
     <t xml:space="preserve">7.97985219955444</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">7.57719850540161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55889654159546</t>
+    <t xml:space="preserve">7.5588960647583</t>
   </si>
   <si>
     <t xml:space="preserve">7.43077898025513</t>
@@ -2234,25 +2234,25 @@
     <t xml:space="preserve">8.40080738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51062202453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94987869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04139232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28847312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65452194213867</t>
+    <t xml:space="preserve">8.51062107086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94987964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04139137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65452289581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.11460113525391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73025035858154</t>
+    <t xml:space="preserve">8.73025131225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.87666988372803</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">9.24271869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82176208496094</t>
+    <t xml:space="preserve">8.82176303863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">9.07799625396729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13290309906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98648357391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02308940887451</t>
+    <t xml:space="preserve">9.13290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98648452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0230884552002</t>
   </si>
   <si>
     <t xml:space="preserve">9.51725387573242</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">9.56301021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79179000854492</t>
+    <t xml:space="preserve">9.79179096221924</t>
   </si>
   <si>
     <t xml:space="preserve">10.2951068878174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3866195678711</t>
+    <t xml:space="preserve">10.3866186141968</t>
   </si>
   <si>
     <t xml:space="preserve">9.83754730224609</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">9.42574214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37998676300049</t>
+    <t xml:space="preserve">9.37998580932617</t>
   </si>
   <si>
     <t xml:space="preserve">9.92905902862549</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">8.93157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8949728012085</t>
+    <t xml:space="preserve">8.89497184753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.78515815734863</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">8.03475856781006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88833999633789</t>
+    <t xml:space="preserve">7.88833904266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.63873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4740161895752</t>
+    <t xml:space="preserve">8.47401714324951</t>
   </si>
   <si>
     <t xml:space="preserve">8.36420249938965</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">7.28436040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9249439239502</t>
+    <t xml:space="preserve">7.92494487762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.13794088363647</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">6.42414665222168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57056570053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49735593795776</t>
+    <t xml:space="preserve">6.57056617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49735641479492</t>
   </si>
   <si>
     <t xml:space="preserve">6.62547302246094</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">6.79019498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53396129608154</t>
+    <t xml:space="preserve">6.53396081924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.99152135848999</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">6.88170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93661451339722</t>
+    <t xml:space="preserve">6.93661403656006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62564563751221</t>
@@ -2766,6 +2766,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.1499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0500001907349</t>
   </si>
 </sst>
 </file>
@@ -69118,7 +69121,7 @@
     </row>
     <row r="2540">
       <c r="A2540" s="1" t="n">
-        <v>46020.6910416667</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2540" t="n">
         <v>73481</v>
@@ -69139,6 +69142,32 @@
         <v>917</v>
       </c>
       <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.6913078704</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>21653</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>9.9399995803833</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>918</v>
+      </c>
+      <c r="H2541" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169578552246</t>
+    <t xml:space="preserve">5.09169673919678</t>
   </si>
   <si>
     <t xml:space="preserve">5.14564228057861</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">5.11659479141235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16224193572998</t>
+    <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24523639678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333185195923</t>
+    <t xml:space="preserve">5.24523591995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">5.31578063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632583618164</t>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632535934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.3489785194397</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">5.34067916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39462518692017</t>
+    <t xml:space="preserve">5.39462614059448</t>
   </si>
   <si>
     <t xml:space="preserve">5.47761964797974</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8676929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05443000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0419807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05857944488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05028009414673</t>
+    <t xml:space="preserve">5.86769247055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05442953109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04198026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0585789680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
     <t xml:space="preserve">6.13327407836914</t>
@@ -164,58 +164,58 @@
     <t xml:space="preserve">6.19137048721313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47355079650879</t>
+    <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
     <t xml:space="preserve">6.36150789260864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55239486694336</t>
+    <t xml:space="preserve">6.5523943901062</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314395904541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5606951713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205308914185</t>
+    <t xml:space="preserve">6.56069421768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.432053565979</t>
   </si>
   <si>
     <t xml:space="preserve">6.53994560241699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59389162063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58559226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61464023590088</t>
+    <t xml:space="preserve">6.59389209747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58559274673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59804201126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61464071273804</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953924179077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80552673339844</t>
+    <t xml:space="preserve">6.8055272102356</t>
   </si>
   <si>
     <t xml:space="preserve">6.96321678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02961158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05450963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12920427322388</t>
+    <t xml:space="preserve">7.01301336288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02961206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05451011657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12920475006104</t>
   </si>
   <si>
     <t xml:space="preserve">7.30349254608154</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">7.99234533309937</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6728982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928485870361</t>
+    <t xml:space="preserve">8.67289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1292839050293</t>
   </si>
   <si>
     <t xml:space="preserve">7.67281675338745</t>
@@ -239,46 +239,46 @@
     <t xml:space="preserve">7.38648653030396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42798376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240262985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788383483887</t>
+    <t xml:space="preserve">7.42798280715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36573839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240310668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634912490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22058057785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788335800171</t>
   </si>
   <si>
     <t xml:space="preserve">6.89468193054199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72961521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9835638999939</t>
+    <t xml:space="preserve">6.72961568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123792648315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77617311477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933101654053</t>
+    <t xml:space="preserve">6.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933149337769</t>
   </si>
   <si>
     <t xml:space="preserve">6.99202919006348</t>
@@ -290,43 +290,43 @@
     <t xml:space="preserve">7.37295055389404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27983617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3644847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994194984436</t>
+    <t xml:space="preserve">7.27983570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29253244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523109436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36448431015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941902160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830051422119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23751163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821346282959</t>
+    <t xml:space="preserve">7.2375111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132593154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821298599243</t>
   </si>
   <si>
     <t xml:space="preserve">7.02588748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87351942062378</t>
+    <t xml:space="preserve">6.87351894378662</t>
   </si>
   <si>
     <t xml:space="preserve">6.68729114532471</t>
@@ -335,70 +335,70 @@
     <t xml:space="preserve">6.45027303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67036104202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56031656265259</t>
+    <t xml:space="preserve">6.67036151885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56031703948975</t>
   </si>
   <si>
     <t xml:space="preserve">7.15286207199097</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08514261245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96663284301758</t>
+    <t xml:space="preserve">7.08514213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96663236618042</t>
   </si>
   <si>
     <t xml:space="preserve">6.99626111984253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72538280487061</t>
+    <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
     <t xml:space="preserve">6.77194023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84812450408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88621664047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18672227859497</t>
+    <t xml:space="preserve">6.8481240272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88621711730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18672180175781</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128288269043</t>
+    <t xml:space="preserve">7.05128240585327</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016485214233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09360694885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08937501907349</t>
+    <t xml:space="preserve">7.10630559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0936074256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08937549591064</t>
   </si>
   <si>
     <t xml:space="preserve">7.05974769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04704999923706</t>
+    <t xml:space="preserve">7.04705047607422</t>
   </si>
   <si>
     <t xml:space="preserve">6.97086572647095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03858423233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03012084960938</t>
+    <t xml:space="preserve">7.03858470916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03012037277222</t>
   </si>
   <si>
     <t xml:space="preserve">7.06398010253906</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">7.09783935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00049352645874</t>
+    <t xml:space="preserve">7.00049304962158</t>
   </si>
   <si>
     <t xml:space="preserve">7.03435325622559</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38987922668457</t>
+    <t xml:space="preserve">7.38987874984741</t>
   </si>
   <si>
     <t xml:space="preserve">7.20365190505981</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">7.23327875137329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17402410507202</t>
+    <t xml:space="preserve">7.17402458190918</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211671829224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24597549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40681028366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43220376968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992322921753</t>
+    <t xml:space="preserve">7.24597644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680980682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.432204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992370605469</t>
   </si>
   <si>
     <t xml:space="preserve">7.42373943328857</t>
@@ -461,16 +461,16 @@
     <t xml:space="preserve">7.38141489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28406810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490194320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39834403991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47452831268311</t>
+    <t xml:space="preserve">7.28406858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490146636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39834451675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47452878952026</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382743835449</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65652418136597</t>
+    <t xml:space="preserve">7.65652513504028</t>
   </si>
   <si>
     <t xml:space="preserve">7.78349781036377</t>
@@ -491,19 +491,19 @@
     <t xml:space="preserve">7.449134349823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53378295898438</t>
+    <t xml:space="preserve">7.53378248214722</t>
   </si>
   <si>
     <t xml:space="preserve">7.61843299865723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58880567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65229272842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69885015487671</t>
+    <t xml:space="preserve">7.58880662918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65229177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69884967803955</t>
   </si>
   <si>
     <t xml:space="preserve">7.74540615081787</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">7.86814785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93163585662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92317008972168</t>
+    <t xml:space="preserve">7.93163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92316913604736</t>
   </si>
   <si>
     <t xml:space="preserve">7.8258228302002</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">7.88930988311768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91470575332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279836654663</t>
+    <t xml:space="preserve">7.9147047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279741287231</t>
   </si>
   <si>
     <t xml:space="preserve">7.94856548309326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07553768157959</t>
+    <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
     <t xml:space="preserve">7.70308208465576</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">7.42797183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34332180023193</t>
+    <t xml:space="preserve">7.34332227706909</t>
   </si>
   <si>
     <t xml:space="preserve">7.25020790100098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45759963989258</t>
+    <t xml:space="preserve">7.45760011672974</t>
   </si>
   <si>
     <t xml:space="preserve">7.63536310195923</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">7.40257692337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34755611419678</t>
+    <t xml:space="preserve">7.34755516052246</t>
   </si>
   <si>
     <t xml:space="preserve">7.27137041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50838851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702981948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01205158233643</t>
+    <t xml:space="preserve">7.50838947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702886581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01205062866211</t>
   </si>
   <si>
     <t xml:space="preserve">8.02474880218506</t>
@@ -599,28 +599,28 @@
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40567207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26599979400635</t>
+    <t xml:space="preserve">8.45222663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26599884033203</t>
   </si>
   <si>
     <t xml:space="preserve">8.23213958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30832481384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32525539398193</t>
+    <t xml:space="preserve">8.30832386016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3252534866333</t>
   </si>
   <si>
     <t xml:space="preserve">8.38027572631836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71040916442871</t>
+    <t xml:space="preserve">8.71040821075439</t>
   </si>
   <si>
     <t xml:space="preserve">8.87970542907715</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514625549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99821662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04053974151611</t>
+    <t xml:space="preserve">9.01514530181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.998215675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04054069519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.02360916137695</t>
@@ -644,25 +644,25 @@
     <t xml:space="preserve">9.19290828704834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1759786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29448795318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5653657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861217498779</t>
+    <t xml:space="preserve">9.17597961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29448699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56536674499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861122131348</t>
   </si>
   <si>
     <t xml:space="preserve">10.4541835784912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71773433685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1325149536133</t>
+    <t xml:space="preserve">9.71773338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1325159072876</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">10.9620780944824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.055193901062</t>
+    <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.4191846847534</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2741413116455</t>
+    <t xml:space="preserve">12.2741422653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.6973886489868</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633981704712</t>
+    <t xml:space="preserve">13.3491868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633991241455</t>
   </si>
   <si>
     <t xml:space="preserve">16.0156383514404</t>
@@ -719,25 +719,25 @@
     <t xml:space="preserve">14.0517749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5111589431763</t>
+    <t xml:space="preserve">12.5111598968506</t>
   </si>
   <si>
     <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6443185806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0940999984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5173463821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0009870529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206331253052</t>
+    <t xml:space="preserve">14.6443204879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0941009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5173454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0009860992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
     <t xml:space="preserve">12.8243608474731</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">13.4761610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4338350296021</t>
+    <t xml:space="preserve">13.4338359832764</t>
   </si>
   <si>
     <t xml:space="preserve">13.5438804626465</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348048210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6019954681396</t>
+    <t xml:space="preserve">14.3480491638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.601996421814</t>
   </si>
   <si>
     <t xml:space="preserve">14.5512084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5596723556519</t>
+    <t xml:space="preserve">14.5596714019775</t>
   </si>
   <si>
     <t xml:space="preserve">14.5088815689087</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">14.4073038101196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4157676696777</t>
+    <t xml:space="preserve">14.4157667160034</t>
   </si>
   <si>
     <t xml:space="preserve">14.3311195373535</t>
@@ -803,22 +803,22 @@
     <t xml:space="preserve">14.1618194580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8655471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7978277206421</t>
+    <t xml:space="preserve">13.8655462265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7978267669678</t>
   </si>
   <si>
     <t xml:space="preserve">13.984058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8994064331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7385730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031341552734</t>
+    <t xml:space="preserve">13.8994073867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7385740280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5523462295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4423017501831</t>
+    <t xml:space="preserve">13.5523452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4423007965088</t>
   </si>
   <si>
     <t xml:space="preserve">13.5430994033813</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">13.2071046829224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348024368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.043417930603</t>
+    <t xml:space="preserve">13.0348014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0434169769287</t>
   </si>
   <si>
     <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.439715385437</t>
+    <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.1726455688477</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">12.8797273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6901931762695</t>
+    <t xml:space="preserve">12.6901941299438</t>
   </si>
   <si>
     <t xml:space="preserve">13.2243366241455</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">13.1209545135498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6557331085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1123390197754</t>
+    <t xml:space="preserve">12.9228057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6557321548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1123380661011</t>
   </si>
   <si>
     <t xml:space="preserve">13.3277187347412</t>
@@ -914,13 +914,13 @@
     <t xml:space="preserve">12.9314193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8194208145142</t>
+    <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2335872650146</t>
+    <t xml:space="preserve">12.233588218689</t>
   </si>
   <si>
     <t xml:space="preserve">12.3369703292847</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">12.1474361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3542003631592</t>
+    <t xml:space="preserve">12.3542013168335</t>
   </si>
   <si>
     <t xml:space="preserve">12.2594337463379</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560506820679</t>
+    <t xml:space="preserve">12.1302061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560516357422</t>
   </si>
   <si>
     <t xml:space="preserve">11.9837465286255</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511367797852</t>
+    <t xml:space="preserve">11.7511358261108</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339057922363</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182085037231</t>
+    <t xml:space="preserve">11.6305227279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612831115723</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">12.0440530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0871295928955</t>
+    <t xml:space="preserve">12.0871286392212</t>
   </si>
   <si>
     <t xml:space="preserve">13.2157211303711</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4661989212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3628158569336</t>
+    <t xml:space="preserve">12.4661979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3628168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">12.8883438110352</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8538827896118</t>
+    <t xml:space="preserve">12.8538818359375</t>
   </si>
   <si>
     <t xml:space="preserve">12.6471176147461</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7246551513672</t>
+    <t xml:space="preserve">12.6126585006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7246541976929</t>
   </si>
   <si>
     <t xml:space="preserve">12.7935762405396</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">12.8280372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7418842315674</t>
+    <t xml:space="preserve">12.7418851852417</t>
   </si>
   <si>
     <t xml:space="preserve">12.8711128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917249679565</t>
+    <t xml:space="preserve">12.9917259216309</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089559555054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9572649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520315170288</t>
+    <t xml:space="preserve">12.9572639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
     <t xml:space="preserve">13.0778779983521</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">13.2674112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914073944092</t>
+    <t xml:space="preserve">13.4914064407349</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550970077515</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7498636245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1289319992065</t>
+    <t xml:space="preserve">13.7498626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1289310455322</t>
   </si>
   <si>
     <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166177749634</t>
+    <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
     <t xml:space="preserve">14.2150850296021</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">13.6981725692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8963222503662</t>
+    <t xml:space="preserve">13.8963212966919</t>
   </si>
   <si>
     <t xml:space="preserve">13.8618612289429</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">13.9221668243408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929401397705</t>
+    <t xml:space="preserve">13.7929391860962</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206359863281</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8704767227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360147476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8015556335449</t>
+    <t xml:space="preserve">13.870475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360157012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8015546798706</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">13.6809425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569463729858</t>
+    <t xml:space="preserve">13.4569473266602</t>
   </si>
   <si>
     <t xml:space="preserve">13.6120204925537</t>
@@ -1241,19 +1241,19 @@
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292505264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.370795249939</t>
+    <t xml:space="preserve">13.6292514801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3707962036133</t>
   </si>
   <si>
     <t xml:space="preserve">13.2846422195435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3363342285156</t>
+    <t xml:space="preserve">13.5603294372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
     <t xml:space="preserve">13.5775594711304</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">13.951714515686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693746566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.775110244751</t>
+    <t xml:space="preserve">13.9693756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7751111984253</t>
   </si>
   <si>
     <t xml:space="preserve">14.1106576919556</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">13.9163942337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6161661148071</t>
+    <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
     <t xml:space="preserve">13.5278644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4219017028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0863552093506</t>
+    <t xml:space="preserve">13.4219026565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0863542556763</t>
   </si>
   <si>
     <t xml:space="preserve">13.2982807159424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2806205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0686950683594</t>
+    <t xml:space="preserve">13.2806196212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0686941146851</t>
   </si>
   <si>
     <t xml:space="preserve">14.3402433395386</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">14.0929975509644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0046949386597</t>
+    <t xml:space="preserve">14.004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7397899627686</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">13.9870357513428</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8457527160645</t>
+    <t xml:space="preserve">13.8457517623901</t>
   </si>
   <si>
     <t xml:space="preserve">13.8280916213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8104314804077</t>
+    <t xml:space="preserve">13.810432434082</t>
   </si>
   <si>
     <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3865814208984</t>
+    <t xml:space="preserve">13.3865823745728</t>
   </si>
   <si>
     <t xml:space="preserve">13.4395627975464</t>
@@ -1361,22 +1361,22 @@
     <t xml:space="preserve">13.7221298217773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6514883041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4748849868774</t>
+    <t xml:space="preserve">13.6514873504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4748840332031</t>
   </si>
   <si>
     <t xml:space="preserve">13.6868085861206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5808458328247</t>
+    <t xml:space="preserve">13.580846786499</t>
   </si>
   <si>
     <t xml:space="preserve">13.6338272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4572238922119</t>
+    <t xml:space="preserve">13.4572229385376</t>
   </si>
   <si>
     <t xml:space="preserve">13.4925441741943</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
+    <t xml:space="preserve">13.2276382446289</t>
   </si>
   <si>
     <t xml:space="preserve">13.3689222335815</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629594802856</t>
+    <t xml:space="preserve">13.2629585266113</t>
   </si>
   <si>
     <t xml:space="preserve">12.9803924560547</t>
@@ -1418,25 +1418,25 @@
     <t xml:space="preserve">12.6095237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5035629272461</t>
+    <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
     <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3159399032593</t>
+    <t xml:space="preserve">13.3159408569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9097509384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8391084671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0333738327026</t>
+    <t xml:space="preserve">12.9097499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.033374786377</t>
   </si>
   <si>
     <t xml:space="preserve">13.1569957733154</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9274110794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8920917510986</t>
+    <t xml:space="preserve">12.9274120330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8920907974243</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.121675491333</t>
+    <t xml:space="preserve">13.1216764450073</t>
   </si>
   <si>
     <t xml:space="preserve">12.7684679031372</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">11.267333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3379764556885</t>
+    <t xml:space="preserve">11.3379755020142</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">11.4615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1790323257446</t>
+    <t xml:space="preserve">11.1790313720703</t>
   </si>
   <si>
     <t xml:space="preserve">11.4262771606445</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">11.0377492904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0024280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2143526077271</t>
+    <t xml:space="preserve">11.0024271011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2143535614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556356430054</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317855834961</t>
+    <t xml:space="preserve">10.9317865371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.0730695724487</t>
@@ -1526,25 +1526,25 @@
     <t xml:space="preserve">11.7794857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7618255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.726505279541</t>
+    <t xml:space="preserve">11.7618246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7265043258667</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1260509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2496728897095</t>
+    <t xml:space="preserve">11.126051902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2496738433838</t>
   </si>
   <si>
     <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2077112197876</t>
+    <t xml:space="preserve">10.2077102661133</t>
   </si>
   <si>
     <t xml:space="preserve">10.3843145370483</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">11.3026552200317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0200872421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9494476318359</t>
+    <t xml:space="preserve">11.0200881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9494466781616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255975723267</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53661441802979</t>
+    <t xml:space="preserve">9.5366153717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.1370677947998</t>
@@ -1595,16 +1595,16 @@
     <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1966924667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551832199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6668796539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2783517837524</t>
+    <t xml:space="preserve">11.1966915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551822662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.666880607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2783527374268</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430305480957</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375211715698</t>
+    <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258237838745</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">10.5609188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2606916427612</t>
+    <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313322067261</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019746780396</t>
+    <t xml:space="preserve">10.4019737243652</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1661,10 +1661,10 @@
     <t xml:space="preserve">10.9141254425049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0554094314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9847679138184</t>
+    <t xml:space="preserve">11.0554103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.984766960144</t>
   </si>
   <si>
     <t xml:space="preserve">11.3203153610229</t>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="921">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">5.1539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09169673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14564275741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18713998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1165943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224145889282</t>
+    <t xml:space="preserve">5.09169626235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14564228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11659479141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224050521851</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
@@ -68,31 +68,31 @@
     <t xml:space="preserve">5.24523591995239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333232879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31163120269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3157811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482860565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38632583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34897947311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35312795639038</t>
+    <t xml:space="preserve">5.30333137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3116307258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31578063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38632535934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3489785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
     <t xml:space="preserve">5.36972665786743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41122436523438</t>
+    <t xml:space="preserve">5.41122388839722</t>
   </si>
   <si>
     <t xml:space="preserve">5.34067916870117</t>
@@ -110,55 +110,55 @@
     <t xml:space="preserve">5.71000385284424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9340877532959</t>
+    <t xml:space="preserve">5.93408823013306</t>
   </si>
   <si>
     <t xml:space="preserve">5.89259052276611</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939311981201</t>
+    <t xml:space="preserve">5.71415376663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939359664917</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728563308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9008903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96313619613647</t>
+    <t xml:space="preserve">5.96728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90089082717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96313571929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.95068645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94653749465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87599182128906</t>
+    <t xml:space="preserve">5.94653701782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87599229812622</t>
   </si>
   <si>
     <t xml:space="preserve">5.86769247055054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05443000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0585789680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05027914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13327360153198</t>
+    <t xml:space="preserve">6.05442953109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0419807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05857992172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05027961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137048721313</t>
@@ -170,43 +170,43 @@
     <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55239534378052</t>
+    <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
     <t xml:space="preserve">6.57314348220825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56069469451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43205261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59389209747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58559226989746</t>
+    <t xml:space="preserve">6.56069374084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.432053565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994607925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5938925743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58559274673462</t>
   </si>
   <si>
     <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61464023590088</t>
+    <t xml:space="preserve">6.61463975906372</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953876495361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80552768707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96321630477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01301288604736</t>
+    <t xml:space="preserve">6.8055272102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96321678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01301240921021</t>
   </si>
   <si>
     <t xml:space="preserve">7.02961206436157</t>
@@ -215,73 +215,73 @@
     <t xml:space="preserve">7.05451059341431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12920570373535</t>
+    <t xml:space="preserve">7.12920522689819</t>
   </si>
   <si>
     <t xml:space="preserve">7.3034930229187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46948146820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234485626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6728982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38648653030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42798471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36573839187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240215301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634912490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43643617630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788478851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961568832397</t>
+    <t xml:space="preserve">7.469482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234676361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281818389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3864860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42798376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3657374382019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240167617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43643712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22058057785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788431167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468193054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961521148682</t>
   </si>
   <si>
     <t xml:space="preserve">6.80156707763672</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98356342315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94123888015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77617263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97933053970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99202871322632</t>
+    <t xml:space="preserve">6.98356294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94123840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77617311477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97933101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99202823638916</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2925329208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676580429077</t>
+    <t xml:space="preserve">7.29253244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676532745361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26290559768677</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">7.30523014068604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36448526382446</t>
+    <t xml:space="preserve">7.36448431015015</t>
   </si>
   <si>
     <t xml:space="preserve">7.19941902160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28830051422119</t>
+    <t xml:space="preserve">7.28830003738403</t>
   </si>
   <si>
     <t xml:space="preserve">7.2375111579895</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">7.06821250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02588796615601</t>
+    <t xml:space="preserve">7.02588844299316</t>
   </si>
   <si>
     <t xml:space="preserve">6.87351894378662</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">6.67036104202271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56031656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15286159515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08514213562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96663284301758</t>
+    <t xml:space="preserve">6.56031703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15286207199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08514261245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96663331985474</t>
   </si>
   <si>
     <t xml:space="preserve">6.99626111984253</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77194023132324</t>
+    <t xml:space="preserve">6.77193975448608</t>
   </si>
   <si>
     <t xml:space="preserve">6.84812498092651</t>
@@ -368,25 +368,25 @@
     <t xml:space="preserve">7.18672132492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11053657531738</t>
+    <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.05128288269043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14016485214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10630512237549</t>
+    <t xml:space="preserve">7.14016532897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10630559921265</t>
   </si>
   <si>
     <t xml:space="preserve">7.0936074256897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08937454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05974769592285</t>
+    <t xml:space="preserve">7.08937501907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05974817276001</t>
   </si>
   <si>
     <t xml:space="preserve">7.04705047607422</t>
@@ -398,46 +398,46 @@
     <t xml:space="preserve">7.03858518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03012037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06398057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05551528930664</t>
+    <t xml:space="preserve">7.03012084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06398010253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0555157661438</t>
   </si>
   <si>
     <t xml:space="preserve">7.09784030914307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435277938843</t>
+    <t xml:space="preserve">7.00049352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435325622559</t>
   </si>
   <si>
     <t xml:space="preserve">7.11900234222412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00895833969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10207223892212</t>
+    <t xml:space="preserve">7.008957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476945877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
     <t xml:space="preserve">7.38987970352173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20365142822266</t>
+    <t xml:space="preserve">7.2036509513855</t>
   </si>
   <si>
     <t xml:space="preserve">7.23327875137329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17402458190918</t>
+    <t xml:space="preserve">7.17402362823486</t>
   </si>
   <si>
     <t xml:space="preserve">7.21211624145508</t>
@@ -446,31 +446,31 @@
     <t xml:space="preserve">7.24597597122192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40681076049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43220376968384</t>
+    <t xml:space="preserve">7.40681028366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.432204246521</t>
   </si>
   <si>
     <t xml:space="preserve">7.49992370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42373991012573</t>
+    <t xml:space="preserve">7.42373943328857</t>
   </si>
   <si>
     <t xml:space="preserve">7.38141536712646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28406810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490146636963</t>
+    <t xml:space="preserve">7.28406715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490194320679</t>
   </si>
   <si>
     <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452926635742</t>
+    <t xml:space="preserve">7.47452831268311</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382696151733</t>
@@ -479,28 +479,28 @@
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6565260887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7834997177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457279205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.449134349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53378295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61843299865723</t>
+    <t xml:space="preserve">7.65652561187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349924087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457326889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53378248214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61843347549438</t>
   </si>
   <si>
     <t xml:space="preserve">7.58880519866943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6522912979126</t>
+    <t xml:space="preserve">7.65229225158691</t>
   </si>
   <si>
     <t xml:space="preserve">7.69884967803955</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">7.74540567398071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86814832687378</t>
+    <t xml:space="preserve">7.86814880371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.93163537979126</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">7.92317008972168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82582330703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88931083679199</t>
+    <t xml:space="preserve">7.82582378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88931035995483</t>
   </si>
   <si>
     <t xml:space="preserve">7.91470575332642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95279741287231</t>
+    <t xml:space="preserve">7.95279693603516</t>
   </si>
   <si>
     <t xml:space="preserve">7.9485650062561</t>
@@ -536,34 +536,34 @@
     <t xml:space="preserve">8.07553863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70308256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61420011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332227706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25020885467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45759963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63536214828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73694229125977</t>
+    <t xml:space="preserve">7.70308208465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6141996383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332323074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25020837783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45759916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63536310195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73694133758545</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3094630241394</t>
+    <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
     <t xml:space="preserve">7.4025764465332</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">7.34755516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27137136459351</t>
+    <t xml:space="preserve">7.27137088775635</t>
   </si>
   <si>
     <t xml:space="preserve">7.21634864807129</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">8.01205158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02474975585938</t>
+    <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
     <t xml:space="preserve">8.06707286834717</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27023124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40990447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45222759246826</t>
+    <t xml:space="preserve">8.27023220062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40990352630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45222663879395</t>
   </si>
   <si>
     <t xml:space="preserve">8.40567016601562</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">8.87970638275146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11672401428223</t>
+    <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
     <t xml:space="preserve">9.01514434814453</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04054069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02361011505127</t>
+    <t xml:space="preserve">9.04053974151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02360916137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448795318604</t>
+    <t xml:space="preserve">9.29448890686035</t>
   </si>
   <si>
     <t xml:space="preserve">9.56536483764648</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">9.71773338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1325159072876</t>
+    <t xml:space="preserve">10.1325168609619</t>
   </si>
   <si>
     <t xml:space="preserve">9.90396213531494</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884819030762</t>
+    <t xml:space="preserve">11.5884809494019</t>
   </si>
   <si>
     <t xml:space="preserve">11.7239217758179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7662467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355440139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2741413116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6973886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1629600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3491888046265</t>
+    <t xml:space="preserve">11.7662448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355449676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2741422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6973876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1629590988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3491868972778</t>
   </si>
   <si>
     <t xml:space="preserve">14.2634000778198</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">16.0156383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.051775932312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111589431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460294723511</t>
+    <t xml:space="preserve">14.0517768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460285186768</t>
   </si>
   <si>
     <t xml:space="preserve">14.6443185806274</t>
@@ -737,25 +737,25 @@
     <t xml:space="preserve">14.5173454284668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1206331253052</t>
+    <t xml:space="preserve">14.0009870529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1206340789795</t>
   </si>
   <si>
     <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169073104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5438804626465</t>
+    <t xml:space="preserve">13.4169063568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4338369369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5438795089722</t>
   </si>
   <si>
     <t xml:space="preserve">13.5100202560425</t>
@@ -767,37 +767,37 @@
     <t xml:space="preserve">13.4930896759033</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7639694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0094509124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057231903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3480491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.601996421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5512075424194</t>
+    <t xml:space="preserve">13.7639684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0094499588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057241439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3480472564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6019954681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5512065887451</t>
   </si>
   <si>
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088815689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5004177093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4073028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157695770264</t>
+    <t xml:space="preserve">14.5088806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5004167556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.407301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157686233521</t>
   </si>
   <si>
     <t xml:space="preserve">14.3311185836792</t>
@@ -809,37 +809,37 @@
     <t xml:space="preserve">13.8655462265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7978286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9840574264526</t>
+    <t xml:space="preserve">13.7978277206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9840564727783</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385721206665</t>
+    <t xml:space="preserve">13.7385730743408</t>
   </si>
   <si>
     <t xml:space="preserve">13.6031341552734</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1290998458862</t>
+    <t xml:space="preserve">13.1290988922119</t>
   </si>
   <si>
     <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397127151489</t>
+    <t xml:space="preserve">12.7397136688232</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5269498825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5523452758789</t>
+    <t xml:space="preserve">13.526948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
     <t xml:space="preserve">13.4423017501831</t>
@@ -851,25 +851,25 @@
     <t xml:space="preserve">13.2071056365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0348014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0434169769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.940034866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1726446151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0175704956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.301872253418</t>
+    <t xml:space="preserve">13.0348024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.043417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9400358200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1726455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3018732070923</t>
   </si>
   <si>
     <t xml:space="preserve">13.1640300750732</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">12.6901931762695</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2243375778198</t>
+    <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812610626221</t>
@@ -899,10 +899,10 @@
     <t xml:space="preserve">12.6557321548462</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1123380661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3277177810669</t>
+    <t xml:space="preserve">13.1123390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3277187347412</t>
   </si>
   <si>
     <t xml:space="preserve">13.2760276794434</t>
@@ -917,31 +917,31 @@
     <t xml:space="preserve">12.9314203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8194217681885</t>
+    <t xml:space="preserve">12.8194227218628</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2335872650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3369693756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0354375839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8975944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1474370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3542003631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2594327926636</t>
+    <t xml:space="preserve">12.233588218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3369703292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0354385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8975954055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1474361419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3542013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2594337463379</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
@@ -959,49 +959,49 @@
     <t xml:space="preserve">11.8372888565063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7855968475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7166767120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114433288574</t>
+    <t xml:space="preserve">11.7855978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7166757583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114423751831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8286733627319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7597513198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8200578689575</t>
+    <t xml:space="preserve">11.7597522735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8200588226318</t>
   </si>
   <si>
     <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7339057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6046772003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6305236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182075500488</t>
+    <t xml:space="preserve">11.7511377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7339067459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6046781539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6305246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182085037231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388206481934</t>
+    <t xml:space="preserve">12.0785150527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388216018677</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
@@ -1019,25 +1019,25 @@
     <t xml:space="preserve">12.6988086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.500659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815776824951</t>
+    <t xml:space="preserve">12.5006589889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
     <t xml:space="preserve">12.7591152191162</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7160396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4231224060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4920444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4661979675293</t>
+    <t xml:space="preserve">12.7160406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4231233596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4920434951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
     <t xml:space="preserve">12.3628168106079</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265045166016</t>
+    <t xml:space="preserve">12.5265054702759</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">12.9141893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.836651802063</t>
+    <t xml:space="preserve">12.8366527557373</t>
   </si>
   <si>
     <t xml:space="preserve">12.8883428573608</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">12.6643476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7505016326904</t>
+    <t xml:space="preserve">12.7505006790161</t>
   </si>
   <si>
     <t xml:space="preserve">12.5868110656738</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">12.6126575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7246541976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7935771942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280372619629</t>
+    <t xml:space="preserve">12.7246551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7935762405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280382156372</t>
   </si>
   <si>
     <t xml:space="preserve">12.7418851852417</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">12.871111869812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917259216309</t>
+    <t xml:space="preserve">12.9917249679565</t>
   </si>
   <si>
     <t xml:space="preserve">13.0089569091797</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">12.9572649002075</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520315170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0778779983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0951080322266</t>
+    <t xml:space="preserve">13.0520324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0778770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0951070785522</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">13.4914073944092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6550970077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7757091522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843246459961</t>
+    <t xml:space="preserve">13.6550960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7757081985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843236923218</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">14.4907712936401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5166177749634</t>
+    <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
     <t xml:space="preserve">14.2150850296021</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">14.3443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0255517959595</t>
+    <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
     <t xml:space="preserve">13.939398765564</t>
@@ -1181,37 +1181,37 @@
     <t xml:space="preserve">13.844630241394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1117010116577</t>
+    <t xml:space="preserve">14.111701965332</t>
   </si>
   <si>
     <t xml:space="preserve">13.9221677780151</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6206350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5517139434814</t>
+    <t xml:space="preserve">13.7929391860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6206359863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5517129898071</t>
   </si>
   <si>
     <t xml:space="preserve">13.6637105941772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8187856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8877077102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8704776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8360147476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8015546798706</t>
+    <t xml:space="preserve">13.8187866210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8877067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8704767227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8360157012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8015556335449</t>
   </si>
   <si>
     <t xml:space="preserve">13.7326326370239</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">13.3535642623901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.405255317688</t>
+    <t xml:space="preserve">13.4052562713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3191032409668</t>
@@ -1244,28 +1244,28 @@
     <t xml:space="preserve">13.7670936584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6292495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3707942962646</t>
+    <t xml:space="preserve">13.6292505264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.370795249939</t>
   </si>
   <si>
     <t xml:space="preserve">13.2846431732178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603294372559</t>
+    <t xml:space="preserve">13.5603284835815</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5775604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5258674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.508638381958</t>
+    <t xml:space="preserve">13.5775594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5258684158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693737030029</t>
+    <t xml:space="preserve">13.9693746566772</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278635025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4219026565552</t>
+    <t xml:space="preserve">13.5278644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4219017028809</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686960220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402423858643</t>
+    <t xml:space="preserve">13.0686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402433395386</t>
   </si>
   <si>
     <t xml:space="preserve">14.2872629165649</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985069274902</t>
+    <t xml:space="preserve">13.5985059738159</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1394,22 +1394,22 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3512601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452993392944</t>
+    <t xml:space="preserve">13.351261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452983856201</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.174656867981</t>
+    <t xml:space="preserve">13.2276372909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1746578216553</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157127380371</t>
+    <t xml:space="preserve">13.0157136917114</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980525970459</t>
+    <t xml:space="preserve">12.9980535507202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391094207764</t>
+    <t xml:space="preserve">12.8391103744507</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099771499634</t>
+    <t xml:space="preserve">13.2099781036377</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.238655090332</t>
+    <t xml:space="preserve">12.2386560440063</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379755020142</t>
+    <t xml:space="preserve">11.2673349380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379764556885</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4262762069702</t>
+    <t xml:space="preserve">11.4262771606445</t>
   </si>
   <si>
     <t xml:space="preserve">11.0377492904663</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907297134399</t>
+    <t xml:space="preserve">11.0907306671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317865371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0730686187744</t>
+    <t xml:space="preserve">10.9317874908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0730695724487</t>
   </si>
   <si>
     <t xml:space="preserve">11.2849950790405</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496728897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728424072266</t>
+    <t xml:space="preserve">11.2496738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728433609009</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549551010132</t>
+    <t xml:space="preserve">10.4549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547298431396</t>
+    <t xml:space="preserve">10.1547288894653</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299152374268</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5366153717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1370687484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7198619842529</t>
+    <t xml:space="preserve">9.53661441802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1370677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7198629379272</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551822662354</t>
+    <t xml:space="preserve">10.7551832199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.24303150177</t>
+    <t xml:space="preserve">10.2430305480957</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902772903442</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.5079374313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5785779953003</t>
+    <t xml:space="preserve">10.5785789489746</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375211715698</t>
+    <t xml:space="preserve">10.7375221252441</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258247375488</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609178543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606916427612</t>
+    <t xml:space="preserve">10.5609188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606906890869</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432567596436</t>
+    <t xml:space="preserve">10.5432577133179</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019746780396</t>
+    <t xml:space="preserve">10.4019756317139</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">10.84348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8964653015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141254425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554094314575</t>
+    <t xml:space="preserve">10.896466255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141263961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554103851318</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -2772,6 +2772,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1000003814697</t>
   </si>
 </sst>
 </file>
@@ -69176,7 +69179,7 @@
     </row>
     <row r="2542">
       <c r="A2542" s="1" t="n">
-        <v>46024.691099537</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B2542" t="n">
         <v>13110</v>
@@ -69197,6 +69200,32 @@
         <v>919</v>
       </c>
       <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" s="1" t="n">
+        <v>46027.691087963</v>
+      </c>
+      <c r="B2543" t="n">
+        <v>23952</v>
+      </c>
+      <c r="C2543" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D2543" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2543" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="F2543" t="n">
+        <v>10.1000003814697</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>920</v>
+      </c>
+      <c r="H2543" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10414600372314</t>
+    <t xml:space="preserve">5.10414552688599</t>
   </si>
   <si>
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1539421081543</t>
+    <t xml:space="preserve">5.15394163131714</t>
   </si>
   <si>
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564228057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11659479141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224050521851</t>
+    <t xml:space="preserve">5.14564180374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18713998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1165943145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224145889282</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24523591995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30333137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3116307258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34482908248901</t>
+    <t xml:space="preserve">5.24523544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30333185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31163120269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3157811164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
     <t xml:space="preserve">5.38632535934448</t>
@@ -89,61 +89,61 @@
     <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972665786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41122388839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34067916870117</t>
+    <t xml:space="preserve">5.36972713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41122436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34067964553833</t>
   </si>
   <si>
     <t xml:space="preserve">5.39462566375732</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47761964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48176908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71000385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93408823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89259052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71415376663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85939359664917</t>
+    <t xml:space="preserve">5.47761917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48176956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71000337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9340877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89259099960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85939311981201</t>
   </si>
   <si>
     <t xml:space="preserve">5.97558498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90089082717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96313571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068645477295</t>
+    <t xml:space="preserve">5.96728563308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9008903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96313619613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068693161011</t>
   </si>
   <si>
     <t xml:space="preserve">5.94653701782227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87599229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86769247055054</t>
+    <t xml:space="preserve">5.87599182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8676929473877</t>
   </si>
   <si>
     <t xml:space="preserve">6.05442953109741</t>
@@ -152,40 +152,40 @@
     <t xml:space="preserve">6.0419807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05857992172241</t>
+    <t xml:space="preserve">6.05857944488525</t>
   </si>
   <si>
     <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19137048721313</t>
+    <t xml:space="preserve">6.13327360153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19137001037598</t>
   </si>
   <si>
     <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3615083694458</t>
+    <t xml:space="preserve">6.36150789260864</t>
   </si>
   <si>
     <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57314348220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56069374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.432053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53994607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5938925743103</t>
+    <t xml:space="preserve">6.57314395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5606951713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43205308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53994512557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59389209747314</t>
   </si>
   <si>
     <t xml:space="preserve">6.58559274673462</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">6.59804201126099</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61463975906372</t>
+    <t xml:space="preserve">6.61464023590088</t>
   </si>
   <si>
     <t xml:space="preserve">6.63953876495361</t>
@@ -206,34 +206,34 @@
     <t xml:space="preserve">6.96321678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01301240921021</t>
+    <t xml:space="preserve">7.01301336288452</t>
   </si>
   <si>
     <t xml:space="preserve">7.02961206436157</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05451059341431</t>
+    <t xml:space="preserve">7.05450963973999</t>
   </si>
   <si>
     <t xml:space="preserve">7.12920522689819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3034930229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.469482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99234676361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67289733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12928485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67281818389893</t>
+    <t xml:space="preserve">7.30349349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46948146820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99234580993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6728982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12928581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67281770706177</t>
   </si>
   <si>
     <t xml:space="preserve">7.3864860534668</t>
@@ -242,34 +242,34 @@
     <t xml:space="preserve">7.42798376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3657374382019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16240167617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21634960174561</t>
+    <t xml:space="preserve">7.36573886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16240262985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21634817123413</t>
   </si>
   <si>
     <t xml:space="preserve">7.43643712997437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22058057785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20788431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89468193054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72961521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80156707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98356294631958</t>
+    <t xml:space="preserve">7.2205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20788335800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89468145370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72961568832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80156755447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98356342315674</t>
   </si>
   <si>
     <t xml:space="preserve">6.94123840332031</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">6.97933101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99202823638916</t>
+    <t xml:space="preserve">6.99202919006348</t>
   </si>
   <si>
     <t xml:space="preserve">7.49145936965942</t>
@@ -293,49 +293,49 @@
     <t xml:space="preserve">7.27983617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29253244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29676532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26290559768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30523014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36448431015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941902160645</t>
+    <t xml:space="preserve">7.2925329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29676628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30523061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3644847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1994194984436</t>
   </si>
   <si>
     <t xml:space="preserve">7.28830003738403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2375111579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16132688522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06821250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02588844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87351894378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68729114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45027303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67036104202271</t>
+    <t xml:space="preserve">7.23751163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16132640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06821346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02588748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87351942062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68729066848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45027256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67036056518555</t>
   </si>
   <si>
     <t xml:space="preserve">6.56031703948975</t>
@@ -347,40 +347,40 @@
     <t xml:space="preserve">7.08514261245728</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96663331985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99626111984253</t>
+    <t xml:space="preserve">6.96663284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99626064300537</t>
   </si>
   <si>
     <t xml:space="preserve">6.72538328170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77193975448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84812498092651</t>
+    <t xml:space="preserve">6.77194023132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84812450408936</t>
   </si>
   <si>
     <t xml:space="preserve">6.88621711730957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18672132492065</t>
+    <t xml:space="preserve">7.18672180175781</t>
   </si>
   <si>
     <t xml:space="preserve">7.11053705215454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05128288269043</t>
+    <t xml:space="preserve">7.05128192901611</t>
   </si>
   <si>
     <t xml:space="preserve">7.14016532897949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10630559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0936074256897</t>
+    <t xml:space="preserve">7.10630512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09360790252686</t>
   </si>
   <si>
     <t xml:space="preserve">7.08937501907349</t>
@@ -389,88 +389,88 @@
     <t xml:space="preserve">7.05974817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04705047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97086572647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03858518600464</t>
+    <t xml:space="preserve">7.04704999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97086524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03858423233032</t>
   </si>
   <si>
     <t xml:space="preserve">7.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06398010253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0555157661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09784030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00049352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03435325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11900234222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.008957862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11476945877075</t>
+    <t xml:space="preserve">7.0639796257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05551528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09783983230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00049304962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03435373306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11900186538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00895833969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11476993560791</t>
   </si>
   <si>
     <t xml:space="preserve">7.10207271575928</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38987970352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2036509513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23327875137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17402362823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21211624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24597597122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40681028366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.432204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49992370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42373943328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38141536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28406715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44490194320679</t>
+    <t xml:space="preserve">7.38987922668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20365190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23327827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17402410507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21211719512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24597644805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40680980682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43220376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49992322921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42374038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38141489028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28406810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44490146636963</t>
   </si>
   <si>
     <t xml:space="preserve">7.39834499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47452831268311</t>
+    <t xml:space="preserve">7.47452926635742</t>
   </si>
   <si>
     <t xml:space="preserve">7.64382696151733</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">7.83005571365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65652561187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78349924087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58457326889038</t>
+    <t xml:space="preserve">7.65652513504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78349685668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58457231521606</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913482666016</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">7.53378248214722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61843347549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58880519866943</t>
+    <t xml:space="preserve">7.61843299865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58880567550659</t>
   </si>
   <si>
     <t xml:space="preserve">7.65229225158691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69884967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74540567398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86814880371094</t>
+    <t xml:space="preserve">7.69885110855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74540519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86814737319946</t>
   </si>
   <si>
     <t xml:space="preserve">7.93163537979126</t>
@@ -524,28 +524,28 @@
     <t xml:space="preserve">7.88931035995483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91470575332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95279693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9485650062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07553863525391</t>
+    <t xml:space="preserve">7.9147047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95279741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94856548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07553768157959</t>
   </si>
   <si>
     <t xml:space="preserve">7.70308208465576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6141996383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42797183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34332323074341</t>
+    <t xml:space="preserve">7.61420059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42797136306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34332275390625</t>
   </si>
   <si>
     <t xml:space="preserve">7.25020837783813</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">7.63536310195923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73694133758545</t>
+    <t xml:space="preserve">7.73694324493408</t>
   </si>
   <si>
     <t xml:space="preserve">7.51685428619385</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">7.30946350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4025764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34755516052246</t>
+    <t xml:space="preserve">7.40257692337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34755563735962</t>
   </si>
   <si>
     <t xml:space="preserve">7.27137088775635</t>
@@ -578,37 +578,37 @@
     <t xml:space="preserve">7.21634864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50838899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01205158233643</t>
+    <t xml:space="preserve">7.50838756561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702981948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01205253601074</t>
   </si>
   <si>
     <t xml:space="preserve">8.02474880218506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06707286834717</t>
+    <t xml:space="preserve">8.06707382202148</t>
   </si>
   <si>
     <t xml:space="preserve">8.21097755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27023220062256</t>
+    <t xml:space="preserve">8.27023124694824</t>
   </si>
   <si>
     <t xml:space="preserve">8.40990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222663879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40567016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26599979400635</t>
+    <t xml:space="preserve">8.45222759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26600074768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.23213958740234</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">8.30832386016846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3252534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38027572631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71040821075439</t>
+    <t xml:space="preserve">8.32525444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38027477264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71040916442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.87970638275146</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">9.11672496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01514434814453</t>
+    <t xml:space="preserve">9.01514625549316</t>
   </si>
   <si>
     <t xml:space="preserve">8.998215675354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04053974151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02360916137695</t>
+    <t xml:space="preserve">9.04054069519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02361011505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.19290924072266</t>
@@ -650,94 +650,94 @@
     <t xml:space="preserve">9.17597961425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29448890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56536483764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98861122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4541826248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71773338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1325168609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90396213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4965076446533</t>
+    <t xml:space="preserve">9.29448699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5653657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98861217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4541835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71773433685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1325149536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90396308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4965057373047</t>
   </si>
   <si>
     <t xml:space="preserve">10.7927799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9451484680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9620780944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0551919937134</t>
+    <t xml:space="preserve">10.9451494216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9620771408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0551929473877</t>
   </si>
   <si>
     <t xml:space="preserve">11.4191837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884809494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7239217758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7662448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9355449676514</t>
+    <t xml:space="preserve">11.5884819030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7239208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.76624584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9355440139771</t>
   </si>
   <si>
     <t xml:space="preserve">12.2741422653198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6973876953125</t>
+    <t xml:space="preserve">12.6973886489868</t>
   </si>
   <si>
     <t xml:space="preserve">13.1629590988159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3491868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2634000778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0156383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0517768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5111598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1460285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6443185806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0941009521484</t>
+    <t xml:space="preserve">13.3491878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633981704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0156364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0517749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5111589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1460294723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6443214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0940999984741</t>
   </si>
   <si>
     <t xml:space="preserve">14.5173454284668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0009870529175</t>
+    <t xml:space="preserve">14.0009860992432</t>
   </si>
   <si>
     <t xml:space="preserve">13.1206340789795</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">12.8243608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4169063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4761610031128</t>
+    <t xml:space="preserve">13.4169073104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4761600494385</t>
   </si>
   <si>
     <t xml:space="preserve">13.4338369369507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5438795089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5100202560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184850692749</t>
+    <t xml:space="preserve">13.5438804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5100212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184860229492</t>
   </si>
   <si>
     <t xml:space="preserve">13.4930896759033</t>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">13.7639684677124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0094499588013</t>
+    <t xml:space="preserve">14.0094509124756</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3480472564697</t>
+    <t xml:space="preserve">14.348048210144</t>
   </si>
   <si>
     <t xml:space="preserve">14.6019954681396</t>
@@ -788,19 +788,19 @@
     <t xml:space="preserve">14.5596723556519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5088806152344</t>
+    <t xml:space="preserve">14.5088815689087</t>
   </si>
   <si>
     <t xml:space="preserve">14.5004167556763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.407301902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4157686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3311185836792</t>
+    <t xml:space="preserve">14.4073038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4157667160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3311195373535</t>
   </si>
   <si>
     <t xml:space="preserve">14.1618194580078</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">13.7978277206421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9840564727783</t>
+    <t xml:space="preserve">13.984058380127</t>
   </si>
   <si>
     <t xml:space="preserve">13.8994073867798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7385730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6031341552734</t>
+    <t xml:space="preserve">13.7385721206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6031351089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1290988922119</t>
@@ -830,22 +830,22 @@
     <t xml:space="preserve">12.782036781311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7397136688232</t>
+    <t xml:space="preserve">12.7397127151489</t>
   </si>
   <si>
     <t xml:space="preserve">13.0275201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">13.526948928833</t>
+    <t xml:space="preserve">13.5269498825073</t>
   </si>
   <si>
     <t xml:space="preserve">13.5523462295532</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4423017501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.543098449707</t>
+    <t xml:space="preserve">13.4423007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5430994033813</t>
   </si>
   <si>
     <t xml:space="preserve">13.2071056365967</t>
@@ -854,19 +854,19 @@
     <t xml:space="preserve">13.0348024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.043417930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9400358200073</t>
+    <t xml:space="preserve">13.0434169769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
     <t xml:space="preserve">13.4397163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1726455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0175714492798</t>
+    <t xml:space="preserve">13.1726446151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0175704956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.3018732070923</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">13.1640300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1295690536499</t>
+    <t xml:space="preserve">13.1295680999756</t>
   </si>
   <si>
     <t xml:space="preserve">12.8797273635864</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">13.2243366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812610626221</t>
+    <t xml:space="preserve">13.1812601089478</t>
   </si>
   <si>
     <t xml:space="preserve">13.1209535598755</t>
@@ -902,52 +902,52 @@
     <t xml:space="preserve">13.1123390197754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3277187347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2760276794434</t>
+    <t xml:space="preserve">13.3277196884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.276026725769</t>
   </si>
   <si>
     <t xml:space="preserve">13.2501821517944</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0606479644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9314203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8194227218628</t>
+    <t xml:space="preserve">13.0606470108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9314184188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8194217681885</t>
   </si>
   <si>
     <t xml:space="preserve">12.4834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.233588218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3369703292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0354385375977</t>
+    <t xml:space="preserve">12.2335872650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3369693756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.035439491272</t>
   </si>
   <si>
     <t xml:space="preserve">11.8975954055786</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1474361419678</t>
+    <t xml:space="preserve">12.1474351882935</t>
   </si>
   <si>
     <t xml:space="preserve">12.3542013168335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2594337463379</t>
+    <t xml:space="preserve">12.2594327926636</t>
   </si>
   <si>
     <t xml:space="preserve">12.3197402954102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302061080933</t>
+    <t xml:space="preserve">12.1302051544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560506820679</t>
@@ -962,25 +962,25 @@
     <t xml:space="preserve">11.7855978012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7166757583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8114423751831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8286733627319</t>
+    <t xml:space="preserve">11.7166767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8114433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8286724090576</t>
   </si>
   <si>
     <t xml:space="preserve">11.7597522735596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8200588226318</t>
+    <t xml:space="preserve">11.8200597763062</t>
   </si>
   <si>
     <t xml:space="preserve">11.7769823074341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7511377334595</t>
+    <t xml:space="preserve">11.7511367797852</t>
   </si>
   <si>
     <t xml:space="preserve">11.7339067459106</t>
@@ -989,19 +989,19 @@
     <t xml:space="preserve">11.6046781539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6305246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0182085037231</t>
+    <t xml:space="preserve">11.6305236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0182075500488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0612840652466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0785150527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1388216018677</t>
+    <t xml:space="preserve">12.0785160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1388206481934</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440530776978</t>
@@ -1019,28 +1019,28 @@
     <t xml:space="preserve">12.6988086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5006589889526</t>
+    <t xml:space="preserve">12.500659942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7591152191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7160406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4231233596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4920434951782</t>
+    <t xml:space="preserve">12.7591161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7160396575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4231214523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4920444488525</t>
   </si>
   <si>
     <t xml:space="preserve">12.4661989212036</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3628168106079</t>
+    <t xml:space="preserve">12.3628149032593</t>
   </si>
   <si>
     <t xml:space="preserve">12.6298875808716</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">12.535120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5265054702759</t>
+    <t xml:space="preserve">12.5265045166016</t>
   </si>
   <si>
     <t xml:space="preserve">12.7849607467651</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141893386841</t>
+    <t xml:space="preserve">12.9141883850098</t>
   </si>
   <si>
     <t xml:space="preserve">12.8366527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8883428573608</t>
+    <t xml:space="preserve">12.8883438110352</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538827896118</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">12.7074241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6126575469971</t>
+    <t xml:space="preserve">12.6126565933228</t>
   </si>
   <si>
     <t xml:space="preserve">12.7246551513672</t>
@@ -1091,52 +1091,52 @@
     <t xml:space="preserve">12.7935762405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8280382156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7418851852417</t>
+    <t xml:space="preserve">12.8280372619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7418842315674</t>
   </si>
   <si>
     <t xml:space="preserve">12.871111869812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9917249679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0089569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9572649002075</t>
+    <t xml:space="preserve">12.9917259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0089559555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9572639465332</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0778770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0951070785522</t>
+    <t xml:space="preserve">13.0778789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0951080322266</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381845474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1984891891479</t>
+    <t xml:space="preserve">13.1984901428223</t>
   </si>
   <si>
     <t xml:space="preserve">13.2674121856689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4914073944092</t>
+    <t xml:space="preserve">13.4914064407349</t>
   </si>
   <si>
     <t xml:space="preserve">13.6550960540771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7757081985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7843236923218</t>
+    <t xml:space="preserve">13.7757091522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7843246459961</t>
   </si>
   <si>
     <t xml:space="preserve">13.7498636245728</t>
@@ -1145,28 +1145,28 @@
     <t xml:space="preserve">14.1289319992065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4907712936401</t>
+    <t xml:space="preserve">14.4907703399658</t>
   </si>
   <si>
     <t xml:space="preserve">14.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2150850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6981725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8963212966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8618612289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7240190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1547784805298</t>
+    <t xml:space="preserve">14.2150840759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6981716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8963203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8618621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7240180969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1547775268555</t>
   </si>
   <si>
     <t xml:space="preserve">14.3443126678467</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">14.0255508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">13.939398765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.844630241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.111701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9221677780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7929391860962</t>
+    <t xml:space="preserve">13.9393978118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8446311950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1117010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9221668243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7929401397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6206359863281</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">13.8187866210938</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8877067565918</t>
+    <t xml:space="preserve">13.8877077102661</t>
   </si>
   <si>
     <t xml:space="preserve">13.8704767227173</t>
@@ -1217,28 +1217,28 @@
     <t xml:space="preserve">13.7326326370239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154035568237</t>
+    <t xml:space="preserve">13.7154026031494</t>
   </si>
   <si>
     <t xml:space="preserve">13.6809415817261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4569463729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.612021446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3535642623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4052562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3191032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3880252838135</t>
+    <t xml:space="preserve">13.4569473266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6120204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3535652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.405255317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3191041946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3880243301392</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670936584473</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">13.2846431732178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5603284835815</t>
+    <t xml:space="preserve">13.5603294372559</t>
   </si>
   <si>
     <t xml:space="preserve">13.3363332748413</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">13.5258684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5086393356323</t>
+    <t xml:space="preserve">13.508638381958</t>
   </si>
   <si>
     <t xml:space="preserve">14.0223560333252</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">13.9517154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9693746566772</t>
+    <t xml:space="preserve">13.9693737030029</t>
   </si>
   <si>
     <t xml:space="preserve">13.7751111984253</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">13.6161670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5278644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4219017028809</t>
+    <t xml:space="preserve">13.5278635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4219026565552</t>
   </si>
   <si>
     <t xml:space="preserve">13.0863542556763</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">13.2806196212769</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0686950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3402433395386</t>
+    <t xml:space="preserve">13.0686960220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3402423858643</t>
   </si>
   <si>
     <t xml:space="preserve">14.2872629165649</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">13.8104314804077</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5985059738159</t>
+    <t xml:space="preserve">13.5985069274902</t>
   </si>
   <si>
     <t xml:space="preserve">13.3865823745728</t>
@@ -1394,22 +1394,22 @@
     <t xml:space="preserve">13.5455255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.351261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2452983856201</t>
+    <t xml:space="preserve">13.3512601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2452993392944</t>
   </si>
   <si>
     <t xml:space="preserve">13.3336009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2276372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3689222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1746578216553</t>
+    <t xml:space="preserve">13.2276382446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.174656867981</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629594802856</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">12.5035619735718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0157136917114</t>
+    <t xml:space="preserve">13.0157127380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.3159399032593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9980535507202</t>
+    <t xml:space="preserve">12.9980525970459</t>
   </si>
   <si>
     <t xml:space="preserve">12.9097509384155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8391103744507</t>
+    <t xml:space="preserve">12.8391094207764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0333738327026</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">13.1569967269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2099781036377</t>
+    <t xml:space="preserve">13.2099771499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.9274120330811</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">12.8037891387939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2386560440063</t>
+    <t xml:space="preserve">12.238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6315593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2673349380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3379764556885</t>
+    <t xml:space="preserve">11.267333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3379755020142</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613721847534</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">11.1790323257446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4262771606445</t>
+    <t xml:space="preserve">11.4262762069702</t>
   </si>
   <si>
     <t xml:space="preserve">11.0377492904663</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">11.3556356430054</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0907306671143</t>
+    <t xml:space="preserve">11.0907297134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8788051605225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9317874908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0730695724487</t>
+    <t xml:space="preserve">10.9317865371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0730686187744</t>
   </si>
   <si>
     <t xml:space="preserve">11.2849950790405</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">11.126051902771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2496738433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728433609009</t>
+    <t xml:space="preserve">11.2496728897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">10.2077102661133</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">10.3843145370483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4549560546875</t>
+    <t xml:space="preserve">10.4549551010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.5962390899658</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">10.5255975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1547288894653</t>
+    <t xml:space="preserve">10.1547298431396</t>
   </si>
   <si>
     <t xml:space="preserve">9.41299152374268</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">9.62491703033447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53661441802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7198629379272</t>
+    <t xml:space="preserve">9.5366153717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1370687484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7198619842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.1966924667358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551832199097</t>
+    <t xml:space="preserve">10.7551822662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.666880607605</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">10.2783517837524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2430305480957</t>
+    <t xml:space="preserve">10.24303150177</t>
   </si>
   <si>
     <t xml:space="preserve">10.4902772903442</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">10.5079374313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5785789489746</t>
+    <t xml:space="preserve">10.5785779953003</t>
   </si>
   <si>
     <t xml:space="preserve">10.6845417022705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7375221252441</t>
+    <t xml:space="preserve">10.7375211715698</t>
   </si>
   <si>
     <t xml:space="preserve">10.8258247375488</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">10.6139001846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5609188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2606906890869</t>
+    <t xml:space="preserve">10.5609178543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2606916427612</t>
   </si>
   <si>
     <t xml:space="preserve">10.3313331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5432577133179</t>
+    <t xml:space="preserve">10.5432567596436</t>
   </si>
   <si>
     <t xml:space="preserve">10.4196348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4019756317139</t>
+    <t xml:space="preserve">10.4019746780396</t>
   </si>
   <si>
     <t xml:space="preserve">10.437294960022</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">10.84348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.896466255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9141263961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0554103851318</t>
+    <t xml:space="preserve">10.8964653015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9141254425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0554094314575</t>
   </si>
   <si>
     <t xml:space="preserve">10.984766960144</t>
@@ -69205,7 +69205,7 @@
     </row>
     <row r="2543">
       <c r="A2543" s="1" t="n">
-        <v>46027.691087963</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2543" t="n">
         <v>23952</v>
@@ -69226,6 +69226,32 @@
         <v>920</v>
       </c>
       <c r="H2543" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="1" t="n">
+        <v>46028.6910185185</v>
+      </c>
+      <c r="B2544" t="n">
+        <v>11163</v>
+      </c>
+      <c r="C2544" t="n">
+        <v>10.5500001907349</v>
+      </c>
+      <c r="D2544" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="E2544" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F2544" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>919</v>
+      </c>
+      <c r="H2544" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ADB.MI.xlsx
+++ b/data/ADB.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">ADB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15394163131714</t>
+    <t xml:space="preserve">5.15394258499146</t>
   </si>
   <si>
     <t xml:space="preserve">5.09169626235962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14564180374146</t>
+    <t xml:space="preserve">5.14564228057861</t>
   </si>
   <si>
     <t xml:space="preserve">5.18713998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1165943145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16224145889282</t>
+    <t xml:space="preserve">5.11659479141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16224193572998</t>
   </si>
   <si>
     <t xml:space="preserve">5.19958877563477</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">5.24523544311523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30333185195923</t>
+    <t xml:space="preserve">5.30333137512207</t>
   </si>
   <si>
     <t xml:space="preserve">5.31163120269775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3157811164856</t>
+    <t xml:space="preserve">5.31578063964844</t>
   </si>
   <si>
     <t xml:space="preserve">5.34482860565186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38632535934448</t>
+    <t xml:space="preserve">5.3863263130188</t>
   </si>
   <si>
     <t xml:space="preserve">5.3489785194397</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">5.35312843322754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36972713470459</t>
+    <t xml:space="preserve">5.36972665786743</t>
   </si>
   <si>
     <t xml:space="preserve">5.41122436523438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34067964553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39462566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47761917114258</t>
+    <t xml:space="preserve">5.34067869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39462518692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47761964797974</t>
   </si>
   <si>
     <t xml:space="preserve">5.48176956176758</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">5.9340877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89259099960327</t>
+    <t xml:space="preserve">5.89259052276611</t>
   </si>
   <si>
     <t xml:space="preserve">5.71415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85939311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97558498382568</t>
+    <t xml:space="preserve">5.85939264297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97558450698853</t>
   </si>
   <si>
     <t xml:space="preserve">5.96728563308716</t>
@@ -131,22 +131,22 @@
     <t xml:space="preserve">5.9008903503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96313619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95068693161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94653701782227</t>
+    <t xml:space="preserve">5.96313571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95068645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94653654098511</t>
   </si>
   <si>
     <t xml:space="preserve">5.87599182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8676929473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05442953109741</t>
+    <t xml:space="preserve">5.86769247055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419807434082</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">6.05027961730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13327360153198</t>
+    <t xml:space="preserve">6.13327407836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.19137001037598</t>
@@ -167,76 +167,76 @@
     <t xml:space="preserve">6.47355031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36150789260864</t>
+    <t xml:space="preserve">6.3615083694458</t>
   </si>
   <si>
     <t xml:space="preserve">6.55239486694336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57314395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5606951713562</t>
+    <t xml:space="preserve">6.57314348220825</t>
+  </si>
+  <si>
+    <